--- a/Modelo Test Plan.xlsx
+++ b/Modelo Test Plan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kiro\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kiro\CoderBits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A10628A-562C-48EE-8AD4-FB94922E0CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A6B122-C029-40E8-8A25-C4A60EDDFED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{96765352-7388-4C61-94B8-5077301D3254}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="120">
   <si>
     <t>MODULOS</t>
   </si>
@@ -183,12 +183,6 @@
   </si>
   <si>
     <t xml:space="preserve">  "detail": "Credenciales incorrectas"</t>
-  </si>
-  <si>
-    <t>Validacion de campos</t>
-  </si>
-  <si>
-    <t>Edgar Pena</t>
   </si>
   <si>
     <t>Status: 201 Created</t>
@@ -338,12 +332,6 @@
     <t>El sistema debe eliminar al personal de manera logica y poder recuperarlo luego</t>
   </si>
   <si>
-    <t>Status: 200 OK</t>
-  </si>
-  <si>
-    <t>Status: 204 No Content</t>
-  </si>
-  <si>
     <t>Recuperacion de personal eliminado</t>
   </si>
   <si>
@@ -422,13 +410,89 @@
   </si>
   <si>
     <t>Conexión al websocke de alertar ws://127.0.0.1:8000/ws/alertas/</t>
+  </si>
+  <si>
+    <t>https://github.com/alejav0240/CoderBits/issues/32</t>
+  </si>
+  <si>
+    <t>Usuario eliminado logicamente</t>
+  </si>
+  <si>
+    <t>Creacion de mitigacion según el ataque</t>
+  </si>
+  <si>
+    <t>El sistema tiene que generar su mitigacion correspondiente a cada registro de ataque que se genere</t>
+  </si>
+  <si>
+    <t>Mitigacion creada respecto a la ip del atacante</t>
+  </si>
+  <si>
+    <t>Envio de los datos en tiempo real</t>
+  </si>
+  <si>
+    <t>El sistema debe mandar los datos atravez del websocket en tiempo real</t>
+  </si>
+  <si>
+    <t>"tipo_evento": "conexion",
+    "conexion": {
+        "ip_src": "47.90.134.154",
+        "ip_dst": "192.168.0.35",
+        "port_dst": null,
+        "protocolo": "UDP",
+        "timestamp": "2025-10-16T02:05:22.998676+00:00"
+    }</t>
+  </si>
+  <si>
+    <t>Hasheo de contraseña</t>
+  </si>
+  <si>
+    <t>El sistema debe hashear la contraseña del usuario</t>
+  </si>
+  <si>
+    <t>Generacion de reportes</t>
+  </si>
+  <si>
+    <t>El sistema debe poder generar reportes con datos recibidos atravez del backend</t>
+  </si>
+  <si>
+    <t>Peticion a: api/dashboard/stats/</t>
+  </si>
+  <si>
+    <t>"ataques_activos": x,
+  "ataques_hoy": x,
+  "conexiones_hoy": x,
+  "mitigaciones_exitosas": x,
+  "ataques_ultimos_30_dias": x</t>
+  </si>
+  <si>
+    <t>Generacion de estadisticas para reportes</t>
+  </si>
+  <si>
+    <t>El sistema debe poder generar reportes estadisticas del dia que se pide el reporte</t>
+  </si>
+  <si>
+    <t>Peticion a: api/dashboard/export/json/</t>
+  </si>
+  <si>
+    <t>"ataques": [
+    {
+      "id": x,
+      "tipo": x,
+      "descripcion": x,
+      "ip_origen": x,
+      "ip_destino":x,
+      "puerto": x,
+      "fecha_detectado": "fecha del dia que se pidio el reporte",
+      "conteo_conexiones": x,
+      "activo": x
+    },.........</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -438,6 +502,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -460,10 +532,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -489,92 +562,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="63">
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -694,6 +690,87 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center"/>
@@ -6562,54 +6639,54 @@
     <dataField name="Cuenta de Estado (Dropdown)" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="43">
+    <format dxfId="16">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="15">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="14">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="39">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="38">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="10">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="9">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="8">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="33">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="4">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -6756,60 +6833,60 @@
     <dataField name="Cuenta de Test Case" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="59">
+    <format dxfId="32">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="58">
+    <format dxfId="31">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="57">
+    <format dxfId="30">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="56">
+    <format dxfId="29">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="55">
+    <format dxfId="28">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="54">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="53">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="52">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="51">
+    <format dxfId="24">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="23">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="22">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="21">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="47">
+    <format dxfId="20">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="44">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -6919,22 +6996,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}" name="TestPlan" displayName="TestPlan" ref="A2:M140" headerRowDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}" name="TestPlan" displayName="TestPlan" ref="A2:M140" headerRowDxfId="59">
   <autoFilter ref="A2:M140" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{7F95280F-E669-4A5D-AEDF-FCAAAC81F275}" name="Modulo (Dropdown)" totalsRowLabel="Total" dataDxfId="24" totalsRowDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{E775B39B-DEB6-4123-A65F-A37EDA4383A3}" name="Test Case" dataDxfId="22" totalsRowDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{4E500E60-0861-4EF2-B610-79885F5EF7FD}" name="Descripción" dataDxfId="20" totalsRowDxfId="21"/>
-    <tableColumn id="14" xr3:uid="{D149BE2F-3E66-4E54-8D0E-BA4D69F73794}" name="Tipo/s de Prueba" dataDxfId="18" totalsRowDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{48166857-FFB0-4E91-A69A-8A057DEBB914}" name="Precondiciones" dataDxfId="16" totalsRowDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{09440620-A437-484D-9292-769D8C979710}" name="Pasos a seguir" dataDxfId="14" totalsRowDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{25FFAFC4-E636-4C78-8EC4-9B105CD6EC6A}" name="Datos de Prueba" dataDxfId="12" totalsRowDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{5C319188-663F-4BD1-ADB0-A93CF2F134F5}" name="Resultado Esperado" dataDxfId="10" totalsRowDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{AC65C1EE-D520-403E-8171-F3B42F898A90}" name="Resultado Actual (Si falla)" dataDxfId="8" totalsRowDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{67BFFC43-BD7A-400D-BCA5-7641851369E7}" name="Ultima ejecución (Fecha)" dataDxfId="6" totalsRowDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{AF2F4479-94ED-46CC-8F6A-9945904E34B4}" name="Encargado de Prueba" dataDxfId="4" totalsRowDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{1AE568CA-11EA-494D-A158-098CEC0427F1}" name="Estado (Dropdown)" dataDxfId="2" totalsRowDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{D7CC1236-1B17-4FEE-A062-7A6AF5789012}" name="Comentario" totalsRowFunction="count" dataDxfId="0" totalsRowDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{7F95280F-E669-4A5D-AEDF-FCAAAC81F275}" name="Modulo (Dropdown)" totalsRowLabel="Total" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{E775B39B-DEB6-4123-A65F-A37EDA4383A3}" name="Test Case" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{4E500E60-0861-4EF2-B610-79885F5EF7FD}" name="Descripción" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="14" xr3:uid="{D149BE2F-3E66-4E54-8D0E-BA4D69F73794}" name="Tipo/s de Prueba" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{48166857-FFB0-4E91-A69A-8A057DEBB914}" name="Precondiciones" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="13" xr3:uid="{09440620-A437-484D-9292-769D8C979710}" name="Pasos a seguir" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="12" xr3:uid="{25FFAFC4-E636-4C78-8EC4-9B105CD6EC6A}" name="Datos de Prueba" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{5C319188-663F-4BD1-ADB0-A93CF2F134F5}" name="Resultado Esperado" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{AC65C1EE-D520-403E-8171-F3B42F898A90}" name="Resultado Actual (Si falla)" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{67BFFC43-BD7A-400D-BCA5-7641851369E7}" name="Ultima ejecución (Fecha)" dataDxfId="40" totalsRowDxfId="39"/>
+    <tableColumn id="10" xr3:uid="{AF2F4479-94ED-46CC-8F6A-9945904E34B4}" name="Encargado de Prueba" dataDxfId="38" totalsRowDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{1AE568CA-11EA-494D-A158-098CEC0427F1}" name="Estado (Dropdown)" dataDxfId="36" totalsRowDxfId="35"/>
+    <tableColumn id="9" xr3:uid="{D7CC1236-1B17-4FEE-A062-7A6AF5789012}" name="Comentario" totalsRowFunction="count" dataDxfId="34" totalsRowDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7452,7 +7529,9 @@
       <c r="D4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="F4" s="7" t="s">
         <v>43</v>
       </c>
@@ -7474,38 +7553,52 @@
       </c>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
       <c r="I5" s="7"/>
-      <c r="J5" s="6"/>
+      <c r="J5" s="6">
+        <v>45940</v>
+      </c>
       <c r="K5" s="6" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>19</v>
@@ -7514,13 +7607,13 @@
         <v>36</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="6">
@@ -7534,15 +7627,15 @@
       </c>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>19</v>
@@ -7551,33 +7644,35 @@
         <v>36</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="6">
         <v>45940</v>
       </c>
-      <c r="K7" s="6"/>
+      <c r="K7" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="L7" s="7" t="s">
         <v>22</v>
       </c>
       <c r="M7" s="7"/>
     </row>
-    <row r="8" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>19</v>
@@ -7586,13 +7681,13 @@
         <v>36</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="6">
@@ -7606,15 +7701,15 @@
       </c>
       <c r="M8" s="7"/>
     </row>
-    <row r="9" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>19</v>
@@ -7623,13 +7718,13 @@
         <v>36</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="6">
@@ -7643,15 +7738,15 @@
       </c>
       <c r="M9" s="7"/>
     </row>
-    <row r="10" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>19</v>
@@ -7660,13 +7755,13 @@
         <v>36</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="6">
@@ -7680,15 +7775,15 @@
       </c>
       <c r="M10" s="7"/>
     </row>
-    <row r="11" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>19</v>
@@ -7697,13 +7792,13 @@
         <v>36</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="6">
@@ -7717,15 +7812,15 @@
       </c>
       <c r="M11" s="7"/>
     </row>
-    <row r="12" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>19</v>
@@ -7734,13 +7829,13 @@
         <v>36</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="6">
@@ -7759,10 +7854,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>19</v>
@@ -7771,17 +7866,15 @@
         <v>36</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>79</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="I13" s="7"/>
       <c r="J13" s="6">
         <v>45940</v>
       </c>
@@ -7789,7 +7882,7 @@
         <v>40</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M13" s="7"/>
     </row>
@@ -7798,10 +7891,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>19</v>
@@ -7810,13 +7903,13 @@
         <v>36</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="6">
@@ -7835,10 +7928,10 @@
         <v>29</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>19</v>
@@ -7847,17 +7940,17 @@
         <v>36</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="6">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>40</v>
@@ -7865,17 +7958,19 @@
       <c r="L15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="M15" s="7"/>
+      <c r="M15" s="9" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="16" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>19</v>
@@ -7884,13 +7979,13 @@
         <v>36</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="6">
@@ -7909,23 +8004,19 @@
         <v>30</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>87</v>
-      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="6">
@@ -7939,30 +8030,46 @@
       </c>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+    <row r="18" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>19</v>
+      </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
+      <c r="H18" s="7" t="s">
+        <v>106</v>
+      </c>
       <c r="I18" s="7"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="7"/>
+      <c r="J18" s="6">
+        <v>45940</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>19</v>
@@ -7971,17 +8078,17 @@
         <v>36</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="6">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>40</v>
@@ -7991,15 +8098,15 @@
       </c>
       <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>19</v>
@@ -8008,17 +8115,17 @@
         <v>36</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="6">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>40</v>
@@ -8028,49 +8135,115 @@
       </c>
       <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+    <row r="21" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="I21" s="7"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="7"/>
+      <c r="J21" s="6">
+        <v>45945</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="M21" s="7"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
+    <row r="22" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>115</v>
+      </c>
       <c r="I22" s="7"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="7"/>
+      <c r="J22" s="6">
+        <v>45945</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="M22" s="7"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
+    <row r="23" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>119</v>
+      </c>
       <c r="I23" s="7"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="7"/>
+      <c r="J23" s="6">
+        <v>45945</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="M23" s="7"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -9831,13 +10004,13 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L3:L140">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"PENDING"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9849,9 +10022,12 @@
       <formula1>INDIRECT("Modulos[MODULOS]")</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="M15" r:id="rId1" xr:uid="{E03BA14B-EB46-4555-B0FE-E6A8B84EE875}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -10031,21 +10207,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E158E2AB9B4F924688B558FA982B40CF" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ce5f689dcf51305603cb0d070870d6dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="def3e2b2-904e-4359-b966-59b7b32cd06e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="252587ffdfea7067e66d630466c44dd6" ns2:_="">
     <xsd:import namespace="def3e2b2-904e-4359-b966-59b7b32cd06e"/>
@@ -10183,24 +10344,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CABA5C2-04D8-4DC5-BBFB-FF9AC004B268}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1F0EA96-F162-49AF-B0BE-A54883795866}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10216,4 +10375,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CABA5C2-04D8-4DC5-BBFB-FF9AC004B268}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Modelo Test Plan.xlsx
+++ b/Modelo Test Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kiro\CoderBits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A6B122-C029-40E8-8A25-C4A60EDDFED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464F033F-7DCD-4B3B-88EE-29ACD3B86471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{96765352-7388-4C61-94B8-5077301D3254}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="129">
   <si>
     <t>MODULOS</t>
   </si>
@@ -486,6 +486,51 @@
       "conteo_conexiones": x,
       "activo": x
     },.........</t>
+  </si>
+  <si>
+    <t>Guardado correcto de los datos</t>
+  </si>
+  <si>
+    <t>El sistema debe guardar de manera correcta todos los datos que se le pide</t>
+  </si>
+  <si>
+    <t>Iniciar sesion                                      Activar el monitore de red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Ingresar a la plataforma
+2. Iniciar sesion                                     3. Activacion del monitoreo de red                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Ingresar a la plataforma
+2. Iniciar sesion                                                            </t>
+  </si>
+  <si>
+    <t>https://github.com/alejav0240/CoderBits/issues/34</t>
+  </si>
+  <si>
+    <t>Peticion a: api/conexiones/activar_monitoreo/</t>
+  </si>
+  <si>
+    <t>id': x,
+  'tipo': 'xxx',
+  'descripcion': 'x',
+  'ip_origen': 'x',
+  'ip_destino': 'x',
+  'puerto': xxxx,
+  'fecha_detectado': x, 
+  'conteo_conexiones': x,
+  'activo': True}</t>
+  </si>
+  <si>
+    <t>id': x,
+  'tipo': 'xxx',
+  'descripcion': 'x',
+  'ip_origen': 'x',
+  'ip_destino': 'x',
+  'puerto': null,
+  'fecha_detectado': x, 
+  'conteo_conexiones': null,
+  'activo': True}</t>
   </si>
 </sst>
 </file>
@@ -7979,7 +8024,7 @@
         <v>36</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>88</v>
@@ -7999,7 +8044,7 @@
       </c>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>30</v>
       </c>
@@ -8012,8 +8057,12 @@
       <c r="D17" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="E17" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>123</v>
+      </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7" t="s">
         <v>90</v>
@@ -8043,8 +8092,12 @@
       <c r="D18" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="E18" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>123</v>
+      </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7" t="s">
         <v>106</v>
@@ -8075,10 +8128,10 @@
         <v>19</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>100</v>
@@ -8112,10 +8165,10 @@
         <v>19</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>100</v>
@@ -8149,10 +8202,10 @@
         <v>19</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>101</v>
@@ -8246,20 +8299,46 @@
       </c>
       <c r="M23" s="7"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
+    <row r="24" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="J24" s="6">
+        <v>45947</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
@@ -10207,6 +10286,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E158E2AB9B4F924688B558FA982B40CF" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ce5f689dcf51305603cb0d070870d6dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="def3e2b2-904e-4359-b966-59b7b32cd06e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="252587ffdfea7067e66d630466c44dd6" ns2:_="">
     <xsd:import namespace="def3e2b2-904e-4359-b966-59b7b32cd06e"/>
@@ -10344,22 +10438,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CABA5C2-04D8-4DC5-BBFB-FF9AC004B268}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1F0EA96-F162-49AF-B0BE-A54883795866}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10375,21 +10471,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CABA5C2-04D8-4DC5-BBFB-FF9AC004B268}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Modelo Test Plan.xlsx
+++ b/Modelo Test Plan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kiro\CoderBits\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\CoderBits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464F033F-7DCD-4B3B-88EE-29ACD3B86471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BCF738-7567-4471-B0C0-3CBA15E3109E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{96765352-7388-4C61-94B8-5077301D3254}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{96765352-7388-4C61-94B8-5077301D3254}"/>
   </bookViews>
   <sheets>
     <sheet name="Gestion de Modulos" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="716">
   <si>
     <t>MODULOS</t>
   </si>
@@ -531,6 +531,2087 @@
   'fecha_detectado': x, 
   'conteo_conexiones': null,
   'activo': True}</t>
+  </si>
+  <si>
+    <t>Carga del modelo</t>
+  </si>
+  <si>
+    <t>Unitaria / Integración</t>
+  </si>
+  <si>
+    <t>1. Ejecutar el script principal
+2. Observar si el modelo se carga sin errores</t>
+  </si>
+  <si>
+    <t>Archivo: modelo_cicids2017.h5</t>
+  </si>
+  <si>
+    <t>15/10/2025</t>
+  </si>
+  <si>
+    <t>Validación de características</t>
+  </si>
+  <si>
+    <t>Modelo cargado</t>
+  </si>
+  <si>
+    <t>1. Ejecutar el script de validación de features
+2. Comparar las columnas recibidas con las esperadas</t>
+  </si>
+  <si>
+    <t>78 features esperadas del dataset CICIDS2017</t>
+  </si>
+  <si>
+    <t>Normalización de datos</t>
+  </si>
+  <si>
+    <t>1. Cargar el scaler
+2. Pasar un conjunto de datos de prueba
+3. Verificar rango de salida</t>
+  </si>
+  <si>
+    <t>Valores numéricos variados (sin normalizar)</t>
+  </si>
+  <si>
+    <t>Predicción en tiempo real</t>
+  </si>
+  <si>
+    <t>Integración / Rendimiento</t>
+  </si>
+  <si>
+    <t>1. Capturar tráfico con scapy
+2. Extraer features
+3. Pasarlas al modelo</t>
+  </si>
+  <si>
+    <t>Tráfico benigno simulado y tráfico DDoS</t>
+  </si>
+  <si>
+    <t>Gestión de errores de entrada</t>
+  </si>
+  <si>
+    <t>Unitaria / Robustez</t>
+  </si>
+  <si>
+    <t>1. Enviar datos con menos de 78 columnas
+2. Observar la salida</t>
+  </si>
+  <si>
+    <t>Features faltantes (ej. 76 columnas)</t>
+  </si>
+  <si>
+    <t>Integración con WebSocket</t>
+  </si>
+  <si>
+    <t>Integración / Interfaz</t>
+  </si>
+  <si>
+    <t>Servidor WebSocket activo</t>
+  </si>
+  <si>
+    <t>1. Activar monitoreo
+2. Observar si los eventos se transmiten por ws://127.0.0.1:8000/ws/alertas/</t>
+  </si>
+  <si>
+    <t>Tráfico de red real o simulado</t>
+  </si>
+  <si>
+    <t>Detección de anomalías</t>
+  </si>
+  <si>
+    <t>Integración / Base de Datos</t>
+  </si>
+  <si>
+    <t>Modelo cargado y BD activa</t>
+  </si>
+  <si>
+    <t>1. Ejecutar monitoreo
+2. Verificar si los ataques se guardan en la BD</t>
+  </si>
+  <si>
+    <t>Ataques tipo DDoS, PortScan</t>
+  </si>
+  <si>
+    <t>Mitigación de ataques</t>
+  </si>
+  <si>
+    <t>Funcional / Integración</t>
+  </si>
+  <si>
+    <t>Monitoreo activo y ataque detectado</t>
+  </si>
+  <si>
+    <t>1. Detectar ataque
+2. Verificar creación de mitigación en el backend</t>
+  </si>
+  <si>
+    <t>Conexión atacante IP: 192.168.1.100</t>
+  </si>
+  <si>
+    <t>Generación de reportes ML</t>
+  </si>
+  <si>
+    <t>Funcional / Reporte</t>
+  </si>
+  <si>
+    <t>1. Consultar endpoint /api/dashboard/stats/
+2. Verificar conteos y métricas</t>
+  </si>
+  <si>
+    <t>Datos históricos de tráfico</t>
+  </si>
+  <si>
+    <t>Fallos del modelo</t>
+  </si>
+  <si>
+    <t>Logger configurado</t>
+  </si>
+  <si>
+    <t>1. Forzar un error de predicción
+2. Revisar archivo de logs</t>
+  </si>
+  <si>
+    <t>Input no numérico o con NaN</t>
+  </si>
+  <si>
+    <t>MonitorSeguridadRedes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alejandro Chipana </t>
+  </si>
+  <si>
+    <t>Modelo cargado 
+exitosamente en memoria</t>
+  </si>
+  <si>
+    <t>Validación correcta 
+todas las columnas coinciden</t>
+  </si>
+  <si>
+    <t>Datos escalados correctamente
+ con media ~0 y desviación ~1</t>
+  </si>
+  <si>
+    <t>Error controlado
+ 'Número de características incorrecto'</t>
+  </si>
+  <si>
+    <t>Datos enviados exitosamente
+ a través del WebSocket</t>
+  </si>
+  <si>
+    <t>Registros guardados
+ correctamente en la tabla 'ataques'</t>
+  </si>
+  <si>
+    <t>Mitigación creada con acción
+ correspondiente (bloqueo, alerta)</t>
+  </si>
+  <si>
+    <t>Reporte generado con métricas de
+ ataques detectados y benignos</t>
+  </si>
+  <si>
+    <t>Error registrado en logs
+ 'ValueError: input contains NaN'</t>
+  </si>
+  <si>
+    <t>Modelo previamente entrenado 
+y guardado (.h5 o .pkl)</t>
+  </si>
+  <si>
+    <t>Scaler entrenado y 
+serializado (scaler.pkl)</t>
+  </si>
+  <si>
+    <t>Modelo y scaler 
+cargados, scapy activo</t>
+  </si>
+  <si>
+    <t>Modelo ejecutado con 
+registros previos</t>
+  </si>
+  <si>
+    <t>El sistema debe cargar correctamente
+ el modelo entrenado en memoria</t>
+  </si>
+  <si>
+    <t>El sistema debe validar que las 78
+ características de entrada sean las correctas</t>
+  </si>
+  <si>
+    <t>El sistema debe normalizar correctamente
+ los datos de entrada usando StandardScaler</t>
+  </si>
+  <si>
+    <t>El sistema debe predecir correctamente
+ si una conexión es BENIGN o ATAQUE</t>
+  </si>
+  <si>
+    <t>El sistema debe manejar errores 
+cuando faltan o sobran características</t>
+  </si>
+  <si>
+    <t>El sistema debe enviar las 
+predicciones en tiempo real al WebSocket</t>
+  </si>
+  <si>
+    <t>El sistema debe registrar las 
+conexiones clasificadas como ataque</t>
+  </si>
+  <si>
+    <t>El sistema debe generar acciones
+ de mitigación al detectar un ataque</t>
+  </si>
+  <si>
+    <t>El sistema debe generar reportes 
+con estadísticas de predicciones</t>
+  </si>
+  <si>
+    <t>El sistema debe registrar los 
+errores de ejecución del modelo en logs</t>
+  </si>
+  <si>
+    <t>Autenticación (Login)</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>Alertas en tiempo real</t>
+  </si>
+  <si>
+    <t>Historial de incidentes</t>
+  </si>
+  <si>
+    <t>Exportación de datos (CSV/PDF)</t>
+  </si>
+  <si>
+    <t>Notificaciones</t>
+  </si>
+  <si>
+    <t>Interfaz general / Navegación</t>
+  </si>
+  <si>
+    <t>Prototipo inicial / Configuración UI</t>
+  </si>
+  <si>
+    <t>10/10/2025</t>
+  </si>
+  <si>
+    <t>Edgar Amilcar Peña Escobar</t>
+  </si>
+  <si>
+    <t>Usabilidad</t>
+  </si>
+  <si>
+    <t>Rendimiento</t>
+  </si>
+  <si>
+    <t>Seguridad</t>
+  </si>
+  <si>
+    <t>Compatibilidad</t>
+  </si>
+  <si>
+    <t>Funcional</t>
+  </si>
+  <si>
+    <t>El sistema debe estar desplegado y operativo.</t>
+  </si>
+  <si>
+    <t>Validación / UI</t>
+  </si>
+  <si>
+    <t>Alejandro Chipana</t>
+  </si>
+  <si>
+    <t>Validación de credenciales correctas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Validación de credenciales correctas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de credenciales correctas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de credenciales correctas.</t>
+  </si>
+  <si>
+    <t>Validación de credenciales incorrectas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Validación de credenciales incorrectas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de credenciales incorrectas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de credenciales incorrectas.</t>
+  </si>
+  <si>
+    <t>Bloqueo de cuenta tras intentos fallidos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Bloqueo de cuenta tras intentos fallidos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Bloqueo de cuenta tras intentos fallidos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Bloqueo de cuenta tras intentos fallidos.</t>
+  </si>
+  <si>
+    <t>Persistencia de sesión (recordarme)</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Persistencia de sesión (recordarme)
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Persistencia de sesión (recordarme)</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Persistencia de sesión (recordarme).</t>
+  </si>
+  <si>
+    <t>Cierre de sesión correcto</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Cierre de sesión correcto
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Cierre de sesión correcto</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Cierre de sesión correcto.</t>
+  </si>
+  <si>
+    <t>Redirección tras login exitoso</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Redirección tras login exitoso
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Redirección tras login exitoso</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Redirección tras login exitoso.</t>
+  </si>
+  <si>
+    <t>Visualización de mensajes de error</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Visualización de mensajes de error
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Visualización de mensajes de error</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Visualización de mensajes de error.</t>
+  </si>
+  <si>
+    <t>Campos requeridos vacíos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Campos requeridos vacíos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Campos requeridos vacíos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Campos requeridos vacíos.</t>
+  </si>
+  <si>
+    <t>Validación de formato de email</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Validación de formato de email
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de formato de email</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de formato de email.</t>
+  </si>
+  <si>
+    <t>Verificación del botón de iniciar sesión</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Verificación del botón de iniciar sesión
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Verificación del botón de iniciar sesión</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Verificación del botón de iniciar sesión.</t>
+  </si>
+  <si>
+    <t>Accesibilidad del formulario de login</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Accesibilidad del formulario de login
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Accesibilidad del formulario de login</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Accesibilidad del formulario de login.</t>
+  </si>
+  <si>
+    <t>Tiempo de respuesta del login</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Tiempo de respuesta del login
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Tiempo de respuesta del login</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Tiempo de respuesta del login.</t>
+  </si>
+  <si>
+    <t>Compatibilidad en diferentes navegadores</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Compatibilidad en diferentes navegadores
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Compatibilidad en diferentes navegadores</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Compatibilidad en diferentes navegadores.</t>
+  </si>
+  <si>
+    <t>Seguridad del envío de credenciales (HTTPS)</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Seguridad del envío de credenciales (HTTPS)
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Seguridad del envío de credenciales (HTTPS)</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Seguridad del envío de credenciales (HTTPS).</t>
+  </si>
+  <si>
+    <t>Autenticación con tokens válidos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Autenticación con tokens válidos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Autenticación con tokens válidos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Autenticación con tokens válidos.</t>
+  </si>
+  <si>
+    <t>Carga inicial del panel</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Carga inicial del panel
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Carga inicial del panel</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Carga inicial del panel.</t>
+  </si>
+  <si>
+    <t>Visualización de métricas de red</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Visualización de métricas de red
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Visualización de métricas de red</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Visualización de métricas de red.</t>
+  </si>
+  <si>
+    <t>Filtrado por rango de fechas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Filtrado por rango de fechas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Filtrado por rango de fechas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Filtrado por rango de fechas.</t>
+  </si>
+  <si>
+    <t>Interacción con gráficas dinámicas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Interacción con gráficas dinámicas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Interacción con gráficas dinámicas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Interacción con gráficas dinámicas.</t>
+  </si>
+  <si>
+    <t>Actualización automática de datos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Actualización automática de datos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Actualización automática de datos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Actualización automática de datos.</t>
+  </si>
+  <si>
+    <t>Error al cargar datos del backend</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Error al cargar datos del backend
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Error al cargar datos del backend</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Error al cargar datos del backend.</t>
+  </si>
+  <si>
+    <t>Validación de roles para contenido visible</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Validación de roles para contenido visible
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de roles para contenido visible</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de roles para contenido visible.</t>
+  </si>
+  <si>
+    <t>Visualización del consumo de ancho de banda</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Visualización del consumo de ancho de banda
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Visualización del consumo de ancho de banda</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Visualización del consumo de ancho de banda.</t>
+  </si>
+  <si>
+    <t>Ordenamiento de registros</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Ordenamiento de registros
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Ordenamiento de registros</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Ordenamiento de registros.</t>
+  </si>
+  <si>
+    <t>Validación de componentes visuales</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Validación de componentes visuales
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de componentes visuales</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de componentes visuales.</t>
+  </si>
+  <si>
+    <t>Usabilidad del dashboard en pantallas pequeñas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Usabilidad del dashboard en pantallas pequeñas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Usabilidad del dashboard en pantallas pequeñas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Usabilidad del dashboard en pantallas pequeñas.</t>
+  </si>
+  <si>
+    <t>Rendimiento del dashboard con gran cantidad de datos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Rendimiento del dashboard con gran cantidad de datos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Rendimiento del dashboard con gran cantidad de datos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Rendimiento del dashboard con gran cantidad de datos.</t>
+  </si>
+  <si>
+    <t>Comportamiento ante desconexión del servidor</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Comportamiento ante desconexión del servidor
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Comportamiento ante desconexión del servidor</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Comportamiento ante desconexión del servidor.</t>
+  </si>
+  <si>
+    <t>Integración con backend para métricas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Integración con backend para métricas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Integración con backend para métricas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Integración con backend para métricas.</t>
+  </si>
+  <si>
+    <t>Comprobación de carga de widgets</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Comprobación de carga de widgets
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Comprobación de carga de widgets</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Comprobación de carga de widgets.</t>
+  </si>
+  <si>
+    <t>Recepción de alerta desde WebSocket</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Recepción de alerta desde WebSocket
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Recepción de alerta desde WebSocket</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Recepción de alerta desde WebSocket.</t>
+  </si>
+  <si>
+    <t>Visualización en tiempo real en la tabla</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Visualización en tiempo real en la tabla
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Visualización en tiempo real en la tabla</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Visualización en tiempo real en la tabla.</t>
+  </si>
+  <si>
+    <t>Notificación emergente en llegada de alerta</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Notificación emergente en llegada de alerta
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Notificación emergente en llegada de alerta</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Notificación emergente en llegada de alerta.</t>
+  </si>
+  <si>
+    <t>Persistencia de alerta en base de datos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Persistencia de alerta en base de datos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Persistencia de alerta en base de datos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Persistencia de alerta en base de datos.</t>
+  </si>
+  <si>
+    <t>Validación del formato del mensaje recibido</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Validación del formato del mensaje recibido
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación del formato del mensaje recibido</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación del formato del mensaje recibido.</t>
+  </si>
+  <si>
+    <t>Desconexión y reconexión del WebSocket</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Desconexión y reconexión del WebSocket
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Desconexión y reconexión del WebSocket</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Desconexión y reconexión del WebSocket.</t>
+  </si>
+  <si>
+    <t>Filtrado por tipo de alerta</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Filtrado por tipo de alerta
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Filtrado por tipo de alerta</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Filtrado por tipo de alerta.</t>
+  </si>
+  <si>
+    <t>Cambio de color según nivel de severidad</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Cambio de color según nivel de severidad
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Cambio de color según nivel de severidad</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Cambio de color según nivel de severidad.</t>
+  </si>
+  <si>
+    <t>Actualización sin recargar la página</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Actualización sin recargar la página
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Actualización sin recargar la página</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Actualización sin recargar la página.</t>
+  </si>
+  <si>
+    <t>Interacción con notificación</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Interacción con notificación
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Interacción con notificación</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Interacción con notificación.</t>
+  </si>
+  <si>
+    <t>Prueba de carga con múltiples alertas simultáneas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Prueba de carga con múltiples alertas simultáneas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Prueba de carga con múltiples alertas simultáneas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Prueba de carga con múltiples alertas simultáneas.</t>
+  </si>
+  <si>
+    <t>Integración con backend /predict</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Integración con backend /predict
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Integración con backend /predict</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Integración con backend /predict.</t>
+  </si>
+  <si>
+    <t>Comprobación del botón limpiar alertas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Comprobación del botón limpiar alertas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Comprobación del botón limpiar alertas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Comprobación del botón limpiar alertas.</t>
+  </si>
+  <si>
+    <t>Exportación de alertas visibles</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Exportación de alertas visibles
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Exportación de alertas visibles</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Exportación de alertas visibles.</t>
+  </si>
+  <si>
+    <t>Sincronización de alertas en dispositivos múltiples</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Sincronización de alertas en dispositivos múltiples
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Sincronización de alertas en dispositivos múltiples</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Sincronización de alertas en dispositivos múltiples.</t>
+  </si>
+  <si>
+    <t>Alertas duplicadas no deben mostrarse</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Alertas duplicadas no deben mostrarse
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Alertas duplicadas no deben mostrarse</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Alertas duplicadas no deben mostrarse.</t>
+  </si>
+  <si>
+    <t>Validación del timestamp recibido</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Validación del timestamp recibido
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación del timestamp recibido</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación del timestamp recibido.</t>
+  </si>
+  <si>
+    <t>Prueba de reconexión automática</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Prueba de reconexión automática
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Prueba de reconexión automática</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Prueba de reconexión automática.</t>
+  </si>
+  <si>
+    <t>Visualización en modo oscuro</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Visualización en modo oscuro
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Visualización en modo oscuro</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Visualización en modo oscuro.</t>
+  </si>
+  <si>
+    <t>Prueba de alerta manual para testeo</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Prueba de alerta manual para testeo
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Prueba de alerta manual para testeo</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Prueba de alerta manual para testeo.</t>
+  </si>
+  <si>
+    <t>Carga inicial del historial</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Carga inicial del historial
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Carga inicial del historial</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Carga inicial del historial.</t>
+  </si>
+  <si>
+    <t>Filtrado por nivel de severidad</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Filtrado por nivel de severidad
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Filtrado por nivel de severidad</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Filtrado por nivel de severidad.</t>
+  </si>
+  <si>
+    <t>Filtrado por dirección IP</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Filtrado por dirección IP
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Filtrado por dirección IP</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Filtrado por dirección IP.</t>
+  </si>
+  <si>
+    <t>Paginación del historial</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Paginación del historial
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Paginación del historial</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Paginación del historial.</t>
+  </si>
+  <si>
+    <t>Exportación del historial en CSV</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Exportación del historial en CSV
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Exportación del historial en CSV</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Exportación del historial en CSV.</t>
+  </si>
+  <si>
+    <t>Exportación en PDF</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Exportación en PDF
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Exportación en PDF</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Exportación en PDF.</t>
+  </si>
+  <si>
+    <t>Visualización de detalles de incidente</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Visualización de detalles de incidente
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Visualización de detalles de incidente</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Visualización de detalles de incidente.</t>
+  </si>
+  <si>
+    <t>Ordenamiento por fecha</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Ordenamiento por fecha
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Ordenamiento por fecha</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Ordenamiento por fecha.</t>
+  </si>
+  <si>
+    <t>Validación de filtros vacíos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Validación de filtros vacíos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de filtros vacíos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de filtros vacíos.</t>
+  </si>
+  <si>
+    <t>Persistencia de filtros aplicados</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Persistencia de filtros aplicados
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Persistencia de filtros aplicados</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Persistencia de filtros aplicados.</t>
+  </si>
+  <si>
+    <t>Prueba con datos vacíos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Prueba con datos vacíos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Prueba con datos vacíos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Prueba con datos vacíos.</t>
+  </si>
+  <si>
+    <t>Compatibilidad con distintos navegadores</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Compatibilidad con distintos navegadores
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Compatibilidad con distintos navegadores</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Compatibilidad con distintos navegadores.</t>
+  </si>
+  <si>
+    <t>Usabilidad del filtro avanzado</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Usabilidad del filtro avanzado
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Usabilidad del filtro avanzado</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Usabilidad del filtro avanzado.</t>
+  </si>
+  <si>
+    <t>Tiempo de respuesta al cargar incidentes</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Tiempo de respuesta al cargar incidentes
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Tiempo de respuesta al cargar incidentes</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Tiempo de respuesta al cargar incidentes.</t>
+  </si>
+  <si>
+    <t>Verificación de formato de datos exportados</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Verificación de formato de datos exportados
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Verificación de formato de datos exportados</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Verificación de formato de datos exportados.</t>
+  </si>
+  <si>
+    <t>Exportación de alertas a CSV</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Exportación de alertas a CSV
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Exportación de alertas a CSV</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Exportación de alertas a CSV.</t>
+  </si>
+  <si>
+    <t>Exportación de incidentes a PDF</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Exportación de incidentes a PDF
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Exportación de incidentes a PDF</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Exportación de incidentes a PDF.</t>
+  </si>
+  <si>
+    <t>Validación del contenido exportado</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Validación del contenido exportado
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación del contenido exportado</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación del contenido exportado.</t>
+  </si>
+  <si>
+    <t>Descarga con nombre de archivo correcto</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Descarga con nombre de archivo correcto
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Descarga con nombre de archivo correcto</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Descarga con nombre de archivo correcto.</t>
+  </si>
+  <si>
+    <t>Validación de formato CSV (separadores)</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Validación de formato CSV (separadores)
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de formato CSV (separadores)</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de formato CSV (separadores).</t>
+  </si>
+  <si>
+    <t>Validación de formato PDF (estructura)</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Validación de formato PDF (estructura)
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de formato PDF (estructura)</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de formato PDF (estructura).</t>
+  </si>
+  <si>
+    <t>Exportación con filtros aplicados</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Exportación con filtros aplicados
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Exportación con filtros aplicados</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Exportación con filtros aplicados.</t>
+  </si>
+  <si>
+    <t>Exportación de datos grandes sin errores</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Exportación de datos grandes sin errores
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Exportación de datos grandes sin errores</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Exportación de datos grandes sin errores.</t>
+  </si>
+  <si>
+    <t>Validación del botón Exportar activo</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Validación del botón Exportar activo
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación del botón Exportar activo</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación del botón Exportar activo.</t>
+  </si>
+  <si>
+    <t>Comportamiento ante exportación vacía</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Comportamiento ante exportación vacía
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Comportamiento ante exportación vacía</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Comportamiento ante exportación vacía.</t>
+  </si>
+  <si>
+    <t>Aparición de notificación en evento crítico</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Aparición de notificación en evento crítico
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Aparición de notificación en evento crítico</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Aparición de notificación en evento crítico.</t>
+  </si>
+  <si>
+    <t>Desaparición automática tras tiempo definido</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Desaparición automática tras tiempo definido
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Desaparición automática tras tiempo definido</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Desaparición automática tras tiempo definido.</t>
+  </si>
+  <si>
+    <t>Cierre manual de notificación</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Cierre manual de notificación
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Cierre manual de notificación</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Cierre manual de notificación.</t>
+  </si>
+  <si>
+    <t>Persistencia en sesión activa</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Persistencia en sesión activa
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Persistencia en sesión activa</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Persistencia en sesión activa.</t>
+  </si>
+  <si>
+    <t>Cambio de color según tipo (éxito/error)</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Cambio de color según tipo (éxito/error)
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Cambio de color según tipo (éxito/error)</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Cambio de color según tipo (éxito/error).</t>
+  </si>
+  <si>
+    <t>Compatibilidad con distintos tamaños de pantalla</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Compatibilidad con distintos tamaños de pantalla
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Compatibilidad con distintos tamaños de pantalla</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Compatibilidad con distintos tamaños de pantalla.</t>
+  </si>
+  <si>
+    <t>No repetición de notificaciones idénticas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: No repetición de notificaciones idénticas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: No repetición de notificaciones idénticas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: No repetición de notificaciones idénticas.</t>
+  </si>
+  <si>
+    <t>Prueba de múltiples notificaciones simultáneas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Prueba de múltiples notificaciones simultáneas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Prueba de múltiples notificaciones simultáneas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Prueba de múltiples notificaciones simultáneas.</t>
+  </si>
+  <si>
+    <t>Validación del icono de notificación</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Validación del icono de notificación
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación del icono de notificación</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación del icono de notificación.</t>
+  </si>
+  <si>
+    <t>Sonido al recibir notificación</t>
+  </si>
+  <si>
+    <t>Validar que sonido al recibir notificación en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Sonido al recibir notificación
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Sonido al recibir notificación</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Sonido al recibir notificación.</t>
+  </si>
+  <si>
+    <t>Carga de la barra de navegación</t>
+  </si>
+  <si>
+    <t>Validar que carga de la barra de navegación en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Carga de la barra de navegación
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Carga de la barra de navegación</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Carga de la barra de navegación.</t>
+  </si>
+  <si>
+    <t>Redirección entre secciones</t>
+  </si>
+  <si>
+    <t>Validar que redirección entre secciones en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Redirección entre secciones
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Redirección entre secciones</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Redirección entre secciones.</t>
+  </si>
+  <si>
+    <t>Comportamiento del botón inicio</t>
+  </si>
+  <si>
+    <t>Validar que comportamiento del botón inicio en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Comportamiento del botón inicio
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Comportamiento del botón inicio</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Comportamiento del botón inicio.</t>
+  </si>
+  <si>
+    <t>Responsive en pantallas móviles</t>
+  </si>
+  <si>
+    <t>Validar que responsive en pantallas móviles en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Responsive en pantallas móviles
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Responsive en pantallas móviles</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Responsive en pantallas móviles.</t>
+  </si>
+  <si>
+    <t>Validación del tema oscuro/claro</t>
+  </si>
+  <si>
+    <t>Validar que validación del tema oscuro/claro en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Validación del tema oscuro/claro
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación del tema oscuro/claro</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación del tema oscuro/claro.</t>
+  </si>
+  <si>
+    <t>Accesibilidad mediante teclado</t>
+  </si>
+  <si>
+    <t>Validar que accesibilidad mediante teclado en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Accesibilidad mediante teclado
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Accesibilidad mediante teclado</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Accesibilidad mediante teclado.</t>
+  </si>
+  <si>
+    <t>Validación de breadcrumbs</t>
+  </si>
+  <si>
+    <t>Validar que validación de breadcrumbs en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Validación de breadcrumbs
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de breadcrumbs</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de breadcrumbs.</t>
+  </si>
+  <si>
+    <t>Prueba de menús desplegables</t>
+  </si>
+  <si>
+    <t>Validar que prueba de menús desplegables en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Prueba de menús desplegables
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Prueba de menús desplegables</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Prueba de menús desplegables.</t>
+  </si>
+  <si>
+    <t>Rendimiento al cambiar de módulo</t>
+  </si>
+  <si>
+    <t>Validar que rendimiento al cambiar de módulo en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Rendimiento al cambiar de módulo
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Rendimiento al cambiar de módulo</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Rendimiento al cambiar de módulo.</t>
+  </si>
+  <si>
+    <t>Manejo de errores de navegación</t>
+  </si>
+  <si>
+    <t>Validar que manejo de errores de navegación en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Manejo de errores de navegación
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Manejo de errores de navegación</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Manejo de errores de navegación.</t>
+  </si>
+  <si>
+    <t>Visualización de componentes base</t>
+  </si>
+  <si>
+    <t>Validar que visualización de componentes base en el módulo Prototipo inicial / Configuración UI.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Prototipo inicial / Configuración UI
+2. Ejecutar la prueba: Visualización de componentes base
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Visualización de componentes base</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Visualización de componentes base.</t>
+  </si>
+  <si>
+    <t>Validación de colores y estilos</t>
+  </si>
+  <si>
+    <t>Validar que validación de colores y estilos en el módulo Prototipo inicial / Configuración UI.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Prototipo inicial / Configuración UI
+2. Ejecutar la prueba: Validación de colores y estilos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de colores y estilos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de colores y estilos.</t>
+  </si>
+  <si>
+    <t>Verificación del logo y branding</t>
+  </si>
+  <si>
+    <t>Validar que verificación del logo y branding en el módulo Prototipo inicial / Configuración UI.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Prototipo inicial / Configuración UI
+2. Ejecutar la prueba: Verificación del logo y branding
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Verificación del logo y branding</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Verificación del logo y branding.</t>
+  </si>
+  <si>
+    <t>Prueba de fuentes y tipografía</t>
+  </si>
+  <si>
+    <t>Validar que prueba de fuentes y tipografía en el módulo Prototipo inicial / Configuración UI.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Prototipo inicial / Configuración UI
+2. Ejecutar la prueba: Prueba de fuentes y tipografía
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Prueba de fuentes y tipografía</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Prueba de fuentes y tipografía.</t>
+  </si>
+  <si>
+    <t>Carga inicial del prototipo sin errores</t>
+  </si>
+  <si>
+    <t>Validar que carga inicial del prototipo sin errores en el módulo Prototipo inicial / Configuración UI.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Prototipo inicial / Configuración UI
+2. Ejecutar la prueba: Carga inicial del prototipo sin errores
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Carga inicial del prototipo sin errores</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Carga inicial del prototipo sin errores.</t>
+  </si>
+  <si>
+    <t>Validar que validación de credenciales
+correctas en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que validación de credenciales
+ incorrectas en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que bloqueo de cuenta tras 
+intentos fallidos en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que persistencia de 
+sesión (recordarme) en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que cierre de sesión 
+correcto en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que redirección tras
+ login exitoso en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que visualización de
+ mensajes de error en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que campos requeridos
+ vacíos en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que validación de 
+formato de email en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que verificación del botón
+ de iniciar sesión en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que accesibilidad del
+ formulario de login en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que tiempo de respuesta
+ del login en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que compatibilidad en
+ diferentes navegadores en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que seguridad del envío
+ de credenciales (https) en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que autenticación con
+ tokens válidos en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que carga inicial 
+del panel en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que visualización de
+ métricas de red en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que filtrado por rango
+ de fechas en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que interacción con 
+gráficas dinámicas en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que actualización automática
+ de datos en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que error al cargar datos 
+del backend en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que validación de roles
+ para contenido visible en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que visualización del 
+consumo de ancho de banda en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que ordenamiento de 
+registros en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que validación de componentes
+ visuales en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que usabilidad del dashboard 
+en pantallas pequeñas en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que rendimiento del dashboard 
+con gran cantidad de datos en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que comportamiento ante desconexión
+ del servidor en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que integración con backend 
+para métricas en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que comprobación de 
+carga de widgets en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que recepción de alerta
+ desde websocket en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que visualización en tiempo
+ real en la tabla en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que notificación emergente en
+ llegada de alerta en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que persistencia de alerta en
+ base de datos en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que validación del formato del
+ mensaje recibido en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que desconexión y reconexión
+ del websocket en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que filtrado por tipo de alerta 
+en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que cambio de color según nivel
+ de severidad en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que actualización sin recargar
+ la página en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que interacción con notificación
+ en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que prueba de carga con múltiples alertas
+ simultáneas en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que integración con backend /predict
+ en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que comprobación del botón limpiar
+ alertas en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que exportación de alertas visibles
+ en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que sincronización de alertas en
+ dispositivos múltiples en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que alertas duplicadas no deben
+ mostrarse en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que validación del timestamp
+ recibido en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que prueba de reconexión 
+automática en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que visualización en modo 
+oscuro en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que prueba de alerta manual
+ para testeo en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que carga inicial del historial 
+en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que filtrado por nivel de severidad
+ en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que filtrado por dirección ip en el
+ módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que paginación del historial en el
+ módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que exportación del historial en 
+csv en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que exportación en pdf en el
+ módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que visualización de detalles 
+de incidente en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que ordenamiento por fecha
+ en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que validación de filtros vacíos
+ en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que persistencia de filtros aplicados
+ en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que prueba con datos vacíos en el 
+módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que compatibilidad con distintos 
+navegadores en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que usabilidad del filtro avanzado
+ en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que tiempo de respuesta al cargar
+ incidentes en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que verificación de formato de datos 
+exportados en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que exportación de alertas a csv en el 
+módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que exportación de incidentes a pdf 
+en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que validación del contenido exportado 
+en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que descarga con nombre de archivo
+ correcto en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que validación de formato csv (separadores) 
+en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que validación de formato pdf (estructura) 
+en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que exportación con filtros aplicados 
+en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que exportación de datos grandes sin 
+errores en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que validación del botón exportar 
+activo en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que comportamiento ante exportación 
+vacía en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que aparición de notificación en 
+evento crítico en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que desaparición automática tras
+ tiempo definido en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que cierre manual de notificación
+ en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que persistencia en sesión 
+activa en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que cambio de color según 
+tipo (éxito/error) en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que compatibilidad con 
+distintos tamaños de pantalla en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que no repetición de 
+notificaciones idénticas en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que prueba de múltiples
+ notificaciones simultáneas en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que validación del icono 
+de notificación en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Predicciones correctas
+ con alta precisión</t>
   </si>
 </sst>
 </file>
@@ -581,7 +2662,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -610,12 +2691,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="63">
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -770,7 +2870,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -788,25 +2888,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -6684,6 +8766,28 @@
     <dataField name="Cuenta de Estado (Dropdown)" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
+    <format dxfId="22">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
     <format dxfId="16">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
@@ -6707,31 +8811,9 @@
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
     <format dxfId="10">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
     <format dxfId="9">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="8">
-      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="7">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="6">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="5">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="4">
-      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -6878,60 +8960,60 @@
     <dataField name="Cuenta de Test Case" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="32">
+    <format dxfId="38">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="37">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="36">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="35">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="34">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="30">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="29">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="28">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="27">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="26">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -7045,18 +9127,18 @@
   <autoFilter ref="A2:M140" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{7F95280F-E669-4A5D-AEDF-FCAAAC81F275}" name="Modulo (Dropdown)" totalsRowLabel="Total" dataDxfId="58" totalsRowDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{E775B39B-DEB6-4123-A65F-A37EDA4383A3}" name="Test Case" dataDxfId="56" totalsRowDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{4E500E60-0861-4EF2-B610-79885F5EF7FD}" name="Descripción" dataDxfId="54" totalsRowDxfId="53"/>
-    <tableColumn id="14" xr3:uid="{D149BE2F-3E66-4E54-8D0E-BA4D69F73794}" name="Tipo/s de Prueba" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{48166857-FFB0-4E91-A69A-8A057DEBB914}" name="Precondiciones" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="13" xr3:uid="{09440620-A437-484D-9292-769D8C979710}" name="Pasos a seguir" dataDxfId="48" totalsRowDxfId="47"/>
-    <tableColumn id="12" xr3:uid="{25FFAFC4-E636-4C78-8EC4-9B105CD6EC6A}" name="Datos de Prueba" dataDxfId="46" totalsRowDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{5C319188-663F-4BD1-ADB0-A93CF2F134F5}" name="Resultado Esperado" dataDxfId="44" totalsRowDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{AC65C1EE-D520-403E-8171-F3B42F898A90}" name="Resultado Actual (Si falla)" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{67BFFC43-BD7A-400D-BCA5-7641851369E7}" name="Ultima ejecución (Fecha)" dataDxfId="40" totalsRowDxfId="39"/>
-    <tableColumn id="10" xr3:uid="{AF2F4479-94ED-46CC-8F6A-9945904E34B4}" name="Encargado de Prueba" dataDxfId="38" totalsRowDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{1AE568CA-11EA-494D-A158-098CEC0427F1}" name="Estado (Dropdown)" dataDxfId="36" totalsRowDxfId="35"/>
-    <tableColumn id="9" xr3:uid="{D7CC1236-1B17-4FEE-A062-7A6AF5789012}" name="Comentario" totalsRowFunction="count" dataDxfId="34" totalsRowDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{E775B39B-DEB6-4123-A65F-A37EDA4383A3}" name="Test Case" dataDxfId="0" totalsRowDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{4E500E60-0861-4EF2-B610-79885F5EF7FD}" name="Descripción" dataDxfId="4" totalsRowDxfId="55"/>
+    <tableColumn id="14" xr3:uid="{D149BE2F-3E66-4E54-8D0E-BA4D69F73794}" name="Tipo/s de Prueba" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{48166857-FFB0-4E91-A69A-8A057DEBB914}" name="Precondiciones" dataDxfId="5" totalsRowDxfId="52"/>
+    <tableColumn id="13" xr3:uid="{09440620-A437-484D-9292-769D8C979710}" name="Pasos a seguir" dataDxfId="1" totalsRowDxfId="51"/>
+    <tableColumn id="12" xr3:uid="{25FFAFC4-E636-4C78-8EC4-9B105CD6EC6A}" name="Datos de Prueba" dataDxfId="3" totalsRowDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{5C319188-663F-4BD1-ADB0-A93CF2F134F5}" name="Resultado Esperado" dataDxfId="2" totalsRowDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{AC65C1EE-D520-403E-8171-F3B42F898A90}" name="Resultado Actual (Si falla)" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{67BFFC43-BD7A-400D-BCA5-7641851369E7}" name="Ultima ejecución (Fecha)" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{AF2F4479-94ED-46CC-8F6A-9945904E34B4}" name="Encargado de Prueba" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{1AE568CA-11EA-494D-A158-098CEC0427F1}" name="Estado (Dropdown)" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="9" xr3:uid="{D7CC1236-1B17-4FEE-A062-7A6AF5789012}" name="Comentario" totalsRowFunction="count" dataDxfId="40" totalsRowDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7380,84 +9462,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ACCE336-D829-4280-938B-27FEC42D7852}">
   <dimension ref="A1:A33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -7469,21 +9587,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D9AFB2-4BAC-4EFB-A2E7-92EA3A8E1FBC}">
   <dimension ref="A2:M140"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.140625" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="4" width="37.42578125" customWidth="1"/>
-    <col min="5" max="6" width="31.7109375" customWidth="1"/>
-    <col min="7" max="7" width="39.42578125" customWidth="1"/>
-    <col min="8" max="8" width="33.85546875" customWidth="1"/>
-    <col min="9" max="9" width="31.42578125" customWidth="1"/>
-    <col min="10" max="11" width="30.42578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" customWidth="1"/>
-    <col min="13" max="13" width="36.140625" customWidth="1"/>
+    <col min="1" max="1" width="22.88671875" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="37.44140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="37.44140625" customWidth="1"/>
+    <col min="5" max="6" width="31.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="39.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="31.44140625" customWidth="1"/>
+    <col min="10" max="11" width="30.44140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" customWidth="1"/>
+    <col min="13" max="13" width="36.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -7524,7 +9643,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
@@ -7561,7 +9680,7 @@
       </c>
       <c r="M3" s="7"/>
     </row>
-    <row r="4" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>1</v>
       </c>
@@ -7598,7 +9717,7 @@
       </c>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>2</v>
       </c>
@@ -7635,7 +9754,7 @@
       </c>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>2</v>
       </c>
@@ -7672,7 +9791,7 @@
       </c>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>2</v>
       </c>
@@ -7709,7 +9828,7 @@
       </c>
       <c r="M7" s="7"/>
     </row>
-    <row r="8" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>2</v>
       </c>
@@ -7746,7 +9865,7 @@
       </c>
       <c r="M8" s="7"/>
     </row>
-    <row r="9" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>2</v>
       </c>
@@ -7783,7 +9902,7 @@
       </c>
       <c r="M9" s="7"/>
     </row>
-    <row r="10" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>2</v>
       </c>
@@ -7820,7 +9939,7 @@
       </c>
       <c r="M10" s="7"/>
     </row>
-    <row r="11" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>2</v>
       </c>
@@ -7857,7 +9976,7 @@
       </c>
       <c r="M11" s="7"/>
     </row>
-    <row r="12" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>2</v>
       </c>
@@ -7894,7 +10013,7 @@
       </c>
       <c r="M12" s="7"/>
     </row>
-    <row r="13" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>3</v>
       </c>
@@ -7931,7 +10050,7 @@
       </c>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>3</v>
       </c>
@@ -7968,7 +10087,7 @@
       </c>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>29</v>
       </c>
@@ -8007,7 +10126,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>29</v>
       </c>
@@ -8044,7 +10163,7 @@
       </c>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>30</v>
       </c>
@@ -8079,7 +10198,7 @@
       </c>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>30</v>
       </c>
@@ -8114,7 +10233,7 @@
       </c>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>32</v>
       </c>
@@ -8151,7 +10270,7 @@
       </c>
       <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>32</v>
       </c>
@@ -8188,7 +10307,7 @@
       </c>
       <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>33</v>
       </c>
@@ -8225,7 +10344,7 @@
       </c>
       <c r="M21" s="7"/>
     </row>
-    <row r="22" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>5</v>
       </c>
@@ -8262,7 +10381,7 @@
       </c>
       <c r="M22" s="7"/>
     </row>
-    <row r="23" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>5</v>
       </c>
@@ -8299,7 +10418,7 @@
       </c>
       <c r="M23" s="7"/>
     </row>
-    <row r="24" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>30</v>
       </c>
@@ -8340,1657 +10459,4077 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="7"/>
+    <row r="25" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M25" s="10"/>
+    </row>
+    <row r="26" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="10"/>
+    </row>
+    <row r="27" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" s="10"/>
+    </row>
+    <row r="28" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28" s="10"/>
+    </row>
+    <row r="29" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M29" s="10"/>
+    </row>
+    <row r="30" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M30" s="10"/>
+    </row>
+    <row r="31" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M31" s="10"/>
+    </row>
+    <row r="32" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M32" s="10"/>
+    </row>
+    <row r="33" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M33" s="10"/>
+    </row>
+    <row r="34" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M34" s="10"/>
+    </row>
+    <row r="35" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M35" s="7"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="7"/>
+    <row r="36" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="7"/>
+    <row r="37" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M37" s="7"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="7"/>
+    <row r="38" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M38" s="7"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="7"/>
+    <row r="39" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M39" s="7"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="7"/>
+    <row r="40" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M40" s="7"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="7"/>
+    <row r="41" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M41" s="7"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="7"/>
+    <row r="42" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M42" s="7"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="7"/>
+    <row r="43" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M43" s="7"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="7"/>
+    <row r="44" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M44" s="7"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="7"/>
+    <row r="45" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M45" s="7"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="7"/>
+    <row r="46" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M46" s="7"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="7"/>
+    <row r="47" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M47" s="7"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="7"/>
+    <row r="48" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M48" s="7"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="7"/>
+    <row r="49" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M49" s="7"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="7"/>
+    <row r="50" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M50" s="7"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="7"/>
+    <row r="51" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M51" s="7"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="7"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="7"/>
+    <row r="52" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M52" s="7"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" s="7"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="7"/>
+    <row r="53" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M53" s="7"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="7"/>
+    <row r="54" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M54" s="7"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55" s="7"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="7"/>
+    <row r="55" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="7"/>
+    <row r="56" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M56" s="7"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A57" s="7"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="7"/>
+    <row r="57" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M57" s="7"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58" s="7"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="7"/>
+    <row r="58" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M58" s="7"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A59" s="7"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="7"/>
+    <row r="59" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M59" s="7"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60" s="7"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="7"/>
+    <row r="60" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M60" s="7"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="7"/>
+    <row r="61" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M61" s="7"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A62" s="7"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="7"/>
+    <row r="62" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M62" s="7"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A63" s="7"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="7"/>
+    <row r="63" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M63" s="7"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A64" s="7"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="7"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="7"/>
+    <row r="64" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M64" s="7"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="7"/>
-      <c r="H65" s="7"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="7"/>
+    <row r="65" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M65" s="7"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
-      <c r="I66" s="7"/>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="7"/>
+    <row r="66" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M66" s="7"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="7"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="7"/>
+    <row r="67" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M67" s="7"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="7"/>
+    <row r="68" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M68" s="7"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="7"/>
+    <row r="69" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M69" s="7"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A70" s="7"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="7"/>
+    <row r="70" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M70" s="7"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A71" s="7"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7"/>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
-      <c r="L71" s="7"/>
+    <row r="71" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M71" s="7"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
-      <c r="L72" s="7"/>
+    <row r="72" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M72" s="7"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73" s="7"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="7"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="7"/>
+    <row r="73" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M73" s="7"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="7"/>
+    <row r="74" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M74" s="7"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="7"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
-      <c r="L75" s="7"/>
+    <row r="75" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M75" s="7"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" s="7"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
-      <c r="L76" s="7"/>
+    <row r="76" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M76" s="7"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7"/>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
-      <c r="L77" s="7"/>
+    <row r="77" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M77" s="7"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" s="7"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
-      <c r="I78" s="7"/>
-      <c r="J78" s="3"/>
-      <c r="K78" s="3"/>
-      <c r="L78" s="7"/>
+    <row r="78" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M78" s="7"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="7"/>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
-      <c r="I79" s="7"/>
-      <c r="J79" s="3"/>
-      <c r="K79" s="3"/>
-      <c r="L79" s="7"/>
+    <row r="79" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M79" s="7"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="7"/>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7"/>
-      <c r="J80" s="3"/>
-      <c r="K80" s="3"/>
-      <c r="L80" s="7"/>
+    <row r="80" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M80" s="7"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="7"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-      <c r="I81" s="7"/>
-      <c r="J81" s="3"/>
-      <c r="K81" s="3"/>
-      <c r="L81" s="7"/>
+    <row r="81" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M81" s="7"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="7"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="7"/>
-      <c r="H82" s="7"/>
-      <c r="I82" s="7"/>
-      <c r="J82" s="3"/>
-      <c r="K82" s="3"/>
-      <c r="L82" s="7"/>
+    <row r="82" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M82" s="7"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="7"/>
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
-      <c r="I83" s="7"/>
-      <c r="J83" s="3"/>
-      <c r="K83" s="3"/>
-      <c r="L83" s="7"/>
+    <row r="83" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M83" s="7"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="7"/>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
-      <c r="I84" s="7"/>
-      <c r="J84" s="3"/>
-      <c r="K84" s="3"/>
-      <c r="L84" s="7"/>
+    <row r="84" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M84" s="7"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="7"/>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
-      <c r="I85" s="7"/>
-      <c r="J85" s="3"/>
-      <c r="K85" s="3"/>
-      <c r="L85" s="7"/>
+    <row r="85" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M85" s="7"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="7"/>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
-      <c r="G86" s="7"/>
-      <c r="H86" s="7"/>
-      <c r="I86" s="7"/>
-      <c r="J86" s="3"/>
-      <c r="K86" s="3"/>
-      <c r="L86" s="7"/>
+    <row r="86" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M86" s="7"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="7"/>
-      <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
-      <c r="I87" s="7"/>
-      <c r="J87" s="3"/>
-      <c r="K87" s="3"/>
-      <c r="L87" s="7"/>
+    <row r="87" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M87" s="7"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="7"/>
-      <c r="B88" s="7"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
-      <c r="G88" s="7"/>
-      <c r="H88" s="7"/>
-      <c r="I88" s="7"/>
-      <c r="J88" s="3"/>
-      <c r="K88" s="3"/>
-      <c r="L88" s="7"/>
+    <row r="88" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M88" s="7"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="7"/>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="7"/>
-      <c r="H89" s="7"/>
-      <c r="I89" s="7"/>
-      <c r="J89" s="3"/>
-      <c r="K89" s="3"/>
-      <c r="L89" s="7"/>
+    <row r="89" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M89" s="7"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="7"/>
-      <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
-      <c r="G90" s="7"/>
-      <c r="H90" s="7"/>
-      <c r="I90" s="7"/>
-      <c r="J90" s="3"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="7"/>
+    <row r="90" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M90" s="7"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A91" s="7"/>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7"/>
-      <c r="I91" s="7"/>
-      <c r="J91" s="3"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="7"/>
+    <row r="91" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M91" s="7"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" s="7"/>
-      <c r="B92" s="7"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-      <c r="G92" s="7"/>
-      <c r="H92" s="7"/>
-      <c r="I92" s="7"/>
-      <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
-      <c r="L92" s="7"/>
+    <row r="92" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M92" s="7"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A93" s="7"/>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
-      <c r="I93" s="7"/>
-      <c r="J93" s="3"/>
-      <c r="K93" s="3"/>
-      <c r="L93" s="7"/>
+    <row r="93" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M93" s="7"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A94" s="7"/>
-      <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="7"/>
-      <c r="H94" s="7"/>
-      <c r="I94" s="7"/>
-      <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
-      <c r="L94" s="7"/>
+    <row r="94" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M94" s="7"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A95" s="7"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
-      <c r="I95" s="7"/>
-      <c r="J95" s="3"/>
-      <c r="K95" s="3"/>
-      <c r="L95" s="7"/>
+    <row r="95" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M95" s="7"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="7"/>
-      <c r="B96" s="7"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
-      <c r="G96" s="7"/>
-      <c r="H96" s="7"/>
-      <c r="I96" s="7"/>
-      <c r="J96" s="3"/>
-      <c r="K96" s="3"/>
-      <c r="L96" s="7"/>
+    <row r="96" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M96" s="7"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A97" s="7"/>
-      <c r="B97" s="7"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="7"/>
-      <c r="H97" s="7"/>
-      <c r="I97" s="7"/>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="7"/>
+    <row r="97" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M97" s="7"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="7"/>
-      <c r="B98" s="7"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="7"/>
-      <c r="H98" s="7"/>
-      <c r="I98" s="7"/>
-      <c r="J98" s="3"/>
-      <c r="K98" s="3"/>
-      <c r="L98" s="7"/>
+    <row r="98" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M98" s="7"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="7"/>
-      <c r="B99" s="7"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="7"/>
-      <c r="H99" s="7"/>
-      <c r="I99" s="7"/>
-      <c r="J99" s="3"/>
-      <c r="K99" s="3"/>
-      <c r="L99" s="7"/>
+    <row r="99" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M99" s="7"/>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="7"/>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="7"/>
-      <c r="H100" s="7"/>
-      <c r="I100" s="7"/>
-      <c r="J100" s="3"/>
-      <c r="K100" s="3"/>
-      <c r="L100" s="7"/>
+    <row r="100" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M100" s="7"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="7"/>
-      <c r="B101" s="7"/>
-      <c r="C101" s="7"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="7"/>
-      <c r="H101" s="7"/>
-      <c r="I101" s="7"/>
-      <c r="J101" s="3"/>
-      <c r="K101" s="3"/>
-      <c r="L101" s="7"/>
+    <row r="101" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M101" s="7"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="7"/>
-      <c r="B102" s="7"/>
-      <c r="C102" s="7"/>
-      <c r="D102" s="7"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="7"/>
-      <c r="G102" s="7"/>
-      <c r="H102" s="7"/>
-      <c r="I102" s="7"/>
-      <c r="J102" s="3"/>
-      <c r="K102" s="3"/>
-      <c r="L102" s="7"/>
+    <row r="102" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M102" s="7"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="7"/>
-      <c r="B103" s="7"/>
-      <c r="C103" s="7"/>
-      <c r="D103" s="7"/>
-      <c r="E103" s="7"/>
-      <c r="F103" s="7"/>
-      <c r="G103" s="7"/>
-      <c r="H103" s="7"/>
-      <c r="I103" s="7"/>
-      <c r="J103" s="3"/>
-      <c r="K103" s="3"/>
-      <c r="L103" s="7"/>
+    <row r="103" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M103" s="7"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A104" s="7"/>
-      <c r="B104" s="7"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
-      <c r="F104" s="7"/>
-      <c r="G104" s="7"/>
-      <c r="H104" s="7"/>
-      <c r="I104" s="7"/>
-      <c r="J104" s="3"/>
-      <c r="K104" s="3"/>
-      <c r="L104" s="7"/>
+    <row r="104" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M104" s="7"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A105" s="7"/>
-      <c r="B105" s="7"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
-      <c r="G105" s="7"/>
-      <c r="H105" s="7"/>
-      <c r="I105" s="7"/>
-      <c r="J105" s="3"/>
-      <c r="K105" s="3"/>
-      <c r="L105" s="7"/>
+    <row r="105" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M105" s="7"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A106" s="7"/>
-      <c r="B106" s="7"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="7"/>
-      <c r="G106" s="7"/>
-      <c r="H106" s="7"/>
-      <c r="I106" s="7"/>
-      <c r="J106" s="3"/>
-      <c r="K106" s="3"/>
-      <c r="L106" s="7"/>
+    <row r="106" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M106" s="7"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="7"/>
-      <c r="B107" s="7"/>
-      <c r="C107" s="7"/>
-      <c r="D107" s="7"/>
-      <c r="E107" s="7"/>
-      <c r="F107" s="7"/>
-      <c r="G107" s="7"/>
-      <c r="H107" s="7"/>
-      <c r="I107" s="7"/>
-      <c r="J107" s="3"/>
-      <c r="K107" s="3"/>
-      <c r="L107" s="7"/>
+    <row r="107" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M107" s="7"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A108" s="7"/>
-      <c r="B108" s="7"/>
-      <c r="C108" s="7"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7"/>
-      <c r="G108" s="7"/>
-      <c r="H108" s="7"/>
-      <c r="I108" s="7"/>
-      <c r="J108" s="3"/>
-      <c r="K108" s="3"/>
-      <c r="L108" s="7"/>
+    <row r="108" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M108" s="7"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A109" s="7"/>
-      <c r="B109" s="7"/>
-      <c r="C109" s="7"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7"/>
-      <c r="G109" s="7"/>
-      <c r="H109" s="7"/>
-      <c r="I109" s="7"/>
-      <c r="J109" s="3"/>
-      <c r="K109" s="3"/>
-      <c r="L109" s="7"/>
+    <row r="109" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M109" s="7"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A110" s="7"/>
-      <c r="B110" s="7"/>
-      <c r="C110" s="7"/>
-      <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7"/>
-      <c r="G110" s="7"/>
-      <c r="H110" s="7"/>
-      <c r="I110" s="7"/>
-      <c r="J110" s="3"/>
-      <c r="K110" s="3"/>
-      <c r="L110" s="7"/>
+    <row r="110" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M110" s="7"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A111" s="7"/>
-      <c r="B111" s="7"/>
-      <c r="C111" s="7"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="7"/>
-      <c r="F111" s="7"/>
-      <c r="G111" s="7"/>
-      <c r="H111" s="7"/>
-      <c r="I111" s="7"/>
-      <c r="J111" s="3"/>
-      <c r="K111" s="3"/>
-      <c r="L111" s="7"/>
+    <row r="111" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M111" s="7"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A112" s="7"/>
-      <c r="B112" s="7"/>
-      <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="7"/>
-      <c r="G112" s="7"/>
-      <c r="H112" s="7"/>
-      <c r="I112" s="7"/>
-      <c r="J112" s="3"/>
-      <c r="K112" s="3"/>
-      <c r="L112" s="7"/>
+    <row r="112" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M112" s="7"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="7"/>
-      <c r="B113" s="7"/>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
-      <c r="G113" s="7"/>
-      <c r="H113" s="7"/>
-      <c r="I113" s="7"/>
-      <c r="J113" s="3"/>
-      <c r="K113" s="3"/>
-      <c r="L113" s="7"/>
+    <row r="113" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M113" s="7"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" s="7"/>
-      <c r="B114" s="7"/>
-      <c r="C114" s="7"/>
-      <c r="D114" s="7"/>
-      <c r="E114" s="7"/>
-      <c r="F114" s="7"/>
-      <c r="G114" s="7"/>
-      <c r="H114" s="7"/>
-      <c r="I114" s="7"/>
-      <c r="J114" s="3"/>
-      <c r="K114" s="3"/>
-      <c r="L114" s="7"/>
+    <row r="114" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M114" s="7"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="7"/>
-      <c r="B115" s="7"/>
-      <c r="C115" s="7"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
-      <c r="G115" s="7"/>
-      <c r="H115" s="7"/>
-      <c r="I115" s="7"/>
-      <c r="J115" s="3"/>
-      <c r="K115" s="3"/>
-      <c r="L115" s="7"/>
+    <row r="115" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M115" s="7"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="7"/>
-      <c r="B116" s="7"/>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="7"/>
-      <c r="H116" s="7"/>
-      <c r="I116" s="7"/>
-      <c r="J116" s="3"/>
-      <c r="K116" s="3"/>
-      <c r="L116" s="7"/>
+    <row r="116" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M116" s="7"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="7"/>
-      <c r="B117" s="7"/>
-      <c r="C117" s="7"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-      <c r="G117" s="7"/>
-      <c r="H117" s="7"/>
-      <c r="I117" s="7"/>
-      <c r="J117" s="3"/>
-      <c r="K117" s="3"/>
-      <c r="L117" s="7"/>
+    <row r="117" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M117" s="7"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="7"/>
-      <c r="B118" s="7"/>
-      <c r="C118" s="7"/>
-      <c r="D118" s="7"/>
-      <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
-      <c r="G118" s="7"/>
-      <c r="H118" s="7"/>
-      <c r="I118" s="7"/>
-      <c r="J118" s="3"/>
-      <c r="K118" s="3"/>
-      <c r="L118" s="7"/>
+    <row r="118" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M118" s="7"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="7"/>
-      <c r="B119" s="7"/>
-      <c r="C119" s="7"/>
-      <c r="D119" s="7"/>
-      <c r="E119" s="7"/>
-      <c r="F119" s="7"/>
-      <c r="G119" s="7"/>
-      <c r="H119" s="7"/>
-      <c r="I119" s="7"/>
-      <c r="J119" s="3"/>
-      <c r="K119" s="3"/>
-      <c r="L119" s="7"/>
+    <row r="119" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M119" s="7"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="7"/>
-      <c r="B120" s="7"/>
-      <c r="C120" s="7"/>
-      <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
-      <c r="G120" s="7"/>
-      <c r="H120" s="7"/>
-      <c r="I120" s="7"/>
-      <c r="J120" s="3"/>
-      <c r="K120" s="3"/>
-      <c r="L120" s="7"/>
+    <row r="120" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M120" s="7"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="7"/>
-      <c r="B121" s="7"/>
-      <c r="C121" s="7"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="7"/>
-      <c r="G121" s="7"/>
-      <c r="H121" s="7"/>
-      <c r="I121" s="7"/>
-      <c r="J121" s="3"/>
-      <c r="K121" s="3"/>
-      <c r="L121" s="7"/>
+    <row r="121" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M121" s="7"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="7"/>
-      <c r="B122" s="7"/>
-      <c r="C122" s="7"/>
-      <c r="D122" s="7"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
-      <c r="G122" s="7"/>
-      <c r="H122" s="7"/>
-      <c r="I122" s="7"/>
-      <c r="J122" s="3"/>
-      <c r="K122" s="3"/>
-      <c r="L122" s="7"/>
+    <row r="122" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M122" s="7"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="7"/>
-      <c r="B123" s="7"/>
-      <c r="C123" s="7"/>
-      <c r="D123" s="7"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="7"/>
-      <c r="G123" s="7"/>
-      <c r="H123" s="7"/>
-      <c r="I123" s="7"/>
-      <c r="J123" s="3"/>
-      <c r="K123" s="3"/>
-      <c r="L123" s="7"/>
+    <row r="123" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M123" s="7"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="7"/>
-      <c r="B124" s="7"/>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
-      <c r="G124" s="7"/>
-      <c r="H124" s="7"/>
-      <c r="I124" s="7"/>
-      <c r="J124" s="3"/>
-      <c r="K124" s="3"/>
-      <c r="L124" s="7"/>
+    <row r="124" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L124" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M124" s="7"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="7"/>
-      <c r="B125" s="7"/>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="7"/>
-      <c r="H125" s="7"/>
-      <c r="I125" s="7"/>
-      <c r="J125" s="3"/>
-      <c r="K125" s="3"/>
-      <c r="L125" s="7"/>
+    <row r="125" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="I125" s="1"/>
+      <c r="J125" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L125" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M125" s="7"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A126" s="7"/>
-      <c r="B126" s="7"/>
-      <c r="C126" s="7"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
-      <c r="F126" s="7"/>
-      <c r="G126" s="7"/>
-      <c r="H126" s="7"/>
-      <c r="I126" s="7"/>
-      <c r="J126" s="3"/>
-      <c r="K126" s="3"/>
-      <c r="L126" s="7"/>
+    <row r="126" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M126" s="7"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="7"/>
-      <c r="B127" s="7"/>
-      <c r="C127" s="7"/>
-      <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="7"/>
-      <c r="G127" s="7"/>
-      <c r="H127" s="7"/>
-      <c r="I127" s="7"/>
-      <c r="J127" s="3"/>
-      <c r="K127" s="3"/>
-      <c r="L127" s="7"/>
+    <row r="127" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M127" s="7"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="7"/>
-      <c r="B128" s="7"/>
-      <c r="C128" s="7"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="7"/>
-      <c r="F128" s="7"/>
-      <c r="G128" s="7"/>
-      <c r="H128" s="7"/>
-      <c r="I128" s="7"/>
-      <c r="J128" s="3"/>
-      <c r="K128" s="3"/>
-      <c r="L128" s="7"/>
+    <row r="128" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M128" s="7"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A129" s="7"/>
-      <c r="B129" s="7"/>
-      <c r="C129" s="7"/>
-      <c r="D129" s="7"/>
-      <c r="E129" s="7"/>
-      <c r="F129" s="7"/>
-      <c r="G129" s="7"/>
-      <c r="H129" s="7"/>
-      <c r="I129" s="7"/>
-      <c r="J129" s="3"/>
-      <c r="K129" s="3"/>
-      <c r="L129" s="7"/>
+    <row r="129" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L129" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M129" s="7"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A130" s="7"/>
-      <c r="B130" s="7"/>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="7"/>
-      <c r="H130" s="7"/>
-      <c r="I130" s="7"/>
-      <c r="J130" s="3"/>
-      <c r="K130" s="3"/>
-      <c r="L130" s="7"/>
+    <row r="130" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L130" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M130" s="7"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A131" s="7"/>
-      <c r="B131" s="7"/>
-      <c r="C131" s="7"/>
-      <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="7"/>
-      <c r="G131" s="7"/>
-      <c r="H131" s="7"/>
-      <c r="I131" s="7"/>
-      <c r="J131" s="3"/>
-      <c r="K131" s="3"/>
-      <c r="L131" s="7"/>
+    <row r="131" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L131" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M131" s="7"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A132" s="7"/>
-      <c r="B132" s="7"/>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7"/>
-      <c r="E132" s="7"/>
-      <c r="F132" s="7"/>
-      <c r="G132" s="7"/>
-      <c r="H132" s="7"/>
-      <c r="I132" s="7"/>
-      <c r="J132" s="3"/>
-      <c r="K132" s="3"/>
-      <c r="L132" s="7"/>
+    <row r="132" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L132" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M132" s="7"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A133" s="7"/>
-      <c r="B133" s="7"/>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="7"/>
-      <c r="G133" s="7"/>
-      <c r="H133" s="7"/>
-      <c r="I133" s="7"/>
-      <c r="J133" s="3"/>
-      <c r="K133" s="3"/>
-      <c r="L133" s="7"/>
+    <row r="133" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F133" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L133" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M133" s="7"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="7"/>
-      <c r="B134" s="7"/>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="7"/>
-      <c r="G134" s="7"/>
-      <c r="H134" s="7"/>
-      <c r="I134" s="7"/>
-      <c r="J134" s="3"/>
-      <c r="K134" s="3"/>
-      <c r="L134" s="7"/>
+    <row r="134" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M134" s="7"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -10005,7 +14544,7 @@
       <c r="L135" s="7"/>
       <c r="M135" s="7"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -10020,7 +14559,7 @@
       <c r="L136" s="7"/>
       <c r="M136" s="7"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -10035,7 +14574,7 @@
       <c r="L137" s="7"/>
       <c r="M137" s="7"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -10050,7 +14589,7 @@
       <c r="L138" s="7"/>
       <c r="M138" s="7"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -10065,7 +14604,7 @@
       <c r="L139" s="7"/>
       <c r="M139" s="7"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -10083,13 +14622,13 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L3:L140">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"PENDING"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10114,25 +14653,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58476477-5BDE-4E9D-BCDF-FD6E3C12EE95}">
   <dimension ref="A2:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.140625" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.109375" customWidth="1"/>
+    <col min="9" max="9" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -10143,7 +14682,7 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
@@ -10160,7 +14699,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -10173,7 +14712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -10186,7 +14725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -10199,7 +14738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -10212,7 +14751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
@@ -10229,7 +14768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
@@ -10237,7 +14776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -10245,7 +14784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>22</v>
       </c>
@@ -10253,7 +14792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>23</v>
       </c>
@@ -10261,7 +14800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -10278,7 +14817,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B55000D3-4297-437F-A419-CEB79EC3F6C0}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -10286,21 +14825,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E158E2AB9B4F924688B558FA982B40CF" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ce5f689dcf51305603cb0d070870d6dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="def3e2b2-904e-4359-b966-59b7b32cd06e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="252587ffdfea7067e66d630466c44dd6" ns2:_="">
     <xsd:import namespace="def3e2b2-904e-4359-b966-59b7b32cd06e"/>
@@ -10438,24 +14962,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CABA5C2-04D8-4DC5-BBFB-FF9AC004B268}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1F0EA96-F162-49AF-B0BE-A54883795866}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10471,4 +14993,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CABA5C2-04D8-4DC5-BBFB-FF9AC004B268}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Modelo Test Plan.xlsx
+++ b/Modelo Test Plan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kiro\CoderBits\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eva Laura\Documents\PROYECTO DE SISTEMAS III\proyecto\CoderBits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464F033F-7DCD-4B3B-88EE-29ACD3B86471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F832D88E-EF25-4644-8279-884CE5A49B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{96765352-7388-4C61-94B8-5077301D3254}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{96765352-7388-4C61-94B8-5077301D3254}"/>
   </bookViews>
   <sheets>
     <sheet name="Gestion de Modulos" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="756">
   <si>
     <t>MODULOS</t>
   </si>
@@ -532,12 +532,2233 @@
   'conteo_conexiones': null,
   'activo': True}</t>
   </si>
+  <si>
+    <t>Carga del modelo</t>
+  </si>
+  <si>
+    <t>Unitaria / Integración</t>
+  </si>
+  <si>
+    <t>1. Ejecutar el script principal
+2. Observar si el modelo se carga sin errores</t>
+  </si>
+  <si>
+    <t>Archivo: modelo_cicids2017.h5</t>
+  </si>
+  <si>
+    <t>15/10/2025</t>
+  </si>
+  <si>
+    <t>Validación de características</t>
+  </si>
+  <si>
+    <t>Modelo cargado</t>
+  </si>
+  <si>
+    <t>1. Ejecutar el script de validación de features
+2. Comparar las columnas recibidas con las esperadas</t>
+  </si>
+  <si>
+    <t>78 features esperadas del dataset CICIDS2017</t>
+  </si>
+  <si>
+    <t>Normalización de datos</t>
+  </si>
+  <si>
+    <t>1. Cargar el scaler
+2. Pasar un conjunto de datos de prueba
+3. Verificar rango de salida</t>
+  </si>
+  <si>
+    <t>Valores numéricos variados (sin normalizar)</t>
+  </si>
+  <si>
+    <t>Predicción en tiempo real</t>
+  </si>
+  <si>
+    <t>Integración / Rendimiento</t>
+  </si>
+  <si>
+    <t>1. Capturar tráfico con scapy
+2. Extraer features
+3. Pasarlas al modelo</t>
+  </si>
+  <si>
+    <t>Tráfico benigno simulado y tráfico DDoS</t>
+  </si>
+  <si>
+    <t>Gestión de errores de entrada</t>
+  </si>
+  <si>
+    <t>Unitaria / Robustez</t>
+  </si>
+  <si>
+    <t>1. Enviar datos con menos de 78 columnas
+2. Observar la salida</t>
+  </si>
+  <si>
+    <t>Features faltantes (ej. 76 columnas)</t>
+  </si>
+  <si>
+    <t>Integración con WebSocket</t>
+  </si>
+  <si>
+    <t>Integración / Interfaz</t>
+  </si>
+  <si>
+    <t>Servidor WebSocket activo</t>
+  </si>
+  <si>
+    <t>1. Activar monitoreo
+2. Observar si los eventos se transmiten por ws://127.0.0.1:8000/ws/alertas/</t>
+  </si>
+  <si>
+    <t>Tráfico de red real o simulado</t>
+  </si>
+  <si>
+    <t>Detección de anomalías</t>
+  </si>
+  <si>
+    <t>Integración / Base de Datos</t>
+  </si>
+  <si>
+    <t>Modelo cargado y BD activa</t>
+  </si>
+  <si>
+    <t>1. Ejecutar monitoreo
+2. Verificar si los ataques se guardan en la BD</t>
+  </si>
+  <si>
+    <t>Ataques tipo DDoS, PortScan</t>
+  </si>
+  <si>
+    <t>Mitigación de ataques</t>
+  </si>
+  <si>
+    <t>Funcional / Integración</t>
+  </si>
+  <si>
+    <t>Monitoreo activo y ataque detectado</t>
+  </si>
+  <si>
+    <t>1. Detectar ataque
+2. Verificar creación de mitigación en el backend</t>
+  </si>
+  <si>
+    <t>Conexión atacante IP: 192.168.1.100</t>
+  </si>
+  <si>
+    <t>Generación de reportes ML</t>
+  </si>
+  <si>
+    <t>Funcional / Reporte</t>
+  </si>
+  <si>
+    <t>1. Consultar endpoint /api/dashboard/stats/
+2. Verificar conteos y métricas</t>
+  </si>
+  <si>
+    <t>Datos históricos de tráfico</t>
+  </si>
+  <si>
+    <t>Fallos del modelo</t>
+  </si>
+  <si>
+    <t>Logger configurado</t>
+  </si>
+  <si>
+    <t>1. Forzar un error de predicción
+2. Revisar archivo de logs</t>
+  </si>
+  <si>
+    <t>Input no numérico o con NaN</t>
+  </si>
+  <si>
+    <t>MonitorSeguridadRedes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alejandro Chipana </t>
+  </si>
+  <si>
+    <t>Modelo cargado 
+exitosamente en memoria</t>
+  </si>
+  <si>
+    <t>Validación correcta 
+todas las columnas coinciden</t>
+  </si>
+  <si>
+    <t>Datos escalados correctamente
+ con media ~0 y desviación ~1</t>
+  </si>
+  <si>
+    <t>Error controlado
+ 'Número de características incorrecto'</t>
+  </si>
+  <si>
+    <t>Datos enviados exitosamente
+ a través del WebSocket</t>
+  </si>
+  <si>
+    <t>Registros guardados
+ correctamente en la tabla 'ataques'</t>
+  </si>
+  <si>
+    <t>Mitigación creada con acción
+ correspondiente (bloqueo, alerta)</t>
+  </si>
+  <si>
+    <t>Reporte generado con métricas de
+ ataques detectados y benignos</t>
+  </si>
+  <si>
+    <t>Error registrado en logs
+ 'ValueError: input contains NaN'</t>
+  </si>
+  <si>
+    <t>Modelo previamente entrenado 
+y guardado (.h5 o .pkl)</t>
+  </si>
+  <si>
+    <t>Scaler entrenado y 
+serializado (scaler.pkl)</t>
+  </si>
+  <si>
+    <t>Modelo y scaler 
+cargados, scapy activo</t>
+  </si>
+  <si>
+    <t>Modelo ejecutado con 
+registros previos</t>
+  </si>
+  <si>
+    <t>El sistema debe cargar correctamente
+ el modelo entrenado en memoria</t>
+  </si>
+  <si>
+    <t>El sistema debe validar que las 78
+ características de entrada sean las correctas</t>
+  </si>
+  <si>
+    <t>El sistema debe normalizar correctamente
+ los datos de entrada usando StandardScaler</t>
+  </si>
+  <si>
+    <t>El sistema debe predecir correctamente
+ si una conexión es BENIGN o ATAQUE</t>
+  </si>
+  <si>
+    <t>El sistema debe manejar errores 
+cuando faltan o sobran características</t>
+  </si>
+  <si>
+    <t>El sistema debe enviar las 
+predicciones en tiempo real al WebSocket</t>
+  </si>
+  <si>
+    <t>El sistema debe registrar las 
+conexiones clasificadas como ataque</t>
+  </si>
+  <si>
+    <t>El sistema debe generar acciones
+ de mitigación al detectar un ataque</t>
+  </si>
+  <si>
+    <t>El sistema debe generar reportes 
+con estadísticas de predicciones</t>
+  </si>
+  <si>
+    <t>El sistema debe registrar los 
+errores de ejecución del modelo en logs</t>
+  </si>
+  <si>
+    <t>Autenticación (Login)</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>Alertas en tiempo real</t>
+  </si>
+  <si>
+    <t>Historial de incidentes</t>
+  </si>
+  <si>
+    <t>Exportación de datos (CSV/PDF)</t>
+  </si>
+  <si>
+    <t>Notificaciones</t>
+  </si>
+  <si>
+    <t>Interfaz general / Navegación</t>
+  </si>
+  <si>
+    <t>Prototipo inicial / Configuración UI</t>
+  </si>
+  <si>
+    <t>10/10/2025</t>
+  </si>
+  <si>
+    <t>Edgar Amilcar Peña Escobar</t>
+  </si>
+  <si>
+    <t>Usabilidad</t>
+  </si>
+  <si>
+    <t>Rendimiento</t>
+  </si>
+  <si>
+    <t>Seguridad</t>
+  </si>
+  <si>
+    <t>Compatibilidad</t>
+  </si>
+  <si>
+    <t>Funcional</t>
+  </si>
+  <si>
+    <t>El sistema debe estar desplegado y operativo.</t>
+  </si>
+  <si>
+    <t>Validación / UI</t>
+  </si>
+  <si>
+    <t>Alejandro Chipana</t>
+  </si>
+  <si>
+    <t>Validación de credenciales correctas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Validación de credenciales correctas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de credenciales correctas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de credenciales correctas.</t>
+  </si>
+  <si>
+    <t>Validación de credenciales incorrectas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Validación de credenciales incorrectas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de credenciales incorrectas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de credenciales incorrectas.</t>
+  </si>
+  <si>
+    <t>Bloqueo de cuenta tras intentos fallidos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Bloqueo de cuenta tras intentos fallidos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Bloqueo de cuenta tras intentos fallidos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Bloqueo de cuenta tras intentos fallidos.</t>
+  </si>
+  <si>
+    <t>Persistencia de sesión (recordarme)</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Persistencia de sesión (recordarme)
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Persistencia de sesión (recordarme)</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Persistencia de sesión (recordarme).</t>
+  </si>
+  <si>
+    <t>Cierre de sesión correcto</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Cierre de sesión correcto
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Cierre de sesión correcto</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Cierre de sesión correcto.</t>
+  </si>
+  <si>
+    <t>Redirección tras login exitoso</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Redirección tras login exitoso
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Redirección tras login exitoso</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Redirección tras login exitoso.</t>
+  </si>
+  <si>
+    <t>Visualización de mensajes de error</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Visualización de mensajes de error
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Visualización de mensajes de error</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Visualización de mensajes de error.</t>
+  </si>
+  <si>
+    <t>Campos requeridos vacíos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Campos requeridos vacíos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Campos requeridos vacíos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Campos requeridos vacíos.</t>
+  </si>
+  <si>
+    <t>Validación de formato de email</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Validación de formato de email
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de formato de email</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de formato de email.</t>
+  </si>
+  <si>
+    <t>Verificación del botón de iniciar sesión</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Verificación del botón de iniciar sesión
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Verificación del botón de iniciar sesión</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Verificación del botón de iniciar sesión.</t>
+  </si>
+  <si>
+    <t>Accesibilidad del formulario de login</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Accesibilidad del formulario de login
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Accesibilidad del formulario de login</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Accesibilidad del formulario de login.</t>
+  </si>
+  <si>
+    <t>Tiempo de respuesta del login</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Tiempo de respuesta del login
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Tiempo de respuesta del login</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Tiempo de respuesta del login.</t>
+  </si>
+  <si>
+    <t>Compatibilidad en diferentes navegadores</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Compatibilidad en diferentes navegadores
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Compatibilidad en diferentes navegadores</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Compatibilidad en diferentes navegadores.</t>
+  </si>
+  <si>
+    <t>Seguridad del envío de credenciales (HTTPS)</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Seguridad del envío de credenciales (HTTPS)
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Seguridad del envío de credenciales (HTTPS)</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Seguridad del envío de credenciales (HTTPS).</t>
+  </si>
+  <si>
+    <t>Autenticación con tokens válidos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Login
+2. Ejecutar la prueba: Autenticación con tokens válidos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Autenticación con tokens válidos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Autenticación con tokens válidos.</t>
+  </si>
+  <si>
+    <t>Carga inicial del panel</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Carga inicial del panel
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Carga inicial del panel</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Carga inicial del panel.</t>
+  </si>
+  <si>
+    <t>Visualización de métricas de red</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Visualización de métricas de red
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Visualización de métricas de red</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Visualización de métricas de red.</t>
+  </si>
+  <si>
+    <t>Filtrado por rango de fechas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Filtrado por rango de fechas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Filtrado por rango de fechas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Filtrado por rango de fechas.</t>
+  </si>
+  <si>
+    <t>Interacción con gráficas dinámicas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Interacción con gráficas dinámicas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Interacción con gráficas dinámicas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Interacción con gráficas dinámicas.</t>
+  </si>
+  <si>
+    <t>Actualización automática de datos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Actualización automática de datos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Actualización automática de datos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Actualización automática de datos.</t>
+  </si>
+  <si>
+    <t>Error al cargar datos del backend</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Error al cargar datos del backend
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Error al cargar datos del backend</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Error al cargar datos del backend.</t>
+  </si>
+  <si>
+    <t>Validación de roles para contenido visible</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Validación de roles para contenido visible
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de roles para contenido visible</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de roles para contenido visible.</t>
+  </si>
+  <si>
+    <t>Visualización del consumo de ancho de banda</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Visualización del consumo de ancho de banda
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Visualización del consumo de ancho de banda</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Visualización del consumo de ancho de banda.</t>
+  </si>
+  <si>
+    <t>Ordenamiento de registros</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Ordenamiento de registros
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Ordenamiento de registros</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Ordenamiento de registros.</t>
+  </si>
+  <si>
+    <t>Validación de componentes visuales</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Validación de componentes visuales
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de componentes visuales</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de componentes visuales.</t>
+  </si>
+  <si>
+    <t>Usabilidad del dashboard en pantallas pequeñas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Usabilidad del dashboard en pantallas pequeñas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Usabilidad del dashboard en pantallas pequeñas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Usabilidad del dashboard en pantallas pequeñas.</t>
+  </si>
+  <si>
+    <t>Rendimiento del dashboard con gran cantidad de datos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Rendimiento del dashboard con gran cantidad de datos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Rendimiento del dashboard con gran cantidad de datos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Rendimiento del dashboard con gran cantidad de datos.</t>
+  </si>
+  <si>
+    <t>Comportamiento ante desconexión del servidor</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Comportamiento ante desconexión del servidor
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Comportamiento ante desconexión del servidor</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Comportamiento ante desconexión del servidor.</t>
+  </si>
+  <si>
+    <t>Integración con backend para métricas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Integración con backend para métricas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Integración con backend para métricas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Integración con backend para métricas.</t>
+  </si>
+  <si>
+    <t>Comprobación de carga de widgets</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Dashboard
+2. Ejecutar la prueba: Comprobación de carga de widgets
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Comprobación de carga de widgets</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Comprobación de carga de widgets.</t>
+  </si>
+  <si>
+    <t>Recepción de alerta desde WebSocket</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Recepción de alerta desde WebSocket
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Recepción de alerta desde WebSocket</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Recepción de alerta desde WebSocket.</t>
+  </si>
+  <si>
+    <t>Visualización en tiempo real en la tabla</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Visualización en tiempo real en la tabla
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Visualización en tiempo real en la tabla</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Visualización en tiempo real en la tabla.</t>
+  </si>
+  <si>
+    <t>Notificación emergente en llegada de alerta</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Notificación emergente en llegada de alerta
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Notificación emergente en llegada de alerta</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Notificación emergente en llegada de alerta.</t>
+  </si>
+  <si>
+    <t>Persistencia de alerta en base de datos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Persistencia de alerta en base de datos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Persistencia de alerta en base de datos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Persistencia de alerta en base de datos.</t>
+  </si>
+  <si>
+    <t>Validación del formato del mensaje recibido</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Validación del formato del mensaje recibido
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación del formato del mensaje recibido</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación del formato del mensaje recibido.</t>
+  </si>
+  <si>
+    <t>Desconexión y reconexión del WebSocket</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Desconexión y reconexión del WebSocket
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Desconexión y reconexión del WebSocket</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Desconexión y reconexión del WebSocket.</t>
+  </si>
+  <si>
+    <t>Filtrado por tipo de alerta</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Filtrado por tipo de alerta
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Filtrado por tipo de alerta</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Filtrado por tipo de alerta.</t>
+  </si>
+  <si>
+    <t>Cambio de color según nivel de severidad</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Cambio de color según nivel de severidad
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Cambio de color según nivel de severidad</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Cambio de color según nivel de severidad.</t>
+  </si>
+  <si>
+    <t>Actualización sin recargar la página</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Actualización sin recargar la página
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Actualización sin recargar la página</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Actualización sin recargar la página.</t>
+  </si>
+  <si>
+    <t>Interacción con notificación</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Interacción con notificación
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Interacción con notificación</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Interacción con notificación.</t>
+  </si>
+  <si>
+    <t>Prueba de carga con múltiples alertas simultáneas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Prueba de carga con múltiples alertas simultáneas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Prueba de carga con múltiples alertas simultáneas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Prueba de carga con múltiples alertas simultáneas.</t>
+  </si>
+  <si>
+    <t>Integración con backend /predict</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Integración con backend /predict
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Integración con backend /predict</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Integración con backend /predict.</t>
+  </si>
+  <si>
+    <t>Comprobación del botón limpiar alertas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Comprobación del botón limpiar alertas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Comprobación del botón limpiar alertas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Comprobación del botón limpiar alertas.</t>
+  </si>
+  <si>
+    <t>Exportación de alertas visibles</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Exportación de alertas visibles
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Exportación de alertas visibles</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Exportación de alertas visibles.</t>
+  </si>
+  <si>
+    <t>Sincronización de alertas en dispositivos múltiples</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Sincronización de alertas en dispositivos múltiples
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Sincronización de alertas en dispositivos múltiples</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Sincronización de alertas en dispositivos múltiples.</t>
+  </si>
+  <si>
+    <t>Alertas duplicadas no deben mostrarse</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Alertas duplicadas no deben mostrarse
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Alertas duplicadas no deben mostrarse</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Alertas duplicadas no deben mostrarse.</t>
+  </si>
+  <si>
+    <t>Validación del timestamp recibido</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Validación del timestamp recibido
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación del timestamp recibido</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación del timestamp recibido.</t>
+  </si>
+  <si>
+    <t>Prueba de reconexión automática</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Prueba de reconexión automática
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Prueba de reconexión automática</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Prueba de reconexión automática.</t>
+  </si>
+  <si>
+    <t>Visualización en modo oscuro</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Visualización en modo oscuro
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Visualización en modo oscuro</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Visualización en modo oscuro.</t>
+  </si>
+  <si>
+    <t>Prueba de alerta manual para testeo</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Alertas en tiempo real
+2. Ejecutar la prueba: Prueba de alerta manual para testeo
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Prueba de alerta manual para testeo</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Prueba de alerta manual para testeo.</t>
+  </si>
+  <si>
+    <t>Carga inicial del historial</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Carga inicial del historial
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Carga inicial del historial</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Carga inicial del historial.</t>
+  </si>
+  <si>
+    <t>Filtrado por nivel de severidad</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Filtrado por nivel de severidad
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Filtrado por nivel de severidad</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Filtrado por nivel de severidad.</t>
+  </si>
+  <si>
+    <t>Filtrado por dirección IP</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Filtrado por dirección IP
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Filtrado por dirección IP</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Filtrado por dirección IP.</t>
+  </si>
+  <si>
+    <t>Paginación del historial</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Paginación del historial
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Paginación del historial</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Paginación del historial.</t>
+  </si>
+  <si>
+    <t>Exportación del historial en CSV</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Exportación del historial en CSV
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Exportación del historial en CSV</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Exportación del historial en CSV.</t>
+  </si>
+  <si>
+    <t>Exportación en PDF</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Exportación en PDF
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Exportación en PDF</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Exportación en PDF.</t>
+  </si>
+  <si>
+    <t>Visualización de detalles de incidente</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Visualización de detalles de incidente
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Visualización de detalles de incidente</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Visualización de detalles de incidente.</t>
+  </si>
+  <si>
+    <t>Ordenamiento por fecha</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Ordenamiento por fecha
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Ordenamiento por fecha</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Ordenamiento por fecha.</t>
+  </si>
+  <si>
+    <t>Validación de filtros vacíos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Validación de filtros vacíos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de filtros vacíos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de filtros vacíos.</t>
+  </si>
+  <si>
+    <t>Persistencia de filtros aplicados</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Persistencia de filtros aplicados
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Persistencia de filtros aplicados</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Persistencia de filtros aplicados.</t>
+  </si>
+  <si>
+    <t>Prueba con datos vacíos</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Prueba con datos vacíos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Prueba con datos vacíos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Prueba con datos vacíos.</t>
+  </si>
+  <si>
+    <t>Compatibilidad con distintos navegadores</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Compatibilidad con distintos navegadores
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Compatibilidad con distintos navegadores</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Compatibilidad con distintos navegadores.</t>
+  </si>
+  <si>
+    <t>Usabilidad del filtro avanzado</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Usabilidad del filtro avanzado
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Usabilidad del filtro avanzado</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Usabilidad del filtro avanzado.</t>
+  </si>
+  <si>
+    <t>Tiempo de respuesta al cargar incidentes</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Tiempo de respuesta al cargar incidentes
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Tiempo de respuesta al cargar incidentes</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Tiempo de respuesta al cargar incidentes.</t>
+  </si>
+  <si>
+    <t>Verificación de formato de datos exportados</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Historial de incidentes
+2. Ejecutar la prueba: Verificación de formato de datos exportados
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Verificación de formato de datos exportados</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Verificación de formato de datos exportados.</t>
+  </si>
+  <si>
+    <t>Exportación de alertas a CSV</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Exportación de alertas a CSV
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Exportación de alertas a CSV</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Exportación de alertas a CSV.</t>
+  </si>
+  <si>
+    <t>Exportación de incidentes a PDF</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Exportación de incidentes a PDF
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Exportación de incidentes a PDF</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Exportación de incidentes a PDF.</t>
+  </si>
+  <si>
+    <t>Validación del contenido exportado</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Validación del contenido exportado
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación del contenido exportado</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación del contenido exportado.</t>
+  </si>
+  <si>
+    <t>Descarga con nombre de archivo correcto</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Descarga con nombre de archivo correcto
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Descarga con nombre de archivo correcto</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Descarga con nombre de archivo correcto.</t>
+  </si>
+  <si>
+    <t>Validación de formato CSV (separadores)</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Validación de formato CSV (separadores)
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de formato CSV (separadores)</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de formato CSV (separadores).</t>
+  </si>
+  <si>
+    <t>Validación de formato PDF (estructura)</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Validación de formato PDF (estructura)
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de formato PDF (estructura)</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de formato PDF (estructura).</t>
+  </si>
+  <si>
+    <t>Exportación con filtros aplicados</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Exportación con filtros aplicados
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Exportación con filtros aplicados</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Exportación con filtros aplicados.</t>
+  </si>
+  <si>
+    <t>Exportación de datos grandes sin errores</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Exportación de datos grandes sin errores
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Exportación de datos grandes sin errores</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Exportación de datos grandes sin errores.</t>
+  </si>
+  <si>
+    <t>Validación del botón Exportar activo</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Validación del botón Exportar activo
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación del botón Exportar activo</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación del botón Exportar activo.</t>
+  </si>
+  <si>
+    <t>Comportamiento ante exportación vacía</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Exportación de datos (CSV/PDF)
+2. Ejecutar la prueba: Comportamiento ante exportación vacía
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Comportamiento ante exportación vacía</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Comportamiento ante exportación vacía.</t>
+  </si>
+  <si>
+    <t>Aparición de notificación en evento crítico</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Aparición de notificación en evento crítico
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Aparición de notificación en evento crítico</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Aparición de notificación en evento crítico.</t>
+  </si>
+  <si>
+    <t>Desaparición automática tras tiempo definido</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Desaparición automática tras tiempo definido
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Desaparición automática tras tiempo definido</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Desaparición automática tras tiempo definido.</t>
+  </si>
+  <si>
+    <t>Cierre manual de notificación</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Cierre manual de notificación
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Cierre manual de notificación</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Cierre manual de notificación.</t>
+  </si>
+  <si>
+    <t>Persistencia en sesión activa</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Persistencia en sesión activa
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Persistencia en sesión activa</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Persistencia en sesión activa.</t>
+  </si>
+  <si>
+    <t>Cambio de color según tipo (éxito/error)</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Cambio de color según tipo (éxito/error)
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Cambio de color según tipo (éxito/error)</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Cambio de color según tipo (éxito/error).</t>
+  </si>
+  <si>
+    <t>Compatibilidad con distintos tamaños de pantalla</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Compatibilidad con distintos tamaños de pantalla
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Compatibilidad con distintos tamaños de pantalla</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Compatibilidad con distintos tamaños de pantalla.</t>
+  </si>
+  <si>
+    <t>No repetición de notificaciones idénticas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: No repetición de notificaciones idénticas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: No repetición de notificaciones idénticas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: No repetición de notificaciones idénticas.</t>
+  </si>
+  <si>
+    <t>Prueba de múltiples notificaciones simultáneas</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Prueba de múltiples notificaciones simultáneas
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Prueba de múltiples notificaciones simultáneas</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Prueba de múltiples notificaciones simultáneas.</t>
+  </si>
+  <si>
+    <t>Validación del icono de notificación</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Validación del icono de notificación
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación del icono de notificación</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación del icono de notificación.</t>
+  </si>
+  <si>
+    <t>Sonido al recibir notificación</t>
+  </si>
+  <si>
+    <t>Validar que sonido al recibir notificación en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Notificaciones
+2. Ejecutar la prueba: Sonido al recibir notificación
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Sonido al recibir notificación</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Sonido al recibir notificación.</t>
+  </si>
+  <si>
+    <t>Carga de la barra de navegación</t>
+  </si>
+  <si>
+    <t>Validar que carga de la barra de navegación en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Carga de la barra de navegación
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Carga de la barra de navegación</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Carga de la barra de navegación.</t>
+  </si>
+  <si>
+    <t>Redirección entre secciones</t>
+  </si>
+  <si>
+    <t>Validar que redirección entre secciones en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Redirección entre secciones
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Redirección entre secciones</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Redirección entre secciones.</t>
+  </si>
+  <si>
+    <t>Comportamiento del botón inicio</t>
+  </si>
+  <si>
+    <t>Validar que comportamiento del botón inicio en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Comportamiento del botón inicio
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Comportamiento del botón inicio</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Comportamiento del botón inicio.</t>
+  </si>
+  <si>
+    <t>Responsive en pantallas móviles</t>
+  </si>
+  <si>
+    <t>Validar que responsive en pantallas móviles en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Responsive en pantallas móviles
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Responsive en pantallas móviles</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Responsive en pantallas móviles.</t>
+  </si>
+  <si>
+    <t>Validación del tema oscuro/claro</t>
+  </si>
+  <si>
+    <t>Validar que validación del tema oscuro/claro en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Validación del tema oscuro/claro
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación del tema oscuro/claro</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación del tema oscuro/claro.</t>
+  </si>
+  <si>
+    <t>Accesibilidad mediante teclado</t>
+  </si>
+  <si>
+    <t>Validar que accesibilidad mediante teclado en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Accesibilidad mediante teclado
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Accesibilidad mediante teclado</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Accesibilidad mediante teclado.</t>
+  </si>
+  <si>
+    <t>Validación de breadcrumbs</t>
+  </si>
+  <si>
+    <t>Validar que validación de breadcrumbs en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Validación de breadcrumbs
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de breadcrumbs</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de breadcrumbs.</t>
+  </si>
+  <si>
+    <t>Prueba de menús desplegables</t>
+  </si>
+  <si>
+    <t>Validar que prueba de menús desplegables en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Prueba de menús desplegables
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Prueba de menús desplegables</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Prueba de menús desplegables.</t>
+  </si>
+  <si>
+    <t>Rendimiento al cambiar de módulo</t>
+  </si>
+  <si>
+    <t>Validar que rendimiento al cambiar de módulo en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Rendimiento al cambiar de módulo
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Rendimiento al cambiar de módulo</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Rendimiento al cambiar de módulo.</t>
+  </si>
+  <si>
+    <t>Manejo de errores de navegación</t>
+  </si>
+  <si>
+    <t>Validar que manejo de errores de navegación en el módulo Interfaz general / Navegación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Interfaz general / Navegación
+2. Ejecutar la prueba: Manejo de errores de navegación
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Manejo de errores de navegación</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Manejo de errores de navegación.</t>
+  </si>
+  <si>
+    <t>Visualización de componentes base</t>
+  </si>
+  <si>
+    <t>Validar que visualización de componentes base en el módulo Prototipo inicial / Configuración UI.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Prototipo inicial / Configuración UI
+2. Ejecutar la prueba: Visualización de componentes base
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Visualización de componentes base</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Visualización de componentes base.</t>
+  </si>
+  <si>
+    <t>Validación de colores y estilos</t>
+  </si>
+  <si>
+    <t>Validar que validación de colores y estilos en el módulo Prototipo inicial / Configuración UI.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Prototipo inicial / Configuración UI
+2. Ejecutar la prueba: Validación de colores y estilos
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Validación de colores y estilos</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Validación de colores y estilos.</t>
+  </si>
+  <si>
+    <t>Verificación del logo y branding</t>
+  </si>
+  <si>
+    <t>Validar que verificación del logo y branding en el módulo Prototipo inicial / Configuración UI.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Prototipo inicial / Configuración UI
+2. Ejecutar la prueba: Verificación del logo y branding
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Verificación del logo y branding</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Verificación del logo y branding.</t>
+  </si>
+  <si>
+    <t>Prueba de fuentes y tipografía</t>
+  </si>
+  <si>
+    <t>Validar que prueba de fuentes y tipografía en el módulo Prototipo inicial / Configuración UI.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Prototipo inicial / Configuración UI
+2. Ejecutar la prueba: Prueba de fuentes y tipografía
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Prueba de fuentes y tipografía</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Prueba de fuentes y tipografía.</t>
+  </si>
+  <si>
+    <t>Carga inicial del prototipo sin errores</t>
+  </si>
+  <si>
+    <t>Validar que carga inicial del prototipo sin errores en el módulo Prototipo inicial / Configuración UI.</t>
+  </si>
+  <si>
+    <t>1. Ingresar al módulo Prototipo inicial / Configuración UI
+2. Ejecutar la prueba: Carga inicial del prototipo sin errores
+3. Verificar resultado esperado.</t>
+  </si>
+  <si>
+    <t>Datos simulados para la prueba: Carga inicial del prototipo sin errores</t>
+  </si>
+  <si>
+    <t>El sistema debe cumplir correctamente con: Carga inicial del prototipo sin errores.</t>
+  </si>
+  <si>
+    <t>Validar que validación de credenciales
+correctas en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que validación de credenciales
+ incorrectas en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que bloqueo de cuenta tras 
+intentos fallidos en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que persistencia de 
+sesión (recordarme) en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que cierre de sesión 
+correcto en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que redirección tras
+ login exitoso en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que visualización de
+ mensajes de error en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que campos requeridos
+ vacíos en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que validación de 
+formato de email en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que verificación del botón
+ de iniciar sesión en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que accesibilidad del
+ formulario de login en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que tiempo de respuesta
+ del login en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que compatibilidad en
+ diferentes navegadores en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que seguridad del envío
+ de credenciales (https) en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que autenticación con
+ tokens válidos en el módulo Login.</t>
+  </si>
+  <si>
+    <t>Validar que carga inicial 
+del panel en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que visualización de
+ métricas de red en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que filtrado por rango
+ de fechas en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que interacción con 
+gráficas dinámicas en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que actualización automática
+ de datos en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que error al cargar datos 
+del backend en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que validación de roles
+ para contenido visible en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que visualización del 
+consumo de ancho de banda en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que ordenamiento de 
+registros en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que validación de componentes
+ visuales en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que usabilidad del dashboard 
+en pantallas pequeñas en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que rendimiento del dashboard 
+con gran cantidad de datos en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que comportamiento ante desconexión
+ del servidor en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que integración con backend 
+para métricas en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que comprobación de 
+carga de widgets en el módulo Dashboard.</t>
+  </si>
+  <si>
+    <t>Validar que recepción de alerta
+ desde websocket en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que visualización en tiempo
+ real en la tabla en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que notificación emergente en
+ llegada de alerta en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que persistencia de alerta en
+ base de datos en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que validación del formato del
+ mensaje recibido en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que desconexión y reconexión
+ del websocket en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que filtrado por tipo de alerta 
+en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que cambio de color según nivel
+ de severidad en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que actualización sin recargar
+ la página en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que interacción con notificación
+ en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que prueba de carga con múltiples alertas
+ simultáneas en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que integración con backend /predict
+ en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que comprobación del botón limpiar
+ alertas en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que exportación de alertas visibles
+ en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que sincronización de alertas en
+ dispositivos múltiples en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que alertas duplicadas no deben
+ mostrarse en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que validación del timestamp
+ recibido en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que prueba de reconexión 
+automática en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que visualización en modo 
+oscuro en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que prueba de alerta manual
+ para testeo en el módulo Alertas en tiempo real.</t>
+  </si>
+  <si>
+    <t>Validar que carga inicial del historial 
+en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que filtrado por nivel de severidad
+ en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que filtrado por dirección ip en el
+ módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que paginación del historial en el
+ módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que exportación del historial en 
+csv en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que exportación en pdf en el
+ módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que visualización de detalles 
+de incidente en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que ordenamiento por fecha
+ en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que validación de filtros vacíos
+ en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que persistencia de filtros aplicados
+ en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que prueba con datos vacíos en el 
+módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que compatibilidad con distintos 
+navegadores en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que usabilidad del filtro avanzado
+ en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que tiempo de respuesta al cargar
+ incidentes en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que verificación de formato de datos 
+exportados en el módulo Historial de incidentes.</t>
+  </si>
+  <si>
+    <t>Validar que exportación de alertas a csv en el 
+módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que exportación de incidentes a pdf 
+en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que validación del contenido exportado 
+en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que descarga con nombre de archivo
+ correcto en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que validación de formato csv (separadores) 
+en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que validación de formato pdf (estructura) 
+en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que exportación con filtros aplicados 
+en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que exportación de datos grandes sin 
+errores en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que validación del botón exportar 
+activo en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que comportamiento ante exportación 
+vacía en el módulo Exportación de datos (CSV/PDF).</t>
+  </si>
+  <si>
+    <t>Validar que aparición de notificación en 
+evento crítico en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que desaparición automática tras
+ tiempo definido en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que cierre manual de notificación
+ en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que persistencia en sesión 
+activa en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que cambio de color según 
+tipo (éxito/error) en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que compatibilidad con 
+distintos tamaños de pantalla en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que no repetición de 
+notificaciones idénticas en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que prueba de múltiples
+ notificaciones simultáneas en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Validar que validación del icono 
+de notificación en el módulo Notificaciones.</t>
+  </si>
+  <si>
+    <t>Predicciones correctas
+ con alta precisión</t>
+  </si>
+  <si>
+    <t>El sistema genera un token válido y navega al Dashboard.</t>
+  </si>
+  <si>
+    <t>Movil conectado con el servidor React</t>
+  </si>
+  <si>
+    <t>1. Ingresar credenciales válidas.         2. Presionar "Ingresar".</t>
+  </si>
+  <si>
+    <t>Usuario: willy, Contraseña: 12345678</t>
+  </si>
+  <si>
+    <t>La app navega a /dashboard y guarda el token en SecureStore.</t>
+  </si>
+  <si>
+    <t>Eva Laura Quispe Murga</t>
+  </si>
+  <si>
+    <t>Login Movil con éxito</t>
+  </si>
+  <si>
+    <t>Login Movil con error</t>
+  </si>
+  <si>
+    <t>El sistema rechaza credenciales inválidas.</t>
+  </si>
+  <si>
+    <t>Usuario: wildjk , Contraseña: 12345679</t>
+  </si>
+  <si>
+    <t>Se muestra el Alert: "Usuario o contraseña inválidos."</t>
+  </si>
+  <si>
+    <t>Alert mostrado, permanece en Login.</t>
+  </si>
+  <si>
+    <t>Dashboard Movil</t>
+  </si>
+  <si>
+    <t>Verificar que los placeholders y la navegación principal carguen.</t>
+  </si>
+  <si>
+    <t>Integración</t>
+  </si>
+  <si>
+    <t>Abrir Dashboard después del login.</t>
+  </si>
+  <si>
+    <t>Los placeholders graficos se muestran correctamente.</t>
+  </si>
+  <si>
+    <t>Movil debe estar conectado con el backend</t>
+  </si>
+  <si>
+    <t>Placeholders no visibles.</t>
+  </si>
+  <si>
+    <t>El sistema notifica al usuario al recibir la alerta.</t>
+  </si>
+  <si>
+    <t>Notificaciones Moviles</t>
+  </si>
+  <si>
+    <t>caundo se ejecuta las pruebas en la web por alguna atque deberia llegar la notificacion</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Datos de la alerta: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>tipo_ataque: 'DDoS'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Una notificación local aparece en el dispositivo con el título y aviso del ataque</t>
+  </si>
+  <si>
+    <t>Carga correcta de la lista de ataques.</t>
+  </si>
+  <si>
+    <t>1. Ingresar LogIn                                         2. Ingresar Dashboard                        3.Navegar a la pantalla de Historial</t>
+  </si>
+  <si>
+    <t>obtenemos desde backend GET /api/ataques/</t>
+  </si>
+  <si>
+    <t>Se muestra una lista de ataques (FlatList) con los campos: IP, Tipo y Fecha.</t>
+  </si>
+  <si>
+    <t>Historial de ataques Movil</t>
+  </si>
+  <si>
+    <t>Visualizacion de graficos de ataques Movil</t>
+  </si>
+  <si>
+    <t>Carga y renderizado de gráficos estadísticos.</t>
+  </si>
+  <si>
+    <t>obtenemos desde backend GET /api/dashboard/stats/</t>
+  </si>
+  <si>
+    <t>Se muestra el gráfico de barras con el conteo de ataques por tipo (ej. DDoS)</t>
+  </si>
+  <si>
+    <t>Descargar archivo CSV/PDF</t>
+  </si>
+  <si>
+    <t>1. Ingresar LogIn                                                 2. Ingresar Dashboard                        3.Navegar a la pantalla de Historial</t>
+  </si>
+  <si>
+    <t>1. Ingresar LogIn                                                 2. Ingresar Dashboard                        3.Navegar a la pantalla de Historial              4. Presionar boton "descargar"</t>
+  </si>
+  <si>
+    <t>Archivo de salida: reporte_&lt;fecha&gt;.json</t>
+  </si>
+  <si>
+    <t>Se realiza la petición HTTP al endpoint de exportación. El archivo se guarda localmente</t>
+  </si>
+  <si>
+    <t>Notificación no visible en el celular.</t>
+  </si>
+  <si>
+    <t>Exportacion y descarga de datos si está disponible descargar.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -558,6 +2779,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -770,7 +2996,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -788,7 +3014,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -800,13 +3026,13 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -7041,8 +9267,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}" name="TestPlan" displayName="TestPlan" ref="A2:M140" headerRowDxfId="59">
-  <autoFilter ref="A2:M140" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}" name="TestPlan" displayName="TestPlan" ref="A2:M141" headerRowDxfId="59">
+  <autoFilter ref="A2:M141" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{7F95280F-E669-4A5D-AEDF-FCAAAC81F275}" name="Modulo (Dropdown)" totalsRowLabel="Total" dataDxfId="58" totalsRowDxfId="57"/>
     <tableColumn id="2" xr3:uid="{E775B39B-DEB6-4123-A65F-A37EDA4383A3}" name="Test Case" dataDxfId="56" totalsRowDxfId="55"/>
@@ -7380,84 +9606,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ACCE336-D829-4280-938B-27FEC42D7852}">
   <dimension ref="A1:A33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="35.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="24.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="24.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="24.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" ht="24.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="24.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="24.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="24.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" ht="24.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="24.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:1" ht="24.75" customHeight="1">
+      <c r="A11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="24.75" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="24.75" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="24.75" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="24.75" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="24.75" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="24.75" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="24.75" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="24.75" customHeight="1">
+      <c r="A19" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="21" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="22" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="23" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="24" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="25" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="26" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="27" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="28" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="29" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="30" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="31" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="32" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="33" ht="24.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -7468,22 +9730,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D9AFB2-4BAC-4EFB-A2E7-92EA3A8E1FBC}">
-  <dimension ref="A2:M140"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:M141"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.140625" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="4" width="37.42578125" customWidth="1"/>
-    <col min="5" max="6" width="31.7109375" customWidth="1"/>
-    <col min="7" max="7" width="39.42578125" customWidth="1"/>
-    <col min="8" max="8" width="33.85546875" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="37.42578125" customWidth="1"/>
+    <col min="5" max="6" width="31.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="39.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.85546875" style="2" customWidth="1"/>
     <col min="9" max="9" width="31.42578125" customWidth="1"/>
     <col min="10" max="11" width="30.42578125" style="1" customWidth="1"/>
     <col min="12" max="12" width="16.42578125" customWidth="1"/>
     <col min="13" max="13" width="36.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" s="2" customFormat="1" ht="30">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -7524,7 +9787,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="41.25" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
@@ -7561,7 +9824,7 @@
       </c>
       <c r="M3" s="7"/>
     </row>
-    <row r="4" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="45">
       <c r="A4" s="7" t="s">
         <v>1</v>
       </c>
@@ -7598,7 +9861,7 @@
       </c>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="120">
       <c r="A5" s="7" t="s">
         <v>2</v>
       </c>
@@ -7635,7 +9898,7 @@
       </c>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="120">
       <c r="A6" s="7" t="s">
         <v>2</v>
       </c>
@@ -7672,7 +9935,7 @@
       </c>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="120">
       <c r="A7" s="7" t="s">
         <v>2</v>
       </c>
@@ -7709,7 +9972,7 @@
       </c>
       <c r="M7" s="7"/>
     </row>
-    <row r="8" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="120">
       <c r="A8" s="7" t="s">
         <v>2</v>
       </c>
@@ -7746,7 +10009,7 @@
       </c>
       <c r="M8" s="7"/>
     </row>
-    <row r="9" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="120">
       <c r="A9" s="7" t="s">
         <v>2</v>
       </c>
@@ -7783,7 +10046,7 @@
       </c>
       <c r="M9" s="7"/>
     </row>
-    <row r="10" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="120">
       <c r="A10" s="7" t="s">
         <v>2</v>
       </c>
@@ -7820,7 +10083,7 @@
       </c>
       <c r="M10" s="7"/>
     </row>
-    <row r="11" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="120">
       <c r="A11" s="7" t="s">
         <v>2</v>
       </c>
@@ -7857,7 +10120,7 @@
       </c>
       <c r="M11" s="7"/>
     </row>
-    <row r="12" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="120">
       <c r="A12" s="7" t="s">
         <v>2</v>
       </c>
@@ -7894,7 +10157,7 @@
       </c>
       <c r="M12" s="7"/>
     </row>
-    <row r="13" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="60">
       <c r="A13" s="7" t="s">
         <v>3</v>
       </c>
@@ -7931,7 +10194,7 @@
       </c>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="60">
       <c r="A14" s="7" t="s">
         <v>3</v>
       </c>
@@ -7968,7 +10231,7 @@
       </c>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="30">
       <c r="A15" s="7" t="s">
         <v>29</v>
       </c>
@@ -8007,7 +10270,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="30">
       <c r="A16" s="7" t="s">
         <v>29</v>
       </c>
@@ -8044,7 +10307,7 @@
       </c>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="45">
       <c r="A17" s="7" t="s">
         <v>30</v>
       </c>
@@ -8079,7 +10342,7 @@
       </c>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="45">
       <c r="A18" s="7" t="s">
         <v>30</v>
       </c>
@@ -8114,7 +10377,7 @@
       </c>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="135">
       <c r="A19" s="7" t="s">
         <v>32</v>
       </c>
@@ -8151,7 +10414,7 @@
       </c>
       <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="45">
       <c r="A20" s="7" t="s">
         <v>32</v>
       </c>
@@ -8188,7 +10451,7 @@
       </c>
       <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="60">
       <c r="A21" s="7" t="s">
         <v>33</v>
       </c>
@@ -8225,7 +10488,7 @@
       </c>
       <c r="M21" s="7"/>
     </row>
-    <row r="22" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="75">
       <c r="A22" s="7" t="s">
         <v>5</v>
       </c>
@@ -8262,7 +10525,7 @@
       </c>
       <c r="M22" s="7"/>
     </row>
-    <row r="23" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="195">
       <c r="A23" s="7" t="s">
         <v>5</v>
       </c>
@@ -8299,7 +10562,7 @@
       </c>
       <c r="M23" s="7"/>
     </row>
-    <row r="24" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="135">
       <c r="A24" s="7" t="s">
         <v>30</v>
       </c>
@@ -8340,1749 +10603,4332 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="7"/>
+    <row r="25" spans="1:13" ht="45">
+      <c r="A25" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="60">
+      <c r="A26" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="60">
+      <c r="A27" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="45">
+      <c r="A28" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="45">
+      <c r="A29" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="60">
+      <c r="A30" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="45">
+      <c r="A31" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="45">
+      <c r="A32" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="45">
+      <c r="A33" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="30">
+      <c r="A34" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="60">
+      <c r="A35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M35" s="7"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="7"/>
+    <row r="36" spans="1:13" ht="60">
+      <c r="A36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M36" s="7"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="7"/>
+    <row r="37" spans="1:13" ht="60">
+      <c r="A37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M37" s="7"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="7"/>
+    <row r="38" spans="1:13" ht="60">
+      <c r="A38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M38" s="7"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="7"/>
+    <row r="39" spans="1:13" ht="60">
+      <c r="A39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M39" s="7"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="7"/>
+    <row r="40" spans="1:13" ht="60">
+      <c r="A40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M40" s="7"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="7"/>
+    <row r="41" spans="1:13" ht="75">
+      <c r="A41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M41" s="7"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="7"/>
+    <row r="42" spans="1:13" ht="60">
+      <c r="A42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M42" s="7"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="7"/>
+    <row r="43" spans="1:13" ht="60">
+      <c r="A43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M43" s="7"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="7"/>
+    <row r="44" spans="1:13" ht="60">
+      <c r="A44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M44" s="7"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="7"/>
+    <row r="45" spans="1:13" ht="75">
+      <c r="A45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M45" s="7"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="7"/>
+    <row r="46" spans="1:13" ht="60">
+      <c r="A46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M46" s="7"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="7"/>
+    <row r="47" spans="1:13" ht="75">
+      <c r="A47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M47" s="7"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="7"/>
+    <row r="48" spans="1:13" ht="60">
+      <c r="A48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M48" s="7"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="7"/>
+    <row r="49" spans="1:13" ht="60">
+      <c r="A49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M49" s="7"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="7"/>
+    <row r="50" spans="1:13" ht="60">
+      <c r="A50" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M50" s="7"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="7"/>
+    <row r="51" spans="1:13" ht="60">
+      <c r="A51" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M51" s="7"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="7"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="7"/>
+    <row r="52" spans="1:13" ht="60">
+      <c r="A52" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M52" s="7"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" s="7"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="7"/>
+    <row r="53" spans="1:13" ht="60">
+      <c r="A53" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M53" s="7"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="7"/>
+    <row r="54" spans="1:13" ht="75">
+      <c r="A54" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M54" s="7"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55" s="7"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="7"/>
+    <row r="55" spans="1:13" ht="60">
+      <c r="A55" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="7"/>
+    <row r="56" spans="1:13" ht="60">
+      <c r="A56" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M56" s="7"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A57" s="7"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="7"/>
+    <row r="57" spans="1:13" ht="75">
+      <c r="A57" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M57" s="7"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58" s="7"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="7"/>
+    <row r="58" spans="1:13" ht="60">
+      <c r="A58" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M58" s="7"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A59" s="7"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="7"/>
+    <row r="59" spans="1:13" ht="60">
+      <c r="A59" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M59" s="7"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60" s="7"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="7"/>
+    <row r="60" spans="1:13" ht="75">
+      <c r="A60" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M60" s="7"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="7"/>
+    <row r="61" spans="1:13" ht="75">
+      <c r="A61" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M61" s="7"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A62" s="7"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="7"/>
+    <row r="62" spans="1:13" ht="75">
+      <c r="A62" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M62" s="7"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A63" s="7"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="7"/>
+    <row r="63" spans="1:13" ht="60">
+      <c r="A63" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M63" s="7"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A64" s="7"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="7"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="7"/>
+    <row r="64" spans="1:13" ht="75">
+      <c r="A64" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M64" s="7"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="7"/>
-      <c r="H65" s="7"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="7"/>
+    <row r="65" spans="1:13" ht="75">
+      <c r="A65" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M65" s="7"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
-      <c r="I66" s="7"/>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="7"/>
+    <row r="66" spans="1:13" ht="90">
+      <c r="A66" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M66" s="7"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="7"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="7"/>
+    <row r="67" spans="1:13" ht="75">
+      <c r="A67" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M67" s="7"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="7"/>
+    <row r="68" spans="1:13" ht="75">
+      <c r="A68" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M68" s="7"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="7"/>
+    <row r="69" spans="1:13" ht="75">
+      <c r="A69" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M69" s="7"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A70" s="7"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="7"/>
+    <row r="70" spans="1:13" ht="90">
+      <c r="A70" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M70" s="7"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A71" s="7"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7"/>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
-      <c r="L71" s="7"/>
+    <row r="71" spans="1:13" ht="75">
+      <c r="A71" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M71" s="7"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
-      <c r="L72" s="7"/>
+    <row r="72" spans="1:13" ht="75">
+      <c r="A72" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M72" s="7"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73" s="7"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="7"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="7"/>
+    <row r="73" spans="1:13" ht="90">
+      <c r="A73" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M73" s="7"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="7"/>
+    <row r="74" spans="1:13" ht="75">
+      <c r="A74" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M74" s="7"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="7"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
-      <c r="L75" s="7"/>
+    <row r="75" spans="1:13" ht="90">
+      <c r="A75" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M75" s="7"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" s="7"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
-      <c r="L76" s="7"/>
+    <row r="76" spans="1:13" ht="75">
+      <c r="A76" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M76" s="7"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7"/>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
-      <c r="L77" s="7"/>
+    <row r="77" spans="1:13" ht="90">
+      <c r="A77" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M77" s="7"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" s="7"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
-      <c r="I78" s="7"/>
-      <c r="J78" s="3"/>
-      <c r="K78" s="3"/>
-      <c r="L78" s="7"/>
+    <row r="78" spans="1:13" ht="75">
+      <c r="A78" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M78" s="7"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="7"/>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
-      <c r="I79" s="7"/>
-      <c r="J79" s="3"/>
-      <c r="K79" s="3"/>
-      <c r="L79" s="7"/>
+    <row r="79" spans="1:13" ht="90">
+      <c r="A79" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M79" s="7"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="7"/>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7"/>
-      <c r="J80" s="3"/>
-      <c r="K80" s="3"/>
-      <c r="L80" s="7"/>
+    <row r="80" spans="1:13" ht="75">
+      <c r="A80" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M80" s="7"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="7"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-      <c r="I81" s="7"/>
-      <c r="J81" s="3"/>
-      <c r="K81" s="3"/>
-      <c r="L81" s="7"/>
+    <row r="81" spans="1:13" ht="75">
+      <c r="A81" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M81" s="7"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="7"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="7"/>
-      <c r="H82" s="7"/>
-      <c r="I82" s="7"/>
-      <c r="J82" s="3"/>
-      <c r="K82" s="3"/>
-      <c r="L82" s="7"/>
+    <row r="82" spans="1:13" ht="75">
+      <c r="A82" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M82" s="7"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="7"/>
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
-      <c r="I83" s="7"/>
-      <c r="J83" s="3"/>
-      <c r="K83" s="3"/>
-      <c r="L83" s="7"/>
+    <row r="83" spans="1:13" ht="75">
+      <c r="A83" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M83" s="7"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="7"/>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
-      <c r="I84" s="7"/>
-      <c r="J84" s="3"/>
-      <c r="K84" s="3"/>
-      <c r="L84" s="7"/>
+    <row r="84" spans="1:13" ht="75">
+      <c r="A84" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M84" s="7"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="7"/>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
-      <c r="I85" s="7"/>
-      <c r="J85" s="3"/>
-      <c r="K85" s="3"/>
-      <c r="L85" s="7"/>
+    <row r="85" spans="1:13" ht="75">
+      <c r="A85" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M85" s="7"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="7"/>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
-      <c r="G86" s="7"/>
-      <c r="H86" s="7"/>
-      <c r="I86" s="7"/>
-      <c r="J86" s="3"/>
-      <c r="K86" s="3"/>
-      <c r="L86" s="7"/>
+    <row r="86" spans="1:13" ht="75">
+      <c r="A86" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M86" s="7"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="7"/>
-      <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
-      <c r="I87" s="7"/>
-      <c r="J87" s="3"/>
-      <c r="K87" s="3"/>
-      <c r="L87" s="7"/>
+    <row r="87" spans="1:13" ht="75">
+      <c r="A87" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M87" s="7"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="7"/>
-      <c r="B88" s="7"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
-      <c r="G88" s="7"/>
-      <c r="H88" s="7"/>
-      <c r="I88" s="7"/>
-      <c r="J88" s="3"/>
-      <c r="K88" s="3"/>
-      <c r="L88" s="7"/>
+    <row r="88" spans="1:13" ht="75">
+      <c r="A88" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M88" s="7"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="7"/>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="7"/>
-      <c r="H89" s="7"/>
-      <c r="I89" s="7"/>
-      <c r="J89" s="3"/>
-      <c r="K89" s="3"/>
-      <c r="L89" s="7"/>
+    <row r="89" spans="1:13" ht="75">
+      <c r="A89" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M89" s="7"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="7"/>
-      <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
-      <c r="G90" s="7"/>
-      <c r="H90" s="7"/>
-      <c r="I90" s="7"/>
-      <c r="J90" s="3"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="7"/>
+    <row r="90" spans="1:13" ht="75">
+      <c r="A90" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M90" s="7"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A91" s="7"/>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7"/>
-      <c r="I91" s="7"/>
-      <c r="J91" s="3"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="7"/>
+    <row r="91" spans="1:13" ht="90">
+      <c r="A91" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M91" s="7"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" s="7"/>
-      <c r="B92" s="7"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-      <c r="G92" s="7"/>
-      <c r="H92" s="7"/>
-      <c r="I92" s="7"/>
-      <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
-      <c r="L92" s="7"/>
+    <row r="92" spans="1:13" ht="75">
+      <c r="A92" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M92" s="7"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A93" s="7"/>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
-      <c r="I93" s="7"/>
-      <c r="J93" s="3"/>
-      <c r="K93" s="3"/>
-      <c r="L93" s="7"/>
+    <row r="93" spans="1:13" ht="75">
+      <c r="A93" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M93" s="7"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A94" s="7"/>
-      <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="7"/>
-      <c r="H94" s="7"/>
-      <c r="I94" s="7"/>
-      <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
-      <c r="L94" s="7"/>
+    <row r="94" spans="1:13" ht="75">
+      <c r="A94" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M94" s="7"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A95" s="7"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
-      <c r="I95" s="7"/>
-      <c r="J95" s="3"/>
-      <c r="K95" s="3"/>
-      <c r="L95" s="7"/>
+    <row r="95" spans="1:13" ht="75">
+      <c r="A95" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M95" s="7"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="7"/>
-      <c r="B96" s="7"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
-      <c r="G96" s="7"/>
-      <c r="H96" s="7"/>
-      <c r="I96" s="7"/>
-      <c r="J96" s="3"/>
-      <c r="K96" s="3"/>
-      <c r="L96" s="7"/>
+    <row r="96" spans="1:13" ht="90">
+      <c r="A96" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M96" s="7"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A97" s="7"/>
-      <c r="B97" s="7"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="7"/>
-      <c r="H97" s="7"/>
-      <c r="I97" s="7"/>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="7"/>
+    <row r="97" spans="1:13" ht="75">
+      <c r="A97" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M97" s="7"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="7"/>
-      <c r="B98" s="7"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="7"/>
-      <c r="H98" s="7"/>
-      <c r="I98" s="7"/>
-      <c r="J98" s="3"/>
-      <c r="K98" s="3"/>
-      <c r="L98" s="7"/>
+    <row r="98" spans="1:13" ht="75">
+      <c r="A98" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M98" s="7"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="7"/>
-      <c r="B99" s="7"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="7"/>
-      <c r="H99" s="7"/>
-      <c r="I99" s="7"/>
-      <c r="J99" s="3"/>
-      <c r="K99" s="3"/>
-      <c r="L99" s="7"/>
+    <row r="99" spans="1:13" ht="75">
+      <c r="A99" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M99" s="7"/>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="7"/>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="7"/>
-      <c r="H100" s="7"/>
-      <c r="I100" s="7"/>
-      <c r="J100" s="3"/>
-      <c r="K100" s="3"/>
-      <c r="L100" s="7"/>
+    <row r="100" spans="1:13" ht="75">
+      <c r="A100" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M100" s="7"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="7"/>
-      <c r="B101" s="7"/>
-      <c r="C101" s="7"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="7"/>
-      <c r="H101" s="7"/>
-      <c r="I101" s="7"/>
-      <c r="J101" s="3"/>
-      <c r="K101" s="3"/>
-      <c r="L101" s="7"/>
+    <row r="101" spans="1:13" ht="75">
+      <c r="A101" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M101" s="7"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="7"/>
-      <c r="B102" s="7"/>
-      <c r="C102" s="7"/>
-      <c r="D102" s="7"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="7"/>
-      <c r="G102" s="7"/>
-      <c r="H102" s="7"/>
-      <c r="I102" s="7"/>
-      <c r="J102" s="3"/>
-      <c r="K102" s="3"/>
-      <c r="L102" s="7"/>
+    <row r="102" spans="1:13" ht="75">
+      <c r="A102" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M102" s="7"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="7"/>
-      <c r="B103" s="7"/>
-      <c r="C103" s="7"/>
-      <c r="D103" s="7"/>
-      <c r="E103" s="7"/>
-      <c r="F103" s="7"/>
-      <c r="G103" s="7"/>
-      <c r="H103" s="7"/>
-      <c r="I103" s="7"/>
-      <c r="J103" s="3"/>
-      <c r="K103" s="3"/>
-      <c r="L103" s="7"/>
+    <row r="103" spans="1:13" ht="75">
+      <c r="A103" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M103" s="7"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A104" s="7"/>
-      <c r="B104" s="7"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
-      <c r="F104" s="7"/>
-      <c r="G104" s="7"/>
-      <c r="H104" s="7"/>
-      <c r="I104" s="7"/>
-      <c r="J104" s="3"/>
-      <c r="K104" s="3"/>
-      <c r="L104" s="7"/>
+    <row r="104" spans="1:13" ht="75">
+      <c r="A104" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M104" s="7"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A105" s="7"/>
-      <c r="B105" s="7"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
-      <c r="G105" s="7"/>
-      <c r="H105" s="7"/>
-      <c r="I105" s="7"/>
-      <c r="J105" s="3"/>
-      <c r="K105" s="3"/>
-      <c r="L105" s="7"/>
+    <row r="105" spans="1:13" ht="75">
+      <c r="A105" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M105" s="7"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A106" s="7"/>
-      <c r="B106" s="7"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="7"/>
-      <c r="G106" s="7"/>
-      <c r="H106" s="7"/>
-      <c r="I106" s="7"/>
-      <c r="J106" s="3"/>
-      <c r="K106" s="3"/>
-      <c r="L106" s="7"/>
+    <row r="106" spans="1:13" ht="75">
+      <c r="A106" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M106" s="7"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="7"/>
-      <c r="B107" s="7"/>
-      <c r="C107" s="7"/>
-      <c r="D107" s="7"/>
-      <c r="E107" s="7"/>
-      <c r="F107" s="7"/>
-      <c r="G107" s="7"/>
-      <c r="H107" s="7"/>
-      <c r="I107" s="7"/>
-      <c r="J107" s="3"/>
-      <c r="K107" s="3"/>
-      <c r="L107" s="7"/>
+    <row r="107" spans="1:13" ht="75">
+      <c r="A107" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M107" s="7"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A108" s="7"/>
-      <c r="B108" s="7"/>
-      <c r="C108" s="7"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7"/>
-      <c r="G108" s="7"/>
-      <c r="H108" s="7"/>
-      <c r="I108" s="7"/>
-      <c r="J108" s="3"/>
-      <c r="K108" s="3"/>
-      <c r="L108" s="7"/>
+    <row r="108" spans="1:13" ht="75">
+      <c r="A108" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M108" s="7"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A109" s="7"/>
-      <c r="B109" s="7"/>
-      <c r="C109" s="7"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7"/>
-      <c r="G109" s="7"/>
-      <c r="H109" s="7"/>
-      <c r="I109" s="7"/>
-      <c r="J109" s="3"/>
-      <c r="K109" s="3"/>
-      <c r="L109" s="7"/>
+    <row r="109" spans="1:13" ht="90">
+      <c r="A109" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M109" s="7"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A110" s="7"/>
-      <c r="B110" s="7"/>
-      <c r="C110" s="7"/>
-      <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7"/>
-      <c r="G110" s="7"/>
-      <c r="H110" s="7"/>
-      <c r="I110" s="7"/>
-      <c r="J110" s="3"/>
-      <c r="K110" s="3"/>
-      <c r="L110" s="7"/>
+    <row r="110" spans="1:13" ht="75">
+      <c r="A110" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M110" s="7"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A111" s="7"/>
-      <c r="B111" s="7"/>
-      <c r="C111" s="7"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="7"/>
-      <c r="F111" s="7"/>
-      <c r="G111" s="7"/>
-      <c r="H111" s="7"/>
-      <c r="I111" s="7"/>
-      <c r="J111" s="3"/>
-      <c r="K111" s="3"/>
-      <c r="L111" s="7"/>
+    <row r="111" spans="1:13" ht="90">
+      <c r="A111" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M111" s="7"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A112" s="7"/>
-      <c r="B112" s="7"/>
-      <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="7"/>
-      <c r="G112" s="7"/>
-      <c r="H112" s="7"/>
-      <c r="I112" s="7"/>
-      <c r="J112" s="3"/>
-      <c r="K112" s="3"/>
-      <c r="L112" s="7"/>
+    <row r="112" spans="1:13" ht="75">
+      <c r="A112" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M112" s="7"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="7"/>
-      <c r="B113" s="7"/>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
-      <c r="G113" s="7"/>
-      <c r="H113" s="7"/>
-      <c r="I113" s="7"/>
-      <c r="J113" s="3"/>
-      <c r="K113" s="3"/>
-      <c r="L113" s="7"/>
+    <row r="113" spans="1:13" ht="75">
+      <c r="A113" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M113" s="7"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" s="7"/>
-      <c r="B114" s="7"/>
-      <c r="C114" s="7"/>
-      <c r="D114" s="7"/>
-      <c r="E114" s="7"/>
-      <c r="F114" s="7"/>
-      <c r="G114" s="7"/>
-      <c r="H114" s="7"/>
-      <c r="I114" s="7"/>
-      <c r="J114" s="3"/>
-      <c r="K114" s="3"/>
-      <c r="L114" s="7"/>
+    <row r="114" spans="1:13" ht="75">
+      <c r="A114" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M114" s="7"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="7"/>
-      <c r="B115" s="7"/>
-      <c r="C115" s="7"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
-      <c r="G115" s="7"/>
-      <c r="H115" s="7"/>
-      <c r="I115" s="7"/>
-      <c r="J115" s="3"/>
-      <c r="K115" s="3"/>
-      <c r="L115" s="7"/>
+    <row r="115" spans="1:13" ht="90">
+      <c r="A115" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M115" s="7"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="7"/>
-      <c r="B116" s="7"/>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="7"/>
-      <c r="H116" s="7"/>
-      <c r="I116" s="7"/>
-      <c r="J116" s="3"/>
-      <c r="K116" s="3"/>
-      <c r="L116" s="7"/>
+    <row r="116" spans="1:13" ht="90">
+      <c r="A116" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M116" s="7"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="7"/>
-      <c r="B117" s="7"/>
-      <c r="C117" s="7"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-      <c r="G117" s="7"/>
-      <c r="H117" s="7"/>
-      <c r="I117" s="7"/>
-      <c r="J117" s="3"/>
-      <c r="K117" s="3"/>
-      <c r="L117" s="7"/>
+    <row r="117" spans="1:13" ht="90">
+      <c r="A117" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M117" s="7"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="7"/>
-      <c r="B118" s="7"/>
-      <c r="C118" s="7"/>
-      <c r="D118" s="7"/>
-      <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
-      <c r="G118" s="7"/>
-      <c r="H118" s="7"/>
-      <c r="I118" s="7"/>
-      <c r="J118" s="3"/>
-      <c r="K118" s="3"/>
-      <c r="L118" s="7"/>
+    <row r="118" spans="1:13" ht="75">
+      <c r="A118" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M118" s="7"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="7"/>
-      <c r="B119" s="7"/>
-      <c r="C119" s="7"/>
-      <c r="D119" s="7"/>
-      <c r="E119" s="7"/>
-      <c r="F119" s="7"/>
-      <c r="G119" s="7"/>
-      <c r="H119" s="7"/>
-      <c r="I119" s="7"/>
-      <c r="J119" s="3"/>
-      <c r="K119" s="3"/>
-      <c r="L119" s="7"/>
+    <row r="119" spans="1:13" ht="75">
+      <c r="A119" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M119" s="7"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="7"/>
-      <c r="B120" s="7"/>
-      <c r="C120" s="7"/>
-      <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
-      <c r="G120" s="7"/>
-      <c r="H120" s="7"/>
-      <c r="I120" s="7"/>
-      <c r="J120" s="3"/>
-      <c r="K120" s="3"/>
-      <c r="L120" s="7"/>
+    <row r="120" spans="1:13" ht="75">
+      <c r="A120" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M120" s="7"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="7"/>
-      <c r="B121" s="7"/>
-      <c r="C121" s="7"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="7"/>
-      <c r="G121" s="7"/>
-      <c r="H121" s="7"/>
-      <c r="I121" s="7"/>
-      <c r="J121" s="3"/>
-      <c r="K121" s="3"/>
-      <c r="L121" s="7"/>
+    <row r="121" spans="1:13" ht="75">
+      <c r="A121" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M121" s="7"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="7"/>
-      <c r="B122" s="7"/>
-      <c r="C122" s="7"/>
-      <c r="D122" s="7"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
-      <c r="G122" s="7"/>
-      <c r="H122" s="7"/>
-      <c r="I122" s="7"/>
-      <c r="J122" s="3"/>
-      <c r="K122" s="3"/>
-      <c r="L122" s="7"/>
+    <row r="122" spans="1:13" ht="75">
+      <c r="A122" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M122" s="7"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="7"/>
-      <c r="B123" s="7"/>
-      <c r="C123" s="7"/>
-      <c r="D123" s="7"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="7"/>
-      <c r="G123" s="7"/>
-      <c r="H123" s="7"/>
-      <c r="I123" s="7"/>
-      <c r="J123" s="3"/>
-      <c r="K123" s="3"/>
-      <c r="L123" s="7"/>
+    <row r="123" spans="1:13" ht="75">
+      <c r="A123" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M123" s="7"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="7"/>
-      <c r="B124" s="7"/>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
-      <c r="G124" s="7"/>
-      <c r="H124" s="7"/>
-      <c r="I124" s="7"/>
-      <c r="J124" s="3"/>
-      <c r="K124" s="3"/>
-      <c r="L124" s="7"/>
+    <row r="124" spans="1:13" ht="75">
+      <c r="A124" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L124" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M124" s="7"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="7"/>
-      <c r="B125" s="7"/>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="7"/>
-      <c r="H125" s="7"/>
-      <c r="I125" s="7"/>
-      <c r="J125" s="3"/>
-      <c r="K125" s="3"/>
-      <c r="L125" s="7"/>
+    <row r="125" spans="1:13" ht="75">
+      <c r="A125" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="I125" s="1"/>
+      <c r="J125" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L125" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M125" s="7"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A126" s="7"/>
-      <c r="B126" s="7"/>
-      <c r="C126" s="7"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
-      <c r="F126" s="7"/>
-      <c r="G126" s="7"/>
-      <c r="H126" s="7"/>
-      <c r="I126" s="7"/>
-      <c r="J126" s="3"/>
-      <c r="K126" s="3"/>
-      <c r="L126" s="7"/>
+    <row r="126" spans="1:13" ht="75">
+      <c r="A126" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M126" s="7"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="7"/>
-      <c r="B127" s="7"/>
-      <c r="C127" s="7"/>
-      <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="7"/>
-      <c r="G127" s="7"/>
-      <c r="H127" s="7"/>
-      <c r="I127" s="7"/>
-      <c r="J127" s="3"/>
-      <c r="K127" s="3"/>
-      <c r="L127" s="7"/>
+    <row r="127" spans="1:13" ht="75">
+      <c r="A127" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M127" s="7"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="7"/>
-      <c r="B128" s="7"/>
-      <c r="C128" s="7"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="7"/>
-      <c r="F128" s="7"/>
-      <c r="G128" s="7"/>
-      <c r="H128" s="7"/>
-      <c r="I128" s="7"/>
-      <c r="J128" s="3"/>
-      <c r="K128" s="3"/>
-      <c r="L128" s="7"/>
+    <row r="128" spans="1:13" ht="75">
+      <c r="A128" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="M128" s="7"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A129" s="7"/>
-      <c r="B129" s="7"/>
-      <c r="C129" s="7"/>
-      <c r="D129" s="7"/>
-      <c r="E129" s="7"/>
-      <c r="F129" s="7"/>
-      <c r="G129" s="7"/>
-      <c r="H129" s="7"/>
-      <c r="I129" s="7"/>
-      <c r="J129" s="3"/>
-      <c r="K129" s="3"/>
-      <c r="L129" s="7"/>
+    <row r="129" spans="1:13" ht="75">
+      <c r="A129" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L129" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M129" s="7"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A130" s="7"/>
-      <c r="B130" s="7"/>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="7"/>
-      <c r="H130" s="7"/>
-      <c r="I130" s="7"/>
-      <c r="J130" s="3"/>
-      <c r="K130" s="3"/>
-      <c r="L130" s="7"/>
+    <row r="130" spans="1:13" ht="90">
+      <c r="A130" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L130" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M130" s="7"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A131" s="7"/>
-      <c r="B131" s="7"/>
-      <c r="C131" s="7"/>
-      <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="7"/>
-      <c r="G131" s="7"/>
-      <c r="H131" s="7"/>
-      <c r="I131" s="7"/>
-      <c r="J131" s="3"/>
-      <c r="K131" s="3"/>
-      <c r="L131" s="7"/>
+    <row r="131" spans="1:13" ht="75">
+      <c r="A131" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L131" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M131" s="7"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A132" s="7"/>
-      <c r="B132" s="7"/>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7"/>
-      <c r="E132" s="7"/>
-      <c r="F132" s="7"/>
-      <c r="G132" s="7"/>
-      <c r="H132" s="7"/>
-      <c r="I132" s="7"/>
-      <c r="J132" s="3"/>
-      <c r="K132" s="3"/>
-      <c r="L132" s="7"/>
+    <row r="132" spans="1:13" ht="75">
+      <c r="A132" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L132" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M132" s="7"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A133" s="7"/>
-      <c r="B133" s="7"/>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="7"/>
-      <c r="G133" s="7"/>
-      <c r="H133" s="7"/>
-      <c r="I133" s="7"/>
-      <c r="J133" s="3"/>
-      <c r="K133" s="3"/>
-      <c r="L133" s="7"/>
+    <row r="133" spans="1:13" ht="75">
+      <c r="A133" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F133" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L133" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M133" s="7"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="7"/>
-      <c r="B134" s="7"/>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="7"/>
-      <c r="G134" s="7"/>
-      <c r="H134" s="7"/>
-      <c r="I134" s="7"/>
-      <c r="J134" s="3"/>
-      <c r="K134" s="3"/>
-      <c r="L134" s="7"/>
+    <row r="134" spans="1:13" ht="75">
+      <c r="A134" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M134" s="7"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A135" s="7"/>
-      <c r="B135" s="7"/>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="7"/>
-      <c r="G135" s="7"/>
-      <c r="H135" s="7"/>
+    <row r="135" spans="1:13" ht="61.5" customHeight="1">
+      <c r="A135" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>722</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="F135" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="G135" s="7" t="s">
+        <v>719</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>720</v>
+      </c>
       <c r="I135" s="7"/>
-      <c r="J135" s="3"/>
-      <c r="K135" s="3"/>
-      <c r="L135" s="7"/>
+      <c r="J135" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K135" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="L135" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="M135" s="7"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A136" s="7"/>
-      <c r="B136" s="7"/>
-      <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="7"/>
-      <c r="G136" s="7"/>
-      <c r="H136" s="7"/>
-      <c r="I136" s="7"/>
-      <c r="J136" s="3"/>
-      <c r="K136" s="3"/>
-      <c r="L136" s="7"/>
+    <row r="136" spans="1:13" ht="45" customHeight="1">
+      <c r="A136" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>723</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="G136" s="7" t="s">
+        <v>725</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="I136" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="J136" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K136" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="L136" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="M136" s="7"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A137" s="7"/>
-      <c r="B137" s="7"/>
-      <c r="C137" s="7"/>
-      <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="7"/>
+    <row r="137" spans="1:13" ht="30">
+      <c r="A137" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>733</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>731</v>
+      </c>
       <c r="G137" s="7"/>
-      <c r="H137" s="7"/>
-      <c r="I137" s="7"/>
-      <c r="J137" s="3"/>
-      <c r="K137" s="3"/>
-      <c r="L137" s="7"/>
+      <c r="H137" s="7" t="s">
+        <v>732</v>
+      </c>
+      <c r="I137" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="J137" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K137" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="L137" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="M137" s="7"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A138" s="7"/>
-      <c r="B138" s="7"/>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
-      <c r="E138" s="7"/>
-      <c r="F138" s="7"/>
-      <c r="G138" s="7"/>
-      <c r="H138" s="7"/>
-      <c r="I138" s="7"/>
-      <c r="J138" s="3"/>
-      <c r="K138" s="3"/>
-      <c r="L138" s="7"/>
+    <row r="138" spans="1:13" ht="45">
+      <c r="A138" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>733</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="I138" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="J138" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K138" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="L138" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="M138" s="7"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A139" s="7"/>
-      <c r="B139" s="7"/>
-      <c r="C139" s="7"/>
-      <c r="D139" s="7"/>
-      <c r="E139" s="7"/>
-      <c r="F139" s="7"/>
-      <c r="G139" s="7"/>
-      <c r="H139" s="7"/>
+    <row r="139" spans="1:13" ht="60">
+      <c r="A139" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>744</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>740</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>733</v>
+      </c>
+      <c r="F139" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="G139" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="H139" s="7" t="s">
+        <v>743</v>
+      </c>
       <c r="I139" s="7"/>
-      <c r="J139" s="3"/>
-      <c r="K139" s="3"/>
-      <c r="L139" s="7"/>
+      <c r="J139" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K139" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="L139" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="M139" s="7"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A140" s="7"/>
-      <c r="B140" s="7"/>
-      <c r="C140" s="7"/>
-      <c r="D140" s="7"/>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
-      <c r="G140" s="7"/>
-      <c r="H140" s="7"/>
+    <row r="140" spans="1:13" ht="60">
+      <c r="A140" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>733</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="H140" s="7" t="s">
+        <v>748</v>
+      </c>
       <c r="I140" s="7"/>
-      <c r="J140" s="3"/>
-      <c r="K140" s="3"/>
-      <c r="L140" s="7"/>
+      <c r="J140" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K140" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="L140" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="M140" s="7"/>
+    </row>
+    <row r="141" spans="1:13" ht="75">
+      <c r="A141" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>755</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>733</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>751</v>
+      </c>
+      <c r="G141" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="H141" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="I141" s="7"/>
+      <c r="J141" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K141" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="L141" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M141" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="L3:L140">
+  <conditionalFormatting sqref="L3:L134 L135:M135 L136:L140">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"PENDING"</formula>
     </cfRule>
@@ -10094,11 +14940,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L140" xr:uid="{1E8D2D6D-4EE7-40E2-A622-3458BDCF08AD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A141" xr:uid="{F4675041-A1B8-4B65-822E-23AD6AB864A0}">
+      <formula1>INDIRECT("Modulos[MODULOS]")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M135 L3:L141" xr:uid="{1E8D2D6D-4EE7-40E2-A622-3458BDCF08AD}">
       <formula1>"PASS,PENDING,FAIL"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A140" xr:uid="{F4675041-A1B8-4B65-822E-23AD6AB864A0}">
-      <formula1>INDIRECT("Modulos[MODULOS]")</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -10114,7 +14960,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58476477-5BDE-4E9D-BCDF-FD6E3C12EE95}">
   <dimension ref="A2:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -10132,7 +14978,7 @@
     <col min="16" max="16" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="23.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -10143,7 +14989,7 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
@@ -10160,7 +15006,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -10173,7 +15019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -10186,7 +15032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="21.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -10199,7 +15045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -10212,7 +15058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
@@ -10229,7 +15075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="30">
       <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
@@ -10237,7 +15083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -10245,7 +15091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
         <v>22</v>
       </c>
@@ -10253,7 +15099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
         <v>23</v>
       </c>
@@ -10261,7 +15107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -10278,7 +15124,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B55000D3-4297-437F-A419-CEB79EC3F6C0}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -10286,21 +15132,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E158E2AB9B4F924688B558FA982B40CF" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ce5f689dcf51305603cb0d070870d6dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="def3e2b2-904e-4359-b966-59b7b32cd06e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="252587ffdfea7067e66d630466c44dd6" ns2:_="">
     <xsd:import namespace="def3e2b2-904e-4359-b966-59b7b32cd06e"/>
@@ -10438,15 +15275,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CABA5C2-04D8-4DC5-BBFB-FF9AC004B268}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -10455,7 +15293,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1F0EA96-F162-49AF-B0BE-A54883795866}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10471,4 +15309,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Modelo Test Plan.xlsx
+++ b/Modelo Test Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eva Laura\Documents\PROYECTO DE SISTEMAS III\proyecto\CoderBits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F832D88E-EF25-4644-8279-884CE5A49B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7253DF-0869-4CCD-AC3D-F2E9531BABE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{96765352-7388-4C61-94B8-5077301D3254}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="873">
   <si>
     <t>MODULOS</t>
   </si>
@@ -2752,6 +2752,357 @@
   </si>
   <si>
     <t>Exportacion y descarga de datos si está disponible descargar.</t>
+  </si>
+  <si>
+    <t>https://github.com/alejav0240/CoderBits/issues/41</t>
+  </si>
+  <si>
+    <t>https://github.com/alejav0240/CoderBits/issues/42</t>
+  </si>
+  <si>
+    <t>Visualización de módulos</t>
+  </si>
+  <si>
+    <t>Validar que el panel principal muestre todos los módulos correctamente.</t>
+  </si>
+  <si>
+    <t>1. Acceder al panel principal.2. Verificar que los módulos estén visibles.</t>
+  </si>
+  <si>
+    <t>Acceso con usuario válido.</t>
+  </si>
+  <si>
+    <t>El sistema muestra todos los módulos disponibles.</t>
+  </si>
+  <si>
+    <t>FABRIZIO PAVEL ROLLANO LUNA</t>
+  </si>
+  <si>
+    <t>Navegación entre módulos</t>
+  </si>
+  <si>
+    <t>Validar la correcta navegación entre diferentes módulos del sistema.</t>
+  </si>
+  <si>
+    <t>1. Seleccionar módulo del menú lateral.2. Verificar cambio de vista.</t>
+  </si>
+  <si>
+    <t>Usuario autenticado.</t>
+  </si>
+  <si>
+    <t>El sistema navega correctamente entre módulos.</t>
+  </si>
+  <si>
+    <t>Adaptación responsive</t>
+  </si>
+  <si>
+    <t>Verificar que la interfaz del panel se adapte correctamente a distintas resoluciones de pantalla.</t>
+  </si>
+  <si>
+    <t>1. Acceder al dashboard desde distintos dispositivos.2. Verificar que la interfaz se adapte correctamente.</t>
+  </si>
+  <si>
+    <t>Dispositivos con diferentes resoluciones.</t>
+  </si>
+  <si>
+    <t>La interfaz se adapta correctamente sin pérdida de información.</t>
+  </si>
+  <si>
+    <t>Conexiones</t>
+  </si>
+  <si>
+    <t>Registro de conexiones</t>
+  </si>
+  <si>
+    <t>Validar que las conexiones se registren correctamente y se muestren en la lista.</t>
+  </si>
+  <si>
+    <t>1. Acceder a “Dashboard &gt; Conexions”.2. Registrar una nueva conexión.3. Verificar su aparición en la lista.</t>
+  </si>
+  <si>
+    <t>Datos simulados de conexión.</t>
+  </si>
+  <si>
+    <t>La conexión se guarda correctamente y aparece listada.</t>
+  </si>
+  <si>
+    <t>Búsqueda de conexiones</t>
+  </si>
+  <si>
+    <t>Verificar que la función de búsqueda devuelva resultados coincidentes.</t>
+  </si>
+  <si>
+    <t>Deben existir registros previos.</t>
+  </si>
+  <si>
+    <t>1. Ingresar término en el buscador.2. Ejecutar búsqueda.</t>
+  </si>
+  <si>
+    <t>Texto parcial o completo de la conexión.</t>
+  </si>
+  <si>
+    <t>El sistema muestra solo las coincidencias.</t>
+  </si>
+  <si>
+    <t>Filtro por fecha</t>
+  </si>
+  <si>
+    <t>Validar que los filtros por fecha funcionen correctamente.</t>
+  </si>
+  <si>
+    <t>Deben existir conexiones registradas.</t>
+  </si>
+  <si>
+    <t>1. Aplicar filtro “Today” o “Past 7 days”.2. Verificar resultados filtrados.</t>
+  </si>
+  <si>
+    <t>Conexiones con fechas distintas.</t>
+  </si>
+  <si>
+    <t>Solo se muestran las conexiones en el rango seleccionado.</t>
+  </si>
+  <si>
+    <t>Paginación de registros</t>
+  </si>
+  <si>
+    <t>Validar que los datos de conexión puedan eliminarse correctamente desde la lista.</t>
+  </si>
+  <si>
+    <t>1. Registrar más de 20 conexiones.2. Navegar entre páginas.</t>
+  </si>
+  <si>
+    <t>Registros de conexión simulados.</t>
+  </si>
+  <si>
+    <t>La paginación funciona sin errores.</t>
+  </si>
+  <si>
+    <t>Registro de ataques</t>
+  </si>
+  <si>
+    <t>Confirmar que se puedan editar registros de conexión sin errores.</t>
+  </si>
+  <si>
+    <t>1. Ingresar a “Ataques &gt; Add”.2. Completar campos requeridos.3. Guardar.</t>
+  </si>
+  <si>
+    <t>Datos de ataque simulados.</t>
+  </si>
+  <si>
+    <t>El registro se crea exitosamente.</t>
+  </si>
+  <si>
+    <t>Edición de ataques</t>
+  </si>
+  <si>
+    <t>Verificar que se muestren correctamente los detalles al abrir un registro.</t>
+  </si>
+  <si>
+    <t>Funcionalidad</t>
+  </si>
+  <si>
+    <t>Debe existir un ataque registrado.</t>
+  </si>
+  <si>
+    <t>1. Seleccionar un registro.2. Modificar campos.3. Guardar cambios.</t>
+  </si>
+  <si>
+    <t>Datos actualizados de ataque.</t>
+  </si>
+  <si>
+    <t>El ataque se actualiza correctamente.</t>
+  </si>
+  <si>
+    <t>Eliminación de ataques</t>
+  </si>
+  <si>
+    <t>Validar que los ataques puedan registrarse exitosamente.</t>
+  </si>
+  <si>
+    <t>1. Seleccionar un ataque.2. Eliminar registro.3. Confirmar acción.</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>El ataque se elimina correctamente sin afectar otros datos.</t>
+  </si>
+  <si>
+    <t>Registro de mitigaciones</t>
+  </si>
+  <si>
+    <t>Verificar que el sistema muestre todos los ataques registrados en la lista.</t>
+  </si>
+  <si>
+    <t>1. Ingresar a “Mitigaciones &gt; Add”.2. Completar los campos.3. Guardar registro.</t>
+  </si>
+  <si>
+    <t>Datos de prueba de mitigación.</t>
+  </si>
+  <si>
+    <t>El sistema guarda correctamente la mitigación.</t>
+  </si>
+  <si>
+    <t>Validación campo obligatorio Ataque</t>
+  </si>
+  <si>
+    <t>Confirmar que se puedan eliminar ataques de forma segura y controlada.</t>
+  </si>
+  <si>
+    <t>1. Intentar guardar sin seleccionar “Ataque”.</t>
+  </si>
+  <si>
+    <t>Campos vacíos.</t>
+  </si>
+  <si>
+    <t>El sistema debe mostrar error de campo obligatorio.</t>
+  </si>
+  <si>
+    <t>Validación de formato IP</t>
+  </si>
+  <si>
+    <t>Verificar que los filtros por tipo de ataque funcionen correctamente.</t>
+  </si>
+  <si>
+    <t>1. Ingresar una IP incorrecta.2. Guardar.</t>
+  </si>
+  <si>
+    <t>IP inválida.</t>
+  </si>
+  <si>
+    <t>El sistema muestra mensaje de error.</t>
+  </si>
+  <si>
+    <t>Creación de ataque desde icono “+”</t>
+  </si>
+  <si>
+    <t>Validar que los ataques puedan ser editados y guardados correctamente.</t>
+  </si>
+  <si>
+    <t>1. Clic en “+” junto a Ataque.2. Crear nuevo ataque.3. Verificar que se vincule.</t>
+  </si>
+  <si>
+    <t>El nuevo ataque se crea y se asocia a la mitigación.</t>
+  </si>
+  <si>
+    <t>Guardado de resultados extensos</t>
+  </si>
+  <si>
+    <t>Verificar que el sistema muestre un mensaje de éxito al guardar una mitigación.</t>
+  </si>
+  <si>
+    <t>1. Ingresar texto largo en “Detalle”.2. Guardar.</t>
+  </si>
+  <si>
+    <t>Texto con más de 1000 caracteres.</t>
+  </si>
+  <si>
+    <t>El sistema guarda sin errores ni cortes.</t>
+  </si>
+  <si>
+    <t>Personales</t>
+  </si>
+  <si>
+    <t>Validar que las mitigaciones estén correctamente asociadas a un ataque.</t>
+  </si>
+  <si>
+    <t>1. Ingresar datos del personal.2. Guardar.</t>
+  </si>
+  <si>
+    <t>Datos personales simulados.</t>
+  </si>
+  <si>
+    <t>El personal se registra correctamente.</t>
+  </si>
+  <si>
+    <t>Edición del personal</t>
+  </si>
+  <si>
+    <t>Confirmar que se guarden correctamente los datos ingresados en los campos de detalle e IP.</t>
+  </si>
+  <si>
+    <t>Debe existir un registro.</t>
+  </si>
+  <si>
+    <t>1. Seleccionar registro.2. Editar.3. Guardar.</t>
+  </si>
+  <si>
+    <t>Nuevos datos personales.</t>
+  </si>
+  <si>
+    <t>El registro se actualiza correctamente.</t>
+  </si>
+  <si>
+    <t>Roles</t>
+  </si>
+  <si>
+    <t>Creación de roles</t>
+  </si>
+  <si>
+    <t>Verificar que el campo “Ejecutado por” funcione correctamente al seleccionar un usuario.</t>
+  </si>
+  <si>
+    <t>1. Ingresar nuevo rol.2. Asignar permisos.3. Guardar.</t>
+  </si>
+  <si>
+    <t>Datos de rol simulados.</t>
+  </si>
+  <si>
+    <t>El rol se crea correctamente.</t>
+  </si>
+  <si>
+    <t>Verificación de permisos por rol</t>
+  </si>
+  <si>
+    <t>Validar que la casilla “Activo” actualice correctamente el estado de la mitigación.</t>
+  </si>
+  <si>
+    <t>Deben existir roles registrados.</t>
+  </si>
+  <si>
+    <t>1. Asignar usuario a rol limitado.2. Intentar acceder a vistas restringidas.</t>
+  </si>
+  <si>
+    <t>Usuario limitado.</t>
+  </si>
+  <si>
+    <t>El sistema bloquea accesos no permitidos.</t>
+  </si>
+  <si>
+    <t>Usuarios</t>
+  </si>
+  <si>
+    <t>Registro de usuarios</t>
+  </si>
+  <si>
+    <t>Verificar que el campo “Resultado” muestre el texto ingresado tras guardar.</t>
+  </si>
+  <si>
+    <t>1. Ingresar usuario nuevo.2. Guardar.</t>
+  </si>
+  <si>
+    <t>Datos simulados de usuario.</t>
+  </si>
+  <si>
+    <t>El usuario se crea correctamente.</t>
+  </si>
+  <si>
+    <t>Cambio de contraseña</t>
+  </si>
+  <si>
+    <t>Validar que el botón “Save” almacene correctamente la mitigación y retorne a la lista.</t>
+  </si>
+  <si>
+    <t>Debe existir usuario registrado.</t>
+  </si>
+  <si>
+    <t>1. Acceder al perfil.2. Cambiar contraseña.3. Verificar autenticación con nueva clave.</t>
+  </si>
+  <si>
+    <t>Contraseña antigua y nueva.</t>
+  </si>
+  <si>
+    <t>El sistema actualiza la contraseña correctamente.</t>
   </si>
 </sst>
 </file>
@@ -2786,12 +3137,18 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2807,7 +3164,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2836,12 +3193,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="66">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2871,6 +3231,117 @@
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -2961,87 +3432,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center"/>
@@ -8910,54 +9300,54 @@
     <dataField name="Cuenta de Estado (Dropdown)" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="16">
+    <format dxfId="46">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="45">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="44">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="41">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="40">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="39">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="38">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="34">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -9104,60 +9494,60 @@
     <dataField name="Cuenta de Test Case" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="32">
+    <format dxfId="62">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="61">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="60">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="59">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="58">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="57">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="54">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="53">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="52">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="51">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="50">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="47">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -9257,32 +9647,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BEF40B4A-F25E-458D-960B-8087E596FA2C}" name="Modulos" displayName="Modulos" ref="A1:A33" totalsRowShown="0" headerRowDxfId="62" dataDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BEF40B4A-F25E-458D-960B-8087E596FA2C}" name="Modulos" displayName="Modulos" ref="A1:A33" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
   <autoFilter ref="A1:A33" xr:uid="{BEF40B4A-F25E-458D-960B-8087E596FA2C}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{A3748FA1-9695-4A2D-A595-64BF200E5D1D}" name="MODULOS" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{A3748FA1-9695-4A2D-A595-64BF200E5D1D}" name="MODULOS" dataDxfId="63"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}" name="TestPlan" displayName="TestPlan" ref="A2:M141" headerRowDxfId="59">
-  <autoFilter ref="A2:M141" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}" name="TestPlan" displayName="TestPlan" ref="A2:M162" headerRowDxfId="32">
+  <autoFilter ref="A2:M162" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{7F95280F-E669-4A5D-AEDF-FCAAAC81F275}" name="Modulo (Dropdown)" totalsRowLabel="Total" dataDxfId="58" totalsRowDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{E775B39B-DEB6-4123-A65F-A37EDA4383A3}" name="Test Case" dataDxfId="56" totalsRowDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{4E500E60-0861-4EF2-B610-79885F5EF7FD}" name="Descripción" dataDxfId="54" totalsRowDxfId="53"/>
-    <tableColumn id="14" xr3:uid="{D149BE2F-3E66-4E54-8D0E-BA4D69F73794}" name="Tipo/s de Prueba" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{48166857-FFB0-4E91-A69A-8A057DEBB914}" name="Precondiciones" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="13" xr3:uid="{09440620-A437-484D-9292-769D8C979710}" name="Pasos a seguir" dataDxfId="48" totalsRowDxfId="47"/>
-    <tableColumn id="12" xr3:uid="{25FFAFC4-E636-4C78-8EC4-9B105CD6EC6A}" name="Datos de Prueba" dataDxfId="46" totalsRowDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{5C319188-663F-4BD1-ADB0-A93CF2F134F5}" name="Resultado Esperado" dataDxfId="44" totalsRowDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{AC65C1EE-D520-403E-8171-F3B42F898A90}" name="Resultado Actual (Si falla)" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{67BFFC43-BD7A-400D-BCA5-7641851369E7}" name="Ultima ejecución (Fecha)" dataDxfId="40" totalsRowDxfId="39"/>
-    <tableColumn id="10" xr3:uid="{AF2F4479-94ED-46CC-8F6A-9945904E34B4}" name="Encargado de Prueba" dataDxfId="38" totalsRowDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{1AE568CA-11EA-494D-A158-098CEC0427F1}" name="Estado (Dropdown)" dataDxfId="36" totalsRowDxfId="35"/>
-    <tableColumn id="9" xr3:uid="{D7CC1236-1B17-4FEE-A062-7A6AF5789012}" name="Comentario" totalsRowFunction="count" dataDxfId="34" totalsRowDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{7F95280F-E669-4A5D-AEDF-FCAAAC81F275}" name="Modulo (Dropdown)" totalsRowLabel="Total" dataDxfId="30" totalsRowDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{E775B39B-DEB6-4123-A65F-A37EDA4383A3}" name="Test Case" dataDxfId="28" totalsRowDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{4E500E60-0861-4EF2-B610-79885F5EF7FD}" name="Descripción" dataDxfId="26" totalsRowDxfId="27"/>
+    <tableColumn id="14" xr3:uid="{D149BE2F-3E66-4E54-8D0E-BA4D69F73794}" name="Tipo/s de Prueba" dataDxfId="24" totalsRowDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{48166857-FFB0-4E91-A69A-8A057DEBB914}" name="Precondiciones" dataDxfId="22" totalsRowDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{09440620-A437-484D-9292-769D8C979710}" name="Pasos a seguir" dataDxfId="20" totalsRowDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{25FFAFC4-E636-4C78-8EC4-9B105CD6EC6A}" name="Datos de Prueba" dataDxfId="18" totalsRowDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{5C319188-663F-4BD1-ADB0-A93CF2F134F5}" name="Resultado Esperado" dataDxfId="16" totalsRowDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{AC65C1EE-D520-403E-8171-F3B42F898A90}" name="Resultado Actual (Si falla)" dataDxfId="14" totalsRowDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{67BFFC43-BD7A-400D-BCA5-7641851369E7}" name="Ultima ejecución (Fecha)" dataDxfId="12" totalsRowDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{AF2F4479-94ED-46CC-8F6A-9945904E34B4}" name="Encargado de Prueba" dataDxfId="10" totalsRowDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{1AE568CA-11EA-494D-A158-098CEC0427F1}" name="Estado (Dropdown)" dataDxfId="8" totalsRowDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{D7CC1236-1B17-4FEE-A062-7A6AF5789012}" name="Comentario" totalsRowFunction="count" dataDxfId="6" totalsRowDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9730,7 +10120,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D9AFB2-4BAC-4EFB-A2E7-92EA3A8E1FBC}">
-  <dimension ref="A2:M141"/>
+  <dimension ref="A2:M162"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -14774,7 +15164,9 @@
       <c r="L137" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="M137" s="7"/>
+      <c r="M137" s="9" t="s">
+        <v>756</v>
+      </c>
     </row>
     <row r="138" spans="1:13" ht="45">
       <c r="A138" s="7" t="s">
@@ -14813,7 +15205,9 @@
       <c r="L138" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="M138" s="7"/>
+      <c r="M138" s="9" t="s">
+        <v>757</v>
+      </c>
     </row>
     <row r="139" spans="1:13" ht="60">
       <c r="A139" s="7" t="s">
@@ -14926,9 +15320,797 @@
       </c>
       <c r="M141" s="7"/>
     </row>
+    <row r="142" spans="1:13" ht="45">
+      <c r="A142" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>758</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>759</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="H142" s="7" t="s">
+        <v>762</v>
+      </c>
+      <c r="I142" s="7"/>
+      <c r="J142" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K142" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L142" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M142" s="7"/>
+    </row>
+    <row r="143" spans="1:13" ht="45">
+      <c r="A143" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>764</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="G143" s="7" t="s">
+        <v>767</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>768</v>
+      </c>
+      <c r="I143" s="7"/>
+      <c r="J143" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K143" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L143" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M143" s="7"/>
+    </row>
+    <row r="144" spans="1:13" ht="60">
+      <c r="A144" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>769</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>770</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="H144" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="I144" s="7"/>
+      <c r="J144" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K144" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L144" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M144" s="7"/>
+    </row>
+    <row r="145" spans="1:13" ht="60">
+      <c r="A145" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>776</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E145" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="H145" s="7" t="s">
+        <v>779</v>
+      </c>
+      <c r="I145" s="7"/>
+      <c r="J145" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K145" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L145" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M145" s="7"/>
+    </row>
+    <row r="146" spans="1:13" ht="30">
+      <c r="A146" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>782</v>
+      </c>
+      <c r="F146" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="H146" s="7" t="s">
+        <v>785</v>
+      </c>
+      <c r="I146" s="7"/>
+      <c r="J146" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K146" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L146" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M146" s="7"/>
+    </row>
+    <row r="147" spans="1:13" ht="45">
+      <c r="A147" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>786</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>787</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>788</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>789</v>
+      </c>
+      <c r="G147" s="7" t="s">
+        <v>790</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>791</v>
+      </c>
+      <c r="I147" s="7"/>
+      <c r="J147" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K147" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L147" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M147" s="7"/>
+    </row>
+    <row r="148" spans="1:13" ht="45">
+      <c r="A148" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>792</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>793</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F148" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>795</v>
+      </c>
+      <c r="H148" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="I148" s="7"/>
+      <c r="J148" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K148" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L148" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M148" s="7"/>
+    </row>
+    <row r="149" spans="1:13" ht="45">
+      <c r="A149" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>797</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F149" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="G149" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="I149" s="7"/>
+      <c r="J149" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K149" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L149" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M149" s="7"/>
+    </row>
+    <row r="150" spans="1:13" ht="45">
+      <c r="A150" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>802</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>807</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="I150" s="7"/>
+      <c r="J150" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K150" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L150" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M150" s="7"/>
+    </row>
+    <row r="151" spans="1:13" ht="45">
+      <c r="A151" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="F151" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="G151" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="I151" s="7"/>
+      <c r="J151" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K151" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L151" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M151" s="7"/>
+    </row>
+    <row r="152" spans="1:13" ht="45">
+      <c r="A152" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>814</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>815</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F152" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="G152" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>818</v>
+      </c>
+      <c r="I152" s="7"/>
+      <c r="J152" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K152" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L152" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M152" s="7"/>
+    </row>
+    <row r="153" spans="1:13" ht="30">
+      <c r="A153" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>819</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>820</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F153" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="G153" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="H153" s="7" t="s">
+        <v>823</v>
+      </c>
+      <c r="I153" s="7"/>
+      <c r="J153" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K153" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L153" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M153" s="7"/>
+    </row>
+    <row r="154" spans="1:13" ht="30">
+      <c r="A154" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>825</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F154" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="G154" s="7" t="s">
+        <v>827</v>
+      </c>
+      <c r="H154" s="7" t="s">
+        <v>828</v>
+      </c>
+      <c r="I154" s="7"/>
+      <c r="J154" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K154" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L154" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M154" s="7"/>
+    </row>
+    <row r="155" spans="1:13" ht="45">
+      <c r="A155" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F155" s="7" t="s">
+        <v>831</v>
+      </c>
+      <c r="G155" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>832</v>
+      </c>
+      <c r="I155" s="7"/>
+      <c r="J155" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K155" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L155" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M155" s="7"/>
+    </row>
+    <row r="156" spans="1:13" ht="45">
+      <c r="A156" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F156" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="G156" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="H156" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="I156" s="7"/>
+      <c r="J156" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K156" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L156" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M156" s="7"/>
+    </row>
+    <row r="157" spans="1:13" ht="30">
+      <c r="A157" s="7" t="s">
+        <v>838</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F157" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="G157" s="7" t="s">
+        <v>841</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="I157" s="7"/>
+      <c r="J157" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K157" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L157" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M157" s="7"/>
+    </row>
+    <row r="158" spans="1:13" ht="45">
+      <c r="A158" s="7" t="s">
+        <v>838</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>843</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="F158" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="H158" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="I158" s="7"/>
+      <c r="J158" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K158" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L158" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M158" s="7"/>
+    </row>
+    <row r="159" spans="1:13" ht="45">
+      <c r="A159" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>850</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F159" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="G159" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="H159" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="I159" s="7"/>
+      <c r="J159" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K159" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L159" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M159" s="7"/>
+    </row>
+    <row r="160" spans="1:13" ht="45">
+      <c r="A160" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>855</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>856</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>857</v>
+      </c>
+      <c r="F160" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="G160" s="7" t="s">
+        <v>859</v>
+      </c>
+      <c r="H160" s="7" t="s">
+        <v>860</v>
+      </c>
+      <c r="I160" s="7"/>
+      <c r="J160" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K160" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L160" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M160" s="7"/>
+    </row>
+    <row r="161" spans="1:13" ht="30">
+      <c r="A161" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>863</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F161" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="G161" s="7" t="s">
+        <v>865</v>
+      </c>
+      <c r="H161" s="7" t="s">
+        <v>866</v>
+      </c>
+      <c r="I161" s="7"/>
+      <c r="J161" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K161" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L161" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M161" s="7"/>
+    </row>
+    <row r="162" spans="1:13" ht="45">
+      <c r="A162" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>867</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>868</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>869</v>
+      </c>
+      <c r="F162" s="7" t="s">
+        <v>870</v>
+      </c>
+      <c r="G162" s="7" t="s">
+        <v>871</v>
+      </c>
+      <c r="H162" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="I162" s="7"/>
+      <c r="J162" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K162" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L162" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M162" s="7"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L3:L134 L135:M135 L136:L140">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>"PENDING"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L142:L162">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"PENDING"</formula>
     </cfRule>
@@ -14940,19 +16122,21 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A141" xr:uid="{F4675041-A1B8-4B65-822E-23AD6AB864A0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A162" xr:uid="{F4675041-A1B8-4B65-822E-23AD6AB864A0}">
       <formula1>INDIRECT("Modulos[MODULOS]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M135 L3:L141" xr:uid="{1E8D2D6D-4EE7-40E2-A622-3458BDCF08AD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M135 L3:L162" xr:uid="{1E8D2D6D-4EE7-40E2-A622-3458BDCF08AD}">
       <formula1>"PASS,PENDING,FAIL"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="M15" r:id="rId1" xr:uid="{E03BA14B-EB46-4555-B0FE-E6A8B84EE875}"/>
+    <hyperlink ref="M137" r:id="rId2" xr:uid="{76C22D69-B896-4F17-9D14-9568E036A5E6}"/>
+    <hyperlink ref="M138" r:id="rId3" xr:uid="{B3EE788D-8E23-4A38-9959-7347F6F58207}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -15132,9 +16316,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15276,19 +16463,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CABA5C2-04D8-4DC5-BBFB-FF9AC004B268}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -15312,9 +16495,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CABA5C2-04D8-4DC5-BBFB-FF9AC004B268}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Modelo Test Plan.xlsx
+++ b/Modelo Test Plan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Downloads\CoderBits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037445D7-00BA-4229-90E6-DBB5C3C7E8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6175F594-422E-46C6-9183-F88D520ACE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{96765352-7388-4C61-94B8-5077301D3254}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="827">
   <si>
     <t>MODULOS</t>
   </si>
@@ -2795,21 +2795,6 @@
   </si>
   <si>
     <t>El sistema debe mostrar error de campo obligatorio.</t>
-  </si>
-  <si>
-    <t>Validación de formato IP</t>
-  </si>
-  <si>
-    <t>Verificar que los filtros por tipo de ataque funcionen correctamente.</t>
-  </si>
-  <si>
-    <t>1. Ingresar una IP incorrecta.2. Guardar.</t>
-  </si>
-  <si>
-    <t>IP inválida.</t>
-  </si>
-  <si>
-    <t>El sistema muestra mensaje de error.</t>
   </si>
   <si>
     <t>Creación de ataque desde icono “+”</t>
@@ -9515,8 +9500,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}" name="TestPlan" displayName="TestPlan" ref="A2:N177" headerRowDxfId="64">
-  <autoFilter ref="A2:N177" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}" name="TestPlan" displayName="TestPlan" ref="A2:N176" headerRowDxfId="64">
+  <autoFilter ref="A2:N176" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{7F95280F-E669-4A5D-AEDF-FCAAAC81F275}" name="Modulo (Dropdown)" totalsRowLabel="Total" dataDxfId="63" totalsRowDxfId="62"/>
     <tableColumn id="2" xr3:uid="{E775B39B-DEB6-4123-A65F-A37EDA4383A3}" name="Test Case" dataDxfId="61" totalsRowDxfId="60"/>
@@ -9979,7 +9964,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D9AFB2-4BAC-4EFB-A2E7-92EA3A8E1FBC}">
-  <dimension ref="A2:N201"/>
+  <dimension ref="A2:N200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -15155,8 +15140,8 @@
       <c r="K137" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="L137" s="10" t="s">
-        <v>147</v>
+      <c r="L137" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M137" s="7"/>
       <c r="N137" s="7"/>
@@ -15193,8 +15178,8 @@
       <c r="K138" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="L138" s="10" t="s">
-        <v>147</v>
+      <c r="L138" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M138" s="7"/>
       <c r="N138" s="7"/>
@@ -15231,8 +15216,8 @@
       <c r="K139" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="L139" s="10" t="s">
-        <v>147</v>
+      <c r="L139" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M139" s="7"/>
       <c r="N139" s="7"/>
@@ -15307,8 +15292,8 @@
       <c r="K141" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="L141" s="10" t="s">
-        <v>147</v>
+      <c r="L141" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M141" s="7"/>
       <c r="N141" s="7"/>
@@ -15345,8 +15330,8 @@
       <c r="K142" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="L142" s="10" t="s">
-        <v>147</v>
+      <c r="L142" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M142" s="7"/>
       <c r="N142" s="7"/>
@@ -15514,7 +15499,7 @@
         <v>778</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>276</v>
+        <v>757</v>
       </c>
       <c r="E147" s="7" t="s">
         <v>204</v>
@@ -15523,10 +15508,10 @@
         <v>779</v>
       </c>
       <c r="G147" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="H147" s="7" t="s">
         <v>780</v>
-      </c>
-      <c r="H147" s="7" t="s">
-        <v>781</v>
       </c>
       <c r="I147" s="7"/>
       <c r="J147" s="6">
@@ -15535,8 +15520,8 @@
       <c r="K147" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="L147" s="10" t="s">
-        <v>147</v>
+      <c r="L147" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M147" s="7"/>
       <c r="N147" s="7"/>
@@ -15546,22 +15531,22 @@
         <v>6</v>
       </c>
       <c r="B148" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="C148" t="s">
         <v>782</v>
       </c>
-      <c r="C148" t="s">
-        <v>783</v>
-      </c>
       <c r="D148" s="7" t="s">
-        <v>757</v>
+        <v>212</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>204</v>
       </c>
       <c r="F148" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="G148" s="7" t="s">
         <v>784</v>
-      </c>
-      <c r="G148" s="7" t="s">
-        <v>753</v>
       </c>
       <c r="H148" s="7" t="s">
         <v>785</v>
@@ -15573,24 +15558,24 @@
       <c r="K148" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="L148" s="10" t="s">
-        <v>147</v>
+      <c r="L148" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M148" s="7"/>
       <c r="N148" s="7"/>
     </row>
     <row r="149" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>6</v>
+        <v>786</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>786</v>
+        <v>47</v>
       </c>
       <c r="C149" t="s">
         <v>787</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>212</v>
+        <v>276</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>204</v>
@@ -15619,28 +15604,28 @@
     </row>
     <row r="150" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
+        <v>786</v>
+      </c>
+      <c r="B150" s="7" t="s">
         <v>791</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="C150" t="s">
         <v>792</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>276</v>
+        <v>757</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>204</v>
+        <v>793</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="G150" s="7" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H150" s="7" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="I150" s="7"/>
       <c r="J150" s="6">
@@ -15657,28 +15642,28 @@
     </row>
     <row r="151" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C151" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>757</v>
+        <v>276</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>798</v>
+        <v>204</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G151" s="7" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="I151" s="7"/>
       <c r="J151" s="6">
@@ -15693,9 +15678,9 @@
       <c r="M151" s="7"/>
       <c r="N151" s="7"/>
     </row>
-    <row r="152" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>803</v>
@@ -15704,19 +15689,19 @@
         <v>804</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>204</v>
+        <v>805</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G152" s="7" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H152" s="7" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="I152" s="7"/>
       <c r="J152" s="6">
@@ -15731,30 +15716,30 @@
       <c r="M152" s="7"/>
       <c r="N152" s="7"/>
     </row>
-    <row r="153" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C153" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>219</v>
+        <v>276</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>810</v>
+        <v>204</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H153" s="7" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="I153" s="7"/>
       <c r="J153" s="6">
@@ -15763,15 +15748,15 @@
       <c r="K153" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="L153" s="10" t="s">
-        <v>147</v>
+      <c r="L153" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M153" s="7"/>
       <c r="N153" s="7"/>
     </row>
     <row r="154" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>815</v>
@@ -15780,19 +15765,19 @@
         <v>816</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>204</v>
+        <v>817</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H154" s="7" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="I154" s="7"/>
       <c r="J154" s="6">
@@ -15807,41 +15792,19 @@
       <c r="M154" s="7"/>
       <c r="N154" s="7"/>
     </row>
-    <row r="155" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A155" s="7" t="s">
-        <v>814</v>
-      </c>
-      <c r="B155" s="7" t="s">
-        <v>820</v>
-      </c>
-      <c r="C155" t="s">
-        <v>821</v>
-      </c>
-      <c r="D155" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E155" s="7" t="s">
-        <v>822</v>
-      </c>
-      <c r="F155" s="7" t="s">
-        <v>823</v>
-      </c>
-      <c r="G155" s="7" t="s">
-        <v>824</v>
-      </c>
-      <c r="H155" s="7" t="s">
-        <v>825</v>
-      </c>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A155" s="7"/>
+      <c r="B155" s="7"/>
+      <c r="C155" s="7"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
+      <c r="F155" s="7"/>
+      <c r="G155" s="7"/>
+      <c r="H155" s="7"/>
       <c r="I155" s="7"/>
-      <c r="J155" s="6">
-        <v>45950</v>
-      </c>
-      <c r="K155" s="7" t="s">
-        <v>716</v>
-      </c>
-      <c r="L155" s="10" t="s">
-        <v>147</v>
-      </c>
+      <c r="J155" s="3"/>
+      <c r="K155" s="3"/>
+      <c r="L155" s="7"/>
       <c r="M155" s="7"/>
       <c r="N155" s="7"/>
     </row>
@@ -16181,7 +16144,7 @@
       <c r="M176" s="7"/>
       <c r="N176" s="7"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="7"/>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -16194,10 +16157,8 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
       <c r="L177" s="7"/>
-      <c r="M177" s="7"/>
-      <c r="N177" s="7"/>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="7"/>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -16211,7 +16172,7 @@
       <c r="K178" s="3"/>
       <c r="L178" s="7"/>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="7"/>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -16225,7 +16186,7 @@
       <c r="K179" s="3"/>
       <c r="L179" s="7"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="7"/>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -16236,10 +16197,10 @@
       <c r="H180" s="7"/>
       <c r="I180" s="7"/>
       <c r="J180" s="3"/>
-      <c r="K180" s="3"/>
+      <c r="K180" s="7"/>
       <c r="L180" s="7"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="7"/>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -16250,10 +16211,10 @@
       <c r="H181" s="7"/>
       <c r="I181" s="7"/>
       <c r="J181" s="3"/>
-      <c r="K181" s="7"/>
+      <c r="K181" s="3"/>
       <c r="L181" s="7"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="7"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -16267,8 +16228,7 @@
       <c r="K182" s="3"/>
       <c r="L182" s="7"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A183" s="7"/>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
@@ -16281,7 +16241,7 @@
       <c r="K183" s="3"/>
       <c r="L183" s="7"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
@@ -16294,7 +16254,7 @@
       <c r="K184" s="3"/>
       <c r="L184" s="7"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B185" s="7"/>
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
@@ -16307,7 +16267,7 @@
       <c r="K185" s="3"/>
       <c r="L185" s="7"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
@@ -16320,7 +16280,7 @@
       <c r="K186" s="3"/>
       <c r="L186" s="7"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B187" s="7"/>
       <c r="C187" s="7"/>
       <c r="D187" s="7"/>
@@ -16333,7 +16293,7 @@
       <c r="K187" s="3"/>
       <c r="L187" s="7"/>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B188" s="7"/>
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
@@ -16346,7 +16306,7 @@
       <c r="K188" s="3"/>
       <c r="L188" s="7"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B189" s="7"/>
       <c r="C189" s="7"/>
       <c r="D189" s="7"/>
@@ -16359,7 +16319,7 @@
       <c r="K189" s="3"/>
       <c r="L189" s="7"/>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B190" s="7"/>
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
@@ -16372,7 +16332,7 @@
       <c r="K190" s="3"/>
       <c r="L190" s="7"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B191" s="7"/>
       <c r="C191" s="7"/>
       <c r="D191" s="7"/>
@@ -16385,7 +16345,7 @@
       <c r="K191" s="3"/>
       <c r="L191" s="7"/>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B192" s="7"/>
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
@@ -16502,22 +16462,9 @@
       <c r="K200" s="3"/>
       <c r="L200" s="7"/>
     </row>
-    <row r="201" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B201" s="7"/>
-      <c r="C201" s="7"/>
-      <c r="D201" s="7"/>
-      <c r="E201" s="7"/>
-      <c r="F201" s="7"/>
-      <c r="G201" s="7"/>
-      <c r="H201" s="7"/>
-      <c r="I201" s="7"/>
-      <c r="J201" s="3"/>
-      <c r="K201" s="3"/>
-      <c r="L201" s="7"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="L3:L155">
+  <conditionalFormatting sqref="L3:L154">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"PENDING"</formula>
     </cfRule>
@@ -16528,7 +16475,7 @@
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L178:L182 K181 L184:L201">
+  <conditionalFormatting sqref="L177:L181 K180 L183:L200">
     <cfRule type="cellIs" dxfId="2" priority="34" operator="equal">
       <formula>"PENDING"</formula>
     </cfRule>
@@ -16540,10 +16487,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L184:L201 K181 L178:L182 L3:L155" xr:uid="{1E8D2D6D-4EE7-40E2-A622-3458BDCF08AD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L183:L200 K180 L177:L181 L3:L154" xr:uid="{1E8D2D6D-4EE7-40E2-A622-3458BDCF08AD}">
       <formula1>"PASS,PENDING,FAIL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A183" xr:uid="{F4675041-A1B8-4B65-822E-23AD6AB864A0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A182" xr:uid="{F4675041-A1B8-4B65-822E-23AD6AB864A0}">
       <formula1>INDIRECT("Modulos[MODULOS]")</formula1>
     </dataValidation>
   </dataValidations>
@@ -16580,10 +16527,10 @@
   <sheetData>
     <row r="2" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -16591,7 +16538,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>130</v>
@@ -16603,12 +16550,12 @@
         <v>147</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -16660,7 +16607,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -16677,10 +16624,10 @@
     </row>
     <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -16709,7 +16656,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="B28" s="1">
         <v>4</v>

--- a/Modelo Test Plan.xlsx
+++ b/Modelo Test Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Downloads\CoderBits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6175F594-422E-46C6-9183-F88D520ACE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A7AC5B-A5E8-43A3-B070-959E1433C1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{96765352-7388-4C61-94B8-5077301D3254}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="898">
   <si>
     <t>MODULOS</t>
   </si>
@@ -2638,9 +2638,6 @@
     <t>Verificar que la interfaz del panel se adapte correctamente a distintas resoluciones de pantalla.</t>
   </si>
   <si>
-    <t>1. Acceder al dashboard desde distintos dispositivos.2. Verificar que la interfaz se adapte correctamente.</t>
-  </si>
-  <si>
     <t>Dispositivos con diferentes resoluciones.</t>
   </si>
   <si>
@@ -2945,13 +2942,229 @@
   </si>
   <si>
     <t>Cuenta de Estado (Dropdown)</t>
+  </si>
+  <si>
+    <t>1. Acceder al dashboard desde distintos2. Verificar que la interfaz se adapte correctamente.</t>
+  </si>
+  <si>
+    <t>Gestión de Personal</t>
+  </si>
+  <si>
+    <t>Recuperación de personal eliminado</t>
+  </si>
+  <si>
+    <t>Verificar que un usuario eliminado pueda ser restaurado correctamente desde el panel de administración</t>
+  </si>
+  <si>
+    <t>Funcional / Base de Datos</t>
+  </si>
+  <si>
+    <t>Usuario previamente eliminado del sistema</t>
+  </si>
+  <si>
+    <t>1. Acceder al módulo de personal</t>
+  </si>
+  <si>
+    <t>2. Filtrar por usuarios eliminados</t>
+  </si>
+  <si>
+    <t>3. Seleccionar “Restaurar”</t>
+  </si>
+  <si>
+    <t>El usuario se restaura y reaparece en la lista activa</t>
+  </si>
+  <si>
+    <t>Monitoreo de Red</t>
+  </si>
+  <si>
+    <t>Activación del monitoreo de red</t>
+  </si>
+  <si>
+    <t>Validar que el sistema inicie la captura de tráfico al activar el monitoreo</t>
+  </si>
+  <si>
+    <t>Backend y sniffer activos</t>
+  </si>
+  <si>
+    <t>1. Ir al panel de monitoreo</t>
+  </si>
+  <si>
+    <t>2. Presionar “Activar Monitoreo”</t>
+  </si>
+  <si>
+    <t>3. Verificar estado</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>El sistema muestra estado “Monitoreo Activo” y comienza la captura</t>
+  </si>
+  <si>
+    <t>Desactivación del monitoreo de red</t>
+  </si>
+  <si>
+    <t>Verificar que el monitoreo pueda ser detenido correctamente</t>
+  </si>
+  <si>
+    <t>Monitoreo activo</t>
+  </si>
+  <si>
+    <t>2. Presionar “Detener Monitoreo”</t>
+  </si>
+  <si>
+    <t>El sistema cambia a “Monitoreo Inactivo” y detiene la captura</t>
+  </si>
+  <si>
+    <t>Registro de Ataques</t>
+  </si>
+  <si>
+    <t>Validar que cada ataque detectado se registre correctamente en la base de datos</t>
+  </si>
+  <si>
+    <t>Funcional / Backend</t>
+  </si>
+  <si>
+    <t>Monitoreo activo e IA cargada</t>
+  </si>
+  <si>
+    <t>1. Simular tráfico malicioso</t>
+  </si>
+  <si>
+    <t>2. Verificar tabla de ataques registrados</t>
+  </si>
+  <si>
+    <t>El ataque se almacena con IP, tipo y hora</t>
+  </si>
+  <si>
+    <t>Mitigación</t>
+  </si>
+  <si>
+    <t>Creación de mitigación según el ataque</t>
+  </si>
+  <si>
+    <t>Verificar que el sistema permita crear acciones de mitigación basadas en ataques detectados</t>
+  </si>
+  <si>
+    <t>Ataques registrados disponibles</t>
+  </si>
+  <si>
+    <t>1. Ingresar a detalle del ataque</t>
+  </si>
+  <si>
+    <t>2. Seleccionar “Crear mitigación”</t>
+  </si>
+  <si>
+    <t>3. Guardar acción</t>
+  </si>
+  <si>
+    <t>Se crea la mitigación y se asocia al ataque</t>
+  </si>
+  <si>
+    <t>Comunicación en tiempo real</t>
+  </si>
+  <si>
+    <t>Envío de datos en tiempo real</t>
+  </si>
+  <si>
+    <t>Validar que los datos de tráfico se envíen y actualicen sin recargar la página</t>
+  </si>
+  <si>
+    <t>Integración / WebSocket</t>
+  </si>
+  <si>
+    <t>Backend con Channels ejecutándose</t>
+  </si>
+  <si>
+    <t>1. Activar monitoreo</t>
+  </si>
+  <si>
+    <t>2. Observar actualización del dashboard</t>
+  </si>
+  <si>
+    <t>Datos de red se actualizan cada pocos segundos en tiempo real</t>
+  </si>
+  <si>
+    <t>Detección Inteligente</t>
+  </si>
+  <si>
+    <t>Análisis automático del tráfico</t>
+  </si>
+  <si>
+    <t>Confirmar que el modelo ML clasifique correctamente tráfico normal y malicioso</t>
+  </si>
+  <si>
+    <t>Funcional / ML</t>
+  </si>
+  <si>
+    <t>Modelo entrenado cargado</t>
+  </si>
+  <si>
+    <t>1. Enviar muestras benignas y maliciosas</t>
+  </si>
+  <si>
+    <t>2. Observar clasificación</t>
+  </si>
+  <si>
+    <t>Detección precisa con etiquetas correctas</t>
+  </si>
+  <si>
+    <t>Funcional / UI</t>
+  </si>
+  <si>
+    <t>Visualización de estadísticas</t>
+  </si>
+  <si>
+    <t>Validar que las métricas (ataques, dispositivos, uptime) se actualicen correctamente</t>
+  </si>
+  <si>
+    <t>Backend activo</t>
+  </si>
+  <si>
+    <t>1. Iniciar sesión</t>
+  </si>
+  <si>
+    <t>2. Revisar tarjetas de estadísticas</t>
+  </si>
+  <si>
+    <t>Datos correctos y actualizados en interfaz</t>
+  </si>
+  <si>
+    <t>App Móvil</t>
+  </si>
+  <si>
+    <t>Sincronización de alertas en app móvil</t>
+  </si>
+  <si>
+    <t>Confirmar que las alertas del backend lleguen a la aplicación móvil en tiempo real</t>
+  </si>
+  <si>
+    <t>Integración / Realtime</t>
+  </si>
+  <si>
+    <t>Backend y WS activos</t>
+  </si>
+  <si>
+    <t>1. Generar alerta desde la web</t>
+  </si>
+  <si>
+    <t>Alerta aparece de inmediato en la app</t>
+  </si>
+  <si>
+    <t>Fabrizio Rollano</t>
+  </si>
+  <si>
+    <t>Usuario: Fabri ROLLANO</t>
+  </si>
+  <si>
+    <t>pe</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2973,8 +3186,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="0.79998168889431442"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2983,7 +3211,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3001,7 +3241,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3030,8 +3270,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3098,6 +3365,12 @@
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -3223,12 +3496,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3287,6 +3554,12 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFF99"/>
+      <color rgb="FFFFFF66"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -9143,54 +9416,54 @@
     <dataField name="Cuenta de Estado (Dropdown)" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="19">
+    <format dxfId="21">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="20">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="19">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="15">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="14">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="13">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="9">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -9337,60 +9610,60 @@
     <dataField name="Cuenta de Test Case" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="35">
+    <format dxfId="37">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="36">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="35">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="34">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="33">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="28">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="29">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="27">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="26">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="25">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -9511,12 +9784,12 @@
     <tableColumn id="13" xr3:uid="{09440620-A437-484D-9292-769D8C979710}" name="Pasos a seguir" dataDxfId="53" totalsRowDxfId="52"/>
     <tableColumn id="12" xr3:uid="{25FFAFC4-E636-4C78-8EC4-9B105CD6EC6A}" name="Datos de Prueba" dataDxfId="51" totalsRowDxfId="50"/>
     <tableColumn id="5" xr3:uid="{5C319188-663F-4BD1-ADB0-A93CF2F134F5}" name="Resultado Esperado" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{AC65C1EE-D520-403E-8171-F3B42F898A90}" name="Resultado Actual (Si falla)" dataDxfId="47" totalsRowDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{67BFFC43-BD7A-400D-BCA5-7641851369E7}" name="Ultima ejecución (Fecha)" dataDxfId="45" totalsRowDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{AF2F4479-94ED-46CC-8F6A-9945904E34B4}" name="Encargado de Prueba" dataDxfId="43" totalsRowDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{1AE568CA-11EA-494D-A158-098CEC0427F1}" name="Estado (Dropdown)" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="9" xr3:uid="{D7CC1236-1B17-4FEE-A062-7A6AF5789012}" name="Comentario" totalsRowFunction="count" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="17" xr3:uid="{A5678D00-4569-41AC-B6BA-DC2546DAF085}" name="Columna1" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{AC65C1EE-D520-403E-8171-F3B42F898A90}" name="Resultado Actual (Si falla)" dataDxfId="6" totalsRowDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{67BFFC43-BD7A-400D-BCA5-7641851369E7}" name="Ultima ejecución (Fecha)" dataDxfId="47" totalsRowDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{AF2F4479-94ED-46CC-8F6A-9945904E34B4}" name="Encargado de Prueba" dataDxfId="45" totalsRowDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{1AE568CA-11EA-494D-A158-098CEC0427F1}" name="Estado (Dropdown)" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="9" xr3:uid="{D7CC1236-1B17-4FEE-A062-7A6AF5789012}" name="Comentario" totalsRowFunction="count" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="17" xr3:uid="{A5678D00-4569-41AC-B6BA-DC2546DAF085}" name="Columna1" dataDxfId="39" totalsRowDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9964,7 +10237,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D9AFB2-4BAC-4EFB-A2E7-92EA3A8E1FBC}">
-  <dimension ref="A2:N200"/>
+  <dimension ref="A2:N198"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -15026,7 +15299,7 @@
       <c r="K134" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L134" s="10" t="s">
+      <c r="L134" s="17" t="s">
         <v>147</v>
       </c>
       <c r="M134" s="7"/>
@@ -15064,7 +15337,7 @@
       <c r="K135" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="L135" s="1" t="s">
+      <c r="L135" s="17" t="s">
         <v>41</v>
       </c>
       <c r="M135" s="7"/>
@@ -15108,7 +15381,7 @@
       <c r="M136" s="7"/>
       <c r="N136" s="7"/>
     </row>
-    <row r="137" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
         <v>12</v>
       </c>
@@ -15125,13 +15398,13 @@
         <v>204</v>
       </c>
       <c r="F137" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="G137" s="7" t="s">
         <v>724</v>
       </c>
-      <c r="G137" s="7" t="s">
+      <c r="H137" s="7" t="s">
         <v>725</v>
-      </c>
-      <c r="H137" s="7" t="s">
-        <v>726</v>
       </c>
       <c r="I137" s="7"/>
       <c r="J137" s="6">
@@ -15148,13 +15421,13 @@
     </row>
     <row r="138" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="B138" s="7" t="s">
         <v>727</v>
       </c>
-      <c r="B138" s="7" t="s">
+      <c r="C138" t="s">
         <v>728</v>
-      </c>
-      <c r="C138" t="s">
-        <v>729</v>
       </c>
       <c r="D138" s="7" t="s">
         <v>276</v>
@@ -15163,13 +15436,13 @@
         <v>204</v>
       </c>
       <c r="F138" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="G138" s="7" t="s">
         <v>730</v>
       </c>
-      <c r="G138" s="7" t="s">
+      <c r="H138" s="7" t="s">
         <v>731</v>
-      </c>
-      <c r="H138" s="7" t="s">
-        <v>732</v>
       </c>
       <c r="I138" s="7"/>
       <c r="J138" s="6">
@@ -15186,28 +15459,28 @@
     </row>
     <row r="139" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B139" s="7" t="s">
+        <v>732</v>
+      </c>
+      <c r="C139" t="s">
         <v>733</v>
-      </c>
-      <c r="C139" t="s">
-        <v>734</v>
       </c>
       <c r="D139" s="7" t="s">
         <v>203</v>
       </c>
       <c r="E139" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="F139" s="7" t="s">
         <v>735</v>
       </c>
-      <c r="F139" s="7" t="s">
+      <c r="G139" s="7" t="s">
         <v>736</v>
       </c>
-      <c r="G139" s="7" t="s">
+      <c r="H139" s="7" t="s">
         <v>737</v>
-      </c>
-      <c r="H139" s="7" t="s">
-        <v>738</v>
       </c>
       <c r="I139" s="7"/>
       <c r="J139" s="6">
@@ -15224,28 +15497,28 @@
     </row>
     <row r="140" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B140" s="7" t="s">
+        <v>738</v>
+      </c>
+      <c r="C140" t="s">
         <v>739</v>
-      </c>
-      <c r="C140" t="s">
-        <v>740</v>
       </c>
       <c r="D140" s="7" t="s">
         <v>203</v>
       </c>
       <c r="E140" s="7" t="s">
+        <v>740</v>
+      </c>
+      <c r="F140" s="7" t="s">
         <v>741</v>
       </c>
-      <c r="F140" s="7" t="s">
+      <c r="G140" s="7" t="s">
         <v>742</v>
       </c>
-      <c r="G140" s="7" t="s">
+      <c r="H140" s="7" t="s">
         <v>743</v>
-      </c>
-      <c r="H140" s="7" t="s">
-        <v>744</v>
       </c>
       <c r="I140" s="7"/>
       <c r="J140" s="6">
@@ -15262,13 +15535,13 @@
     </row>
     <row r="141" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B141" s="7" t="s">
+        <v>744</v>
+      </c>
+      <c r="C141" t="s">
         <v>745</v>
-      </c>
-      <c r="C141" t="s">
-        <v>746</v>
       </c>
       <c r="D141" s="7" t="s">
         <v>297</v>
@@ -15277,13 +15550,13 @@
         <v>204</v>
       </c>
       <c r="F141" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="G141" s="7" t="s">
         <v>747</v>
       </c>
-      <c r="G141" s="7" t="s">
+      <c r="H141" s="7" t="s">
         <v>748</v>
-      </c>
-      <c r="H141" s="7" t="s">
-        <v>749</v>
       </c>
       <c r="I141" s="7"/>
       <c r="J141" s="6">
@@ -15303,10 +15576,10 @@
         <v>5</v>
       </c>
       <c r="B142" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="C142" t="s">
         <v>750</v>
-      </c>
-      <c r="C142" t="s">
-        <v>751</v>
       </c>
       <c r="D142" s="7" t="s">
         <v>276</v>
@@ -15315,13 +15588,13 @@
         <v>204</v>
       </c>
       <c r="F142" s="7" t="s">
+        <v>751</v>
+      </c>
+      <c r="G142" s="7" t="s">
         <v>752</v>
       </c>
-      <c r="G142" s="7" t="s">
+      <c r="H142" s="7" t="s">
         <v>753</v>
-      </c>
-      <c r="H142" s="7" t="s">
-        <v>754</v>
       </c>
       <c r="I142" s="7"/>
       <c r="J142" s="6">
@@ -15341,25 +15614,25 @@
         <v>5</v>
       </c>
       <c r="B143" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="C143" t="s">
         <v>755</v>
       </c>
-      <c r="C143" t="s">
+      <c r="D143" s="7" t="s">
         <v>756</v>
       </c>
-      <c r="D143" s="7" t="s">
+      <c r="E143" s="7" t="s">
         <v>757</v>
       </c>
-      <c r="E143" s="7" t="s">
+      <c r="F143" s="7" t="s">
         <v>758</v>
       </c>
-      <c r="F143" s="7" t="s">
+      <c r="G143" s="7" t="s">
         <v>759</v>
       </c>
-      <c r="G143" s="7" t="s">
+      <c r="H143" s="7" t="s">
         <v>760</v>
-      </c>
-      <c r="H143" s="7" t="s">
-        <v>761</v>
       </c>
       <c r="I143" s="7"/>
       <c r="J143" s="6">
@@ -15379,25 +15652,25 @@
         <v>5</v>
       </c>
       <c r="B144" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="C144" t="s">
         <v>762</v>
       </c>
-      <c r="C144" t="s">
+      <c r="D144" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>757</v>
+      </c>
+      <c r="F144" s="7" t="s">
         <v>763</v>
       </c>
-      <c r="D144" s="7" t="s">
-        <v>757</v>
-      </c>
-      <c r="E144" s="7" t="s">
-        <v>758</v>
-      </c>
-      <c r="F144" s="7" t="s">
+      <c r="G144" s="7" t="s">
         <v>764</v>
       </c>
-      <c r="G144" s="7" t="s">
+      <c r="H144" s="7" t="s">
         <v>765</v>
-      </c>
-      <c r="H144" s="7" t="s">
-        <v>766</v>
       </c>
       <c r="I144" s="7"/>
       <c r="J144" s="6">
@@ -15417,10 +15690,10 @@
         <v>6</v>
       </c>
       <c r="B145" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="C145" t="s">
         <v>767</v>
-      </c>
-      <c r="C145" t="s">
-        <v>768</v>
       </c>
       <c r="D145" s="7" t="s">
         <v>276</v>
@@ -15429,13 +15702,13 @@
         <v>204</v>
       </c>
       <c r="F145" s="7" t="s">
+        <v>768</v>
+      </c>
+      <c r="G145" s="7" t="s">
         <v>769</v>
       </c>
-      <c r="G145" s="7" t="s">
+      <c r="H145" s="7" t="s">
         <v>770</v>
-      </c>
-      <c r="H145" s="7" t="s">
-        <v>771</v>
       </c>
       <c r="I145" s="7"/>
       <c r="J145" s="6">
@@ -15455,10 +15728,10 @@
         <v>6</v>
       </c>
       <c r="B146" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="C146" t="s">
         <v>772</v>
-      </c>
-      <c r="C146" t="s">
-        <v>773</v>
       </c>
       <c r="D146" s="7" t="s">
         <v>219</v>
@@ -15467,13 +15740,13 @@
         <v>204</v>
       </c>
       <c r="F146" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="G146" s="7" t="s">
         <v>774</v>
       </c>
-      <c r="G146" s="7" t="s">
+      <c r="H146" s="7" t="s">
         <v>775</v>
-      </c>
-      <c r="H146" s="7" t="s">
-        <v>776</v>
       </c>
       <c r="I146" s="7"/>
       <c r="J146" s="6">
@@ -15493,25 +15766,25 @@
         <v>6</v>
       </c>
       <c r="B147" s="7" t="s">
+        <v>776</v>
+      </c>
+      <c r="C147" t="s">
         <v>777</v>
       </c>
-      <c r="C147" t="s">
-        <v>778</v>
-      </c>
       <c r="D147" s="7" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E147" s="7" t="s">
         <v>204</v>
       </c>
       <c r="F147" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="G147" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="H147" s="7" t="s">
         <v>779</v>
-      </c>
-      <c r="G147" s="7" t="s">
-        <v>753</v>
-      </c>
-      <c r="H147" s="7" t="s">
-        <v>780</v>
       </c>
       <c r="I147" s="7"/>
       <c r="J147" s="6">
@@ -15531,10 +15804,10 @@
         <v>6</v>
       </c>
       <c r="B148" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="C148" t="s">
         <v>781</v>
-      </c>
-      <c r="C148" t="s">
-        <v>782</v>
       </c>
       <c r="D148" s="7" t="s">
         <v>212</v>
@@ -15543,13 +15816,13 @@
         <v>204</v>
       </c>
       <c r="F148" s="7" t="s">
+        <v>782</v>
+      </c>
+      <c r="G148" s="7" t="s">
         <v>783</v>
       </c>
-      <c r="G148" s="7" t="s">
+      <c r="H148" s="7" t="s">
         <v>784</v>
-      </c>
-      <c r="H148" s="7" t="s">
-        <v>785</v>
       </c>
       <c r="I148" s="7"/>
       <c r="J148" s="6">
@@ -15566,13 +15839,13 @@
     </row>
     <row r="149" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C149" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D149" s="7" t="s">
         <v>276</v>
@@ -15581,13 +15854,13 @@
         <v>204</v>
       </c>
       <c r="F149" s="7" t="s">
+        <v>787</v>
+      </c>
+      <c r="G149" s="7" t="s">
         <v>788</v>
       </c>
-      <c r="G149" s="7" t="s">
+      <c r="H149" s="7" t="s">
         <v>789</v>
-      </c>
-      <c r="H149" s="7" t="s">
-        <v>790</v>
       </c>
       <c r="I149" s="7"/>
       <c r="J149" s="6">
@@ -15604,28 +15877,28 @@
     </row>
     <row r="150" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B150" s="7" t="s">
+        <v>790</v>
+      </c>
+      <c r="C150" t="s">
         <v>791</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D150" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="E150" s="7" t="s">
         <v>792</v>
       </c>
-      <c r="D150" s="7" t="s">
-        <v>757</v>
-      </c>
-      <c r="E150" s="7" t="s">
+      <c r="F150" s="7" t="s">
         <v>793</v>
       </c>
-      <c r="F150" s="7" t="s">
+      <c r="G150" s="7" t="s">
         <v>794</v>
       </c>
-      <c r="G150" s="7" t="s">
+      <c r="H150" s="7" t="s">
         <v>795</v>
-      </c>
-      <c r="H150" s="7" t="s">
-        <v>796</v>
       </c>
       <c r="I150" s="7"/>
       <c r="J150" s="6">
@@ -15642,13 +15915,13 @@
     </row>
     <row r="151" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="B151" s="7" t="s">
         <v>797</v>
       </c>
-      <c r="B151" s="7" t="s">
+      <c r="C151" t="s">
         <v>798</v>
-      </c>
-      <c r="C151" t="s">
-        <v>799</v>
       </c>
       <c r="D151" s="7" t="s">
         <v>276</v>
@@ -15657,13 +15930,13 @@
         <v>204</v>
       </c>
       <c r="F151" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="G151" s="7" t="s">
         <v>800</v>
       </c>
-      <c r="G151" s="7" t="s">
+      <c r="H151" s="7" t="s">
         <v>801</v>
-      </c>
-      <c r="H151" s="7" t="s">
-        <v>802</v>
       </c>
       <c r="I151" s="7"/>
       <c r="J151" s="6">
@@ -15680,28 +15953,28 @@
     </row>
     <row r="152" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B152" s="7" t="s">
+        <v>802</v>
+      </c>
+      <c r="C152" t="s">
         <v>803</v>
-      </c>
-      <c r="C152" t="s">
-        <v>804</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>219</v>
       </c>
       <c r="E152" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="F152" s="7" t="s">
         <v>805</v>
       </c>
-      <c r="F152" s="7" t="s">
+      <c r="G152" s="7" t="s">
         <v>806</v>
       </c>
-      <c r="G152" s="7" t="s">
+      <c r="H152" s="7" t="s">
         <v>807</v>
-      </c>
-      <c r="H152" s="7" t="s">
-        <v>808</v>
       </c>
       <c r="I152" s="7"/>
       <c r="J152" s="6">
@@ -15718,13 +15991,13 @@
     </row>
     <row r="153" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="B153" s="7" t="s">
         <v>809</v>
       </c>
-      <c r="B153" s="7" t="s">
+      <c r="C153" t="s">
         <v>810</v>
-      </c>
-      <c r="C153" t="s">
-        <v>811</v>
       </c>
       <c r="D153" s="7" t="s">
         <v>276</v>
@@ -15733,13 +16006,13 @@
         <v>204</v>
       </c>
       <c r="F153" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="G153" s="7" t="s">
         <v>812</v>
       </c>
-      <c r="G153" s="7" t="s">
+      <c r="H153" s="7" t="s">
         <v>813</v>
-      </c>
-      <c r="H153" s="7" t="s">
-        <v>814</v>
       </c>
       <c r="I153" s="7"/>
       <c r="J153" s="6">
@@ -15756,28 +16029,28 @@
     </row>
     <row r="154" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B154" s="7" t="s">
+        <v>814</v>
+      </c>
+      <c r="C154" t="s">
         <v>815</v>
-      </c>
-      <c r="C154" t="s">
-        <v>816</v>
       </c>
       <c r="D154" s="7" t="s">
         <v>219</v>
       </c>
       <c r="E154" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="F154" s="7" t="s">
         <v>817</v>
       </c>
-      <c r="F154" s="7" t="s">
+      <c r="G154" s="7" t="s">
         <v>818</v>
       </c>
-      <c r="G154" s="7" t="s">
+      <c r="H154" s="7" t="s">
         <v>819</v>
-      </c>
-      <c r="H154" s="7" t="s">
-        <v>820</v>
       </c>
       <c r="I154" s="7"/>
       <c r="J154" s="6">
@@ -15792,323 +16065,539 @@
       <c r="M154" s="7"/>
       <c r="N154" s="7"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A155" s="7"/>
-      <c r="B155" s="7"/>
-      <c r="C155" s="7"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7"/>
-      <c r="G155" s="7"/>
-      <c r="H155" s="7"/>
-      <c r="I155" s="7"/>
-      <c r="J155" s="3"/>
-      <c r="K155" s="3"/>
-      <c r="L155" s="7"/>
+    <row r="155" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="10" t="s">
+        <v>827</v>
+      </c>
+      <c r="B155" s="10" t="s">
+        <v>828</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="D155" s="10" t="s">
+        <v>830</v>
+      </c>
+      <c r="E155" s="10" t="s">
+        <v>831</v>
+      </c>
+      <c r="F155" s="7" t="s">
+        <v>832</v>
+      </c>
+      <c r="G155" s="10" t="s">
+        <v>896</v>
+      </c>
+      <c r="H155" s="10" t="s">
+        <v>835</v>
+      </c>
+      <c r="I155" s="10"/>
+      <c r="J155" s="13">
+        <v>45954</v>
+      </c>
+      <c r="K155" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="L155" s="14" t="s">
+        <v>41</v>
+      </c>
       <c r="M155" s="7"/>
       <c r="N155" s="7"/>
     </row>
     <row r="156" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="7"/>
-      <c r="B156" s="7"/>
-      <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
-      <c r="F156" s="7"/>
-      <c r="G156" s="7"/>
-      <c r="H156" s="7"/>
-      <c r="I156" s="7"/>
-      <c r="J156" s="3"/>
-      <c r="K156" s="3"/>
-      <c r="L156" s="7"/>
+      <c r="A156" s="10"/>
+      <c r="B156" s="10"/>
+      <c r="C156" s="10"/>
+      <c r="D156" s="10"/>
+      <c r="E156" s="10"/>
+      <c r="F156" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="G156" s="10"/>
+      <c r="H156" s="10"/>
+      <c r="I156" s="10"/>
+      <c r="J156" s="13"/>
+      <c r="K156" s="12"/>
+      <c r="L156" s="15"/>
       <c r="M156" s="7"/>
       <c r="N156" s="7"/>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A157" s="7"/>
-      <c r="B157" s="7"/>
-      <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="7"/>
-      <c r="G157" s="7"/>
-      <c r="H157" s="7"/>
-      <c r="I157" s="7"/>
-      <c r="J157" s="3"/>
-      <c r="K157" s="3"/>
-      <c r="L157" s="7"/>
+      <c r="A157" s="10"/>
+      <c r="B157" s="10"/>
+      <c r="C157" s="10"/>
+      <c r="D157" s="10"/>
+      <c r="E157" s="10"/>
+      <c r="F157" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="G157" s="10"/>
+      <c r="H157" s="10"/>
+      <c r="I157" s="10"/>
+      <c r="J157" s="13"/>
+      <c r="K157" s="12"/>
+      <c r="L157" s="15"/>
       <c r="M157" s="7"/>
       <c r="N157" s="7"/>
     </row>
     <row r="158" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="7"/>
-      <c r="B158" s="7"/>
-      <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
-      <c r="F158" s="7"/>
-      <c r="G158" s="7"/>
-      <c r="H158" s="7"/>
-      <c r="I158" s="7"/>
-      <c r="J158" s="3"/>
-      <c r="K158" s="3"/>
-      <c r="L158" s="7"/>
+      <c r="A158" s="10" t="s">
+        <v>836</v>
+      </c>
+      <c r="B158" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>838</v>
+      </c>
+      <c r="D158" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E158" s="10" t="s">
+        <v>839</v>
+      </c>
+      <c r="F158" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="G158" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="H158" s="10" t="s">
+        <v>844</v>
+      </c>
+      <c r="I158" s="10"/>
+      <c r="J158" s="13">
+        <v>45954</v>
+      </c>
+      <c r="K158" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="L158" s="16" t="s">
+        <v>41</v>
+      </c>
       <c r="M158" s="7"/>
       <c r="N158" s="7"/>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A159" s="7"/>
-      <c r="B159" s="7"/>
-      <c r="C159" s="7"/>
-      <c r="D159" s="7"/>
-      <c r="E159" s="7"/>
-      <c r="F159" s="7"/>
-      <c r="G159" s="7"/>
-      <c r="H159" s="7"/>
-      <c r="I159" s="7"/>
-      <c r="J159" s="3"/>
-      <c r="K159" s="3"/>
-      <c r="L159" s="7"/>
+      <c r="A159" s="10"/>
+      <c r="B159" s="10"/>
+      <c r="C159" s="10"/>
+      <c r="D159" s="10"/>
+      <c r="E159" s="10"/>
+      <c r="F159" s="7" t="s">
+        <v>841</v>
+      </c>
+      <c r="G159" s="10"/>
+      <c r="H159" s="10"/>
+      <c r="I159" s="10"/>
+      <c r="J159" s="13"/>
+      <c r="K159" s="12"/>
+      <c r="L159" s="16"/>
       <c r="M159" s="7"/>
       <c r="N159" s="7"/>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A160" s="7"/>
-      <c r="B160" s="7"/>
-      <c r="C160" s="7"/>
-      <c r="D160" s="7"/>
-      <c r="E160" s="7"/>
-      <c r="F160" s="7"/>
-      <c r="G160" s="7"/>
-      <c r="H160" s="7"/>
-      <c r="I160" s="7"/>
-      <c r="J160" s="3"/>
-      <c r="K160" s="3"/>
-      <c r="L160" s="7"/>
+      <c r="A160" s="10"/>
+      <c r="B160" s="10"/>
+      <c r="C160" s="10"/>
+      <c r="D160" s="10"/>
+      <c r="E160" s="10"/>
+      <c r="F160" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="G160" s="10"/>
+      <c r="H160" s="10"/>
+      <c r="I160" s="10"/>
+      <c r="J160" s="13"/>
+      <c r="K160" s="12"/>
+      <c r="L160" s="16"/>
       <c r="M160" s="7"/>
       <c r="N160" s="7"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A161" s="7"/>
-      <c r="B161" s="7"/>
-      <c r="C161" s="7"/>
-      <c r="D161" s="7"/>
-      <c r="E161" s="7"/>
-      <c r="F161" s="7"/>
-      <c r="G161" s="7"/>
-      <c r="H161" s="7"/>
-      <c r="I161" s="7"/>
-      <c r="J161" s="3"/>
-      <c r="K161" s="3"/>
-      <c r="L161" s="7"/>
+    <row r="161" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="10" t="s">
+        <v>836</v>
+      </c>
+      <c r="B161" s="10" t="s">
+        <v>845</v>
+      </c>
+      <c r="C161" s="10" t="s">
+        <v>846</v>
+      </c>
+      <c r="D161" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="E161" s="10" t="s">
+        <v>847</v>
+      </c>
+      <c r="F161" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="G161" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="H161" s="10" t="s">
+        <v>849</v>
+      </c>
+      <c r="I161" s="10"/>
+      <c r="J161" s="13">
+        <v>45954</v>
+      </c>
+      <c r="K161" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="L161" s="16" t="s">
+        <v>41</v>
+      </c>
       <c r="M161" s="7"/>
       <c r="N161" s="7"/>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A162" s="7"/>
-      <c r="B162" s="7"/>
-      <c r="C162" s="7"/>
-      <c r="D162" s="7"/>
-      <c r="E162" s="7"/>
-      <c r="F162" s="7"/>
-      <c r="G162" s="7"/>
-      <c r="H162" s="7"/>
-      <c r="I162" s="7"/>
-      <c r="J162" s="3"/>
-      <c r="K162" s="3"/>
-      <c r="L162" s="7"/>
+      <c r="A162" s="10"/>
+      <c r="B162" s="10"/>
+      <c r="C162" s="10"/>
+      <c r="D162" s="10"/>
+      <c r="E162" s="10"/>
+      <c r="F162" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="G162" s="10"/>
+      <c r="H162" s="10"/>
+      <c r="I162" s="10"/>
+      <c r="J162" s="13"/>
+      <c r="K162" s="12"/>
+      <c r="L162" s="16"/>
       <c r="M162" s="7"/>
       <c r="N162" s="7"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A163" s="7"/>
-      <c r="B163" s="7"/>
-      <c r="C163" s="7"/>
-      <c r="D163" s="7"/>
-      <c r="E163" s="7"/>
-      <c r="F163" s="7"/>
-      <c r="G163" s="7"/>
-      <c r="H163" s="7"/>
-      <c r="I163" s="7"/>
-      <c r="J163" s="3"/>
-      <c r="K163" s="3"/>
-      <c r="L163" s="7"/>
+    <row r="163" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="10" t="s">
+        <v>850</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C163" s="10" t="s">
+        <v>851</v>
+      </c>
+      <c r="D163" s="10" t="s">
+        <v>852</v>
+      </c>
+      <c r="E163" s="10" t="s">
+        <v>853</v>
+      </c>
+      <c r="F163" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="G163" s="10"/>
+      <c r="H163" s="10" t="s">
+        <v>856</v>
+      </c>
+      <c r="I163" s="10"/>
+      <c r="J163" s="13">
+        <v>45954</v>
+      </c>
+      <c r="K163" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="L163" s="16" t="s">
+        <v>41</v>
+      </c>
       <c r="M163" s="7"/>
       <c r="N163" s="7"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A164" s="7"/>
-      <c r="B164" s="7"/>
-      <c r="C164" s="7"/>
-      <c r="D164" s="7"/>
-      <c r="E164" s="7"/>
-      <c r="F164" s="7"/>
-      <c r="G164" s="7"/>
-      <c r="H164" s="7"/>
-      <c r="I164" s="7"/>
-      <c r="J164" s="3"/>
-      <c r="K164" s="3"/>
-      <c r="L164" s="7"/>
+    <row r="164" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A164" s="10"/>
+      <c r="B164" s="10"/>
+      <c r="C164" s="10"/>
+      <c r="D164" s="10"/>
+      <c r="E164" s="10"/>
+      <c r="F164" s="7" t="s">
+        <v>855</v>
+      </c>
+      <c r="G164" s="10"/>
+      <c r="H164" s="10"/>
+      <c r="I164" s="10"/>
+      <c r="J164" s="13"/>
+      <c r="K164" s="12"/>
+      <c r="L164" s="16"/>
       <c r="M164" s="7"/>
       <c r="N164" s="7"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A165" s="7"/>
-      <c r="B165" s="7"/>
-      <c r="C165" s="7"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
-      <c r="F165" s="7"/>
-      <c r="G165" s="7"/>
-      <c r="H165" s="7"/>
-      <c r="I165" s="7"/>
-      <c r="J165" s="3"/>
-      <c r="K165" s="3"/>
-      <c r="L165" s="7"/>
+    <row r="165" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="10" t="s">
+        <v>857</v>
+      </c>
+      <c r="B165" s="10" t="s">
+        <v>858</v>
+      </c>
+      <c r="C165" s="10" t="s">
+        <v>859</v>
+      </c>
+      <c r="D165" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E165" s="10" t="s">
+        <v>860</v>
+      </c>
+      <c r="F165" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="G165" s="10"/>
+      <c r="H165" s="10" t="s">
+        <v>864</v>
+      </c>
+      <c r="I165" s="10"/>
+      <c r="J165" s="13">
+        <v>45957</v>
+      </c>
+      <c r="K165" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="L165" s="18" t="s">
+        <v>147</v>
+      </c>
       <c r="M165" s="7"/>
       <c r="N165" s="7"/>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A166" s="7"/>
-      <c r="B166" s="7"/>
-      <c r="C166" s="7"/>
-      <c r="D166" s="7"/>
-      <c r="E166" s="7"/>
-      <c r="F166" s="7"/>
-      <c r="G166" s="7"/>
-      <c r="H166" s="7"/>
-      <c r="I166" s="7"/>
-      <c r="J166" s="3"/>
-      <c r="K166" s="3"/>
-      <c r="L166" s="7"/>
+      <c r="A166" s="10"/>
+      <c r="B166" s="10"/>
+      <c r="C166" s="10"/>
+      <c r="D166" s="10"/>
+      <c r="E166" s="10"/>
+      <c r="F166" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="G166" s="10"/>
+      <c r="H166" s="10"/>
+      <c r="I166" s="10"/>
+      <c r="J166" s="13"/>
+      <c r="K166" s="12"/>
+      <c r="L166" s="18"/>
       <c r="M166" s="7"/>
       <c r="N166" s="7"/>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A167" s="7"/>
-      <c r="B167" s="7"/>
-      <c r="C167" s="7"/>
-      <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7"/>
-      <c r="G167" s="7"/>
-      <c r="H167" s="7"/>
-      <c r="I167" s="7"/>
-      <c r="J167" s="3"/>
-      <c r="K167" s="3"/>
-      <c r="L167" s="7"/>
+      <c r="A167" s="10"/>
+      <c r="B167" s="10"/>
+      <c r="C167" s="10"/>
+      <c r="D167" s="10"/>
+      <c r="E167" s="10"/>
+      <c r="F167" s="7" t="s">
+        <v>863</v>
+      </c>
+      <c r="G167" s="10"/>
+      <c r="H167" s="10"/>
+      <c r="I167" s="10"/>
+      <c r="J167" s="13"/>
+      <c r="K167" s="12"/>
+      <c r="L167" s="18"/>
       <c r="M167" s="7"/>
       <c r="N167" s="7"/>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A168" s="7"/>
-      <c r="B168" s="7"/>
-      <c r="C168" s="7"/>
-      <c r="D168" s="7"/>
-      <c r="E168" s="7"/>
-      <c r="F168" s="7"/>
-      <c r="G168" s="7"/>
-      <c r="H168" s="7"/>
-      <c r="I168" s="7"/>
-      <c r="J168" s="3"/>
-      <c r="K168" s="3"/>
-      <c r="L168" s="7"/>
+      <c r="A168" s="10" t="s">
+        <v>865</v>
+      </c>
+      <c r="B168" s="10" t="s">
+        <v>866</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>867</v>
+      </c>
+      <c r="D168" s="10" t="s">
+        <v>868</v>
+      </c>
+      <c r="E168" s="10" t="s">
+        <v>869</v>
+      </c>
+      <c r="F168" s="7" t="s">
+        <v>870</v>
+      </c>
+      <c r="G168" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="H168" s="10" t="s">
+        <v>872</v>
+      </c>
+      <c r="I168" s="10"/>
+      <c r="J168" s="13">
+        <v>45957</v>
+      </c>
+      <c r="K168" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="L168" s="16" t="s">
+        <v>41</v>
+      </c>
       <c r="M168" s="7"/>
       <c r="N168" s="7"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A169" s="7"/>
-      <c r="B169" s="7"/>
-      <c r="C169" s="7"/>
-      <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
-      <c r="F169" s="7"/>
-      <c r="G169" s="7"/>
-      <c r="H169" s="7"/>
-      <c r="I169" s="7"/>
-      <c r="J169" s="3"/>
-      <c r="K169" s="3"/>
-      <c r="L169" s="7"/>
+    <row r="169" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A169" s="10"/>
+      <c r="B169" s="10"/>
+      <c r="C169" s="10"/>
+      <c r="D169" s="10"/>
+      <c r="E169" s="10"/>
+      <c r="F169" s="7" t="s">
+        <v>871</v>
+      </c>
+      <c r="G169" s="10"/>
+      <c r="H169" s="10"/>
+      <c r="I169" s="10"/>
+      <c r="J169" s="13"/>
+      <c r="K169" s="12"/>
+      <c r="L169" s="16"/>
       <c r="M169" s="7"/>
       <c r="N169" s="7"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A170" s="7"/>
-      <c r="B170" s="7"/>
-      <c r="C170" s="7"/>
-      <c r="D170" s="7"/>
-      <c r="E170" s="7"/>
-      <c r="F170" s="7"/>
-      <c r="G170" s="7"/>
-      <c r="H170" s="7"/>
-      <c r="I170" s="7"/>
-      <c r="J170" s="3"/>
-      <c r="K170" s="3"/>
-      <c r="L170" s="7"/>
+    <row r="170" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A170" s="10" t="s">
+        <v>873</v>
+      </c>
+      <c r="B170" s="10" t="s">
+        <v>874</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>875</v>
+      </c>
+      <c r="D170" s="10" t="s">
+        <v>876</v>
+      </c>
+      <c r="E170" s="10" t="s">
+        <v>877</v>
+      </c>
+      <c r="F170" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="G170" s="10"/>
+      <c r="H170" s="10" t="s">
+        <v>880</v>
+      </c>
+      <c r="I170" s="10"/>
+      <c r="J170" s="13">
+        <v>45957</v>
+      </c>
+      <c r="K170" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="L170" s="18" t="s">
+        <v>147</v>
+      </c>
       <c r="M170" s="7"/>
       <c r="N170" s="7"/>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A171" s="7"/>
-      <c r="B171" s="7"/>
-      <c r="C171" s="7"/>
-      <c r="D171" s="7"/>
-      <c r="E171" s="7"/>
-      <c r="F171" s="7"/>
-      <c r="G171" s="7"/>
-      <c r="H171" s="7"/>
-      <c r="I171" s="7"/>
-      <c r="J171" s="3"/>
-      <c r="K171" s="3"/>
-      <c r="L171" s="7"/>
+      <c r="A171" s="10"/>
+      <c r="B171" s="10"/>
+      <c r="C171" s="10"/>
+      <c r="D171" s="10"/>
+      <c r="E171" s="10"/>
+      <c r="F171" s="7" t="s">
+        <v>879</v>
+      </c>
+      <c r="G171" s="10"/>
+      <c r="H171" s="10"/>
+      <c r="I171" s="10"/>
+      <c r="J171" s="13"/>
+      <c r="K171" s="12"/>
+      <c r="L171" s="18"/>
       <c r="M171" s="7"/>
       <c r="N171" s="7"/>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A172" s="7"/>
-      <c r="B172" s="7"/>
-      <c r="C172" s="7"/>
-      <c r="D172" s="7"/>
-      <c r="E172" s="7"/>
-      <c r="F172" s="7"/>
-      <c r="G172" s="7"/>
-      <c r="H172" s="7"/>
-      <c r="I172" s="7"/>
-      <c r="J172" s="3"/>
-      <c r="K172" s="3"/>
-      <c r="L172" s="7"/>
-      <c r="M172" s="7"/>
+      <c r="A172" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B172" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="C172" s="10" t="s">
+        <v>883</v>
+      </c>
+      <c r="D172" s="10" t="s">
+        <v>881</v>
+      </c>
+      <c r="E172" s="10" t="s">
+        <v>884</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="G172" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="H172" s="10" t="s">
+        <v>887</v>
+      </c>
+      <c r="I172" s="10"/>
+      <c r="J172" s="13">
+        <v>45957</v>
+      </c>
+      <c r="K172" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="L172" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="M172" s="7" t="s">
+        <v>897</v>
+      </c>
       <c r="N172" s="7"/>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A173" s="7"/>
-      <c r="B173" s="7"/>
-      <c r="C173" s="7"/>
-      <c r="D173" s="7"/>
-      <c r="E173" s="7"/>
-      <c r="F173" s="7"/>
-      <c r="G173" s="7"/>
-      <c r="H173" s="7"/>
-      <c r="I173" s="7"/>
-      <c r="J173" s="3"/>
-      <c r="K173" s="3"/>
-      <c r="L173" s="7"/>
+      <c r="A173" s="10"/>
+      <c r="B173" s="10"/>
+      <c r="C173" s="10"/>
+      <c r="D173" s="10"/>
+      <c r="E173" s="10"/>
+      <c r="F173" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="G173" s="10"/>
+      <c r="H173" s="10"/>
+      <c r="I173" s="10"/>
+      <c r="J173" s="13"/>
+      <c r="K173" s="12"/>
+      <c r="L173" s="19"/>
       <c r="M173" s="7"/>
       <c r="N173" s="7"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A174" s="7"/>
-      <c r="B174" s="7"/>
-      <c r="C174" s="7"/>
-      <c r="D174" s="7"/>
-      <c r="E174" s="7"/>
-      <c r="F174" s="7"/>
-      <c r="G174" s="7"/>
-      <c r="H174" s="7"/>
+    <row r="174" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="7" t="s">
+        <v>888</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>889</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="F174" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="G174" s="7" t="s">
+        <v>843</v>
+      </c>
+      <c r="H174" s="7" t="s">
+        <v>894</v>
+      </c>
       <c r="I174" s="7"/>
-      <c r="J174" s="3"/>
-      <c r="K174" s="3"/>
-      <c r="L174" s="7"/>
+      <c r="J174" s="6">
+        <v>45957</v>
+      </c>
+      <c r="K174" s="11" t="s">
+        <v>895</v>
+      </c>
+      <c r="L174" s="19" t="s">
+        <v>147</v>
+      </c>
       <c r="M174" s="7"/>
       <c r="N174" s="7"/>
     </row>
@@ -16125,8 +16614,6 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
       <c r="L175" s="7"/>
-      <c r="M175" s="7"/>
-      <c r="N175" s="7"/>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" s="7"/>
@@ -16141,8 +16628,6 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
       <c r="L176" s="7"/>
-      <c r="M176" s="7"/>
-      <c r="N176" s="7"/>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="7"/>
@@ -16169,7 +16654,7 @@
       <c r="H178" s="7"/>
       <c r="I178" s="7"/>
       <c r="J178" s="3"/>
-      <c r="K178" s="3"/>
+      <c r="K178" s="7"/>
       <c r="L178" s="7"/>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
@@ -16197,11 +16682,10 @@
       <c r="H180" s="7"/>
       <c r="I180" s="7"/>
       <c r="J180" s="3"/>
-      <c r="K180" s="7"/>
+      <c r="K180" s="3"/>
       <c r="L180" s="7"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A181" s="7"/>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
@@ -16215,7 +16699,6 @@
       <c r="L181" s="7"/>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A182" s="7"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
@@ -16436,33 +16919,96 @@
       <c r="K198" s="3"/>
       <c r="L198" s="7"/>
     </row>
-    <row r="199" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B199" s="7"/>
-      <c r="C199" s="7"/>
-      <c r="D199" s="7"/>
-      <c r="E199" s="7"/>
-      <c r="F199" s="7"/>
-      <c r="G199" s="7"/>
-      <c r="H199" s="7"/>
-      <c r="I199" s="7"/>
-      <c r="J199" s="3"/>
-      <c r="K199" s="3"/>
-      <c r="L199" s="7"/>
-    </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B200" s="7"/>
-      <c r="C200" s="7"/>
-      <c r="D200" s="7"/>
-      <c r="E200" s="7"/>
-      <c r="F200" s="7"/>
-      <c r="G200" s="7"/>
-      <c r="H200" s="7"/>
-      <c r="I200" s="7"/>
-      <c r="J200" s="3"/>
-      <c r="K200" s="3"/>
-      <c r="L200" s="7"/>
-    </row>
   </sheetData>
+  <mergeCells count="87">
+    <mergeCell ref="L155:L157"/>
+    <mergeCell ref="L158:L160"/>
+    <mergeCell ref="K172:K173"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="C172:C173"/>
+    <mergeCell ref="D172:D173"/>
+    <mergeCell ref="E172:E173"/>
+    <mergeCell ref="G172:G173"/>
+    <mergeCell ref="H172:H173"/>
+    <mergeCell ref="I172:I173"/>
+    <mergeCell ref="H170:H171"/>
+    <mergeCell ref="I170:I171"/>
+    <mergeCell ref="J170:J171"/>
+    <mergeCell ref="K170:K171"/>
+    <mergeCell ref="L170:L171"/>
+    <mergeCell ref="I168:I169"/>
+    <mergeCell ref="J168:J169"/>
+    <mergeCell ref="K168:K169"/>
+    <mergeCell ref="L168:L169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="C170:C171"/>
+    <mergeCell ref="D170:D171"/>
+    <mergeCell ref="E170:E171"/>
+    <mergeCell ref="G170:G171"/>
+    <mergeCell ref="J165:J167"/>
+    <mergeCell ref="K165:K167"/>
+    <mergeCell ref="L165:L167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="C168:C169"/>
+    <mergeCell ref="D168:D169"/>
+    <mergeCell ref="E168:E169"/>
+    <mergeCell ref="G168:G169"/>
+    <mergeCell ref="H168:H169"/>
+    <mergeCell ref="K163:K164"/>
+    <mergeCell ref="L163:L164"/>
+    <mergeCell ref="A165:A167"/>
+    <mergeCell ref="B165:B167"/>
+    <mergeCell ref="C165:C167"/>
+    <mergeCell ref="D165:D167"/>
+    <mergeCell ref="E165:E167"/>
+    <mergeCell ref="G165:G167"/>
+    <mergeCell ref="H165:H167"/>
+    <mergeCell ref="I165:I167"/>
+    <mergeCell ref="L161:L162"/>
+    <mergeCell ref="A163:A164"/>
+    <mergeCell ref="B163:B164"/>
+    <mergeCell ref="C163:C164"/>
+    <mergeCell ref="D163:D164"/>
+    <mergeCell ref="E163:E164"/>
+    <mergeCell ref="G163:G164"/>
+    <mergeCell ref="H163:H164"/>
+    <mergeCell ref="I163:I164"/>
+    <mergeCell ref="J163:J164"/>
+    <mergeCell ref="E161:E162"/>
+    <mergeCell ref="G161:G162"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="J161:J162"/>
+    <mergeCell ref="K161:K162"/>
+    <mergeCell ref="G158:G160"/>
+    <mergeCell ref="H158:H160"/>
+    <mergeCell ref="I158:I160"/>
+    <mergeCell ref="J158:J160"/>
+    <mergeCell ref="K158:K160"/>
+    <mergeCell ref="H155:H157"/>
+    <mergeCell ref="I155:I157"/>
+    <mergeCell ref="J155:J157"/>
+    <mergeCell ref="K155:K157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="B158:B160"/>
+    <mergeCell ref="C158:C160"/>
+    <mergeCell ref="D158:D160"/>
+    <mergeCell ref="E158:E160"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="B155:B157"/>
+    <mergeCell ref="C155:C157"/>
+    <mergeCell ref="D155:D157"/>
+    <mergeCell ref="E155:E157"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="C161:C162"/>
+    <mergeCell ref="D161:D162"/>
+    <mergeCell ref="J172:J173"/>
+    <mergeCell ref="G155:G157"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L3:L154">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
@@ -16475,7 +17021,7 @@
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L177:L181 K180 L183:L200">
+  <conditionalFormatting sqref="L175:L179 K178 L181:L198">
     <cfRule type="cellIs" dxfId="2" priority="34" operator="equal">
       <formula>"PENDING"</formula>
     </cfRule>
@@ -16487,10 +17033,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L183:L200 K180 L177:L181 L3:L154" xr:uid="{1E8D2D6D-4EE7-40E2-A622-3458BDCF08AD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L181:L198 K178 L175:L179 L3:L154" xr:uid="{1E8D2D6D-4EE7-40E2-A622-3458BDCF08AD}">
       <formula1>"PASS,PENDING,FAIL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A182" xr:uid="{F4675041-A1B8-4B65-822E-23AD6AB864A0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A175:A180 A3:A154" xr:uid="{F4675041-A1B8-4B65-822E-23AD6AB864A0}">
       <formula1>INDIRECT("Modulos[MODULOS]")</formula1>
     </dataValidation>
   </dataValidations>
@@ -16527,10 +17073,10 @@
   <sheetData>
     <row r="2" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>821</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>822</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -16538,7 +17084,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>130</v>
@@ -16550,12 +17096,12 @@
         <v>147</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -16607,7 +17153,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -16624,10 +17170,10 @@
     </row>
     <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -16656,7 +17202,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B28" s="1">
         <v>4</v>
@@ -16679,9 +17225,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16823,19 +17372,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CABA5C2-04D8-4DC5-BBFB-FF9AC004B268}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16859,9 +17404,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CABA5C2-04D8-4DC5-BBFB-FF9AC004B268}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Modelo Test Plan.xlsx
+++ b/Modelo Test Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Downloads\CoderBits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A7AC5B-A5E8-43A3-B070-959E1433C1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{583EBDDA-4325-4542-AB66-E04CB91D7A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{96765352-7388-4C61-94B8-5077301D3254}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="876">
   <si>
     <t>MODULOS</t>
   </si>
@@ -2962,45 +2962,15 @@
     <t>Usuario previamente eliminado del sistema</t>
   </si>
   <si>
-    <t>1. Acceder al módulo de personal</t>
-  </si>
-  <si>
-    <t>2. Filtrar por usuarios eliminados</t>
-  </si>
-  <si>
-    <t>3. Seleccionar “Restaurar”</t>
-  </si>
-  <si>
     <t>El usuario se restaura y reaparece en la lista activa</t>
   </si>
   <si>
     <t>Monitoreo de Red</t>
   </si>
   <si>
-    <t>Activación del monitoreo de red</t>
-  </si>
-  <si>
-    <t>Validar que el sistema inicie la captura de tráfico al activar el monitoreo</t>
-  </si>
-  <si>
-    <t>Backend y sniffer activos</t>
-  </si>
-  <si>
-    <t>1. Ir al panel de monitoreo</t>
-  </si>
-  <si>
-    <t>2. Presionar “Activar Monitoreo”</t>
-  </si>
-  <si>
-    <t>3. Verificar estado</t>
-  </si>
-  <si>
     <t>—</t>
   </si>
   <si>
-    <t>El sistema muestra estado “Monitoreo Activo” y comienza la captura</t>
-  </si>
-  <si>
     <t>Desactivación del monitoreo de red</t>
   </si>
   <si>
@@ -3010,9 +2980,6 @@
     <t>Monitoreo activo</t>
   </si>
   <si>
-    <t>2. Presionar “Detener Monitoreo”</t>
-  </si>
-  <si>
     <t>El sistema cambia a “Monitoreo Inactivo” y detiene la captura</t>
   </si>
   <si>
@@ -3028,12 +2995,6 @@
     <t>Monitoreo activo e IA cargada</t>
   </si>
   <si>
-    <t>1. Simular tráfico malicioso</t>
-  </si>
-  <si>
-    <t>2. Verificar tabla de ataques registrados</t>
-  </si>
-  <si>
     <t>El ataque se almacena con IP, tipo y hora</t>
   </si>
   <si>
@@ -3049,15 +3010,6 @@
     <t>Ataques registrados disponibles</t>
   </si>
   <si>
-    <t>1. Ingresar a detalle del ataque</t>
-  </si>
-  <si>
-    <t>2. Seleccionar “Crear mitigación”</t>
-  </si>
-  <si>
-    <t>3. Guardar acción</t>
-  </si>
-  <si>
     <t>Se crea la mitigación y se asocia al ataque</t>
   </si>
   <si>
@@ -3076,12 +3028,6 @@
     <t>Backend con Channels ejecutándose</t>
   </si>
   <si>
-    <t>1. Activar monitoreo</t>
-  </si>
-  <si>
-    <t>2. Observar actualización del dashboard</t>
-  </si>
-  <si>
     <t>Datos de red se actualizan cada pocos segundos en tiempo real</t>
   </si>
   <si>
@@ -3100,12 +3046,6 @@
     <t>Modelo entrenado cargado</t>
   </si>
   <si>
-    <t>1. Enviar muestras benignas y maliciosas</t>
-  </si>
-  <si>
-    <t>2. Observar clasificación</t>
-  </si>
-  <si>
     <t>Detección precisa con etiquetas correctas</t>
   </si>
   <si>
@@ -3121,50 +3061,44 @@
     <t>Backend activo</t>
   </si>
   <si>
-    <t>1. Iniciar sesión</t>
-  </si>
-  <si>
-    <t>2. Revisar tarjetas de estadísticas</t>
-  </si>
-  <si>
     <t>Datos correctos y actualizados en interfaz</t>
   </si>
   <si>
-    <t>App Móvil</t>
-  </si>
-  <si>
-    <t>Sincronización de alertas en app móvil</t>
-  </si>
-  <si>
-    <t>Confirmar que las alertas del backend lleguen a la aplicación móvil en tiempo real</t>
-  </si>
-  <si>
-    <t>Integración / Realtime</t>
-  </si>
-  <si>
-    <t>Backend y WS activos</t>
-  </si>
-  <si>
-    <t>1. Generar alerta desde la web</t>
-  </si>
-  <si>
-    <t>Alerta aparece de inmediato en la app</t>
-  </si>
-  <si>
-    <t>Fabrizio Rollano</t>
-  </si>
-  <si>
     <t>Usuario: Fabri ROLLANO</t>
   </si>
   <si>
     <t>pe</t>
+  </si>
+  <si>
+    <t>Columna2</t>
+  </si>
+  <si>
+    <t>1. Iniciar sesión2. Revisar tarjetas de estadísticas</t>
+  </si>
+  <si>
+    <t>1. Enviar muestras benignas y maliciosas2. Observar clasificación</t>
+  </si>
+  <si>
+    <t>1. Activar monitoreo2. Observar actualización del dashboard</t>
+  </si>
+  <si>
+    <t>1. Ingresar a detalle del ataque2. Seleccionar “Crear mitigación”3. Guardar acción</t>
+  </si>
+  <si>
+    <t>1. Simular tráfico malicioso2. Verificar tabla de ataques registrados</t>
+  </si>
+  <si>
+    <t>1. Ir al panel de monitoreo2. Presionar “Detener Monitoreo”</t>
+  </si>
+  <si>
+    <t>1. Acceder al módulo de personal2. Filtrar por usuarios eliminados3. Seleccionar “Restaurar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3186,23 +3120,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="9" tint="0.79998168889431442"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3221,12 +3140,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -3241,7 +3154,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3270,42 +3183,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="68">
+  <dxfs count="51">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3365,12 +3254,6 @@
           <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -3463,40 +3346,36 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3514,7 +3393,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3524,24 +3403,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center"/>
@@ -9416,54 +9277,54 @@
     <dataField name="Cuenta de Estado (Dropdown)" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="21">
+    <format dxfId="19">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="18">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="17">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="13">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="12">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="11">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="7">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -9610,60 +9471,60 @@
     <dataField name="Cuenta de Test Case" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="37">
+    <format dxfId="35">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="34">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="33">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="32">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="31">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="30">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="27">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="26">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="25">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="24">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="23">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -9763,35 +9624,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BEF40B4A-F25E-458D-960B-8087E596FA2C}" name="Modulos" displayName="Modulos" ref="A1:A33" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BEF40B4A-F25E-458D-960B-8087E596FA2C}" name="Modulos" displayName="Modulos" ref="A1:A33" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
   <autoFilter ref="A1:A33" xr:uid="{BEF40B4A-F25E-458D-960B-8087E596FA2C}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{A3748FA1-9695-4A2D-A595-64BF200E5D1D}" name="MODULOS" dataDxfId="65"/>
+    <tableColumn id="1" xr3:uid="{A3748FA1-9695-4A2D-A595-64BF200E5D1D}" name="MODULOS" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}" name="TestPlan" displayName="TestPlan" ref="A2:N176" headerRowDxfId="64">
-  <autoFilter ref="A2:N176" xr:uid="{580B5FFA-030D-4D17-8F6D-90DDF4342984}"/>
-  <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{7F95280F-E669-4A5D-AEDF-FCAAAC81F275}" name="Modulo (Dropdown)" totalsRowLabel="Total" dataDxfId="63" totalsRowDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{E775B39B-DEB6-4123-A65F-A37EDA4383A3}" name="Test Case" dataDxfId="61" totalsRowDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{4E500E60-0861-4EF2-B610-79885F5EF7FD}" name="Descripción" dataDxfId="59" totalsRowDxfId="58"/>
-    <tableColumn id="14" xr3:uid="{D149BE2F-3E66-4E54-8D0E-BA4D69F73794}" name="Tipo/s de Prueba" dataDxfId="57" totalsRowDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{48166857-FFB0-4E91-A69A-8A057DEBB914}" name="Precondiciones" dataDxfId="55" totalsRowDxfId="54"/>
-    <tableColumn id="13" xr3:uid="{09440620-A437-484D-9292-769D8C979710}" name="Pasos a seguir" dataDxfId="53" totalsRowDxfId="52"/>
-    <tableColumn id="12" xr3:uid="{25FFAFC4-E636-4C78-8EC4-9B105CD6EC6A}" name="Datos de Prueba" dataDxfId="51" totalsRowDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{5C319188-663F-4BD1-ADB0-A93CF2F134F5}" name="Resultado Esperado" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{AC65C1EE-D520-403E-8171-F3B42F898A90}" name="Resultado Actual (Si falla)" dataDxfId="6" totalsRowDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{67BFFC43-BD7A-400D-BCA5-7641851369E7}" name="Ultima ejecución (Fecha)" dataDxfId="47" totalsRowDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{AF2F4479-94ED-46CC-8F6A-9945904E34B4}" name="Encargado de Prueba" dataDxfId="45" totalsRowDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{1AE568CA-11EA-494D-A158-098CEC0427F1}" name="Estado (Dropdown)" dataDxfId="43" totalsRowDxfId="42"/>
-    <tableColumn id="9" xr3:uid="{D7CC1236-1B17-4FEE-A062-7A6AF5789012}" name="Comentario" totalsRowFunction="count" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="17" xr3:uid="{A5678D00-4569-41AC-B6BA-DC2546DAF085}" name="Columna1" dataDxfId="39" totalsRowDxfId="38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{343BA946-EF1B-4A3B-B511-74A6334C62D3}" name="Tabla1" displayName="Tabla1" ref="A1:L162" totalsRowShown="0">
+  <autoFilter ref="A1:L162" xr:uid="{343BA946-EF1B-4A3B-B511-74A6334C62D3}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{9B76ED1C-581E-403B-9039-C4D1437837BF}" name="Columna1" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{B227DD10-4412-4DA1-B9AE-57DBBAAC5FDB}" name="Columna2" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{946681D4-26C8-4625-A0B6-192416560D49}" name="Descripción" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{1B53AA13-C73C-4BDB-96DD-F68A91E0C473}" name="Tipo/s de Prueba" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{38F51641-8D65-4D91-9238-C57B7E0DC8C4}" name="Precondiciones" dataDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{F67DADA5-19EF-41E4-9B0E-3EB1E6E4AEC7}" name="Pasos a seguir" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{1E37B7C6-6237-424F-9825-DBAC920A3A92}" name="Datos de Prueba" dataDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{6808706D-288F-4E5F-B1EE-9FC3C5DA1057}" name="Resultado Esperado" dataDxfId="40"/>
+    <tableColumn id="9" xr3:uid="{2D9093F3-889A-450D-9A36-E88B55FE392C}" name="Resultado Actual (Si falla)" dataDxfId="39"/>
+    <tableColumn id="10" xr3:uid="{1DD114CA-C7C7-4EE6-9D13-890DFE1B49F9}" name="Ultima ejecución (Fecha)" dataDxfId="38"/>
+    <tableColumn id="11" xr3:uid="{78CB6362-EDEC-4F76-AA97-664327DEED9B}" name="Encargado de Prueba" dataDxfId="37"/>
+    <tableColumn id="12" xr3:uid="{E14C667D-B48D-4C28-B1C7-EA7F85B8361A}" name="Estado (Dropdown)" dataDxfId="36"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -10237,14 +10096,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D9AFB2-4BAC-4EFB-A2E7-92EA3A8E1FBC}">
-  <dimension ref="A2:N198"/>
+  <dimension ref="A1:N186"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
     <col min="2" max="2" width="30.85546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="37.42578125" style="2" customWidth="1"/>
     <col min="4" max="4" width="37.42578125" customWidth="1"/>
-    <col min="5" max="6" width="31.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="31.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="49.85546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="39.42578125" style="2" customWidth="1"/>
     <col min="8" max="8" width="33.85546875" style="2" customWidth="1"/>
     <col min="9" max="9" width="31.42578125" customWidth="1"/>
@@ -10253,43 +10113,51 @@
     <col min="13" max="13" width="36.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="3" t="s">
+    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D1" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>30</v>
       </c>
+    </row>
+    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2"/>
+      <c r="D2"/>
+      <c r="I2"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2"/>
       <c r="M2" s="3" t="s">
         <v>31</v>
       </c>
@@ -10298,39 +10166,41 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="6">
-        <v>45940</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>41</v>
+      <c r="A3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
@@ -10340,10 +10210,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>35</v>
@@ -10352,13 +10222,13 @@
         <v>36</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="6">
@@ -10373,30 +10243,30 @@
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
     </row>
-    <row r="5" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>51</v>
+        <v>44</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="6">
@@ -10416,10 +10286,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>35</v>
@@ -10454,10 +10324,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>35</v>
@@ -10469,10 +10339,10 @@
         <v>50</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="6">
@@ -10492,10 +10362,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>35</v>
@@ -10506,11 +10376,11 @@
       <c r="F8" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>61</v>
+      <c r="G8" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="6">
@@ -10530,10 +10400,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>35</v>
@@ -10545,10 +10415,10 @@
         <v>50</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="6">
@@ -10568,10 +10438,10 @@
         <v>2</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>35</v>
@@ -10583,10 +10453,10 @@
         <v>50</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="6">
@@ -10606,10 +10476,10 @@
         <v>2</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>35</v>
@@ -10621,10 +10491,10 @@
         <v>50</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="6">
@@ -10644,10 +10514,10 @@
         <v>2</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>35</v>
@@ -10659,10 +10529,10 @@
         <v>50</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="6">
@@ -10677,15 +10547,15 @@
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
     </row>
-    <row r="13" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>35</v>
@@ -10694,13 +10564,13 @@
         <v>49</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="6">
@@ -10715,15 +10585,15 @@
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
     </row>
-    <row r="14" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>35</v>
@@ -10735,10 +10605,10 @@
         <v>80</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="6">
@@ -10753,15 +10623,15 @@
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
     </row>
-    <row r="15" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>35</v>
@@ -10770,17 +10640,17 @@
         <v>49</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="6">
-        <v>45945</v>
+        <v>45940</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>40</v>
@@ -10798,10 +10668,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>35</v>
@@ -10810,17 +10680,17 @@
         <v>49</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="6">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>40</v>
@@ -10831,28 +10701,30 @@
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
     </row>
-    <row r="17" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="G17" s="7"/>
+        <v>95</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>96</v>
+      </c>
       <c r="H17" s="7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="6">
@@ -10872,10 +10744,10 @@
         <v>5</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>35</v>
@@ -10888,7 +10760,7 @@
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="6">
@@ -10903,15 +10775,15 @@
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
     </row>
-    <row r="19" spans="1:14" ht="135" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>35</v>
@@ -10922,15 +10794,13 @@
       <c r="F19" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>108</v>
-      </c>
+      <c r="G19" s="7"/>
       <c r="H19" s="7" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="6">
-        <v>45945</v>
+        <v>45940</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>40</v>
@@ -10941,15 +10811,15 @@
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
     </row>
-    <row r="20" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="135" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>35</v>
@@ -10964,7 +10834,7 @@
         <v>108</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="6">
@@ -10979,15 +10849,15 @@
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
     </row>
-    <row r="21" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>35</v>
@@ -10999,10 +10869,10 @@
         <v>101</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="6">
@@ -11017,30 +10887,30 @@
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
     </row>
-    <row r="22" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="6">
@@ -11055,15 +10925,15 @@
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
     </row>
-    <row r="23" spans="1:14" ht="195" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>35</v>
@@ -11075,10 +10945,10 @@
         <v>89</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="6">
@@ -11093,109 +10963,109 @@
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
     </row>
-    <row r="24" spans="1:14" ht="135" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="195" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>129</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I24" s="7"/>
       <c r="J24" s="6">
-        <v>45947</v>
+        <v>45945</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>40</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="M24" s="7" t="s">
         <v>131</v>
       </c>
       <c r="N24" s="7"/>
     </row>
-    <row r="25" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="135" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>135</v>
+        <v>5</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>41</v>
+        <v>101</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="J25" s="6">
+        <v>45947</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>130</v>
       </c>
       <c r="N25" s="7"/>
     </row>
-    <row r="26" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>134</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
@@ -11205,34 +11075,34 @@
         <v>140</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="N26" s="7"/>
     </row>
-    <row r="27" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>134</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
@@ -11242,34 +11112,34 @@
         <v>140</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="N27" s="7"/>
     </row>
-    <row r="28" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1" t="s">
@@ -11288,25 +11158,25 @@
         <v>10</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1" t="s">
@@ -11316,34 +11186,34 @@
         <v>140</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="N29" s="7"/>
     </row>
-    <row r="30" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
@@ -11362,25 +11232,25 @@
         <v>10</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
@@ -11390,34 +11260,34 @@
         <v>140</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="N31" s="7"/>
     </row>
-    <row r="32" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
@@ -11431,30 +11301,30 @@
       </c>
       <c r="N32" s="7"/>
     </row>
-    <row r="33" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
@@ -11464,7 +11334,7 @@
         <v>140</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="N33" s="7"/>
     </row>
@@ -11473,25 +11343,25 @@
         <v>10</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1" t="s">
@@ -11505,37 +11375,37 @@
       </c>
       <c r="N34" s="7"/>
     </row>
-    <row r="35" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>1</v>
+    <row r="35" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>10</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
-        <v>208</v>
+        <v>139</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>209</v>
+        <v>140</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>147</v>
@@ -11548,32 +11418,32 @@
         <v>1</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>147</v>
@@ -11586,35 +11456,35 @@
         <v>1</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
@@ -11624,25 +11494,25 @@
         <v>1</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
@@ -11652,7 +11522,7 @@
         <v>209</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
@@ -11662,25 +11532,25 @@
         <v>1</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1" t="s">
@@ -11690,35 +11560,35 @@
         <v>209</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
     </row>
-    <row r="40" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>35</v>
+        <v>219</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1" t="s">
@@ -11728,42 +11598,42 @@
         <v>209</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
     </row>
-    <row r="41" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>212</v>
+        <v>35</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>147</v>
@@ -11776,25 +11646,25 @@
         <v>1</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>35</v>
+        <v>212</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1" t="s">
@@ -11804,20 +11674,20 @@
         <v>216</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
     </row>
-    <row r="43" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>35</v>
@@ -11826,58 +11696,58 @@
         <v>204</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
     </row>
-    <row r="44" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>147</v>
@@ -11885,37 +11755,37 @@
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
     </row>
-    <row r="45" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>260</v>
+        <v>134</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>147</v>
@@ -11928,25 +11798,25 @@
         <v>1</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>35</v>
+        <v>260</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1" t="s">
@@ -11956,20 +11826,20 @@
         <v>209</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
     </row>
-    <row r="47" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>35</v>
@@ -11978,13 +11848,13 @@
         <v>204</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1" t="s">
@@ -12004,32 +11874,32 @@
         <v>1</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>276</v>
+        <v>35</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>41</v>
@@ -12042,25 +11912,25 @@
         <v>1</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>35</v>
+        <v>276</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1" t="s">
@@ -12070,42 +11940,42 @@
         <v>216</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
     </row>
     <row r="50" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>212</v>
+        <v>35</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>147</v>
@@ -12113,30 +11983,30 @@
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
     </row>
-    <row r="51" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>134</v>
+        <v>212</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1" t="s">
@@ -12151,30 +12021,30 @@
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
     </row>
-    <row r="52" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>297</v>
+        <v>134</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1" t="s">
@@ -12189,30 +12059,30 @@
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
     </row>
-    <row r="53" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>134</v>
+        <v>297</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1" t="s">
@@ -12227,30 +12097,30 @@
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
     </row>
-    <row r="54" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>276</v>
+        <v>134</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1" t="s">
@@ -12270,32 +12140,32 @@
         <v>12</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>147</v>
@@ -12308,32 +12178,32 @@
         <v>12</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>147</v>
@@ -12341,30 +12211,30 @@
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
     </row>
-    <row r="57" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1" t="s">
@@ -12384,32 +12254,32 @@
         <v>12</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>203</v>
+        <v>297</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>147</v>
@@ -12417,37 +12287,37 @@
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
     </row>
-    <row r="59" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>147</v>
@@ -12455,37 +12325,37 @@
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
     </row>
-    <row r="60" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>147</v>
@@ -12493,30 +12363,30 @@
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
     </row>
-    <row r="61" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1" t="s">
@@ -12531,37 +12401,37 @@
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
     </row>
-    <row r="62" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L62" s="1" t="s">
         <v>147</v>
@@ -12574,32 +12444,32 @@
         <v>12</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>134</v>
+        <v>203</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>147</v>
@@ -12607,37 +12477,37 @@
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
     </row>
-    <row r="64" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>297</v>
+        <v>134</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L64" s="1" t="s">
         <v>147</v>
@@ -12645,30 +12515,30 @@
       <c r="M64" s="7"/>
       <c r="N64" s="7"/>
     </row>
-    <row r="65" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>203</v>
+        <v>297</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1" t="s">
@@ -12683,15 +12553,15 @@
       <c r="M65" s="7"/>
       <c r="N65" s="7"/>
     </row>
-    <row r="66" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>203</v>
@@ -12700,13 +12570,13 @@
         <v>204</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1" t="s">
@@ -12721,30 +12591,30 @@
       <c r="M66" s="7"/>
       <c r="N66" s="7"/>
     </row>
-    <row r="67" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1" t="s">
@@ -12759,37 +12629,37 @@
       <c r="M67" s="7"/>
       <c r="N67" s="7"/>
     </row>
-    <row r="68" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>219</v>
+        <v>35</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="I68" s="1"/>
       <c r="J68" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L68" s="1" t="s">
         <v>147</v>
@@ -12797,37 +12667,37 @@
       <c r="M68" s="7"/>
       <c r="N68" s="7"/>
     </row>
-    <row r="69" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>134</v>
+        <v>219</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="I69" s="1"/>
       <c r="J69" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>147</v>
@@ -12835,30 +12705,30 @@
       <c r="M69" s="7"/>
       <c r="N69" s="7"/>
     </row>
-    <row r="70" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>297</v>
+        <v>134</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="I70" s="1"/>
       <c r="J70" s="1" t="s">
@@ -12873,30 +12743,30 @@
       <c r="M70" s="7"/>
       <c r="N70" s="7"/>
     </row>
-    <row r="71" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>134</v>
+        <v>297</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1" t="s">
@@ -12911,30 +12781,30 @@
       <c r="M71" s="7"/>
       <c r="N71" s="7"/>
     </row>
-    <row r="72" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>297</v>
+        <v>134</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1" t="s">
@@ -12949,30 +12819,30 @@
       <c r="M72" s="7"/>
       <c r="N72" s="7"/>
     </row>
-    <row r="73" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1" t="s">
@@ -12987,30 +12857,30 @@
       <c r="M73" s="7"/>
       <c r="N73" s="7"/>
     </row>
-    <row r="74" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>219</v>
+        <v>276</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1" t="s">
@@ -13025,15 +12895,15 @@
       <c r="M74" s="7"/>
       <c r="N74" s="7"/>
     </row>
-    <row r="75" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>219</v>
@@ -13042,20 +12912,20 @@
         <v>204</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L75" s="1" t="s">
         <v>147</v>
@@ -13063,37 +12933,37 @@
       <c r="M75" s="7"/>
       <c r="N75" s="7"/>
     </row>
-    <row r="76" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L76" s="1" t="s">
         <v>147</v>
@@ -13101,37 +12971,37 @@
       <c r="M76" s="7"/>
       <c r="N76" s="7"/>
     </row>
-    <row r="77" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L77" s="1" t="s">
         <v>147</v>
@@ -13139,30 +13009,30 @@
       <c r="M77" s="7"/>
       <c r="N77" s="7"/>
     </row>
-    <row r="78" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>219</v>
+        <v>297</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1" t="s">
@@ -13177,37 +13047,37 @@
       <c r="M78" s="7"/>
       <c r="N78" s="7"/>
     </row>
-    <row r="79" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>35</v>
+        <v>219</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>147</v>
@@ -13215,30 +13085,30 @@
       <c r="M79" s="7"/>
       <c r="N79" s="7"/>
     </row>
-    <row r="80" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>212</v>
+        <v>35</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1" t="s">
@@ -13253,30 +13123,30 @@
       <c r="M80" s="7"/>
       <c r="N80" s="7"/>
     </row>
-    <row r="81" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>297</v>
+        <v>212</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1" t="s">
@@ -13291,30 +13161,30 @@
       <c r="M81" s="7"/>
       <c r="N81" s="7"/>
     </row>
-    <row r="82" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1" t="s">
@@ -13329,37 +13199,37 @@
       <c r="M82" s="7"/>
       <c r="N82" s="7"/>
     </row>
-    <row r="83" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>35</v>
+        <v>276</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>147</v>
@@ -13367,37 +13237,37 @@
       <c r="M83" s="7"/>
       <c r="N83" s="7"/>
     </row>
-    <row r="84" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L84" s="1" t="s">
         <v>147</v>
@@ -13405,30 +13275,30 @@
       <c r="M84" s="7"/>
       <c r="N84" s="7"/>
     </row>
-    <row r="85" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>276</v>
+        <v>134</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1" t="s">
@@ -13443,37 +13313,37 @@
       <c r="M85" s="7"/>
       <c r="N85" s="7"/>
     </row>
-    <row r="86" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L86" s="1" t="s">
         <v>147</v>
@@ -13481,37 +13351,37 @@
       <c r="M86" s="7"/>
       <c r="N86" s="7"/>
     </row>
-    <row r="87" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>203</v>
+        <v>297</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L87" s="1" t="s">
         <v>147</v>
@@ -13519,30 +13389,30 @@
       <c r="M87" s="7"/>
       <c r="N87" s="7"/>
     </row>
-    <row r="88" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>134</v>
+        <v>203</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1" t="s">
@@ -13557,30 +13427,30 @@
       <c r="M88" s="7"/>
       <c r="N88" s="7"/>
     </row>
-    <row r="89" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1" t="s">
@@ -13595,30 +13465,30 @@
       <c r="M89" s="7"/>
       <c r="N89" s="7"/>
     </row>
-    <row r="90" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>203</v>
+        <v>35</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1" t="s">
@@ -13633,30 +13503,30 @@
       <c r="M90" s="7"/>
       <c r="N90" s="7"/>
     </row>
-    <row r="91" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>134</v>
+        <v>203</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1" t="s">
@@ -13666,80 +13536,80 @@
         <v>209</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M91" s="7"/>
       <c r="N91" s="7"/>
     </row>
-    <row r="92" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>219</v>
+        <v>134</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="M92" s="7"/>
       <c r="N92" s="7"/>
     </row>
-    <row r="93" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>134</v>
+        <v>219</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L93" s="1" t="s">
         <v>147</v>
@@ -13747,30 +13617,30 @@
       <c r="M93" s="7"/>
       <c r="N93" s="7"/>
     </row>
-    <row r="94" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="I94" s="1"/>
       <c r="J94" s="1" t="s">
@@ -13785,30 +13655,30 @@
       <c r="M94" s="7"/>
       <c r="N94" s="7"/>
     </row>
-    <row r="95" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>219</v>
+        <v>35</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1" t="s">
@@ -13818,73 +13688,73 @@
         <v>209</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M95" s="7"/>
       <c r="N95" s="7"/>
     </row>
-    <row r="96" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="M96" s="7"/>
       <c r="N96" s="7"/>
     </row>
-    <row r="97" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1" t="s">
@@ -13899,37 +13769,37 @@
       <c r="M97" s="7"/>
       <c r="N97" s="7"/>
     </row>
-    <row r="98" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>297</v>
+        <v>212</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L98" s="1" t="s">
         <v>147</v>
@@ -13937,30 +13807,30 @@
       <c r="M98" s="7"/>
       <c r="N98" s="7"/>
     </row>
-    <row r="99" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1" t="s">
@@ -13975,15 +13845,15 @@
       <c r="M99" s="7"/>
       <c r="N99" s="7"/>
     </row>
-    <row r="100" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>260</v>
@@ -13992,13 +13862,13 @@
         <v>204</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1" t="s">
@@ -14013,37 +13883,37 @@
       <c r="M100" s="7"/>
       <c r="N100" s="7"/>
     </row>
-    <row r="101" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L101" s="1" t="s">
         <v>147</v>
@@ -14051,30 +13921,30 @@
       <c r="M101" s="7"/>
       <c r="N101" s="7"/>
     </row>
-    <row r="102" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1" t="s">
@@ -14089,37 +13959,37 @@
       <c r="M102" s="7"/>
       <c r="N102" s="7"/>
     </row>
-    <row r="103" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>219</v>
+        <v>297</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L103" s="1" t="s">
         <v>147</v>
@@ -14127,106 +13997,106 @@
       <c r="M103" s="7"/>
       <c r="N103" s="7"/>
     </row>
-    <row r="104" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M104" s="7"/>
       <c r="N104" s="7"/>
     </row>
-    <row r="105" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="M105" s="7"/>
       <c r="N105" s="7"/>
     </row>
-    <row r="106" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>276</v>
+        <v>212</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1" t="s">
@@ -14236,35 +14106,35 @@
         <v>209</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M106" s="7"/>
       <c r="N106" s="7"/>
     </row>
-    <row r="107" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1" t="s">
@@ -14274,35 +14144,35 @@
         <v>209</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="M107" s="7"/>
       <c r="N107" s="7"/>
     </row>
-    <row r="108" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>35</v>
+        <v>260</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1" t="s">
@@ -14317,53 +14187,53 @@
       <c r="M108" s="7"/>
       <c r="N108" s="7"/>
     </row>
-    <row r="109" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>219</v>
+        <v>35</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M109" s="7"/>
       <c r="N109" s="7"/>
     </row>
-    <row r="110" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>219</v>
@@ -14372,51 +14242,51 @@
         <v>204</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="M110" s="7"/>
       <c r="N110" s="7"/>
     </row>
-    <row r="111" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1" t="s">
@@ -14431,30 +14301,30 @@
       <c r="M111" s="7"/>
       <c r="N111" s="7"/>
     </row>
-    <row r="112" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>297</v>
+        <v>203</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1" t="s">
@@ -14469,30 +14339,30 @@
       <c r="M112" s="7"/>
       <c r="N112" s="7"/>
     </row>
-    <row r="113" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1" t="s">
@@ -14507,30 +14377,30 @@
       <c r="M113" s="7"/>
       <c r="N113" s="7"/>
     </row>
-    <row r="114" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1" t="s">
@@ -14545,37 +14415,37 @@
       <c r="M114" s="7"/>
       <c r="N114" s="7"/>
     </row>
-    <row r="115" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>35</v>
+        <v>219</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L115" s="1" t="s">
         <v>147</v>
@@ -14583,37 +14453,37 @@
       <c r="M115" s="7"/>
       <c r="N115" s="7"/>
     </row>
-    <row r="116" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>276</v>
+        <v>35</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L116" s="1" t="s">
         <v>147</v>
@@ -14621,37 +14491,37 @@
       <c r="M116" s="7"/>
       <c r="N116" s="7"/>
     </row>
-    <row r="117" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L117" s="1" t="s">
         <v>147</v>
@@ -14659,37 +14529,37 @@
       <c r="M117" s="7"/>
       <c r="N117" s="7"/>
     </row>
-    <row r="118" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L118" s="1" t="s">
         <v>147</v>
@@ -14697,91 +14567,91 @@
       <c r="M118" s="7"/>
       <c r="N118" s="7"/>
     </row>
-    <row r="119" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="I119" s="1"/>
       <c r="J119" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M119" s="7"/>
       <c r="N119" s="7"/>
     </row>
-    <row r="120" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="I120" s="1"/>
       <c r="J120" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="M120" s="7"/>
       <c r="N120" s="7"/>
     </row>
-    <row r="121" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>35</v>
@@ -14790,13 +14660,13 @@
         <v>204</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="I121" s="1"/>
       <c r="J121" s="1" t="s">
@@ -14811,75 +14681,75 @@
       <c r="M121" s="7"/>
       <c r="N121" s="7"/>
     </row>
-    <row r="122" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>276</v>
+        <v>35</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="I122" s="1"/>
       <c r="J122" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M122" s="7"/>
       <c r="N122" s="7"/>
     </row>
-    <row r="123" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>134</v>
+        <v>276</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="I123" s="1"/>
       <c r="J123" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L123" s="1" t="s">
         <v>41</v>
@@ -14887,30 +14757,30 @@
       <c r="M123" s="7"/>
       <c r="N123" s="7"/>
     </row>
-    <row r="124" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="I124" s="1"/>
       <c r="J124" s="1" t="s">
@@ -14920,20 +14790,20 @@
         <v>209</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="M124" s="7"/>
       <c r="N124" s="7"/>
     </row>
-    <row r="125" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>35</v>
@@ -14942,51 +14812,51 @@
         <v>204</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="I125" s="1"/>
       <c r="J125" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M125" s="7"/>
       <c r="N125" s="7"/>
     </row>
-    <row r="126" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>297</v>
+        <v>35</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="I126" s="1"/>
       <c r="J126" s="1" t="s">
@@ -14996,20 +14866,20 @@
         <v>216</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="M126" s="7"/>
       <c r="N126" s="7"/>
     </row>
-    <row r="127" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>297</v>
@@ -15018,58 +14888,58 @@
         <v>204</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="I127" s="1"/>
       <c r="J127" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M127" s="7"/>
       <c r="N127" s="7"/>
     </row>
-    <row r="128" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>212</v>
+        <v>297</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="I128" s="1"/>
       <c r="J128" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L128" s="1" t="s">
         <v>41</v>
@@ -15077,30 +14947,30 @@
       <c r="M128" s="7"/>
       <c r="N128" s="7"/>
     </row>
-    <row r="129" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>297</v>
+        <v>212</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="I129" s="1"/>
       <c r="J129" s="1" t="s">
@@ -15110,35 +14980,35 @@
         <v>216</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="M129" s="7"/>
       <c r="N129" s="7"/>
     </row>
-    <row r="130" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="I130" s="1"/>
       <c r="J130" s="1" t="s">
@@ -15158,32 +15028,32 @@
         <v>18</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>219</v>
+        <v>276</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L131" s="1" t="s">
         <v>147</v>
@@ -15191,37 +15061,37 @@
       <c r="M131" s="7"/>
       <c r="N131" s="7"/>
     </row>
-    <row r="132" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L132" s="1" t="s">
         <v>147</v>
@@ -15229,30 +15099,30 @@
       <c r="M132" s="7"/>
       <c r="N132" s="7"/>
     </row>
-    <row r="133" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>297</v>
+        <v>203</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1" t="s">
@@ -15267,106 +15137,106 @@
       <c r="M133" s="7"/>
       <c r="N133" s="7"/>
     </row>
-    <row r="134" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1" t="s">
         <v>208</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="L134" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="L134" s="1" t="s">
         <v>147</v>
       </c>
       <c r="M134" s="7"/>
       <c r="N134" s="7"/>
     </row>
     <row r="135" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>711</v>
-      </c>
-      <c r="C135" t="s">
-        <v>712</v>
-      </c>
-      <c r="D135" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E135" s="7" t="s">
+      <c r="A135" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E135" s="3" t="s">
         <v>204</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>713</v>
-      </c>
-      <c r="G135" s="7" t="s">
-        <v>714</v>
-      </c>
-      <c r="H135" s="7" t="s">
-        <v>715</v>
-      </c>
-      <c r="I135" s="7"/>
-      <c r="J135" s="6">
-        <v>45950</v>
-      </c>
-      <c r="K135" s="7" t="s">
-        <v>716</v>
-      </c>
-      <c r="L135" s="17" t="s">
-        <v>41</v>
+        <v>708</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="I135" s="1"/>
+      <c r="J135" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L135" s="11" t="s">
+        <v>147</v>
       </c>
       <c r="M135" s="7"/>
       <c r="N135" s="7"/>
     </row>
-    <row r="136" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="C136" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>203</v>
+        <v>297</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>204</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="G136" s="7" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="H136" s="7" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="I136" s="7"/>
       <c r="J136" s="6">
@@ -15375,36 +15245,36 @@
       <c r="K136" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="L136" s="1" t="s">
+      <c r="L136" s="11" t="s">
         <v>41</v>
       </c>
       <c r="M136" s="7"/>
       <c r="N136" s="7"/>
     </row>
-    <row r="137" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="C137" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>297</v>
+        <v>203</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>204</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>826</v>
+        <v>719</v>
       </c>
       <c r="G137" s="7" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="H137" s="7" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="I137" s="7"/>
       <c r="J137" s="6">
@@ -15421,28 +15291,28 @@
     </row>
     <row r="138" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
-        <v>726</v>
+        <v>12</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="C138" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="E138" s="7" t="s">
         <v>204</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>729</v>
+        <v>826</v>
       </c>
       <c r="G138" s="7" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="H138" s="7" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I138" s="7"/>
       <c r="J138" s="6">
@@ -15462,25 +15332,25 @@
         <v>726</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="C139" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>203</v>
+        <v>276</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>734</v>
+        <v>204</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="G139" s="7" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="H139" s="7" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="I139" s="7"/>
       <c r="J139" s="6">
@@ -15495,30 +15365,30 @@
       <c r="M139" s="7"/>
       <c r="N139" s="7"/>
     </row>
-    <row r="140" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
         <v>726</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="C140" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="D140" s="7" t="s">
         <v>203</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="G140" s="7" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="H140" s="7" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="I140" s="7"/>
       <c r="J140" s="6">
@@ -15533,30 +15403,30 @@
       <c r="M140" s="7"/>
       <c r="N140" s="7"/>
     </row>
-    <row r="141" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
         <v>726</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="C141" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>297</v>
+        <v>203</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>204</v>
+        <v>740</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="H141" s="7" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="I141" s="7"/>
       <c r="J141" s="6">
@@ -15573,28 +15443,28 @@
     </row>
     <row r="142" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
-        <v>5</v>
+        <v>726</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="C142" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>204</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="H142" s="7" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="I142" s="7"/>
       <c r="J142" s="6">
@@ -15609,30 +15479,30 @@
       <c r="M142" s="7"/>
       <c r="N142" s="7"/>
     </row>
-    <row r="143" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="C143" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>756</v>
+        <v>276</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>757</v>
+        <v>204</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="H143" s="7" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="I143" s="7"/>
       <c r="J143" s="6">
@@ -15652,10 +15522,10 @@
         <v>5</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="C144" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="D144" s="7" t="s">
         <v>756</v>
@@ -15664,13 +15534,13 @@
         <v>757</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="G144" s="7" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="H144" s="7" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="I144" s="7"/>
       <c r="J144" s="6">
@@ -15685,30 +15555,30 @@
       <c r="M144" s="7"/>
       <c r="N144" s="7"/>
     </row>
-    <row r="145" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C145" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>276</v>
+        <v>756</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>204</v>
+        <v>757</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="G145" s="7" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="H145" s="7" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="I145" s="7"/>
       <c r="J145" s="6">
@@ -15728,25 +15598,25 @@
         <v>6</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="C146" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>219</v>
+        <v>276</v>
       </c>
       <c r="E146" s="7" t="s">
         <v>204</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="H146" s="7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="I146" s="7"/>
       <c r="J146" s="6">
@@ -15766,25 +15636,25 @@
         <v>6</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="C147" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>756</v>
+        <v>219</v>
       </c>
       <c r="E147" s="7" t="s">
         <v>204</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>752</v>
+        <v>774</v>
       </c>
       <c r="H147" s="7" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="I147" s="7"/>
       <c r="J147" s="6">
@@ -15804,25 +15674,25 @@
         <v>6</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C148" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>212</v>
+        <v>756</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>204</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>783</v>
+        <v>752</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="I148" s="7"/>
       <c r="J148" s="6">
@@ -15839,28 +15709,28 @@
     </row>
     <row r="149" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>785</v>
+        <v>6</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>47</v>
+        <v>780</v>
       </c>
       <c r="C149" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>276</v>
+        <v>212</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>204</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="I149" s="7"/>
       <c r="J149" s="6">
@@ -15880,25 +15750,25 @@
         <v>785</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>790</v>
+        <v>47</v>
       </c>
       <c r="C150" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>756</v>
+        <v>276</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>792</v>
+        <v>204</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="G150" s="7" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="H150" s="7" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="I150" s="7"/>
       <c r="J150" s="6">
@@ -15915,28 +15785,28 @@
     </row>
     <row r="151" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="C151" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>276</v>
+        <v>756</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>204</v>
+        <v>792</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="G151" s="7" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="I151" s="7"/>
       <c r="J151" s="6">
@@ -15951,30 +15821,30 @@
       <c r="M151" s="7"/>
       <c r="N151" s="7"/>
     </row>
-    <row r="152" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
         <v>796</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C152" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>219</v>
+        <v>276</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>804</v>
+        <v>204</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="G152" s="7" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="H152" s="7" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="I152" s="7"/>
       <c r="J152" s="6">
@@ -15991,28 +15861,28 @@
     </row>
     <row r="153" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="C153" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>204</v>
+        <v>804</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="H153" s="7" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="I153" s="7"/>
       <c r="J153" s="6">
@@ -16032,25 +15902,25 @@
         <v>808</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="C154" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>219</v>
+        <v>276</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>816</v>
+        <v>204</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="H154" s="7" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="I154" s="7"/>
       <c r="J154" s="6">
@@ -16066,543 +15936,492 @@
       <c r="N154" s="7"/>
     </row>
     <row r="155" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="10" t="s">
-        <v>827</v>
-      </c>
-      <c r="B155" s="10" t="s">
-        <v>828</v>
-      </c>
-      <c r="C155" s="10" t="s">
-        <v>829</v>
-      </c>
-      <c r="D155" s="10" t="s">
-        <v>830</v>
-      </c>
-      <c r="E155" s="10" t="s">
-        <v>831</v>
+      <c r="A155" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>814</v>
+      </c>
+      <c r="C155" t="s">
+        <v>815</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>816</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>832</v>
-      </c>
-      <c r="G155" s="10" t="s">
-        <v>896</v>
-      </c>
-      <c r="H155" s="10" t="s">
-        <v>835</v>
-      </c>
-      <c r="I155" s="10"/>
-      <c r="J155" s="13">
-        <v>45954</v>
-      </c>
-      <c r="K155" s="12" t="s">
-        <v>895</v>
-      </c>
-      <c r="L155" s="14" t="s">
+        <v>817</v>
+      </c>
+      <c r="G155" s="7" t="s">
+        <v>818</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>819</v>
+      </c>
+      <c r="I155" s="7"/>
+      <c r="J155" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K155" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="L155" s="1" t="s">
         <v>41</v>
       </c>
       <c r="M155" s="7"/>
       <c r="N155" s="7"/>
     </row>
     <row r="156" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="10"/>
-      <c r="B156" s="10"/>
-      <c r="C156" s="10"/>
-      <c r="D156" s="10"/>
-      <c r="E156" s="10"/>
+      <c r="A156" s="7" t="s">
+        <v>827</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>828</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>831</v>
+      </c>
       <c r="F156" s="7" t="s">
-        <v>833</v>
-      </c>
-      <c r="G156" s="10"/>
-      <c r="H156" s="10"/>
-      <c r="I156" s="10"/>
-      <c r="J156" s="13"/>
-      <c r="K156" s="12"/>
-      <c r="L156" s="15"/>
+        <v>875</v>
+      </c>
+      <c r="G156" s="7" t="s">
+        <v>866</v>
+      </c>
+      <c r="H156" s="7" t="s">
+        <v>832</v>
+      </c>
+      <c r="I156" s="7"/>
+      <c r="J156" s="6">
+        <v>45954</v>
+      </c>
+      <c r="K156" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="L156" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="M156" s="7"/>
       <c r="N156" s="7"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A157" s="10"/>
-      <c r="B157" s="10"/>
-      <c r="C157" s="10"/>
-      <c r="D157" s="10"/>
-      <c r="E157" s="10"/>
+    <row r="157" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A157" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>837</v>
+      </c>
       <c r="F157" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="G157" s="7" t="s">
         <v>834</v>
       </c>
-      <c r="G157" s="10"/>
-      <c r="H157" s="10"/>
-      <c r="I157" s="10"/>
-      <c r="J157" s="13"/>
-      <c r="K157" s="12"/>
-      <c r="L157" s="15"/>
+      <c r="H157" s="7" t="s">
+        <v>838</v>
+      </c>
+      <c r="I157" s="7"/>
+      <c r="J157" s="6">
+        <v>45954</v>
+      </c>
+      <c r="K157" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="L157" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="M157" s="7"/>
       <c r="N157" s="7"/>
     </row>
     <row r="158" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="10" t="s">
-        <v>836</v>
-      </c>
-      <c r="B158" s="10" t="s">
-        <v>837</v>
-      </c>
-      <c r="C158" s="10" t="s">
-        <v>838</v>
-      </c>
-      <c r="D158" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="E158" s="10" t="s">
+      <c r="A158" s="7" t="s">
         <v>839</v>
       </c>
+      <c r="B158" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>841</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>842</v>
+      </c>
       <c r="F158" s="7" t="s">
-        <v>840</v>
-      </c>
-      <c r="G158" s="10" t="s">
+        <v>873</v>
+      </c>
+      <c r="G158" s="7"/>
+      <c r="H158" s="7" t="s">
         <v>843</v>
       </c>
-      <c r="H158" s="10" t="s">
-        <v>844</v>
-      </c>
-      <c r="I158" s="10"/>
-      <c r="J158" s="13">
+      <c r="I158" s="7"/>
+      <c r="J158" s="6">
         <v>45954</v>
       </c>
-      <c r="K158" s="12" t="s">
-        <v>895</v>
-      </c>
-      <c r="L158" s="16" t="s">
+      <c r="K158" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="L158" s="10" t="s">
         <v>41</v>
       </c>
       <c r="M158" s="7"/>
       <c r="N158" s="7"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A159" s="10"/>
-      <c r="B159" s="10"/>
-      <c r="C159" s="10"/>
-      <c r="D159" s="10"/>
-      <c r="E159" s="10"/>
+    <row r="159" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A159" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>847</v>
+      </c>
       <c r="F159" s="7" t="s">
-        <v>841</v>
-      </c>
-      <c r="G159" s="10"/>
-      <c r="H159" s="10"/>
-      <c r="I159" s="10"/>
-      <c r="J159" s="13"/>
-      <c r="K159" s="12"/>
-      <c r="L159" s="16"/>
+        <v>872</v>
+      </c>
+      <c r="G159" s="7"/>
+      <c r="H159" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="I159" s="7"/>
+      <c r="J159" s="6">
+        <v>45957</v>
+      </c>
+      <c r="K159" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="L159" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="M159" s="7"/>
       <c r="N159" s="7"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A160" s="10"/>
-      <c r="B160" s="10"/>
-      <c r="C160" s="10"/>
-      <c r="D160" s="10"/>
-      <c r="E160" s="10"/>
+    <row r="160" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A160" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>850</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>853</v>
+      </c>
       <c r="F160" s="7" t="s">
-        <v>842</v>
-      </c>
-      <c r="G160" s="10"/>
-      <c r="H160" s="10"/>
-      <c r="I160" s="10"/>
-      <c r="J160" s="13"/>
-      <c r="K160" s="12"/>
-      <c r="L160" s="16"/>
+        <v>871</v>
+      </c>
+      <c r="G160" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="H160" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="I160" s="7"/>
+      <c r="J160" s="6">
+        <v>45957</v>
+      </c>
+      <c r="K160" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="L160" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="M160" s="7"/>
       <c r="N160" s="7"/>
     </row>
     <row r="161" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="10" t="s">
-        <v>836</v>
-      </c>
-      <c r="B161" s="10" t="s">
-        <v>845</v>
-      </c>
-      <c r="C161" s="10" t="s">
-        <v>846</v>
-      </c>
-      <c r="D161" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="E161" s="10" t="s">
-        <v>847</v>
+      <c r="A161" s="7" t="s">
+        <v>855</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>856</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>857</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>859</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>840</v>
-      </c>
-      <c r="G161" s="10" t="s">
-        <v>843</v>
-      </c>
-      <c r="H161" s="10" t="s">
-        <v>849</v>
-      </c>
-      <c r="I161" s="10"/>
-      <c r="J161" s="13">
-        <v>45954</v>
-      </c>
-      <c r="K161" s="12" t="s">
-        <v>895</v>
-      </c>
-      <c r="L161" s="16" t="s">
+        <v>870</v>
+      </c>
+      <c r="G161" s="7"/>
+      <c r="H161" s="7" t="s">
+        <v>860</v>
+      </c>
+      <c r="I161" s="7"/>
+      <c r="J161" s="6">
+        <v>45957</v>
+      </c>
+      <c r="K161" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="L161" s="10" t="s">
         <v>41</v>
       </c>
       <c r="M161" s="7"/>
       <c r="N161" s="7"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A162" s="10"/>
-      <c r="B162" s="10"/>
-      <c r="C162" s="10"/>
-      <c r="D162" s="10"/>
-      <c r="E162" s="10"/>
+    <row r="162" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A162" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>863</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>864</v>
+      </c>
       <c r="F162" s="7" t="s">
-        <v>848</v>
-      </c>
-      <c r="G162" s="10"/>
-      <c r="H162" s="10"/>
-      <c r="I162" s="10"/>
-      <c r="J162" s="13"/>
-      <c r="K162" s="12"/>
-      <c r="L162" s="16"/>
+        <v>869</v>
+      </c>
+      <c r="G162" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="H162" s="7" t="s">
+        <v>865</v>
+      </c>
+      <c r="I162" s="7"/>
+      <c r="J162" s="6">
+        <v>45957</v>
+      </c>
+      <c r="K162" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="L162" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="M162" s="7"/>
       <c r="N162" s="7"/>
     </row>
     <row r="163" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="10" t="s">
-        <v>850</v>
-      </c>
-      <c r="B163" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C163" s="10" t="s">
-        <v>851</v>
-      </c>
-      <c r="D163" s="10" t="s">
-        <v>852</v>
-      </c>
-      <c r="E163" s="10" t="s">
-        <v>853</v>
-      </c>
-      <c r="F163" s="7" t="s">
-        <v>854</v>
-      </c>
-      <c r="G163" s="10"/>
-      <c r="H163" s="10" t="s">
-        <v>856</v>
-      </c>
-      <c r="I163" s="10"/>
-      <c r="J163" s="13">
-        <v>45954</v>
-      </c>
-      <c r="K163" s="12" t="s">
-        <v>895</v>
-      </c>
-      <c r="L163" s="16" t="s">
-        <v>41</v>
-      </c>
+      <c r="A163" s="7"/>
+      <c r="B163" s="7"/>
+      <c r="C163" s="7"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
+      <c r="F163" s="7"/>
+      <c r="G163" s="7"/>
+      <c r="H163" s="7"/>
+      <c r="I163" s="7"/>
+      <c r="J163" s="3"/>
+      <c r="K163" s="3"/>
+      <c r="L163" s="7"/>
       <c r="M163" s="7"/>
       <c r="N163" s="7"/>
     </row>
-    <row r="164" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A164" s="10"/>
-      <c r="B164" s="10"/>
-      <c r="C164" s="10"/>
-      <c r="D164" s="10"/>
-      <c r="E164" s="10"/>
-      <c r="F164" s="7" t="s">
-        <v>855</v>
-      </c>
-      <c r="G164" s="10"/>
-      <c r="H164" s="10"/>
-      <c r="I164" s="10"/>
-      <c r="J164" s="13"/>
-      <c r="K164" s="12"/>
-      <c r="L164" s="16"/>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A164" s="7"/>
+      <c r="B164" s="7"/>
+      <c r="C164" s="7"/>
+      <c r="D164" s="7"/>
+      <c r="E164" s="7"/>
+      <c r="F164" s="7"/>
+      <c r="G164" s="7"/>
+      <c r="H164" s="7"/>
+      <c r="I164" s="7"/>
+      <c r="J164" s="3"/>
+      <c r="K164" s="3"/>
+      <c r="L164" s="7"/>
       <c r="M164" s="7"/>
       <c r="N164" s="7"/>
     </row>
     <row r="165" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="10" t="s">
-        <v>857</v>
-      </c>
-      <c r="B165" s="10" t="s">
-        <v>858</v>
-      </c>
-      <c r="C165" s="10" t="s">
-        <v>859</v>
-      </c>
-      <c r="D165" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="E165" s="10" t="s">
-        <v>860</v>
-      </c>
-      <c r="F165" s="7" t="s">
-        <v>861</v>
-      </c>
-      <c r="G165" s="10"/>
-      <c r="H165" s="10" t="s">
-        <v>864</v>
-      </c>
-      <c r="I165" s="10"/>
-      <c r="J165" s="13">
-        <v>45957</v>
-      </c>
-      <c r="K165" s="12" t="s">
-        <v>895</v>
-      </c>
-      <c r="L165" s="18" t="s">
-        <v>147</v>
-      </c>
+      <c r="A165" s="7"/>
+      <c r="B165" s="7"/>
+      <c r="C165" s="7"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
+      <c r="F165" s="7"/>
+      <c r="G165" s="7"/>
+      <c r="H165" s="7"/>
+      <c r="I165" s="7"/>
+      <c r="J165" s="3"/>
+      <c r="K165" s="3"/>
+      <c r="L165" s="7"/>
       <c r="M165" s="7"/>
       <c r="N165" s="7"/>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A166" s="10"/>
-      <c r="B166" s="10"/>
-      <c r="C166" s="10"/>
-      <c r="D166" s="10"/>
-      <c r="E166" s="10"/>
-      <c r="F166" s="7" t="s">
-        <v>862</v>
-      </c>
-      <c r="G166" s="10"/>
-      <c r="H166" s="10"/>
-      <c r="I166" s="10"/>
-      <c r="J166" s="13"/>
-      <c r="K166" s="12"/>
-      <c r="L166" s="18"/>
+      <c r="A166" s="7"/>
+      <c r="B166" s="7"/>
+      <c r="C166" s="7"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="7"/>
+      <c r="F166" s="7"/>
+      <c r="G166" s="7"/>
+      <c r="H166" s="7"/>
+      <c r="I166" s="7"/>
+      <c r="J166" s="3"/>
+      <c r="K166" s="7"/>
+      <c r="L166" s="7"/>
       <c r="M166" s="7"/>
       <c r="N166" s="7"/>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A167" s="10"/>
-      <c r="B167" s="10"/>
-      <c r="C167" s="10"/>
-      <c r="D167" s="10"/>
-      <c r="E167" s="10"/>
-      <c r="F167" s="7" t="s">
-        <v>863</v>
-      </c>
-      <c r="G167" s="10"/>
-      <c r="H167" s="10"/>
-      <c r="I167" s="10"/>
-      <c r="J167" s="13"/>
-      <c r="K167" s="12"/>
-      <c r="L167" s="18"/>
+      <c r="A167" s="7"/>
+      <c r="B167" s="7"/>
+      <c r="C167" s="7"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="7"/>
+      <c r="F167" s="7"/>
+      <c r="G167" s="7"/>
+      <c r="H167" s="7"/>
+      <c r="I167" s="7"/>
+      <c r="J167" s="3"/>
+      <c r="K167" s="3"/>
+      <c r="L167" s="7"/>
       <c r="M167" s="7"/>
       <c r="N167" s="7"/>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A168" s="10" t="s">
-        <v>865</v>
-      </c>
-      <c r="B168" s="10" t="s">
-        <v>866</v>
-      </c>
-      <c r="C168" s="10" t="s">
-        <v>867</v>
-      </c>
-      <c r="D168" s="10" t="s">
-        <v>868</v>
-      </c>
-      <c r="E168" s="10" t="s">
-        <v>869</v>
-      </c>
-      <c r="F168" s="7" t="s">
-        <v>870</v>
-      </c>
-      <c r="G168" s="10" t="s">
-        <v>843</v>
-      </c>
-      <c r="H168" s="10" t="s">
-        <v>872</v>
-      </c>
-      <c r="I168" s="10"/>
-      <c r="J168" s="13">
-        <v>45957</v>
-      </c>
-      <c r="K168" s="12" t="s">
-        <v>895</v>
-      </c>
-      <c r="L168" s="16" t="s">
-        <v>41</v>
-      </c>
+    <row r="168" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="7"/>
+      <c r="B168" s="7"/>
+      <c r="C168" s="7"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
+      <c r="F168" s="7"/>
+      <c r="G168" s="7"/>
+      <c r="H168" s="7"/>
+      <c r="I168" s="7"/>
+      <c r="J168" s="3"/>
+      <c r="K168" s="3"/>
+      <c r="L168" s="7"/>
       <c r="M168" s="7"/>
       <c r="N168" s="7"/>
     </row>
-    <row r="169" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A169" s="10"/>
-      <c r="B169" s="10"/>
-      <c r="C169" s="10"/>
-      <c r="D169" s="10"/>
-      <c r="E169" s="10"/>
-      <c r="F169" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="G169" s="10"/>
-      <c r="H169" s="10"/>
-      <c r="I169" s="10"/>
-      <c r="J169" s="13"/>
-      <c r="K169" s="12"/>
-      <c r="L169" s="16"/>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B169" s="7"/>
+      <c r="C169" s="7"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="7"/>
+      <c r="F169" s="7"/>
+      <c r="G169" s="7"/>
+      <c r="H169" s="7"/>
+      <c r="I169" s="7"/>
+      <c r="J169" s="3"/>
+      <c r="K169" s="3"/>
+      <c r="L169" s="7"/>
       <c r="M169" s="7"/>
       <c r="N169" s="7"/>
     </row>
-    <row r="170" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A170" s="10" t="s">
-        <v>873</v>
-      </c>
-      <c r="B170" s="10" t="s">
-        <v>874</v>
-      </c>
-      <c r="C170" s="10" t="s">
-        <v>875</v>
-      </c>
-      <c r="D170" s="10" t="s">
-        <v>876</v>
-      </c>
-      <c r="E170" s="10" t="s">
-        <v>877</v>
-      </c>
-      <c r="F170" s="7" t="s">
-        <v>878</v>
-      </c>
-      <c r="G170" s="10"/>
-      <c r="H170" s="10" t="s">
-        <v>880</v>
-      </c>
-      <c r="I170" s="10"/>
-      <c r="J170" s="13">
-        <v>45957</v>
-      </c>
-      <c r="K170" s="12" t="s">
-        <v>895</v>
-      </c>
-      <c r="L170" s="18" t="s">
-        <v>147</v>
-      </c>
+    <row r="170" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B170" s="7"/>
+      <c r="C170" s="7"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="7"/>
+      <c r="F170" s="7"/>
+      <c r="G170" s="7"/>
+      <c r="H170" s="7"/>
+      <c r="I170" s="7"/>
+      <c r="J170" s="3"/>
+      <c r="K170" s="3"/>
+      <c r="L170" s="7"/>
       <c r="M170" s="7"/>
       <c r="N170" s="7"/>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A171" s="10"/>
-      <c r="B171" s="10"/>
-      <c r="C171" s="10"/>
-      <c r="D171" s="10"/>
-      <c r="E171" s="10"/>
-      <c r="F171" s="7" t="s">
-        <v>879</v>
-      </c>
-      <c r="G171" s="10"/>
-      <c r="H171" s="10"/>
-      <c r="I171" s="10"/>
-      <c r="J171" s="13"/>
-      <c r="K171" s="12"/>
-      <c r="L171" s="18"/>
+      <c r="B171" s="7"/>
+      <c r="C171" s="7"/>
+      <c r="D171" s="7"/>
+      <c r="E171" s="7"/>
+      <c r="F171" s="7"/>
+      <c r="G171" s="7"/>
+      <c r="H171" s="7"/>
+      <c r="I171" s="7"/>
+      <c r="J171" s="3"/>
+      <c r="K171" s="3"/>
+      <c r="L171" s="7"/>
       <c r="M171" s="7"/>
       <c r="N171" s="7"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A172" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B172" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="C172" s="10" t="s">
-        <v>883</v>
-      </c>
-      <c r="D172" s="10" t="s">
-        <v>881</v>
-      </c>
-      <c r="E172" s="10" t="s">
-        <v>884</v>
-      </c>
-      <c r="F172" s="7" t="s">
-        <v>885</v>
-      </c>
-      <c r="G172" s="10" t="s">
-        <v>843</v>
-      </c>
-      <c r="H172" s="10" t="s">
-        <v>887</v>
-      </c>
-      <c r="I172" s="10"/>
-      <c r="J172" s="13">
-        <v>45957</v>
-      </c>
-      <c r="K172" s="12" t="s">
-        <v>895</v>
-      </c>
-      <c r="L172" s="19" t="s">
-        <v>147</v>
-      </c>
+    <row r="172" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B172" s="7"/>
+      <c r="C172" s="7"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="7"/>
+      <c r="F172" s="7"/>
+      <c r="G172" s="7"/>
+      <c r="H172" s="7"/>
+      <c r="I172" s="7"/>
+      <c r="J172" s="3"/>
+      <c r="K172" s="3"/>
+      <c r="L172" s="7"/>
       <c r="M172" s="7" t="s">
-        <v>897</v>
+        <v>867</v>
       </c>
       <c r="N172" s="7"/>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A173" s="10"/>
-      <c r="B173" s="10"/>
-      <c r="C173" s="10"/>
-      <c r="D173" s="10"/>
-      <c r="E173" s="10"/>
-      <c r="F173" s="7" t="s">
-        <v>886</v>
-      </c>
-      <c r="G173" s="10"/>
-      <c r="H173" s="10"/>
-      <c r="I173" s="10"/>
-      <c r="J173" s="13"/>
-      <c r="K173" s="12"/>
-      <c r="L173" s="19"/>
+      <c r="B173" s="7"/>
+      <c r="C173" s="7"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
+      <c r="F173" s="7"/>
+      <c r="G173" s="7"/>
+      <c r="H173" s="7"/>
+      <c r="I173" s="7"/>
+      <c r="J173" s="3"/>
+      <c r="K173" s="3"/>
+      <c r="L173" s="7"/>
       <c r="M173" s="7"/>
       <c r="N173" s="7"/>
     </row>
     <row r="174" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="7" t="s">
-        <v>888</v>
-      </c>
-      <c r="B174" s="7" t="s">
-        <v>889</v>
-      </c>
-      <c r="C174" s="7" t="s">
-        <v>890</v>
-      </c>
-      <c r="D174" s="7" t="s">
-        <v>891</v>
-      </c>
-      <c r="E174" s="7" t="s">
-        <v>892</v>
-      </c>
-      <c r="F174" s="7" t="s">
-        <v>893</v>
-      </c>
-      <c r="G174" s="7" t="s">
-        <v>843</v>
-      </c>
-      <c r="H174" s="7" t="s">
-        <v>894</v>
-      </c>
+      <c r="B174" s="7"/>
+      <c r="C174" s="7"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="7"/>
+      <c r="F174" s="7"/>
+      <c r="G174" s="7"/>
+      <c r="H174" s="7"/>
       <c r="I174" s="7"/>
-      <c r="J174" s="6">
-        <v>45957</v>
-      </c>
-      <c r="K174" s="11" t="s">
-        <v>895</v>
-      </c>
-      <c r="L174" s="19" t="s">
-        <v>147</v>
-      </c>
+      <c r="J174" s="3"/>
+      <c r="K174" s="3"/>
+      <c r="L174" s="7"/>
       <c r="M174" s="7"/>
       <c r="N174" s="7"/>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A175" s="7"/>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
@@ -16616,7 +16435,6 @@
       <c r="L175" s="7"/>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A176" s="7"/>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
@@ -16629,8 +16447,7 @@
       <c r="K176" s="3"/>
       <c r="L176" s="7"/>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A177" s="7"/>
+    <row r="177" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
@@ -16643,8 +16460,7 @@
       <c r="K177" s="3"/>
       <c r="L177" s="7"/>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A178" s="7"/>
+    <row r="178" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
@@ -16654,11 +16470,10 @@
       <c r="H178" s="7"/>
       <c r="I178" s="7"/>
       <c r="J178" s="3"/>
-      <c r="K178" s="7"/>
+      <c r="K178" s="3"/>
       <c r="L178" s="7"/>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A179" s="7"/>
+    <row r="179" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
@@ -16671,8 +16486,7 @@
       <c r="K179" s="3"/>
       <c r="L179" s="7"/>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A180" s="7"/>
+    <row r="180" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
@@ -16685,7 +16499,7 @@
       <c r="K180" s="3"/>
       <c r="L180" s="7"/>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
@@ -16698,7 +16512,7 @@
       <c r="K181" s="3"/>
       <c r="L181" s="7"/>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
@@ -16711,7 +16525,7 @@
       <c r="K182" s="3"/>
       <c r="L182" s="7"/>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
@@ -16724,7 +16538,7 @@
       <c r="K183" s="3"/>
       <c r="L183" s="7"/>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
@@ -16737,7 +16551,7 @@
       <c r="K184" s="3"/>
       <c r="L184" s="7"/>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B185" s="7"/>
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
@@ -16750,7 +16564,7 @@
       <c r="K185" s="3"/>
       <c r="L185" s="7"/>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
@@ -16763,254 +16577,9 @@
       <c r="K186" s="3"/>
       <c r="L186" s="7"/>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B187" s="7"/>
-      <c r="C187" s="7"/>
-      <c r="D187" s="7"/>
-      <c r="E187" s="7"/>
-      <c r="F187" s="7"/>
-      <c r="G187" s="7"/>
-      <c r="H187" s="7"/>
-      <c r="I187" s="7"/>
-      <c r="J187" s="3"/>
-      <c r="K187" s="3"/>
-      <c r="L187" s="7"/>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B188" s="7"/>
-      <c r="C188" s="7"/>
-      <c r="D188" s="7"/>
-      <c r="E188" s="7"/>
-      <c r="F188" s="7"/>
-      <c r="G188" s="7"/>
-      <c r="H188" s="7"/>
-      <c r="I188" s="7"/>
-      <c r="J188" s="3"/>
-      <c r="K188" s="3"/>
-      <c r="L188" s="7"/>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B189" s="7"/>
-      <c r="C189" s="7"/>
-      <c r="D189" s="7"/>
-      <c r="E189" s="7"/>
-      <c r="F189" s="7"/>
-      <c r="G189" s="7"/>
-      <c r="H189" s="7"/>
-      <c r="I189" s="7"/>
-      <c r="J189" s="3"/>
-      <c r="K189" s="3"/>
-      <c r="L189" s="7"/>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B190" s="7"/>
-      <c r="C190" s="7"/>
-      <c r="D190" s="7"/>
-      <c r="E190" s="7"/>
-      <c r="F190" s="7"/>
-      <c r="G190" s="7"/>
-      <c r="H190" s="7"/>
-      <c r="I190" s="7"/>
-      <c r="J190" s="3"/>
-      <c r="K190" s="3"/>
-      <c r="L190" s="7"/>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B191" s="7"/>
-      <c r="C191" s="7"/>
-      <c r="D191" s="7"/>
-      <c r="E191" s="7"/>
-      <c r="F191" s="7"/>
-      <c r="G191" s="7"/>
-      <c r="H191" s="7"/>
-      <c r="I191" s="7"/>
-      <c r="J191" s="3"/>
-      <c r="K191" s="3"/>
-      <c r="L191" s="7"/>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B192" s="7"/>
-      <c r="C192" s="7"/>
-      <c r="D192" s="7"/>
-      <c r="E192" s="7"/>
-      <c r="F192" s="7"/>
-      <c r="G192" s="7"/>
-      <c r="H192" s="7"/>
-      <c r="I192" s="7"/>
-      <c r="J192" s="3"/>
-      <c r="K192" s="3"/>
-      <c r="L192" s="7"/>
-    </row>
-    <row r="193" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B193" s="7"/>
-      <c r="C193" s="7"/>
-      <c r="D193" s="7"/>
-      <c r="E193" s="7"/>
-      <c r="F193" s="7"/>
-      <c r="G193" s="7"/>
-      <c r="H193" s="7"/>
-      <c r="I193" s="7"/>
-      <c r="J193" s="3"/>
-      <c r="K193" s="3"/>
-      <c r="L193" s="7"/>
-    </row>
-    <row r="194" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B194" s="7"/>
-      <c r="C194" s="7"/>
-      <c r="D194" s="7"/>
-      <c r="E194" s="7"/>
-      <c r="F194" s="7"/>
-      <c r="G194" s="7"/>
-      <c r="H194" s="7"/>
-      <c r="I194" s="7"/>
-      <c r="J194" s="3"/>
-      <c r="K194" s="3"/>
-      <c r="L194" s="7"/>
-    </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B195" s="7"/>
-      <c r="C195" s="7"/>
-      <c r="D195" s="7"/>
-      <c r="E195" s="7"/>
-      <c r="F195" s="7"/>
-      <c r="G195" s="7"/>
-      <c r="H195" s="7"/>
-      <c r="I195" s="7"/>
-      <c r="J195" s="3"/>
-      <c r="K195" s="3"/>
-      <c r="L195" s="7"/>
-    </row>
-    <row r="196" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B196" s="7"/>
-      <c r="C196" s="7"/>
-      <c r="D196" s="7"/>
-      <c r="E196" s="7"/>
-      <c r="F196" s="7"/>
-      <c r="G196" s="7"/>
-      <c r="H196" s="7"/>
-      <c r="I196" s="7"/>
-      <c r="J196" s="3"/>
-      <c r="K196" s="3"/>
-      <c r="L196" s="7"/>
-    </row>
-    <row r="197" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B197" s="7"/>
-      <c r="C197" s="7"/>
-      <c r="D197" s="7"/>
-      <c r="E197" s="7"/>
-      <c r="F197" s="7"/>
-      <c r="G197" s="7"/>
-      <c r="H197" s="7"/>
-      <c r="I197" s="7"/>
-      <c r="J197" s="3"/>
-      <c r="K197" s="3"/>
-      <c r="L197" s="7"/>
-    </row>
-    <row r="198" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B198" s="7"/>
-      <c r="C198" s="7"/>
-      <c r="D198" s="7"/>
-      <c r="E198" s="7"/>
-      <c r="F198" s="7"/>
-      <c r="G198" s="7"/>
-      <c r="H198" s="7"/>
-      <c r="I198" s="7"/>
-      <c r="J198" s="3"/>
-      <c r="K198" s="3"/>
-      <c r="L198" s="7"/>
-    </row>
   </sheetData>
-  <mergeCells count="87">
-    <mergeCell ref="L155:L157"/>
-    <mergeCell ref="L158:L160"/>
-    <mergeCell ref="K172:K173"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="C172:C173"/>
-    <mergeCell ref="D172:D173"/>
-    <mergeCell ref="E172:E173"/>
-    <mergeCell ref="G172:G173"/>
-    <mergeCell ref="H172:H173"/>
-    <mergeCell ref="I172:I173"/>
-    <mergeCell ref="H170:H171"/>
-    <mergeCell ref="I170:I171"/>
-    <mergeCell ref="J170:J171"/>
-    <mergeCell ref="K170:K171"/>
-    <mergeCell ref="L170:L171"/>
-    <mergeCell ref="I168:I169"/>
-    <mergeCell ref="J168:J169"/>
-    <mergeCell ref="K168:K169"/>
-    <mergeCell ref="L168:L169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="C170:C171"/>
-    <mergeCell ref="D170:D171"/>
-    <mergeCell ref="E170:E171"/>
-    <mergeCell ref="G170:G171"/>
-    <mergeCell ref="J165:J167"/>
-    <mergeCell ref="K165:K167"/>
-    <mergeCell ref="L165:L167"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="C168:C169"/>
-    <mergeCell ref="D168:D169"/>
-    <mergeCell ref="E168:E169"/>
-    <mergeCell ref="G168:G169"/>
-    <mergeCell ref="H168:H169"/>
-    <mergeCell ref="K163:K164"/>
-    <mergeCell ref="L163:L164"/>
-    <mergeCell ref="A165:A167"/>
-    <mergeCell ref="B165:B167"/>
-    <mergeCell ref="C165:C167"/>
-    <mergeCell ref="D165:D167"/>
-    <mergeCell ref="E165:E167"/>
-    <mergeCell ref="G165:G167"/>
-    <mergeCell ref="H165:H167"/>
-    <mergeCell ref="I165:I167"/>
-    <mergeCell ref="L161:L162"/>
-    <mergeCell ref="A163:A164"/>
-    <mergeCell ref="B163:B164"/>
-    <mergeCell ref="C163:C164"/>
-    <mergeCell ref="D163:D164"/>
-    <mergeCell ref="E163:E164"/>
-    <mergeCell ref="G163:G164"/>
-    <mergeCell ref="H163:H164"/>
-    <mergeCell ref="I163:I164"/>
-    <mergeCell ref="J163:J164"/>
-    <mergeCell ref="E161:E162"/>
-    <mergeCell ref="G161:G162"/>
-    <mergeCell ref="H161:H162"/>
-    <mergeCell ref="I161:I162"/>
-    <mergeCell ref="J161:J162"/>
-    <mergeCell ref="K161:K162"/>
-    <mergeCell ref="G158:G160"/>
-    <mergeCell ref="H158:H160"/>
-    <mergeCell ref="I158:I160"/>
-    <mergeCell ref="J158:J160"/>
-    <mergeCell ref="K158:K160"/>
-    <mergeCell ref="H155:H157"/>
-    <mergeCell ref="I155:I157"/>
-    <mergeCell ref="J155:J157"/>
-    <mergeCell ref="K155:K157"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="B158:B160"/>
-    <mergeCell ref="C158:C160"/>
-    <mergeCell ref="D158:D160"/>
-    <mergeCell ref="E158:E160"/>
-    <mergeCell ref="A155:A157"/>
-    <mergeCell ref="B155:B157"/>
-    <mergeCell ref="C155:C157"/>
-    <mergeCell ref="D155:D157"/>
-    <mergeCell ref="E155:E157"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="C161:C162"/>
-    <mergeCell ref="D161:D162"/>
-    <mergeCell ref="J172:J173"/>
-    <mergeCell ref="G155:G157"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="L3:L154">
+  <conditionalFormatting sqref="L4:L155">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"PENDING"</formula>
     </cfRule>
@@ -17021,7 +16590,7 @@
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L175:L179 K178 L181:L198">
+  <conditionalFormatting sqref="L163:L167 K166 L169:L186">
     <cfRule type="cellIs" dxfId="2" priority="34" operator="equal">
       <formula>"PENDING"</formula>
     </cfRule>
@@ -17033,10 +16602,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L181:L198 K178 L175:L179 L3:L154" xr:uid="{1E8D2D6D-4EE7-40E2-A622-3458BDCF08AD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L169:L186 K166 L163:L167 L4:L155" xr:uid="{1E8D2D6D-4EE7-40E2-A622-3458BDCF08AD}">
       <formula1>"PASS,PENDING,FAIL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A175:A180 A3:A154" xr:uid="{F4675041-A1B8-4B65-822E-23AD6AB864A0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A163:A168 A4:A155" xr:uid="{F4675041-A1B8-4B65-822E-23AD6AB864A0}">
       <formula1>INDIRECT("Modulos[MODULOS]")</formula1>
     </dataValidation>
   </dataValidations>

--- a/Modelo Test Plan.xlsx
+++ b/Modelo Test Plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Downloads\CoderBits\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alumno\CoderBits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{583EBDDA-4325-4542-AB66-E04CB91D7A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD6634C-5DF2-4E15-B1DF-93BE23FD02D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{96765352-7388-4C61-94B8-5077301D3254}"/>
   </bookViews>
@@ -27,23 +27,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="865">
   <si>
     <t>MODULOS</t>
   </si>
@@ -144,48 +133,13 @@
     <t>Columna1</t>
   </si>
   <si>
-    <t>Generacion de tokens</t>
-  </si>
-  <si>
-    <t>El sistema debe generar tokens para el usuario que inicio sesion</t>
-  </si>
-  <si>
     <t>Unitaria / Interfaz</t>
   </si>
   <si>
-    <t>Tener un usuario registrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Ingresar a la plataforma                2. Ingresar usuario y contraseña    </t>
-  </si>
-  <si>
-    <t>"usuario": "will",
-"contrasena": "12345678"</t>
-  </si>
-  <si>
-    <t>Generacion de token: access: eyJhbGciOiJIUzI1N…..........                Refresh: eyJhbGciOiJIUzI1…..........</t>
-  </si>
-  <si>
     <t>Willy Condori</t>
   </si>
   <si>
     <t>PASS</t>
-  </si>
-  <si>
-    <t>Validacion de credenciales</t>
-  </si>
-  <si>
-    <t>El sistema debe mostrar mensaje de error en caso de credenciales incorrectas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Ingresar a la plataforma                2. Ingresar usuario y contraseña </t>
-  </si>
-  <si>
-    <t>"usuario": "will",
-"contrasena": "1234567"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "detail": "Credenciales incorrectas"</t>
   </si>
   <si>
     <t>Registro del personal</t>
@@ -241,9 +195,6 @@
   Status: 400 Bad Request</t>
   </si>
   <si>
-    <t>Validacion de correo</t>
-  </si>
-  <si>
     <t>El sistema debe mostrar mensaje de error si el correo ya existe</t>
   </si>
   <si>
@@ -272,9 +223,6 @@
   ],Status: 400 Bad Request</t>
   </si>
   <si>
-    <t>Validacion de numero</t>
-  </si>
-  <si>
     <t>El sistema debe mostrar mensaje de error si el numero de contacto es menor o mayor de 8 caracteres</t>
   </si>
   <si>
@@ -312,9 +260,6 @@
     <t>"numero": [
     "A valid number is required."
   ],Status: 400 Bad Request</t>
-  </si>
-  <si>
-    <t>Validacion de que el numero solo tenga valores numericos</t>
   </si>
   <si>
     <t>El sistema debe mostrar mensaje de error si el numero contiene letras o caracteres</t>
@@ -576,10 +521,6 @@
     <t>Validación de características</t>
   </si>
   <si>
-    <t>El sistema debe validar que las 78
- características de entrada sean las correctas</t>
-  </si>
-  <si>
     <t>Modelo cargado</t>
   </si>
   <si>
@@ -3092,13 +3033,26 @@
   </si>
   <si>
     <t>1. Acceder al módulo de personal2. Filtrar por usuarios eliminados3. Seleccionar “Restaurar</t>
+  </si>
+  <si>
+    <t>El sistema debe validar que las 40
+ características de entrada sean las correctas</t>
+  </si>
+  <si>
+    <t>Validacion de correo electronico</t>
+  </si>
+  <si>
+    <t>Validacion de numero telefonico</t>
+  </si>
+  <si>
+    <t>Validacion de que el numero de telefono solo tenga valores numericos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3374,7 +3328,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
+      <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4694,7 +4648,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4702,6 +4655,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -5245,7 +5199,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5253,6 +5206,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -9634,8 +9588,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{343BA946-EF1B-4A3B-B511-74A6334C62D3}" name="Tabla1" displayName="Tabla1" ref="A1:L162" totalsRowShown="0">
-  <autoFilter ref="A1:L162" xr:uid="{343BA946-EF1B-4A3B-B511-74A6334C62D3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{343BA946-EF1B-4A3B-B511-74A6334C62D3}" name="Tabla1" displayName="Tabla1" ref="A1:L160" totalsRowShown="0">
+  <autoFilter ref="A1:L160" xr:uid="{343BA946-EF1B-4A3B-B511-74A6334C62D3}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{9B76ED1C-581E-403B-9039-C4D1437837BF}" name="Columna1" dataDxfId="47"/>
     <tableColumn id="2" xr3:uid="{B227DD10-4412-4DA1-B9AE-57DBBAAC5FDB}" name="Columna2" dataDxfId="46"/>
@@ -9972,120 +9926,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ACCE336-D829-4280-938B-27FEC42D7852}">
   <dimension ref="A1:A33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="27.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="24.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="24.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="24.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" ht="24.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="24.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="24.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="24.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" ht="24.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="24.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" ht="24.75" customHeight="1">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" ht="24.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="24.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" ht="24.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" ht="24.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" ht="24.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="24.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="24.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="24.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="21" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="22" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="23" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="24" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="25" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="26" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="27" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="28" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="29" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="30" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="31" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="32" spans="1:1" ht="24.75" customHeight="1"/>
+    <row r="33" ht="24.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -10096,29 +10050,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D9AFB2-4BAC-4EFB-A2E7-92EA3A8E1FBC}">
-  <dimension ref="A1:N186"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N184"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="37.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="37.42578125" customWidth="1"/>
-    <col min="5" max="5" width="31.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="49.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="39.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="33.85546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="31.42578125" customWidth="1"/>
-    <col min="10" max="11" width="30.42578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" customWidth="1"/>
-    <col min="13" max="13" width="36.140625" customWidth="1"/>
+    <col min="1" max="1" width="22.875" customWidth="1"/>
+    <col min="2" max="2" width="30.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="37.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="37.375" customWidth="1"/>
+    <col min="5" max="5" width="31.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="49.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="39.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="31.375" customWidth="1"/>
+    <col min="10" max="11" width="30.375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.375" customWidth="1"/>
+    <col min="13" max="13" width="36.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="28.5">
       <c r="A1" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>868</v>
+        <v>853</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>21</v>
@@ -10151,7 +10105,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" s="2" customFormat="1">
       <c r="A2"/>
       <c r="D2"/>
       <c r="I2"/>
@@ -10165,7 +10119,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="41.25" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
@@ -10205,47 +10159,47 @@
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="114">
       <c r="A4" s="7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>35</v>
-      </c>
       <c r="E4" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="6">
         <v>45940</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="114">
       <c r="A5" s="7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>42</v>
@@ -10254,806 +10208,804 @@
         <v>43</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="6">
         <v>45940</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
     </row>
-    <row r="6" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="114">
       <c r="A6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="6">
         <v>45940</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
     </row>
-    <row r="7" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="114">
       <c r="A7" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>53</v>
+        <v>862</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>50</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="6">
         <v>45940</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
     </row>
-    <row r="8" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="114">
       <c r="A8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>57</v>
+        <v>39</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="6">
         <v>45940</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
     </row>
-    <row r="9" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="114">
       <c r="A9" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>59</v>
+        <v>863</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="6">
         <v>45940</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
     </row>
-    <row r="10" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="114">
       <c r="A10" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="6">
         <v>45940</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
     </row>
-    <row r="11" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="114">
       <c r="A11" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>66</v>
+        <v>864</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="6">
         <v>45940</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
     </row>
-    <row r="12" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="42.75">
       <c r="A12" s="7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="6">
         <v>45940</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
     </row>
-    <row r="13" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="42.75">
       <c r="A13" s="7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="6">
         <v>45940</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M13" s="7"/>
+        <v>35</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>78</v>
+      </c>
       <c r="N13" s="7"/>
     </row>
-    <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="28.5">
       <c r="A14" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="6">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
     </row>
-    <row r="15" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="28.5">
       <c r="A15" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>86</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="6">
         <v>45940</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>92</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="M15" s="7"/>
       <c r="N15" s="7"/>
     </row>
-    <row r="16" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="42.75">
       <c r="A16" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="G16" s="7"/>
+      <c r="H16" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>91</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="6">
-        <v>45945</v>
+        <v>45940</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
     </row>
-    <row r="17" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="42.75">
       <c r="A17" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>96</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="G17" s="7"/>
       <c r="H17" s="7" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="6">
         <v>45940</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
     </row>
-    <row r="18" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="128.25">
       <c r="A18" s="7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="G18" s="7"/>
+        <v>87</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>94</v>
+      </c>
       <c r="H18" s="7" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="6">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
     </row>
-    <row r="19" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="42.75">
       <c r="A19" s="7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="G19" s="7"/>
+        <v>87</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>94</v>
+      </c>
       <c r="H19" s="7" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="6">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
     </row>
-    <row r="20" spans="1:14" ht="135" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="42.75">
       <c r="A20" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="F20" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>108</v>
-      </c>
       <c r="H20" s="7" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="6">
         <v>45945</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
     </row>
-    <row r="21" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="71.25">
       <c r="A21" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="6">
         <v>45945</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
     </row>
-    <row r="22" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="185.25">
       <c r="A22" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="6">
         <v>45945</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M22" s="7"/>
+        <v>35</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>117</v>
+      </c>
       <c r="N22" s="7"/>
     </row>
-    <row r="23" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="128.25">
       <c r="A23" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C23" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="J23" s="6">
+        <v>45947</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="N23" s="7"/>
+    </row>
+    <row r="24" spans="1:14" ht="28.5">
+      <c r="A24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="C24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="H23" s="7" t="s">
+      <c r="N24" s="7"/>
+    </row>
+    <row r="25" spans="1:14" ht="42.75">
+      <c r="A25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I23" s="7"/>
-      <c r="J23" s="6">
-        <v>45945</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-    </row>
-    <row r="24" spans="1:14" ht="195" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D24" s="7" t="s">
+      <c r="E25" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="I24" s="7"/>
-      <c r="J24" s="6">
-        <v>45945</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="N24" s="7"/>
-    </row>
-    <row r="25" spans="1:14" ht="135" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="J25" s="6">
-        <v>45947</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>130</v>
-      </c>
       <c r="N25" s="7"/>
     </row>
-    <row r="26" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="42.75">
       <c r="A26" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>135</v>
@@ -11069,315 +11021,317 @@
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="N26" s="7"/>
     </row>
-    <row r="27" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="42.75">
       <c r="A27" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="G27" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="N27" s="7"/>
     </row>
-    <row r="28" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="28.5">
       <c r="A28" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="E28" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E28" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="H28" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="N28" s="7"/>
     </row>
-    <row r="29" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="42.75">
       <c r="A29" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="F29" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="H29" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="N29" s="7"/>
     </row>
-    <row r="30" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="28.5">
       <c r="A30" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="F30" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="F30" s="7" t="s">
+      <c r="G30" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="N30" s="7"/>
     </row>
-    <row r="31" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="28.5">
       <c r="A31" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="G31" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="N31" s="7"/>
     </row>
-    <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="28.5">
       <c r="A32" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="G32" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="N32" s="7"/>
     </row>
-    <row r="33" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="28.5">
       <c r="A33" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="F33" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="G33" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="H33" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>41</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="M33" s="7"/>
       <c r="N33" s="7"/>
     </row>
-    <row r="34" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>10</v>
+    <row r="34" spans="1:14" ht="42.75">
+      <c r="A34" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="F34" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="G34" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="H34" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="M34" s="7"/>
       <c r="N34" s="7"/>
     </row>
-    <row r="35" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>10</v>
+    <row r="35" spans="1:14" ht="57">
+      <c r="A35" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>195</v>
@@ -11386,10 +11340,10 @@
         <v>196</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>198</v>
@@ -11402,32 +11356,32 @@
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
     </row>
-    <row r="36" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="57">
       <c r="A36" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>205</v>
@@ -11440,4800 +11394,4756 @@
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M36" s="7"/>
       <c r="N36" s="7"/>
     </row>
-    <row r="37" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="42.75">
       <c r="A37" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="G37" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="H37" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
     </row>
-    <row r="38" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" ht="42.75">
       <c r="A38" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
     </row>
-    <row r="39" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" ht="42.75">
       <c r="A39" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>212</v>
+        <v>33</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
     </row>
-    <row r="40" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="42.75">
       <c r="A40" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
     </row>
-    <row r="41" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="42.75">
       <c r="A41" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
     </row>
-    <row r="42" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="42.75">
       <c r="A42" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>212</v>
+        <v>33</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
     </row>
-    <row r="43" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="57">
       <c r="A43" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
     </row>
-    <row r="44" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" ht="42.75">
       <c r="A44" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
     </row>
-    <row r="45" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="42.75">
       <c r="A45" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>257</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
     </row>
-    <row r="46" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="57">
       <c r="A46" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>263</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
     </row>
-    <row r="47" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="57">
       <c r="A47" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>264</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>268</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
     </row>
-    <row r="48" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="42.75">
       <c r="A48" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
     </row>
-    <row r="49" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" ht="42.75">
       <c r="A49" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>279</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
     </row>
-    <row r="50" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="42.75">
       <c r="A50" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
     </row>
-    <row r="51" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="42.75">
       <c r="A51" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="H51" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
     </row>
-    <row r="52" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="42.75">
       <c r="A52" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
     </row>
-    <row r="53" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" ht="42.75">
       <c r="A53" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="H53" s="3" t="s">
         <v>295</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>300</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
     </row>
-    <row r="54" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="42.75">
       <c r="A54" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>134</v>
+        <v>282</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
     </row>
-    <row r="55" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="57">
       <c r="A55" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>276</v>
+        <v>245</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
     </row>
-    <row r="56" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" ht="57">
       <c r="A56" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
     </row>
-    <row r="57" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" ht="42.75">
       <c r="A57" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>260</v>
+        <v>188</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
     </row>
-    <row r="58" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" ht="42.75">
       <c r="A58" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>297</v>
+        <v>204</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
     </row>
-    <row r="59" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" ht="57">
       <c r="A59" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
     </row>
-    <row r="60" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" ht="57">
       <c r="A60" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
     </row>
-    <row r="61" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" ht="57">
       <c r="A61" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
     </row>
-    <row r="62" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" ht="57">
       <c r="A62" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>212</v>
+        <v>120</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M62" s="7"/>
       <c r="N62" s="7"/>
     </row>
-    <row r="63" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" ht="42.75">
       <c r="A63" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>203</v>
+        <v>282</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
     </row>
-    <row r="64" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" ht="57">
       <c r="A64" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M64" s="7"/>
       <c r="N64" s="7"/>
     </row>
-    <row r="65" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" ht="57">
       <c r="A65" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>297</v>
+        <v>188</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M65" s="7"/>
       <c r="N65" s="7"/>
     </row>
-    <row r="66" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" ht="57">
       <c r="A66" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>203</v>
+        <v>33</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M66" s="7"/>
       <c r="N66" s="7"/>
     </row>
-    <row r="67" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" ht="57">
       <c r="A67" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M67" s="7"/>
       <c r="N67" s="7"/>
     </row>
-    <row r="68" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" ht="57">
       <c r="A68" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I68" s="1"/>
       <c r="J68" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M68" s="7"/>
       <c r="N68" s="7"/>
     </row>
-    <row r="69" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" ht="57">
       <c r="A69" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>219</v>
+        <v>282</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="I69" s="1"/>
       <c r="J69" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M69" s="7"/>
       <c r="N69" s="7"/>
     </row>
-    <row r="70" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" ht="42.75">
       <c r="A70" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="I70" s="1"/>
       <c r="J70" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M70" s="7"/>
       <c r="N70" s="7"/>
     </row>
-    <row r="71" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" ht="57">
       <c r="A71" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M71" s="7"/>
       <c r="N71" s="7"/>
     </row>
-    <row r="72" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" ht="42.75">
       <c r="A72" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M72" s="7"/>
       <c r="N72" s="7"/>
     </row>
-    <row r="73" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" ht="42.75">
       <c r="A73" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>297</v>
+        <v>204</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M73" s="7"/>
       <c r="N73" s="7"/>
     </row>
-    <row r="74" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" ht="57">
       <c r="A74" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>276</v>
+        <v>204</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M74" s="7"/>
       <c r="N74" s="7"/>
     </row>
-    <row r="75" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" ht="42.75">
       <c r="A75" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M75" s="7"/>
       <c r="N75" s="7"/>
     </row>
-    <row r="76" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" ht="57">
       <c r="A76" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>219</v>
+        <v>282</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M76" s="7"/>
       <c r="N76" s="7"/>
     </row>
-    <row r="77" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" ht="42.75">
       <c r="A77" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>276</v>
+        <v>204</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M77" s="7"/>
       <c r="N77" s="7"/>
     </row>
-    <row r="78" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" ht="57">
       <c r="A78" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>297</v>
+        <v>33</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M78" s="7"/>
       <c r="N78" s="7"/>
     </row>
-    <row r="79" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" ht="57">
       <c r="A79" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M79" s="7"/>
       <c r="N79" s="7"/>
     </row>
-    <row r="80" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" ht="42.75">
       <c r="A80" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>35</v>
+        <v>282</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M80" s="7"/>
       <c r="N80" s="7"/>
     </row>
-    <row r="81" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" ht="42.75">
       <c r="A81" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M81" s="7"/>
       <c r="N81" s="7"/>
     </row>
-    <row r="82" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" ht="42.75">
       <c r="A82" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>297</v>
+        <v>33</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M82" s="7"/>
       <c r="N82" s="7"/>
     </row>
-    <row r="83" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" ht="42.75">
       <c r="A83" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>276</v>
+        <v>120</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M83" s="7"/>
       <c r="N83" s="7"/>
     </row>
-    <row r="84" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" ht="42.75">
       <c r="A84" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>35</v>
+        <v>261</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M84" s="7"/>
       <c r="N84" s="7"/>
     </row>
-    <row r="85" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" ht="42.75">
       <c r="A85" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>134</v>
+        <v>282</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M85" s="7"/>
       <c r="N85" s="7"/>
     </row>
-    <row r="86" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" ht="42.75">
       <c r="A86" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>276</v>
+        <v>188</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M86" s="7"/>
       <c r="N86" s="7"/>
     </row>
-    <row r="87" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" ht="42.75">
       <c r="A87" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>297</v>
+        <v>120</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M87" s="7"/>
       <c r="N87" s="7"/>
     </row>
-    <row r="88" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" ht="42.75">
       <c r="A88" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>203</v>
+        <v>33</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M88" s="7"/>
       <c r="N88" s="7"/>
     </row>
-    <row r="89" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" ht="42.75">
       <c r="A89" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M89" s="7"/>
       <c r="N89" s="7"/>
     </row>
-    <row r="90" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" ht="42.75">
       <c r="A90" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M90" s="7"/>
       <c r="N90" s="7"/>
     </row>
-    <row r="91" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" ht="42.75">
       <c r="A91" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M91" s="7"/>
       <c r="N91" s="7"/>
     </row>
-    <row r="92" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" ht="42.75">
       <c r="A92" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M92" s="7"/>
       <c r="N92" s="7"/>
     </row>
-    <row r="93" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" ht="42.75">
       <c r="A93" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>219</v>
+        <v>33</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M93" s="7"/>
       <c r="N93" s="7"/>
     </row>
-    <row r="94" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" ht="42.75">
       <c r="A94" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>134</v>
+        <v>204</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="I94" s="1"/>
       <c r="J94" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M94" s="7"/>
       <c r="N94" s="7"/>
     </row>
-    <row r="95" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" ht="57">
       <c r="A95" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>35</v>
+        <v>188</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M95" s="7"/>
       <c r="N95" s="7"/>
     </row>
-    <row r="96" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" ht="42.75">
       <c r="A96" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M96" s="7"/>
       <c r="N96" s="7"/>
     </row>
-    <row r="97" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" ht="57">
       <c r="A97" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>203</v>
+        <v>282</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M97" s="7"/>
       <c r="N97" s="7"/>
     </row>
-    <row r="98" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" ht="57">
       <c r="A98" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M98" s="7"/>
       <c r="N98" s="7"/>
     </row>
-    <row r="99" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" ht="42.75">
       <c r="A99" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>297</v>
+        <v>245</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M99" s="7"/>
       <c r="N99" s="7"/>
     </row>
-    <row r="100" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" ht="42.75">
       <c r="A100" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M100" s="7"/>
       <c r="N100" s="7"/>
     </row>
-    <row r="101" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" ht="57">
       <c r="A101" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M101" s="7"/>
       <c r="N101" s="7"/>
     </row>
-    <row r="102" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" ht="57">
       <c r="A102" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>276</v>
+        <v>204</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M102" s="7"/>
       <c r="N102" s="7"/>
     </row>
-    <row r="103" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" ht="57">
       <c r="A103" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>297</v>
+        <v>188</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M103" s="7"/>
       <c r="N103" s="7"/>
     </row>
-    <row r="104" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" ht="57">
       <c r="A104" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M104" s="7"/>
       <c r="N104" s="7"/>
     </row>
-    <row r="105" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" ht="42.75">
       <c r="A105" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>203</v>
+        <v>261</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M105" s="7"/>
       <c r="N105" s="7"/>
     </row>
-    <row r="106" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" ht="57">
       <c r="A106" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M106" s="7"/>
       <c r="N106" s="7"/>
     </row>
-    <row r="107" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" ht="42.75">
       <c r="A107" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>276</v>
+        <v>33</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M107" s="7"/>
       <c r="N107" s="7"/>
     </row>
-    <row r="108" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" ht="57">
       <c r="A108" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>260</v>
+        <v>204</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M108" s="7"/>
       <c r="N108" s="7"/>
     </row>
-    <row r="109" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" ht="57">
       <c r="A109" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>35</v>
+        <v>204</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M109" s="7"/>
       <c r="N109" s="7"/>
     </row>
-    <row r="110" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" ht="57">
       <c r="A110" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M110" s="7"/>
       <c r="N110" s="7"/>
     </row>
-    <row r="111" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" ht="42.75">
       <c r="A111" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>219</v>
+        <v>282</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M111" s="7"/>
       <c r="N111" s="7"/>
     </row>
-    <row r="112" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" ht="42.75">
       <c r="A112" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M112" s="7"/>
       <c r="N112" s="7"/>
     </row>
-    <row r="113" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" ht="57">
       <c r="A113" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>297</v>
+        <v>204</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M113" s="7"/>
       <c r="N113" s="7"/>
     </row>
-    <row r="114" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" ht="57">
       <c r="A114" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>260</v>
+        <v>33</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M114" s="7"/>
       <c r="N114" s="7"/>
     </row>
-    <row r="115" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" ht="57">
       <c r="A115" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M115" s="7"/>
       <c r="N115" s="7"/>
     </row>
-    <row r="116" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" ht="57">
       <c r="A116" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>35</v>
+        <v>245</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M116" s="7"/>
       <c r="N116" s="7"/>
     </row>
-    <row r="117" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" ht="42.75">
       <c r="A117" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>276</v>
+        <v>204</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M117" s="7"/>
       <c r="N117" s="7"/>
     </row>
-    <row r="118" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" ht="42.75">
       <c r="A118" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>260</v>
+        <v>188</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M118" s="7"/>
       <c r="N118" s="7"/>
     </row>
-    <row r="119" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" ht="42.75">
       <c r="A119" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>219</v>
+        <v>33</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="I119" s="1"/>
       <c r="J119" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M119" s="7"/>
       <c r="N119" s="7"/>
     </row>
-    <row r="120" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" ht="42.75">
       <c r="A120" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>203</v>
+        <v>33</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="I120" s="1"/>
       <c r="J120" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M120" s="7"/>
       <c r="N120" s="7"/>
     </row>
-    <row r="121" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" ht="42.75">
       <c r="A121" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>35</v>
+        <v>261</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="I121" s="1"/>
       <c r="J121" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M121" s="7"/>
       <c r="N121" s="7"/>
     </row>
-    <row r="122" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" ht="42.75">
       <c r="A122" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="I122" s="1"/>
       <c r="J122" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M122" s="7"/>
       <c r="N122" s="7"/>
     </row>
-    <row r="123" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" ht="42.75">
       <c r="A123" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>276</v>
+        <v>33</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="I123" s="1"/>
       <c r="J123" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M123" s="7"/>
       <c r="N123" s="7"/>
     </row>
-    <row r="124" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" ht="42.75">
       <c r="A124" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="I124" s="1"/>
       <c r="J124" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M124" s="7"/>
       <c r="N124" s="7"/>
     </row>
-    <row r="125" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" ht="42.75">
       <c r="A125" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>35</v>
+        <v>282</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="I125" s="1"/>
       <c r="J125" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M125" s="7"/>
       <c r="N125" s="7"/>
     </row>
-    <row r="126" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" ht="42.75">
       <c r="A126" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>35</v>
+        <v>282</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="I126" s="1"/>
       <c r="J126" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M126" s="7"/>
       <c r="N126" s="7"/>
     </row>
-    <row r="127" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" ht="42.75">
       <c r="A127" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>297</v>
+        <v>197</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="I127" s="1"/>
       <c r="J127" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M127" s="7"/>
       <c r="N127" s="7"/>
     </row>
-    <row r="128" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" ht="42.75">
       <c r="A128" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="I128" s="1"/>
       <c r="J128" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M128" s="7"/>
       <c r="N128" s="7"/>
     </row>
-    <row r="129" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" ht="42.75">
       <c r="A129" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="I129" s="1"/>
       <c r="J129" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M129" s="7"/>
       <c r="N129" s="7"/>
     </row>
-    <row r="130" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" ht="42.75">
       <c r="A130" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>297</v>
+        <v>204</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="I130" s="1"/>
       <c r="J130" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M130" s="7"/>
       <c r="N130" s="7"/>
     </row>
-    <row r="131" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" ht="42.75">
       <c r="A131" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>276</v>
+        <v>188</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M131" s="7"/>
       <c r="N131" s="7"/>
     </row>
-    <row r="132" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" ht="42.75">
       <c r="A132" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>219</v>
+        <v>282</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M132" s="7"/>
       <c r="N132" s="7"/>
     </row>
-    <row r="133" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" ht="45" customHeight="1">
       <c r="A133" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>203</v>
+        <v>261</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="M133" s="7"/>
       <c r="N133" s="7"/>
     </row>
-    <row r="134" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A134" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B134" s="3" t="s">
+    <row r="134" spans="1:14" ht="28.5">
+      <c r="A134" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C134" t="s">
+        <v>697</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="I134" s="7"/>
+      <c r="J134" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K134" s="7" t="s">
         <v>701</v>
       </c>
-      <c r="C134" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E134" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F134" s="7" t="s">
-        <v>703</v>
-      </c>
-      <c r="G134" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="H134" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="I134" s="1"/>
-      <c r="J134" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="K134" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="L134" s="1" t="s">
-        <v>147</v>
+      <c r="L134" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="M134" s="7"/>
       <c r="N134" s="7"/>
     </row>
-    <row r="135" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B135" s="3" t="s">
+    <row r="135" spans="1:14" ht="28.5">
+      <c r="A135" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="C135" t="s">
+        <v>703</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F135" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="G135" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="H135" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="C135" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F135" s="7" t="s">
-        <v>708</v>
-      </c>
-      <c r="G135" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="H135" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="I135" s="1"/>
-      <c r="J135" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="K135" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="L135" s="11" t="s">
-        <v>147</v>
+      <c r="I135" s="7"/>
+      <c r="J135" s="6">
+        <v>45950</v>
+      </c>
+      <c r="K135" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="L135" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="M135" s="7"/>
       <c r="N135" s="7"/>
     </row>
-    <row r="136" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" ht="15" customHeight="1">
       <c r="A136" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C136" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>713</v>
+        <v>811</v>
       </c>
       <c r="G136" s="7" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="H136" s="7" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="I136" s="7"/>
       <c r="J136" s="6">
         <v>45950</v>
       </c>
       <c r="K136" s="7" t="s">
-        <v>716</v>
-      </c>
-      <c r="L136" s="11" t="s">
-        <v>41</v>
+        <v>701</v>
+      </c>
+      <c r="L136" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="M136" s="7"/>
       <c r="N136" s="7"/>
     </row>
-    <row r="137" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" ht="28.5">
       <c r="A137" s="7" t="s">
-        <v>12</v>
+        <v>711</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="C137" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>203</v>
+        <v>261</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="G137" s="7" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="H137" s="7" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="I137" s="7"/>
       <c r="J137" s="6">
         <v>45950</v>
       </c>
       <c r="K137" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M137" s="7"/>
       <c r="N137" s="7"/>
     </row>
-    <row r="138" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" ht="28.5">
       <c r="A138" s="7" t="s">
-        <v>12</v>
+        <v>711</v>
       </c>
       <c r="B138" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="C138" t="s">
+        <v>718</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>719</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="G138" s="7" t="s">
+        <v>721</v>
+      </c>
+      <c r="H138" s="7" t="s">
         <v>722</v>
-      </c>
-      <c r="C138" t="s">
-        <v>723</v>
-      </c>
-      <c r="D138" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E138" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F138" s="7" t="s">
-        <v>826</v>
-      </c>
-      <c r="G138" s="7" t="s">
-        <v>724</v>
-      </c>
-      <c r="H138" s="7" t="s">
-        <v>725</v>
       </c>
       <c r="I138" s="7"/>
       <c r="J138" s="6">
         <v>45950</v>
       </c>
       <c r="K138" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M138" s="7"/>
       <c r="N138" s="7"/>
     </row>
-    <row r="139" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" ht="28.5">
       <c r="A139" s="7" t="s">
+        <v>711</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>723</v>
+      </c>
+      <c r="C139" t="s">
+        <v>724</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>725</v>
+      </c>
+      <c r="F139" s="7" t="s">
         <v>726</v>
       </c>
-      <c r="B139" s="7" t="s">
+      <c r="G139" s="7" t="s">
         <v>727</v>
       </c>
-      <c r="C139" t="s">
+      <c r="H139" s="7" t="s">
         <v>728</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E139" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F139" s="7" t="s">
-        <v>729</v>
-      </c>
-      <c r="G139" s="7" t="s">
-        <v>730</v>
-      </c>
-      <c r="H139" s="7" t="s">
-        <v>731</v>
       </c>
       <c r="I139" s="7"/>
       <c r="J139" s="6">
         <v>45950</v>
       </c>
       <c r="K139" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M139" s="7"/>
       <c r="N139" s="7"/>
     </row>
-    <row r="140" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" ht="15" customHeight="1">
       <c r="A140" s="7" t="s">
-        <v>726</v>
+        <v>711</v>
       </c>
       <c r="B140" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="C140" t="s">
+        <v>730</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>731</v>
+      </c>
+      <c r="G140" s="7" t="s">
         <v>732</v>
       </c>
-      <c r="C140" t="s">
+      <c r="H140" s="7" t="s">
         <v>733</v>
-      </c>
-      <c r="D140" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E140" s="7" t="s">
-        <v>734</v>
-      </c>
-      <c r="F140" s="7" t="s">
-        <v>735</v>
-      </c>
-      <c r="G140" s="7" t="s">
-        <v>736</v>
-      </c>
-      <c r="H140" s="7" t="s">
-        <v>737</v>
       </c>
       <c r="I140" s="7"/>
       <c r="J140" s="6">
         <v>45950</v>
       </c>
       <c r="K140" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M140" s="7"/>
       <c r="N140" s="7"/>
     </row>
-    <row r="141" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" ht="28.5">
       <c r="A141" s="7" t="s">
-        <v>726</v>
+        <v>5</v>
       </c>
       <c r="B141" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="C141" t="s">
+        <v>735</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="G141" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="H141" s="7" t="s">
         <v>738</v>
-      </c>
-      <c r="C141" t="s">
-        <v>739</v>
-      </c>
-      <c r="D141" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E141" s="7" t="s">
-        <v>740</v>
-      </c>
-      <c r="F141" s="7" t="s">
-        <v>741</v>
-      </c>
-      <c r="G141" s="7" t="s">
-        <v>742</v>
-      </c>
-      <c r="H141" s="7" t="s">
-        <v>743</v>
       </c>
       <c r="I141" s="7"/>
       <c r="J141" s="6">
         <v>45950</v>
       </c>
       <c r="K141" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M141" s="7"/>
       <c r="N141" s="7"/>
     </row>
-    <row r="142" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" ht="15" customHeight="1">
       <c r="A142" s="7" t="s">
-        <v>726</v>
+        <v>5</v>
       </c>
       <c r="B142" s="7" t="s">
+        <v>739</v>
+      </c>
+      <c r="C142" t="s">
+        <v>740</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>743</v>
+      </c>
+      <c r="G142" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="C142" t="s">
+      <c r="H142" s="7" t="s">
         <v>745</v>
-      </c>
-      <c r="D142" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E142" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F142" s="7" t="s">
-        <v>746</v>
-      </c>
-      <c r="G142" s="7" t="s">
-        <v>747</v>
-      </c>
-      <c r="H142" s="7" t="s">
-        <v>748</v>
       </c>
       <c r="I142" s="7"/>
       <c r="J142" s="6">
         <v>45950</v>
       </c>
       <c r="K142" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M142" s="7"/>
       <c r="N142" s="7"/>
     </row>
-    <row r="143" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" ht="28.5">
       <c r="A143" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B143" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="C143" t="s">
+        <v>747</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="G143" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="C143" t="s">
+      <c r="H143" s="7" t="s">
         <v>750</v>
-      </c>
-      <c r="D143" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E143" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F143" s="7" t="s">
-        <v>751</v>
-      </c>
-      <c r="G143" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="H143" s="7" t="s">
-        <v>753</v>
       </c>
       <c r="I143" s="7"/>
       <c r="J143" s="6">
         <v>45950</v>
       </c>
       <c r="K143" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M143" s="7"/>
       <c r="N143" s="7"/>
     </row>
-    <row r="144" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" ht="75" customHeight="1">
       <c r="A144" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B144" s="7" t="s">
+        <v>751</v>
+      </c>
+      <c r="C144" t="s">
+        <v>752</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="G144" s="7" t="s">
         <v>754</v>
       </c>
-      <c r="C144" t="s">
+      <c r="H144" s="7" t="s">
         <v>755</v>
-      </c>
-      <c r="D144" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="E144" s="7" t="s">
-        <v>757</v>
-      </c>
-      <c r="F144" s="7" t="s">
-        <v>758</v>
-      </c>
-      <c r="G144" s="7" t="s">
-        <v>759</v>
-      </c>
-      <c r="H144" s="7" t="s">
-        <v>760</v>
       </c>
       <c r="I144" s="7"/>
       <c r="J144" s="6">
         <v>45950</v>
       </c>
       <c r="K144" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M144" s="7"/>
       <c r="N144" s="7"/>
     </row>
-    <row r="145" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" ht="15" customHeight="1">
       <c r="A145" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="C145" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>756</v>
+        <v>204</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>757</v>
+        <v>189</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="G145" s="7" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="H145" s="7" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="I145" s="7"/>
       <c r="J145" s="6">
         <v>45950</v>
       </c>
       <c r="K145" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M145" s="7"/>
       <c r="N145" s="7"/>
     </row>
-    <row r="146" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" ht="15" customHeight="1">
       <c r="A146" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C146" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>276</v>
+        <v>741</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>769</v>
+        <v>737</v>
       </c>
       <c r="H146" s="7" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="I146" s="7"/>
       <c r="J146" s="6">
         <v>45950</v>
       </c>
       <c r="K146" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M146" s="7"/>
       <c r="N146" s="7"/>
     </row>
-    <row r="147" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" ht="28.5">
       <c r="A147" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="C147" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="H147" s="7" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="I147" s="7"/>
       <c r="J147" s="6">
         <v>45950</v>
       </c>
       <c r="K147" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M147" s="7"/>
       <c r="N147" s="7"/>
     </row>
-    <row r="148" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" ht="28.5">
       <c r="A148" s="7" t="s">
-        <v>6</v>
+        <v>770</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>776</v>
+        <v>36</v>
       </c>
       <c r="C148" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>756</v>
+        <v>261</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>752</v>
+        <v>773</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="I148" s="7"/>
       <c r="J148" s="6">
         <v>45950</v>
       </c>
       <c r="K148" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M148" s="7"/>
       <c r="N148" s="7"/>
     </row>
-    <row r="149" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" ht="15" customHeight="1">
       <c r="A149" s="7" t="s">
-        <v>6</v>
+        <v>770</v>
       </c>
       <c r="B149" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="C149" t="s">
+        <v>776</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="F149" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="G149" s="7" t="s">
+        <v>779</v>
+      </c>
+      <c r="H149" s="7" t="s">
         <v>780</v>
-      </c>
-      <c r="C149" t="s">
-        <v>781</v>
-      </c>
-      <c r="D149" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E149" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F149" s="7" t="s">
-        <v>782</v>
-      </c>
-      <c r="G149" s="7" t="s">
-        <v>783</v>
-      </c>
-      <c r="H149" s="7" t="s">
-        <v>784</v>
       </c>
       <c r="I149" s="7"/>
       <c r="J149" s="6">
         <v>45950</v>
       </c>
       <c r="K149" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M149" s="7"/>
       <c r="N149" s="7"/>
     </row>
-    <row r="150" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" ht="28.5">
       <c r="A150" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>782</v>
+      </c>
+      <c r="C150" t="s">
+        <v>783</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="G150" s="7" t="s">
         <v>785</v>
       </c>
-      <c r="B150" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C150" t="s">
+      <c r="H150" s="7" t="s">
         <v>786</v>
-      </c>
-      <c r="D150" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E150" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F150" s="7" t="s">
-        <v>787</v>
-      </c>
-      <c r="G150" s="7" t="s">
-        <v>788</v>
-      </c>
-      <c r="H150" s="7" t="s">
-        <v>789</v>
       </c>
       <c r="I150" s="7"/>
       <c r="J150" s="6">
         <v>45950</v>
       </c>
       <c r="K150" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M150" s="7"/>
       <c r="N150" s="7"/>
     </row>
-    <row r="151" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" ht="28.5">
       <c r="A151" s="7" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B151" s="7" t="s">
+        <v>787</v>
+      </c>
+      <c r="C151" t="s">
+        <v>788</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>789</v>
+      </c>
+      <c r="F151" s="7" t="s">
         <v>790</v>
       </c>
-      <c r="C151" t="s">
+      <c r="G151" s="7" t="s">
         <v>791</v>
       </c>
-      <c r="D151" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="E151" s="7" t="s">
+      <c r="H151" s="7" t="s">
         <v>792</v>
-      </c>
-      <c r="F151" s="7" t="s">
-        <v>793</v>
-      </c>
-      <c r="G151" s="7" t="s">
-        <v>794</v>
-      </c>
-      <c r="H151" s="7" t="s">
-        <v>795</v>
       </c>
       <c r="I151" s="7"/>
       <c r="J151" s="6">
         <v>45950</v>
       </c>
       <c r="K151" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M151" s="7"/>
       <c r="N151" s="7"/>
     </row>
-    <row r="152" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" ht="15" customHeight="1">
       <c r="A152" s="7" t="s">
+        <v>793</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="C152" t="s">
+        <v>795</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F152" s="7" t="s">
         <v>796</v>
       </c>
-      <c r="B152" s="7" t="s">
+      <c r="G152" s="7" t="s">
         <v>797</v>
       </c>
-      <c r="C152" t="s">
+      <c r="H152" s="7" t="s">
         <v>798</v>
-      </c>
-      <c r="D152" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E152" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F152" s="7" t="s">
-        <v>799</v>
-      </c>
-      <c r="G152" s="7" t="s">
-        <v>800</v>
-      </c>
-      <c r="H152" s="7" t="s">
-        <v>801</v>
       </c>
       <c r="I152" s="7"/>
       <c r="J152" s="6">
         <v>45950</v>
       </c>
       <c r="K152" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M152" s="7"/>
       <c r="N152" s="7"/>
     </row>
-    <row r="153" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" ht="15" customHeight="1">
       <c r="A153" s="7" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B153" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="C153" t="s">
+        <v>800</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="F153" s="7" t="s">
         <v>802</v>
       </c>
-      <c r="C153" t="s">
+      <c r="G153" s="7" t="s">
         <v>803</v>
       </c>
-      <c r="D153" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E153" s="7" t="s">
+      <c r="H153" s="7" t="s">
         <v>804</v>
-      </c>
-      <c r="F153" s="7" t="s">
-        <v>805</v>
-      </c>
-      <c r="G153" s="7" t="s">
-        <v>806</v>
-      </c>
-      <c r="H153" s="7" t="s">
-        <v>807</v>
       </c>
       <c r="I153" s="7"/>
       <c r="J153" s="6">
         <v>45950</v>
       </c>
       <c r="K153" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M153" s="7"/>
       <c r="N153" s="7"/>
     </row>
-    <row r="154" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" ht="15" customHeight="1">
       <c r="A154" s="7" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>809</v>
-      </c>
-      <c r="C154" t="s">
-        <v>810</v>
+        <v>813</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>814</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>276</v>
+        <v>815</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>204</v>
+        <v>816</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>811</v>
+        <v>860</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>812</v>
+        <v>851</v>
       </c>
       <c r="H154" s="7" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="I154" s="7"/>
       <c r="J154" s="6">
-        <v>45950</v>
+        <v>45954</v>
       </c>
       <c r="K154" s="7" t="s">
-        <v>716</v>
-      </c>
-      <c r="L154" s="1" t="s">
-        <v>41</v>
+        <v>701</v>
+      </c>
+      <c r="L154" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="M154" s="7"/>
       <c r="N154" s="7"/>
     </row>
-    <row r="155" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" ht="28.5">
       <c r="A155" s="7" t="s">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>814</v>
-      </c>
-      <c r="C155" t="s">
-        <v>815</v>
+        <v>820</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>821</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>817</v>
+        <v>859</v>
       </c>
       <c r="G155" s="7" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H155" s="7" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="I155" s="7"/>
       <c r="J155" s="6">
-        <v>45950</v>
+        <v>45954</v>
       </c>
       <c r="K155" s="7" t="s">
-        <v>716</v>
-      </c>
-      <c r="L155" s="1" t="s">
-        <v>41</v>
+        <v>701</v>
+      </c>
+      <c r="L155" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="M155" s="7"/>
       <c r="N155" s="7"/>
     </row>
-    <row r="156" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" ht="15" customHeight="1">
       <c r="A156" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>825</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="E156" s="7" t="s">
         <v>827</v>
       </c>
-      <c r="B156" s="7" t="s">
+      <c r="F156" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="G156" s="7"/>
+      <c r="H156" s="7" t="s">
         <v>828</v>
-      </c>
-      <c r="C156" s="7" t="s">
-        <v>829</v>
-      </c>
-      <c r="D156" s="7" t="s">
-        <v>830</v>
-      </c>
-      <c r="E156" s="7" t="s">
-        <v>831</v>
-      </c>
-      <c r="F156" s="7" t="s">
-        <v>875</v>
-      </c>
-      <c r="G156" s="7" t="s">
-        <v>866</v>
-      </c>
-      <c r="H156" s="7" t="s">
-        <v>832</v>
       </c>
       <c r="I156" s="7"/>
       <c r="J156" s="6">
         <v>45954</v>
       </c>
       <c r="K156" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L156" s="10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M156" s="7"/>
       <c r="N156" s="7"/>
     </row>
-    <row r="157" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" ht="42.75">
       <c r="A157" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>831</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>832</v>
+      </c>
+      <c r="F157" s="7" t="s">
+        <v>857</v>
+      </c>
+      <c r="G157" s="7"/>
+      <c r="H157" s="7" t="s">
         <v>833</v>
-      </c>
-      <c r="B157" s="7" t="s">
-        <v>835</v>
-      </c>
-      <c r="C157" s="7" t="s">
-        <v>836</v>
-      </c>
-      <c r="D157" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="E157" s="7" t="s">
-        <v>837</v>
-      </c>
-      <c r="F157" s="7" t="s">
-        <v>874</v>
-      </c>
-      <c r="G157" s="7" t="s">
-        <v>834</v>
-      </c>
-      <c r="H157" s="7" t="s">
-        <v>838</v>
       </c>
       <c r="I157" s="7"/>
       <c r="J157" s="6">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="K157" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L157" s="10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M157" s="7"/>
       <c r="N157" s="7"/>
     </row>
-    <row r="158" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" ht="28.5">
       <c r="A158" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>838</v>
+      </c>
+      <c r="F158" s="7" t="s">
+        <v>856</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>819</v>
+      </c>
+      <c r="H158" s="7" t="s">
         <v>839</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C158" s="7" t="s">
-        <v>840</v>
-      </c>
-      <c r="D158" s="7" t="s">
-        <v>841</v>
-      </c>
-      <c r="E158" s="7" t="s">
-        <v>842</v>
-      </c>
-      <c r="F158" s="7" t="s">
-        <v>873</v>
-      </c>
-      <c r="G158" s="7"/>
-      <c r="H158" s="7" t="s">
-        <v>843</v>
       </c>
       <c r="I158" s="7"/>
       <c r="J158" s="6">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="K158" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L158" s="10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M158" s="7"/>
       <c r="N158" s="7"/>
     </row>
-    <row r="159" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" ht="15" customHeight="1">
       <c r="A159" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>841</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>843</v>
+      </c>
+      <c r="E159" s="7" t="s">
         <v>844</v>
       </c>
-      <c r="B159" s="7" t="s">
-        <v>845</v>
-      </c>
-      <c r="C159" s="7" t="s">
-        <v>846</v>
-      </c>
-      <c r="D159" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="E159" s="7" t="s">
-        <v>847</v>
-      </c>
       <c r="F159" s="7" t="s">
-        <v>872</v>
+        <v>855</v>
       </c>
       <c r="G159" s="7"/>
       <c r="H159" s="7" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="I159" s="7"/>
       <c r="J159" s="6">
         <v>45957</v>
       </c>
       <c r="K159" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L159" s="10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M159" s="7"/>
       <c r="N159" s="7"/>
     </row>
-    <row r="160" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" ht="42.75">
       <c r="A160" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="E160" s="7" t="s">
         <v>849</v>
       </c>
-      <c r="B160" s="7" t="s">
+      <c r="F160" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="G160" s="7" t="s">
+        <v>819</v>
+      </c>
+      <c r="H160" s="7" t="s">
         <v>850</v>
-      </c>
-      <c r="C160" s="7" t="s">
-        <v>851</v>
-      </c>
-      <c r="D160" s="7" t="s">
-        <v>852</v>
-      </c>
-      <c r="E160" s="7" t="s">
-        <v>853</v>
-      </c>
-      <c r="F160" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="G160" s="7" t="s">
-        <v>834</v>
-      </c>
-      <c r="H160" s="7" t="s">
-        <v>854</v>
       </c>
       <c r="I160" s="7"/>
       <c r="J160" s="6">
         <v>45957</v>
       </c>
       <c r="K160" s="7" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="L160" s="10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M160" s="7"/>
       <c r="N160" s="7"/>
     </row>
-    <row r="161" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="7" t="s">
-        <v>855</v>
-      </c>
-      <c r="B161" s="7" t="s">
-        <v>856</v>
-      </c>
-      <c r="C161" s="7" t="s">
-        <v>857</v>
-      </c>
-      <c r="D161" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="E161" s="7" t="s">
-        <v>859</v>
-      </c>
-      <c r="F161" s="7" t="s">
-        <v>870</v>
-      </c>
+    <row r="161" spans="1:14" ht="15" customHeight="1">
+      <c r="A161" s="7"/>
+      <c r="B161" s="7"/>
+      <c r="C161" s="7"/>
+      <c r="D161" s="7"/>
+      <c r="E161" s="7"/>
+      <c r="F161" s="7"/>
       <c r="G161" s="7"/>
-      <c r="H161" s="7" t="s">
-        <v>860</v>
-      </c>
+      <c r="H161" s="7"/>
       <c r="I161" s="7"/>
-      <c r="J161" s="6">
-        <v>45957</v>
-      </c>
-      <c r="K161" s="7" t="s">
-        <v>716</v>
-      </c>
-      <c r="L161" s="10" t="s">
-        <v>41</v>
-      </c>
+      <c r="J161" s="3"/>
+      <c r="K161" s="3"/>
+      <c r="L161" s="7"/>
       <c r="M161" s="7"/>
       <c r="N161" s="7"/>
     </row>
-    <row r="162" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A162" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>862</v>
-      </c>
-      <c r="C162" s="7" t="s">
-        <v>863</v>
-      </c>
-      <c r="D162" s="7" t="s">
-        <v>861</v>
-      </c>
-      <c r="E162" s="7" t="s">
-        <v>864</v>
-      </c>
-      <c r="F162" s="7" t="s">
-        <v>869</v>
-      </c>
-      <c r="G162" s="7" t="s">
-        <v>834</v>
-      </c>
-      <c r="H162" s="7" t="s">
-        <v>865</v>
-      </c>
+    <row r="162" spans="1:14">
+      <c r="A162" s="7"/>
+      <c r="B162" s="7"/>
+      <c r="C162" s="7"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="7"/>
+      <c r="F162" s="7"/>
+      <c r="G162" s="7"/>
+      <c r="H162" s="7"/>
       <c r="I162" s="7"/>
-      <c r="J162" s="6">
-        <v>45957</v>
-      </c>
-      <c r="K162" s="7" t="s">
-        <v>716</v>
-      </c>
-      <c r="L162" s="10" t="s">
-        <v>41</v>
-      </c>
+      <c r="J162" s="3"/>
+      <c r="K162" s="3"/>
+      <c r="L162" s="7"/>
       <c r="M162" s="7"/>
       <c r="N162" s="7"/>
     </row>
-    <row r="163" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" ht="15" customHeight="1">
       <c r="A163" s="7"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
@@ -16249,7 +16159,7 @@
       <c r="M163" s="7"/>
       <c r="N163" s="7"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
@@ -16260,12 +16170,12 @@
       <c r="H164" s="7"/>
       <c r="I164" s="7"/>
       <c r="J164" s="3"/>
-      <c r="K164" s="3"/>
+      <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c r="M164" s="7"/>
       <c r="N164" s="7"/>
     </row>
-    <row r="165" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14">
       <c r="A165" s="7"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
@@ -16281,7 +16191,7 @@
       <c r="M165" s="7"/>
       <c r="N165" s="7"/>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" ht="15" customHeight="1">
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
@@ -16292,13 +16202,12 @@
       <c r="H166" s="7"/>
       <c r="I166" s="7"/>
       <c r="J166" s="3"/>
-      <c r="K166" s="7"/>
+      <c r="K166" s="3"/>
       <c r="L166" s="7"/>
       <c r="M166" s="7"/>
       <c r="N166" s="7"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A167" s="7"/>
+    <row r="167" spans="1:14">
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
@@ -16313,8 +16222,7 @@
       <c r="M167" s="7"/>
       <c r="N167" s="7"/>
     </row>
-    <row r="168" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="7"/>
+    <row r="168" spans="1:14" ht="30" customHeight="1">
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
@@ -16329,7 +16237,7 @@
       <c r="M168" s="7"/>
       <c r="N168" s="7"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14">
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
@@ -16344,7 +16252,7 @@
       <c r="M169" s="7"/>
       <c r="N169" s="7"/>
     </row>
-    <row r="170" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" ht="15" customHeight="1">
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
@@ -16356,10 +16264,12 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
       <c r="L170" s="7"/>
-      <c r="M170" s="7"/>
+      <c r="M170" s="7" t="s">
+        <v>852</v>
+      </c>
       <c r="N170" s="7"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14">
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
@@ -16374,7 +16284,7 @@
       <c r="M171" s="7"/>
       <c r="N171" s="7"/>
     </row>
-    <row r="172" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" ht="30" customHeight="1">
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
@@ -16386,12 +16296,10 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
       <c r="L172" s="7"/>
-      <c r="M172" s="7" t="s">
-        <v>867</v>
-      </c>
+      <c r="M172" s="7"/>
       <c r="N172" s="7"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14">
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
@@ -16403,10 +16311,8 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
       <c r="L173" s="7"/>
-      <c r="M173" s="7"/>
-      <c r="N173" s="7"/>
-    </row>
-    <row r="174" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:14">
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
@@ -16418,10 +16324,8 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
       <c r="L174" s="7"/>
-      <c r="M174" s="7"/>
-      <c r="N174" s="7"/>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:14">
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
@@ -16434,7 +16338,7 @@
       <c r="K175" s="3"/>
       <c r="L175" s="7"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14">
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
@@ -16447,7 +16351,7 @@
       <c r="K176" s="3"/>
       <c r="L176" s="7"/>
     </row>
-    <row r="177" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:12">
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
@@ -16460,7 +16364,7 @@
       <c r="K177" s="3"/>
       <c r="L177" s="7"/>
     </row>
-    <row r="178" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:12">
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
@@ -16473,7 +16377,7 @@
       <c r="K178" s="3"/>
       <c r="L178" s="7"/>
     </row>
-    <row r="179" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:12">
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
@@ -16486,7 +16390,7 @@
       <c r="K179" s="3"/>
       <c r="L179" s="7"/>
     </row>
-    <row r="180" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:12">
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
@@ -16499,7 +16403,7 @@
       <c r="K180" s="3"/>
       <c r="L180" s="7"/>
     </row>
-    <row r="181" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:12">
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
@@ -16512,7 +16416,7 @@
       <c r="K181" s="3"/>
       <c r="L181" s="7"/>
     </row>
-    <row r="182" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:12">
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
@@ -16525,7 +16429,7 @@
       <c r="K182" s="3"/>
       <c r="L182" s="7"/>
     </row>
-    <row r="183" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:12">
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
@@ -16538,7 +16442,7 @@
       <c r="K183" s="3"/>
       <c r="L183" s="7"/>
     </row>
-    <row r="184" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:12">
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
@@ -16551,35 +16455,9 @@
       <c r="K184" s="3"/>
       <c r="L184" s="7"/>
     </row>
-    <row r="185" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B185" s="7"/>
-      <c r="C185" s="7"/>
-      <c r="D185" s="7"/>
-      <c r="E185" s="7"/>
-      <c r="F185" s="7"/>
-      <c r="G185" s="7"/>
-      <c r="H185" s="7"/>
-      <c r="I185" s="7"/>
-      <c r="J185" s="3"/>
-      <c r="K185" s="3"/>
-      <c r="L185" s="7"/>
-    </row>
-    <row r="186" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B186" s="7"/>
-      <c r="C186" s="7"/>
-      <c r="D186" s="7"/>
-      <c r="E186" s="7"/>
-      <c r="F186" s="7"/>
-      <c r="G186" s="7"/>
-      <c r="H186" s="7"/>
-      <c r="I186" s="7"/>
-      <c r="J186" s="3"/>
-      <c r="K186" s="3"/>
-      <c r="L186" s="7"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="L4:L155">
+  <conditionalFormatting sqref="L4:L153">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"PENDING"</formula>
     </cfRule>
@@ -16590,7 +16468,7 @@
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L163:L167 K166 L169:L186">
+  <conditionalFormatting sqref="L161:L165 K164 L167:L184">
     <cfRule type="cellIs" dxfId="2" priority="34" operator="equal">
       <formula>"PENDING"</formula>
     </cfRule>
@@ -16602,15 +16480,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L169:L186 K166 L163:L167 L4:L155" xr:uid="{1E8D2D6D-4EE7-40E2-A622-3458BDCF08AD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L167:L184 K164 L161:L165 L4:L153" xr:uid="{1E8D2D6D-4EE7-40E2-A622-3458BDCF08AD}">
       <formula1>"PASS,PENDING,FAIL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A163:A168 A4:A155" xr:uid="{F4675041-A1B8-4B65-822E-23AD6AB864A0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A161:A166 A4:A153" xr:uid="{F4675041-A1B8-4B65-822E-23AD6AB864A0}">
       <formula1>INDIRECT("Modulos[MODULOS]")</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="M15" r:id="rId1" xr:uid="{E03BA14B-EB46-4555-B0FE-E6A8B84EE875}"/>
+    <hyperlink ref="M13" r:id="rId1" xr:uid="{E03BA14B-EB46-4555-B0FE-E6A8B84EE875}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -16622,55 +16500,55 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58476477-5BDE-4E9D-BCDF-FD6E3C12EE95}">
   <dimension ref="A2:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.140625" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.125" customWidth="1"/>
+    <col min="9" max="9" width="24.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="22.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="23.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>824</v>
+        <v>809</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -16681,7 +16559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -16694,7 +16572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="21.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -16707,7 +16585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -16720,9 +16598,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -16737,41 +16615,41 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="28.5">
       <c r="A24" s="5" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B25" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B26" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B27" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="B28" s="1">
         <v>4</v>
@@ -16786,7 +16664,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B55000D3-4297-437F-A419-CEB79EC3F6C0}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -16794,15 +16672,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E158E2AB9B4F924688B558FA982B40CF" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ce5f689dcf51305603cb0d070870d6dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="def3e2b2-904e-4359-b966-59b7b32cd06e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="252587ffdfea7067e66d630466c44dd6" ns2:_="">
     <xsd:import namespace="def3e2b2-904e-4359-b966-59b7b32cd06e"/>
@@ -16940,6 +16809,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -16947,14 +16825,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1F0EA96-F162-49AF-B0BE-A54883795866}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16972,6 +16842,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CABA5C2-04D8-4DC5-BBFB-FF9AC004B268}">
   <ds:schemaRefs>

--- a/Modelo Test Plan.xlsx
+++ b/Modelo Test Plan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alumno\CoderBits\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kiro\CoderBits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD6634C-5DF2-4E15-B1DF-93BE23FD02D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9F9C59-B031-4841-905A-833D149FEAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{96765352-7388-4C61-94B8-5077301D3254}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{96765352-7388-4C61-94B8-5077301D3254}"/>
   </bookViews>
   <sheets>
     <sheet name="Gestion de Modulos" sheetId="4" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="876">
   <si>
     <t>MODULOS</t>
   </si>
@@ -3047,12 +3047,45 @@
   <si>
     <t>Validacion de que el numero de telefono solo tenga valores numericos</t>
   </si>
+  <si>
+    <t>Bloqueo a nivel firewall</t>
+  </si>
+  <si>
+    <t>Desbloqueo a nivel firewall</t>
+  </si>
+  <si>
+    <t>Verificar que el sistema tiene que bloquear a nivel firewall la ip atacante</t>
+  </si>
+  <si>
+    <t>Verificar que el sistema tiene que desbloquear a nivel firewall la ip atacante</t>
+  </si>
+  <si>
+    <t>Unitaria</t>
+  </si>
+  <si>
+    <t>Mitigaciones registradas disponibles</t>
+  </si>
+  <si>
+    <t>Mitigaciones bloqueadas</t>
+  </si>
+  <si>
+    <t>1. Iniciar sesion 2. Iniciar el monitoreo de red 3. realizar ataque de prueba 4. Mitigar manual mente</t>
+  </si>
+  <si>
+    <t>1. Iniciar sesion 2. Iniciar el monitoreo de red 3. Desbloquear ip bloqueada</t>
+  </si>
+  <si>
+    <t>Se bloquea la ip del atacante</t>
+  </si>
+  <si>
+    <t>Se desbloquea la ip del atacante</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3070,6 +3103,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3108,7 +3149,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3143,12 +3184,74 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="51">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3298,65 +3401,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center"/>
@@ -4648,6 +4692,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4655,7 +4700,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -5199,6 +5243,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5206,7 +5251,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -9231,54 +9275,54 @@
     <dataField name="Cuenta de Estado (Dropdown)" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="19">
+    <format dxfId="31">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="30">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="29">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="25">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="24">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="23">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="19">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -9425,60 +9469,60 @@
     <dataField name="Cuenta de Test Case" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="35">
+    <format dxfId="47">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="46">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="45">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="44">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="43">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="41">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="28">
+    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="39">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="38">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="37">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="36">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="35">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -9588,21 +9632,21 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{343BA946-EF1B-4A3B-B511-74A6334C62D3}" name="Tabla1" displayName="Tabla1" ref="A1:L160" totalsRowShown="0">
-  <autoFilter ref="A1:L160" xr:uid="{343BA946-EF1B-4A3B-B511-74A6334C62D3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{343BA946-EF1B-4A3B-B511-74A6334C62D3}" name="Tabla1" displayName="Tabla1" ref="A1:L162" totalsRowShown="0">
+  <autoFilter ref="A1:L162" xr:uid="{343BA946-EF1B-4A3B-B511-74A6334C62D3}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{9B76ED1C-581E-403B-9039-C4D1437837BF}" name="Columna1" dataDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{B227DD10-4412-4DA1-B9AE-57DBBAAC5FDB}" name="Columna2" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{946681D4-26C8-4625-A0B6-192416560D49}" name="Descripción" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{1B53AA13-C73C-4BDB-96DD-F68A91E0C473}" name="Tipo/s de Prueba" dataDxfId="44"/>
-    <tableColumn id="5" xr3:uid="{38F51641-8D65-4D91-9238-C57B7E0DC8C4}" name="Precondiciones" dataDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{F67DADA5-19EF-41E4-9B0E-3EB1E6E4AEC7}" name="Pasos a seguir" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{1E37B7C6-6237-424F-9825-DBAC920A3A92}" name="Datos de Prueba" dataDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{6808706D-288F-4E5F-B1EE-9FC3C5DA1057}" name="Resultado Esperado" dataDxfId="40"/>
-    <tableColumn id="9" xr3:uid="{2D9093F3-889A-450D-9A36-E88B55FE392C}" name="Resultado Actual (Si falla)" dataDxfId="39"/>
-    <tableColumn id="10" xr3:uid="{1DD114CA-C7C7-4EE6-9D13-890DFE1B49F9}" name="Ultima ejecución (Fecha)" dataDxfId="38"/>
-    <tableColumn id="11" xr3:uid="{78CB6362-EDEC-4F76-AA97-664327DEED9B}" name="Encargado de Prueba" dataDxfId="37"/>
-    <tableColumn id="12" xr3:uid="{E14C667D-B48D-4C28-B1C7-EA7F85B8361A}" name="Estado (Dropdown)" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{9B76ED1C-581E-403B-9039-C4D1437837BF}" name="Columna1" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{B227DD10-4412-4DA1-B9AE-57DBBAAC5FDB}" name="Columna2" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{946681D4-26C8-4625-A0B6-192416560D49}" name="Descripción" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{1B53AA13-C73C-4BDB-96DD-F68A91E0C473}" name="Tipo/s de Prueba" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{38F51641-8D65-4D91-9238-C57B7E0DC8C4}" name="Precondiciones" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{F67DADA5-19EF-41E4-9B0E-3EB1E6E4AEC7}" name="Pasos a seguir" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{1E37B7C6-6237-424F-9825-DBAC920A3A92}" name="Datos de Prueba" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{6808706D-288F-4E5F-B1EE-9FC3C5DA1057}" name="Resultado Esperado" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{2D9093F3-889A-450D-9A36-E88B55FE392C}" name="Resultado Actual (Si falla)" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{1DD114CA-C7C7-4EE6-9D13-890DFE1B49F9}" name="Ultima ejecución (Fecha)" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{78CB6362-EDEC-4F76-AA97-664327DEED9B}" name="Encargado de Prueba" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{E14C667D-B48D-4C28-B1C7-EA7F85B8361A}" name="Estado (Dropdown)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9926,120 +9970,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ACCE336-D829-4280-938B-27FEC42D7852}">
   <dimension ref="A1:A33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="24.75" customHeight="1">
+    <row r="2" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="24.75" customHeight="1">
+    <row r="3" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="24.75" customHeight="1">
+    <row r="4" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="24.75" customHeight="1">
+    <row r="5" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="24.75" customHeight="1">
+    <row r="6" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="24.75" customHeight="1">
+    <row r="7" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="24.75" customHeight="1">
+    <row r="8" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="24.75" customHeight="1">
+    <row r="9" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="24.75" customHeight="1">
+    <row r="10" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="24.75" customHeight="1">
+    <row r="11" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="24.75" customHeight="1">
+    <row r="12" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="24.75" customHeight="1">
+    <row r="13" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="24.75" customHeight="1">
+    <row r="14" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="24.75" customHeight="1">
+    <row r="15" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="24.75" customHeight="1">
+    <row r="16" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="24.75" customHeight="1">
+    <row r="17" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="24.75" customHeight="1">
+    <row r="18" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="24.75" customHeight="1">
+    <row r="19" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="24.75" customHeight="1"/>
-    <row r="21" spans="1:1" ht="24.75" customHeight="1"/>
-    <row r="22" spans="1:1" ht="24.75" customHeight="1"/>
-    <row r="23" spans="1:1" ht="24.75" customHeight="1"/>
-    <row r="24" spans="1:1" ht="24.75" customHeight="1"/>
-    <row r="25" spans="1:1" ht="24.75" customHeight="1"/>
-    <row r="26" spans="1:1" ht="24.75" customHeight="1"/>
-    <row r="27" spans="1:1" ht="24.75" customHeight="1"/>
-    <row r="28" spans="1:1" ht="24.75" customHeight="1"/>
-    <row r="29" spans="1:1" ht="24.75" customHeight="1"/>
-    <row r="30" spans="1:1" ht="24.75" customHeight="1"/>
-    <row r="31" spans="1:1" ht="24.75" customHeight="1"/>
-    <row r="32" spans="1:1" ht="24.75" customHeight="1"/>
-    <row r="33" ht="24.75" customHeight="1"/>
+    <row r="20" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -10051,23 +10095,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D9AFB2-4BAC-4EFB-A2E7-92EA3A8E1FBC}">
   <dimension ref="A1:N184"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.875" customWidth="1"/>
-    <col min="2" max="2" width="30.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="37.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="37.375" customWidth="1"/>
-    <col min="5" max="5" width="31.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="49.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="39.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="33.875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="31.375" customWidth="1"/>
-    <col min="10" max="11" width="30.375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.375" customWidth="1"/>
-    <col min="13" max="13" width="36.125" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="37.42578125" customWidth="1"/>
+    <col min="5" max="5" width="31.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="49.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="39.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="31.42578125" customWidth="1"/>
+    <col min="10" max="11" width="30.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" customWidth="1"/>
+    <col min="13" max="13" width="36.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.5">
+    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -10105,7 +10149,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="2" customFormat="1">
+    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="D2"/>
       <c r="I2"/>
@@ -10119,7 +10163,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="41.25" customHeight="1">
+    <row r="3" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
@@ -10159,7 +10203,7 @@
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
     </row>
-    <row r="4" spans="1:14" ht="114">
+    <row r="4" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
@@ -10197,7 +10241,7 @@
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
     </row>
-    <row r="5" spans="1:14" ht="114">
+    <row r="5" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>2</v>
       </c>
@@ -10235,7 +10279,7 @@
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
     </row>
-    <row r="6" spans="1:14" ht="114">
+    <row r="6" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>2</v>
       </c>
@@ -10273,7 +10317,7 @@
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
     </row>
-    <row r="7" spans="1:14" ht="114">
+    <row r="7" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>2</v>
       </c>
@@ -10311,7 +10355,7 @@
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
     </row>
-    <row r="8" spans="1:14" ht="114">
+    <row r="8" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>2</v>
       </c>
@@ -10349,7 +10393,7 @@
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
     </row>
-    <row r="9" spans="1:14" ht="114">
+    <row r="9" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>2</v>
       </c>
@@ -10387,7 +10431,7 @@
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
     </row>
-    <row r="10" spans="1:14" ht="114">
+    <row r="10" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>2</v>
       </c>
@@ -10425,7 +10469,7 @@
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
     </row>
-    <row r="11" spans="1:14" ht="114">
+    <row r="11" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>2</v>
       </c>
@@ -10463,7 +10507,7 @@
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
     </row>
-    <row r="12" spans="1:14" ht="42.75">
+    <row r="12" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>3</v>
       </c>
@@ -10501,7 +10545,7 @@
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
     </row>
-    <row r="13" spans="1:14" ht="42.75">
+    <row r="13" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>3</v>
       </c>
@@ -10541,7 +10585,7 @@
       </c>
       <c r="N13" s="7"/>
     </row>
-    <row r="14" spans="1:14" ht="28.5">
+    <row r="14" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>4</v>
       </c>
@@ -10579,7 +10623,7 @@
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
     </row>
-    <row r="15" spans="1:14" ht="28.5">
+    <row r="15" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>4</v>
       </c>
@@ -10617,7 +10661,7 @@
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
     </row>
-    <row r="16" spans="1:14" ht="42.75">
+    <row r="16" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>5</v>
       </c>
@@ -10653,7 +10697,7 @@
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
     </row>
-    <row r="17" spans="1:14" ht="42.75">
+    <row r="17" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>5</v>
       </c>
@@ -10689,7 +10733,7 @@
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
     </row>
-    <row r="18" spans="1:14" ht="128.25">
+    <row r="18" spans="1:14" ht="135" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -10727,7 +10771,7 @@
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
     </row>
-    <row r="19" spans="1:14" ht="42.75">
+    <row r="19" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>7</v>
       </c>
@@ -10765,7 +10809,7 @@
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
     </row>
-    <row r="20" spans="1:14" ht="42.75">
+    <row r="20" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>8</v>
       </c>
@@ -10803,7 +10847,7 @@
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
     </row>
-    <row r="21" spans="1:14" ht="71.25">
+    <row r="21" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>9</v>
       </c>
@@ -10841,7 +10885,7 @@
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
     </row>
-    <row r="22" spans="1:14" ht="185.25">
+    <row r="22" spans="1:14" ht="195" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>9</v>
       </c>
@@ -10881,7 +10925,7 @@
       </c>
       <c r="N22" s="7"/>
     </row>
-    <row r="23" spans="1:14" ht="128.25">
+    <row r="23" spans="1:14" ht="135" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>5</v>
       </c>
@@ -10920,7 +10964,7 @@
       </c>
       <c r="N23" s="7"/>
     </row>
-    <row r="24" spans="1:14" ht="28.5">
+    <row r="24" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>10</v>
       </c>
@@ -10957,7 +11001,7 @@
       </c>
       <c r="N24" s="7"/>
     </row>
-    <row r="25" spans="1:14" ht="42.75">
+    <row r="25" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>10</v>
       </c>
@@ -10994,7 +11038,7 @@
       </c>
       <c r="N25" s="7"/>
     </row>
-    <row r="26" spans="1:14" ht="42.75">
+    <row r="26" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>10</v>
       </c>
@@ -11031,7 +11075,7 @@
       </c>
       <c r="N26" s="7"/>
     </row>
-    <row r="27" spans="1:14" ht="42.75">
+    <row r="27" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>10</v>
       </c>
@@ -11068,7 +11112,7 @@
       </c>
       <c r="N27" s="7"/>
     </row>
-    <row r="28" spans="1:14" ht="28.5">
+    <row r="28" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>10</v>
       </c>
@@ -11105,7 +11149,7 @@
       </c>
       <c r="N28" s="7"/>
     </row>
-    <row r="29" spans="1:14" ht="42.75">
+    <row r="29" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>10</v>
       </c>
@@ -11142,7 +11186,7 @@
       </c>
       <c r="N29" s="7"/>
     </row>
-    <row r="30" spans="1:14" ht="28.5">
+    <row r="30" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>10</v>
       </c>
@@ -11179,7 +11223,7 @@
       </c>
       <c r="N30" s="7"/>
     </row>
-    <row r="31" spans="1:14" ht="28.5">
+    <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>10</v>
       </c>
@@ -11216,7 +11260,7 @@
       </c>
       <c r="N31" s="7"/>
     </row>
-    <row r="32" spans="1:14" ht="28.5">
+    <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>10</v>
       </c>
@@ -11253,7 +11297,7 @@
       </c>
       <c r="N32" s="7"/>
     </row>
-    <row r="33" spans="1:14" ht="28.5">
+    <row r="33" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>10</v>
       </c>
@@ -11291,7 +11335,7 @@
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
     </row>
-    <row r="34" spans="1:14" ht="42.75">
+    <row r="34" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>1</v>
       </c>
@@ -11329,7 +11373,7 @@
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
     </row>
-    <row r="35" spans="1:14" ht="57">
+    <row r="35" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>1</v>
       </c>
@@ -11367,7 +11411,7 @@
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
     </row>
-    <row r="36" spans="1:14" ht="57">
+    <row r="36" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>1</v>
       </c>
@@ -11405,7 +11449,7 @@
       <c r="M36" s="7"/>
       <c r="N36" s="7"/>
     </row>
-    <row r="37" spans="1:14" ht="42.75">
+    <row r="37" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>1</v>
       </c>
@@ -11443,7 +11487,7 @@
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
     </row>
-    <row r="38" spans="1:14" ht="42.75">
+    <row r="38" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>1</v>
       </c>
@@ -11481,7 +11525,7 @@
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
     </row>
-    <row r="39" spans="1:14" ht="42.75">
+    <row r="39" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>1</v>
       </c>
@@ -11519,7 +11563,7 @@
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
     </row>
-    <row r="40" spans="1:14" ht="42.75">
+    <row r="40" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>1</v>
       </c>
@@ -11557,7 +11601,7 @@
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
     </row>
-    <row r="41" spans="1:14" ht="42.75">
+    <row r="41" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>1</v>
       </c>
@@ -11595,7 +11639,7 @@
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
     </row>
-    <row r="42" spans="1:14" ht="42.75">
+    <row r="42" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>1</v>
       </c>
@@ -11633,7 +11677,7 @@
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
     </row>
-    <row r="43" spans="1:14" ht="57">
+    <row r="43" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>1</v>
       </c>
@@ -11671,7 +11715,7 @@
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
     </row>
-    <row r="44" spans="1:14" ht="42.75">
+    <row r="44" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>1</v>
       </c>
@@ -11709,7 +11753,7 @@
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
     </row>
-    <row r="45" spans="1:14" ht="42.75">
+    <row r="45" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>1</v>
       </c>
@@ -11747,7 +11791,7 @@
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
     </row>
-    <row r="46" spans="1:14" ht="57">
+    <row r="46" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>1</v>
       </c>
@@ -11785,7 +11829,7 @@
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
     </row>
-    <row r="47" spans="1:14" ht="57">
+    <row r="47" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>1</v>
       </c>
@@ -11823,7 +11867,7 @@
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
     </row>
-    <row r="48" spans="1:14" ht="42.75">
+    <row r="48" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>1</v>
       </c>
@@ -11861,7 +11905,7 @@
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
     </row>
-    <row r="49" spans="1:14" ht="42.75">
+    <row r="49" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>12</v>
       </c>
@@ -11899,7 +11943,7 @@
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
     </row>
-    <row r="50" spans="1:14" ht="42.75">
+    <row r="50" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>12</v>
       </c>
@@ -11937,7 +11981,7 @@
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
     </row>
-    <row r="51" spans="1:14" ht="42.75">
+    <row r="51" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>12</v>
       </c>
@@ -11975,7 +12019,7 @@
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
     </row>
-    <row r="52" spans="1:14" ht="42.75">
+    <row r="52" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>12</v>
       </c>
@@ -12013,7 +12057,7 @@
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
     </row>
-    <row r="53" spans="1:14" ht="42.75">
+    <row r="53" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>12</v>
       </c>
@@ -12051,7 +12095,7 @@
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
     </row>
-    <row r="54" spans="1:14" ht="42.75">
+    <row r="54" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>12</v>
       </c>
@@ -12089,7 +12133,7 @@
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
     </row>
-    <row r="55" spans="1:14" ht="57">
+    <row r="55" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>12</v>
       </c>
@@ -12127,7 +12171,7 @@
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
     </row>
-    <row r="56" spans="1:14" ht="57">
+    <row r="56" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>12</v>
       </c>
@@ -12165,7 +12209,7 @@
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
     </row>
-    <row r="57" spans="1:14" ht="42.75">
+    <row r="57" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>12</v>
       </c>
@@ -12203,7 +12247,7 @@
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
     </row>
-    <row r="58" spans="1:14" ht="42.75">
+    <row r="58" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>12</v>
       </c>
@@ -12241,7 +12285,7 @@
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
     </row>
-    <row r="59" spans="1:14" ht="57">
+    <row r="59" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>12</v>
       </c>
@@ -12279,7 +12323,7 @@
       <c r="M59" s="7"/>
       <c r="N59" s="7"/>
     </row>
-    <row r="60" spans="1:14" ht="57">
+    <row r="60" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>12</v>
       </c>
@@ -12317,7 +12361,7 @@
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
     </row>
-    <row r="61" spans="1:14" ht="57">
+    <row r="61" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>12</v>
       </c>
@@ -12355,7 +12399,7 @@
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
     </row>
-    <row r="62" spans="1:14" ht="57">
+    <row r="62" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>12</v>
       </c>
@@ -12393,7 +12437,7 @@
       <c r="M62" s="7"/>
       <c r="N62" s="7"/>
     </row>
-    <row r="63" spans="1:14" ht="42.75">
+    <row r="63" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>12</v>
       </c>
@@ -12431,7 +12475,7 @@
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
     </row>
-    <row r="64" spans="1:14" ht="57">
+    <row r="64" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>13</v>
       </c>
@@ -12469,7 +12513,7 @@
       <c r="M64" s="7"/>
       <c r="N64" s="7"/>
     </row>
-    <row r="65" spans="1:14" ht="57">
+    <row r="65" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>13</v>
       </c>
@@ -12507,7 +12551,7 @@
       <c r="M65" s="7"/>
       <c r="N65" s="7"/>
     </row>
-    <row r="66" spans="1:14" ht="57">
+    <row r="66" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>13</v>
       </c>
@@ -12545,7 +12589,7 @@
       <c r="M66" s="7"/>
       <c r="N66" s="7"/>
     </row>
-    <row r="67" spans="1:14" ht="57">
+    <row r="67" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>13</v>
       </c>
@@ -12583,7 +12627,7 @@
       <c r="M67" s="7"/>
       <c r="N67" s="7"/>
     </row>
-    <row r="68" spans="1:14" ht="57">
+    <row r="68" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>13</v>
       </c>
@@ -12621,7 +12665,7 @@
       <c r="M68" s="7"/>
       <c r="N68" s="7"/>
     </row>
-    <row r="69" spans="1:14" ht="57">
+    <row r="69" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>13</v>
       </c>
@@ -12659,7 +12703,7 @@
       <c r="M69" s="7"/>
       <c r="N69" s="7"/>
     </row>
-    <row r="70" spans="1:14" ht="42.75">
+    <row r="70" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>13</v>
       </c>
@@ -12697,7 +12741,7 @@
       <c r="M70" s="7"/>
       <c r="N70" s="7"/>
     </row>
-    <row r="71" spans="1:14" ht="57">
+    <row r="71" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>13</v>
       </c>
@@ -12735,7 +12779,7 @@
       <c r="M71" s="7"/>
       <c r="N71" s="7"/>
     </row>
-    <row r="72" spans="1:14" ht="42.75">
+    <row r="72" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>13</v>
       </c>
@@ -12773,7 +12817,7 @@
       <c r="M72" s="7"/>
       <c r="N72" s="7"/>
     </row>
-    <row r="73" spans="1:14" ht="42.75">
+    <row r="73" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>13</v>
       </c>
@@ -12811,7 +12855,7 @@
       <c r="M73" s="7"/>
       <c r="N73" s="7"/>
     </row>
-    <row r="74" spans="1:14" ht="57">
+    <row r="74" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>13</v>
       </c>
@@ -12849,7 +12893,7 @@
       <c r="M74" s="7"/>
       <c r="N74" s="7"/>
     </row>
-    <row r="75" spans="1:14" ht="42.75">
+    <row r="75" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>13</v>
       </c>
@@ -12887,7 +12931,7 @@
       <c r="M75" s="7"/>
       <c r="N75" s="7"/>
     </row>
-    <row r="76" spans="1:14" ht="57">
+    <row r="76" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>13</v>
       </c>
@@ -12925,7 +12969,7 @@
       <c r="M76" s="7"/>
       <c r="N76" s="7"/>
     </row>
-    <row r="77" spans="1:14" ht="42.75">
+    <row r="77" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>13</v>
       </c>
@@ -12963,7 +13007,7 @@
       <c r="M77" s="7"/>
       <c r="N77" s="7"/>
     </row>
-    <row r="78" spans="1:14" ht="57">
+    <row r="78" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>13</v>
       </c>
@@ -13001,7 +13045,7 @@
       <c r="M78" s="7"/>
       <c r="N78" s="7"/>
     </row>
-    <row r="79" spans="1:14" ht="57">
+    <row r="79" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>13</v>
       </c>
@@ -13039,7 +13083,7 @@
       <c r="M79" s="7"/>
       <c r="N79" s="7"/>
     </row>
-    <row r="80" spans="1:14" ht="42.75">
+    <row r="80" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>13</v>
       </c>
@@ -13077,7 +13121,7 @@
       <c r="M80" s="7"/>
       <c r="N80" s="7"/>
     </row>
-    <row r="81" spans="1:14" ht="42.75">
+    <row r="81" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>13</v>
       </c>
@@ -13115,7 +13159,7 @@
       <c r="M81" s="7"/>
       <c r="N81" s="7"/>
     </row>
-    <row r="82" spans="1:14" ht="42.75">
+    <row r="82" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>13</v>
       </c>
@@ -13153,7 +13197,7 @@
       <c r="M82" s="7"/>
       <c r="N82" s="7"/>
     </row>
-    <row r="83" spans="1:14" ht="42.75">
+    <row r="83" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>13</v>
       </c>
@@ -13191,7 +13235,7 @@
       <c r="M83" s="7"/>
       <c r="N83" s="7"/>
     </row>
-    <row r="84" spans="1:14" ht="42.75">
+    <row r="84" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>14</v>
       </c>
@@ -13229,7 +13273,7 @@
       <c r="M84" s="7"/>
       <c r="N84" s="7"/>
     </row>
-    <row r="85" spans="1:14" ht="42.75">
+    <row r="85" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>14</v>
       </c>
@@ -13267,7 +13311,7 @@
       <c r="M85" s="7"/>
       <c r="N85" s="7"/>
     </row>
-    <row r="86" spans="1:14" ht="42.75">
+    <row r="86" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>14</v>
       </c>
@@ -13305,7 +13349,7 @@
       <c r="M86" s="7"/>
       <c r="N86" s="7"/>
     </row>
-    <row r="87" spans="1:14" ht="42.75">
+    <row r="87" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>14</v>
       </c>
@@ -13343,7 +13387,7 @@
       <c r="M87" s="7"/>
       <c r="N87" s="7"/>
     </row>
-    <row r="88" spans="1:14" ht="42.75">
+    <row r="88" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>14</v>
       </c>
@@ -13381,7 +13425,7 @@
       <c r="M88" s="7"/>
       <c r="N88" s="7"/>
     </row>
-    <row r="89" spans="1:14" ht="42.75">
+    <row r="89" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>14</v>
       </c>
@@ -13419,7 +13463,7 @@
       <c r="M89" s="7"/>
       <c r="N89" s="7"/>
     </row>
-    <row r="90" spans="1:14" ht="42.75">
+    <row r="90" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>14</v>
       </c>
@@ -13457,7 +13501,7 @@
       <c r="M90" s="7"/>
       <c r="N90" s="7"/>
     </row>
-    <row r="91" spans="1:14" ht="42.75">
+    <row r="91" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>14</v>
       </c>
@@ -13495,7 +13539,7 @@
       <c r="M91" s="7"/>
       <c r="N91" s="7"/>
     </row>
-    <row r="92" spans="1:14" ht="42.75">
+    <row r="92" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>14</v>
       </c>
@@ -13533,7 +13577,7 @@
       <c r="M92" s="7"/>
       <c r="N92" s="7"/>
     </row>
-    <row r="93" spans="1:14" ht="42.75">
+    <row r="93" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>14</v>
       </c>
@@ -13571,7 +13615,7 @@
       <c r="M93" s="7"/>
       <c r="N93" s="7"/>
     </row>
-    <row r="94" spans="1:14" ht="42.75">
+    <row r="94" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>14</v>
       </c>
@@ -13609,7 +13653,7 @@
       <c r="M94" s="7"/>
       <c r="N94" s="7"/>
     </row>
-    <row r="95" spans="1:14" ht="57">
+    <row r="95" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>14</v>
       </c>
@@ -13647,7 +13691,7 @@
       <c r="M95" s="7"/>
       <c r="N95" s="7"/>
     </row>
-    <row r="96" spans="1:14" ht="42.75">
+    <row r="96" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>14</v>
       </c>
@@ -13685,7 +13729,7 @@
       <c r="M96" s="7"/>
       <c r="N96" s="7"/>
     </row>
-    <row r="97" spans="1:14" ht="57">
+    <row r="97" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>14</v>
       </c>
@@ -13723,7 +13767,7 @@
       <c r="M97" s="7"/>
       <c r="N97" s="7"/>
     </row>
-    <row r="98" spans="1:14" ht="57">
+    <row r="98" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>14</v>
       </c>
@@ -13761,7 +13805,7 @@
       <c r="M98" s="7"/>
       <c r="N98" s="7"/>
     </row>
-    <row r="99" spans="1:14" ht="42.75">
+    <row r="99" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>15</v>
       </c>
@@ -13799,7 +13843,7 @@
       <c r="M99" s="7"/>
       <c r="N99" s="7"/>
     </row>
-    <row r="100" spans="1:14" ht="42.75">
+    <row r="100" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>15</v>
       </c>
@@ -13837,7 +13881,7 @@
       <c r="M100" s="7"/>
       <c r="N100" s="7"/>
     </row>
-    <row r="101" spans="1:14" ht="57">
+    <row r="101" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>15</v>
       </c>
@@ -13875,7 +13919,7 @@
       <c r="M101" s="7"/>
       <c r="N101" s="7"/>
     </row>
-    <row r="102" spans="1:14" ht="57">
+    <row r="102" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>15</v>
       </c>
@@ -13913,7 +13957,7 @@
       <c r="M102" s="7"/>
       <c r="N102" s="7"/>
     </row>
-    <row r="103" spans="1:14" ht="57">
+    <row r="103" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>15</v>
       </c>
@@ -13951,7 +13995,7 @@
       <c r="M103" s="7"/>
       <c r="N103" s="7"/>
     </row>
-    <row r="104" spans="1:14" ht="57">
+    <row r="104" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>15</v>
       </c>
@@ -13989,7 +14033,7 @@
       <c r="M104" s="7"/>
       <c r="N104" s="7"/>
     </row>
-    <row r="105" spans="1:14" ht="42.75">
+    <row r="105" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>15</v>
       </c>
@@ -14027,7 +14071,7 @@
       <c r="M105" s="7"/>
       <c r="N105" s="7"/>
     </row>
-    <row r="106" spans="1:14" ht="57">
+    <row r="106" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>15</v>
       </c>
@@ -14065,7 +14109,7 @@
       <c r="M106" s="7"/>
       <c r="N106" s="7"/>
     </row>
-    <row r="107" spans="1:14" ht="42.75">
+    <row r="107" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>15</v>
       </c>
@@ -14103,7 +14147,7 @@
       <c r="M107" s="7"/>
       <c r="N107" s="7"/>
     </row>
-    <row r="108" spans="1:14" ht="57">
+    <row r="108" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>15</v>
       </c>
@@ -14141,7 +14185,7 @@
       <c r="M108" s="7"/>
       <c r="N108" s="7"/>
     </row>
-    <row r="109" spans="1:14" ht="57">
+    <row r="109" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>16</v>
       </c>
@@ -14179,7 +14223,7 @@
       <c r="M109" s="7"/>
       <c r="N109" s="7"/>
     </row>
-    <row r="110" spans="1:14" ht="57">
+    <row r="110" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>16</v>
       </c>
@@ -14217,7 +14261,7 @@
       <c r="M110" s="7"/>
       <c r="N110" s="7"/>
     </row>
-    <row r="111" spans="1:14" ht="42.75">
+    <row r="111" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>16</v>
       </c>
@@ -14255,7 +14299,7 @@
       <c r="M111" s="7"/>
       <c r="N111" s="7"/>
     </row>
-    <row r="112" spans="1:14" ht="42.75">
+    <row r="112" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>16</v>
       </c>
@@ -14293,7 +14337,7 @@
       <c r="M112" s="7"/>
       <c r="N112" s="7"/>
     </row>
-    <row r="113" spans="1:14" ht="57">
+    <row r="113" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>16</v>
       </c>
@@ -14331,7 +14375,7 @@
       <c r="M113" s="7"/>
       <c r="N113" s="7"/>
     </row>
-    <row r="114" spans="1:14" ht="57">
+    <row r="114" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>16</v>
       </c>
@@ -14369,7 +14413,7 @@
       <c r="M114" s="7"/>
       <c r="N114" s="7"/>
     </row>
-    <row r="115" spans="1:14" ht="57">
+    <row r="115" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>16</v>
       </c>
@@ -14407,7 +14451,7 @@
       <c r="M115" s="7"/>
       <c r="N115" s="7"/>
     </row>
-    <row r="116" spans="1:14" ht="57">
+    <row r="116" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>16</v>
       </c>
@@ -14445,7 +14489,7 @@
       <c r="M116" s="7"/>
       <c r="N116" s="7"/>
     </row>
-    <row r="117" spans="1:14" ht="42.75">
+    <row r="117" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>16</v>
       </c>
@@ -14483,7 +14527,7 @@
       <c r="M117" s="7"/>
       <c r="N117" s="7"/>
     </row>
-    <row r="118" spans="1:14" ht="42.75">
+    <row r="118" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>16</v>
       </c>
@@ -14521,7 +14565,7 @@
       <c r="M118" s="7"/>
       <c r="N118" s="7"/>
     </row>
-    <row r="119" spans="1:14" ht="42.75">
+    <row r="119" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>17</v>
       </c>
@@ -14559,7 +14603,7 @@
       <c r="M119" s="7"/>
       <c r="N119" s="7"/>
     </row>
-    <row r="120" spans="1:14" ht="42.75">
+    <row r="120" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>17</v>
       </c>
@@ -14597,7 +14641,7 @@
       <c r="M120" s="7"/>
       <c r="N120" s="7"/>
     </row>
-    <row r="121" spans="1:14" ht="42.75">
+    <row r="121" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>17</v>
       </c>
@@ -14635,7 +14679,7 @@
       <c r="M121" s="7"/>
       <c r="N121" s="7"/>
     </row>
-    <row r="122" spans="1:14" ht="42.75">
+    <row r="122" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>17</v>
       </c>
@@ -14673,7 +14717,7 @@
       <c r="M122" s="7"/>
       <c r="N122" s="7"/>
     </row>
-    <row r="123" spans="1:14" ht="42.75">
+    <row r="123" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>17</v>
       </c>
@@ -14711,7 +14755,7 @@
       <c r="M123" s="7"/>
       <c r="N123" s="7"/>
     </row>
-    <row r="124" spans="1:14" ht="42.75">
+    <row r="124" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>17</v>
       </c>
@@ -14749,7 +14793,7 @@
       <c r="M124" s="7"/>
       <c r="N124" s="7"/>
     </row>
-    <row r="125" spans="1:14" ht="42.75">
+    <row r="125" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>17</v>
       </c>
@@ -14787,7 +14831,7 @@
       <c r="M125" s="7"/>
       <c r="N125" s="7"/>
     </row>
-    <row r="126" spans="1:14" ht="42.75">
+    <row r="126" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>17</v>
       </c>
@@ -14825,7 +14869,7 @@
       <c r="M126" s="7"/>
       <c r="N126" s="7"/>
     </row>
-    <row r="127" spans="1:14" ht="42.75">
+    <row r="127" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>17</v>
       </c>
@@ -14863,7 +14907,7 @@
       <c r="M127" s="7"/>
       <c r="N127" s="7"/>
     </row>
-    <row r="128" spans="1:14" ht="42.75">
+    <row r="128" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>17</v>
       </c>
@@ -14901,7 +14945,7 @@
       <c r="M128" s="7"/>
       <c r="N128" s="7"/>
     </row>
-    <row r="129" spans="1:14" ht="42.75">
+    <row r="129" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>18</v>
       </c>
@@ -14939,7 +14983,7 @@
       <c r="M129" s="7"/>
       <c r="N129" s="7"/>
     </row>
-    <row r="130" spans="1:14" ht="42.75">
+    <row r="130" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>18</v>
       </c>
@@ -14977,7 +15021,7 @@
       <c r="M130" s="7"/>
       <c r="N130" s="7"/>
     </row>
-    <row r="131" spans="1:14" ht="42.75">
+    <row r="131" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>18</v>
       </c>
@@ -15015,7 +15059,7 @@
       <c r="M131" s="7"/>
       <c r="N131" s="7"/>
     </row>
-    <row r="132" spans="1:14" ht="42.75">
+    <row r="132" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>18</v>
       </c>
@@ -15053,7 +15097,7 @@
       <c r="M132" s="7"/>
       <c r="N132" s="7"/>
     </row>
-    <row r="133" spans="1:14" ht="45" customHeight="1">
+    <row r="133" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>18</v>
       </c>
@@ -15091,7 +15135,7 @@
       <c r="M133" s="7"/>
       <c r="N133" s="7"/>
     </row>
-    <row r="134" spans="1:14" ht="28.5">
+    <row r="134" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
         <v>12</v>
       </c>
@@ -15129,7 +15173,7 @@
       <c r="M134" s="7"/>
       <c r="N134" s="7"/>
     </row>
-    <row r="135" spans="1:14" ht="28.5">
+    <row r="135" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
         <v>12</v>
       </c>
@@ -15167,7 +15211,7 @@
       <c r="M135" s="7"/>
       <c r="N135" s="7"/>
     </row>
-    <row r="136" spans="1:14" ht="15" customHeight="1">
+    <row r="136" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
         <v>12</v>
       </c>
@@ -15205,7 +15249,7 @@
       <c r="M136" s="7"/>
       <c r="N136" s="7"/>
     </row>
-    <row r="137" spans="1:14" ht="28.5">
+    <row r="137" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
         <v>711</v>
       </c>
@@ -15243,7 +15287,7 @@
       <c r="M137" s="7"/>
       <c r="N137" s="7"/>
     </row>
-    <row r="138" spans="1:14" ht="28.5">
+    <row r="138" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
         <v>711</v>
       </c>
@@ -15281,7 +15325,7 @@
       <c r="M138" s="7"/>
       <c r="N138" s="7"/>
     </row>
-    <row r="139" spans="1:14" ht="28.5">
+    <row r="139" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
         <v>711</v>
       </c>
@@ -15319,7 +15363,7 @@
       <c r="M139" s="7"/>
       <c r="N139" s="7"/>
     </row>
-    <row r="140" spans="1:14" ht="15" customHeight="1">
+    <row r="140" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
         <v>711</v>
       </c>
@@ -15357,7 +15401,7 @@
       <c r="M140" s="7"/>
       <c r="N140" s="7"/>
     </row>
-    <row r="141" spans="1:14" ht="28.5">
+    <row r="141" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
         <v>5</v>
       </c>
@@ -15395,7 +15439,7 @@
       <c r="M141" s="7"/>
       <c r="N141" s="7"/>
     </row>
-    <row r="142" spans="1:14" ht="15" customHeight="1">
+    <row r="142" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
         <v>5</v>
       </c>
@@ -15433,7 +15477,7 @@
       <c r="M142" s="7"/>
       <c r="N142" s="7"/>
     </row>
-    <row r="143" spans="1:14" ht="28.5">
+    <row r="143" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
         <v>5</v>
       </c>
@@ -15471,7 +15515,7 @@
       <c r="M143" s="7"/>
       <c r="N143" s="7"/>
     </row>
-    <row r="144" spans="1:14" ht="75" customHeight="1">
+    <row r="144" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
         <v>6</v>
       </c>
@@ -15509,7 +15553,7 @@
       <c r="M144" s="7"/>
       <c r="N144" s="7"/>
     </row>
-    <row r="145" spans="1:14" ht="15" customHeight="1">
+    <row r="145" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
         <v>6</v>
       </c>
@@ -15547,7 +15591,7 @@
       <c r="M145" s="7"/>
       <c r="N145" s="7"/>
     </row>
-    <row r="146" spans="1:14" ht="15" customHeight="1">
+    <row r="146" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
         <v>6</v>
       </c>
@@ -15585,7 +15629,7 @@
       <c r="M146" s="7"/>
       <c r="N146" s="7"/>
     </row>
-    <row r="147" spans="1:14" ht="28.5">
+    <row r="147" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
         <v>6</v>
       </c>
@@ -15623,7 +15667,7 @@
       <c r="M147" s="7"/>
       <c r="N147" s="7"/>
     </row>
-    <row r="148" spans="1:14" ht="28.5">
+    <row r="148" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
         <v>770</v>
       </c>
@@ -15661,7 +15705,7 @@
       <c r="M148" s="7"/>
       <c r="N148" s="7"/>
     </row>
-    <row r="149" spans="1:14" ht="15" customHeight="1">
+    <row r="149" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
         <v>770</v>
       </c>
@@ -15699,7 +15743,7 @@
       <c r="M149" s="7"/>
       <c r="N149" s="7"/>
     </row>
-    <row r="150" spans="1:14" ht="28.5">
+    <row r="150" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
         <v>781</v>
       </c>
@@ -15737,7 +15781,7 @@
       <c r="M150" s="7"/>
       <c r="N150" s="7"/>
     </row>
-    <row r="151" spans="1:14" ht="28.5">
+    <row r="151" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
         <v>781</v>
       </c>
@@ -15775,7 +15819,7 @@
       <c r="M151" s="7"/>
       <c r="N151" s="7"/>
     </row>
-    <row r="152" spans="1:14" ht="15" customHeight="1">
+    <row r="152" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
         <v>793</v>
       </c>
@@ -15813,7 +15857,7 @@
       <c r="M152" s="7"/>
       <c r="N152" s="7"/>
     </row>
-    <row r="153" spans="1:14" ht="15" customHeight="1">
+    <row r="153" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
         <v>793</v>
       </c>
@@ -15851,7 +15895,7 @@
       <c r="M153" s="7"/>
       <c r="N153" s="7"/>
     </row>
-    <row r="154" spans="1:14" ht="15" customHeight="1">
+    <row r="154" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
         <v>812</v>
       </c>
@@ -15889,7 +15933,7 @@
       <c r="M154" s="7"/>
       <c r="N154" s="7"/>
     </row>
-    <row r="155" spans="1:14" ht="28.5">
+    <row r="155" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
         <v>818</v>
       </c>
@@ -15927,7 +15971,7 @@
       <c r="M155" s="7"/>
       <c r="N155" s="7"/>
     </row>
-    <row r="156" spans="1:14" ht="15" customHeight="1">
+    <row r="156" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
         <v>824</v>
       </c>
@@ -15963,7 +16007,7 @@
       <c r="M156" s="7"/>
       <c r="N156" s="7"/>
     </row>
-    <row r="157" spans="1:14" ht="42.75">
+    <row r="157" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
         <v>829</v>
       </c>
@@ -15999,7 +16043,7 @@
       <c r="M157" s="7"/>
       <c r="N157" s="7"/>
     </row>
-    <row r="158" spans="1:14" ht="28.5">
+    <row r="158" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
         <v>834</v>
       </c>
@@ -16037,7 +16081,7 @@
       <c r="M158" s="7"/>
       <c r="N158" s="7"/>
     </row>
-    <row r="159" spans="1:14" ht="15" customHeight="1">
+    <row r="159" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
         <v>840</v>
       </c>
@@ -16073,7 +16117,7 @@
       <c r="M159" s="7"/>
       <c r="N159" s="7"/>
     </row>
-    <row r="160" spans="1:14" ht="42.75">
+    <row r="160" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
         <v>12</v>
       </c>
@@ -16111,39 +16155,79 @@
       <c r="M160" s="7"/>
       <c r="N160" s="7"/>
     </row>
-    <row r="161" spans="1:14" ht="15" customHeight="1">
-      <c r="A161" s="7"/>
-      <c r="B161" s="7"/>
-      <c r="C161" s="7"/>
-      <c r="D161" s="7"/>
-      <c r="E161" s="7"/>
-      <c r="F161" s="7"/>
+    <row r="161" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>865</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>867</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>869</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>870</v>
+      </c>
+      <c r="F161" s="7" t="s">
+        <v>872</v>
+      </c>
       <c r="G161" s="7"/>
-      <c r="H161" s="7"/>
+      <c r="H161" s="7" t="s">
+        <v>874</v>
+      </c>
       <c r="I161" s="7"/>
-      <c r="J161" s="3"/>
-      <c r="K161" s="3"/>
-      <c r="L161" s="7"/>
+      <c r="J161" s="6">
+        <v>45957</v>
+      </c>
+      <c r="K161" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L161" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="M161" s="7"/>
       <c r="N161" s="7"/>
     </row>
-    <row r="162" spans="1:14">
-      <c r="A162" s="7"/>
-      <c r="B162" s="7"/>
-      <c r="C162" s="7"/>
-      <c r="D162" s="7"/>
-      <c r="E162" s="7"/>
-      <c r="F162" s="7"/>
+    <row r="162" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A162" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>866</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>868</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>869</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>871</v>
+      </c>
+      <c r="F162" s="7" t="s">
+        <v>873</v>
+      </c>
       <c r="G162" s="7"/>
-      <c r="H162" s="7"/>
+      <c r="H162" s="7" t="s">
+        <v>875</v>
+      </c>
       <c r="I162" s="7"/>
-      <c r="J162" s="3"/>
-      <c r="K162" s="3"/>
-      <c r="L162" s="7"/>
+      <c r="J162" s="6">
+        <v>45957</v>
+      </c>
+      <c r="K162" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L162" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="M162" s="7"/>
       <c r="N162" s="7"/>
     </row>
-    <row r="163" spans="1:14" ht="15" customHeight="1">
+    <row r="163" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="7"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
@@ -16159,7 +16243,7 @@
       <c r="M163" s="7"/>
       <c r="N163" s="7"/>
     </row>
-    <row r="164" spans="1:14">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
@@ -16175,7 +16259,7 @@
       <c r="M164" s="7"/>
       <c r="N164" s="7"/>
     </row>
-    <row r="165" spans="1:14">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="7"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
@@ -16191,7 +16275,7 @@
       <c r="M165" s="7"/>
       <c r="N165" s="7"/>
     </row>
-    <row r="166" spans="1:14" ht="15" customHeight="1">
+    <row r="166" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
@@ -16207,7 +16291,7 @@
       <c r="M166" s="7"/>
       <c r="N166" s="7"/>
     </row>
-    <row r="167" spans="1:14">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
@@ -16222,7 +16306,7 @@
       <c r="M167" s="7"/>
       <c r="N167" s="7"/>
     </row>
-    <row r="168" spans="1:14" ht="30" customHeight="1">
+    <row r="168" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
@@ -16237,7 +16321,7 @@
       <c r="M168" s="7"/>
       <c r="N168" s="7"/>
     </row>
-    <row r="169" spans="1:14">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
@@ -16252,7 +16336,7 @@
       <c r="M169" s="7"/>
       <c r="N169" s="7"/>
     </row>
-    <row r="170" spans="1:14" ht="15" customHeight="1">
+    <row r="170" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
@@ -16269,7 +16353,7 @@
       </c>
       <c r="N170" s="7"/>
     </row>
-    <row r="171" spans="1:14">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
@@ -16284,7 +16368,7 @@
       <c r="M171" s="7"/>
       <c r="N171" s="7"/>
     </row>
-    <row r="172" spans="1:14" ht="30" customHeight="1">
+    <row r="172" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
@@ -16299,7 +16383,7 @@
       <c r="M172" s="7"/>
       <c r="N172" s="7"/>
     </row>
-    <row r="173" spans="1:14">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
@@ -16312,7 +16396,7 @@
       <c r="K173" s="3"/>
       <c r="L173" s="7"/>
     </row>
-    <row r="174" spans="1:14">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
@@ -16325,7 +16409,7 @@
       <c r="K174" s="3"/>
       <c r="L174" s="7"/>
     </row>
-    <row r="175" spans="1:14">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
@@ -16338,7 +16422,7 @@
       <c r="K175" s="3"/>
       <c r="L175" s="7"/>
     </row>
-    <row r="176" spans="1:14">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
@@ -16351,7 +16435,7 @@
       <c r="K176" s="3"/>
       <c r="L176" s="7"/>
     </row>
-    <row r="177" spans="2:12">
+    <row r="177" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
@@ -16364,7 +16448,7 @@
       <c r="K177" s="3"/>
       <c r="L177" s="7"/>
     </row>
-    <row r="178" spans="2:12">
+    <row r="178" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
@@ -16377,7 +16461,7 @@
       <c r="K178" s="3"/>
       <c r="L178" s="7"/>
     </row>
-    <row r="179" spans="2:12">
+    <row r="179" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
@@ -16390,7 +16474,7 @@
       <c r="K179" s="3"/>
       <c r="L179" s="7"/>
     </row>
-    <row r="180" spans="2:12">
+    <row r="180" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
@@ -16403,7 +16487,7 @@
       <c r="K180" s="3"/>
       <c r="L180" s="7"/>
     </row>
-    <row r="181" spans="2:12">
+    <row r="181" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
@@ -16416,7 +16500,7 @@
       <c r="K181" s="3"/>
       <c r="L181" s="7"/>
     </row>
-    <row r="182" spans="2:12">
+    <row r="182" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
@@ -16429,7 +16513,7 @@
       <c r="K182" s="3"/>
       <c r="L182" s="7"/>
     </row>
-    <row r="183" spans="2:12">
+    <row r="183" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
@@ -16442,7 +16526,7 @@
       <c r="K183" s="3"/>
       <c r="L183" s="7"/>
     </row>
-    <row r="184" spans="2:12">
+    <row r="184" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
@@ -16458,32 +16542,32 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L153">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"PENDING"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L161:L165 K164 L167:L184">
-    <cfRule type="cellIs" dxfId="2" priority="34" operator="equal">
+  <conditionalFormatting sqref="L163:L165 K164 L167:L184">
+    <cfRule type="cellIs" dxfId="14" priority="34" operator="equal">
       <formula>"PENDING"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="35" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="36" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L167:L184 K164 L161:L165 L4:L153" xr:uid="{1E8D2D6D-4EE7-40E2-A622-3458BDCF08AD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L167:L184 K164 L4:L153 L163:L165" xr:uid="{1E8D2D6D-4EE7-40E2-A622-3458BDCF08AD}">
       <formula1>"PASS,PENDING,FAIL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A161:A166 A4:A153" xr:uid="{F4675041-A1B8-4B65-822E-23AD6AB864A0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A4:A153 A163:A166" xr:uid="{F4675041-A1B8-4B65-822E-23AD6AB864A0}">
       <formula1>INDIRECT("Modulos[MODULOS]")</formula1>
     </dataValidation>
   </dataValidations>
@@ -16500,25 +16584,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58476477-5BDE-4E9D-BCDF-FD6E3C12EE95}">
   <dimension ref="A2:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.125" customWidth="1"/>
-    <col min="9" max="9" width="24.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="22.875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.140625" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="23.25" customHeight="1">
+    <row r="2" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>805</v>
       </c>
@@ -16529,7 +16613,7 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>807</v>
       </c>
@@ -16546,7 +16630,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>809</v>
       </c>
@@ -16559,7 +16643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -16572,7 +16656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="21.75" customHeight="1">
+    <row r="6" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -16585,7 +16669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -16598,7 +16682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>808</v>
       </c>
@@ -16615,7 +16699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="28.5">
+    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>807</v>
       </c>
@@ -16623,7 +16707,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>116</v>
       </c>
@@ -16631,7 +16715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
@@ -16639,7 +16723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>132</v>
       </c>
@@ -16647,7 +16731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>808</v>
       </c>
@@ -16664,7 +16748,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B55000D3-4297-437F-A419-CEB79EC3F6C0}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -16672,6 +16756,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E158E2AB9B4F924688B558FA982B40CF" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ce5f689dcf51305603cb0d070870d6dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="def3e2b2-904e-4359-b966-59b7b32cd06e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="252587ffdfea7067e66d630466c44dd6" ns2:_="">
     <xsd:import namespace="def3e2b2-904e-4359-b966-59b7b32cd06e"/>
@@ -16809,22 +16908,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CABA5C2-04D8-4DC5-BBFB-FF9AC004B268}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1F0EA96-F162-49AF-B0BE-A54883795866}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16840,21 +16941,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A2950B-6D37-4A45-BCA2-DEBA33559D5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CABA5C2-04D8-4DC5-BBFB-FF9AC004B268}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>